--- a/Översikt UPPLANDS-BRO.xlsx
+++ b/Översikt UPPLANDS-BRO.xlsx
@@ -601,7 +601,7 @@
         <v>44481</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -714,7 +714,7 @@
         <v>44552</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -822,7 +822,7 @@
         <v>44552</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -930,7 +930,7 @@
         <v>45232</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1025,7 +1025,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 18790-2026</t>
+          <t>A 18772-2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1042,7 +1042,7 @@
         <v>46128</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1060,16 +1060,16 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>5.5</v>
+        <v>19.5</v>
       </c>
       <c r="J6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
@@ -1084,7 +1084,7 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -1100,147 +1100,147 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
+          <t>Svedjenäva
+Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="W6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 18772-2026 artfynd.xlsx", "A 18772-2026")</f>
+        <v/>
+      </c>
+      <c r="X6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 18772-2026 karta.png", "A 18772-2026")</f>
+        <v/>
+      </c>
+      <c r="Y6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 18772-2026 georefererad karta.tif", "A 18772-2026")</f>
+        <v/>
+      </c>
+      <c r="AA6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 18772-2026 FSC-klagomål.docx", "A 18772-2026")</f>
+        <v/>
+      </c>
+      <c r="AB6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 18772-2026 FSC-klagomål mail.docx", "A 18772-2026")</f>
+        <v/>
+      </c>
+      <c r="AC6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 18772-2026 tillsynsbegäran.docx", "A 18772-2026")</f>
+        <v/>
+      </c>
+      <c r="AD6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 18772-2026 tillsynsbegäran mail.docx", "A 18772-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>A 18790-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>46128</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>UPPLANDS-BRO</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="J7" t="n">
+        <v>2</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>2</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
           <t>Fläcknycklar
 Nattviol</t>
         </is>
       </c>
-      <c r="W6">
+      <c r="W7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 18790-2026 artfynd.xlsx", "A 18790-2026")</f>
         <v/>
       </c>
-      <c r="X6">
+      <c r="X7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 18790-2026 karta.png", "A 18790-2026")</f>
         <v/>
       </c>
-      <c r="Y6">
+      <c r="Y7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 18790-2026 georefererad karta.tif", "A 18790-2026")</f>
         <v/>
       </c>
-      <c r="AA6">
+      <c r="AA7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 18790-2026 FSC-klagomål.docx", "A 18790-2026")</f>
         <v/>
       </c>
-      <c r="AB6">
+      <c r="AB7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 18790-2026 FSC-klagomål mail.docx", "A 18790-2026")</f>
         <v/>
       </c>
-      <c r="AC6">
+      <c r="AC7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 18790-2026 tillsynsbegäran.docx", "A 18790-2026")</f>
         <v/>
       </c>
-      <c r="AD6">
+      <c r="AD7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 18790-2026 tillsynsbegäran mail.docx", "A 18790-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>A 18772-2026</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>46128</v>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>UPPLANDS-BRO</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="J7" t="n">
-        <v>1</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>1</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>1</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
-        <v>2</v>
-      </c>
-      <c r="T7" t="n">
-        <v>2</v>
-      </c>
-      <c r="U7" t="n">
-        <v>0</v>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>Svedjenäva
-Fläcknycklar</t>
-        </is>
-      </c>
-      <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 18772-2026 artfynd.xlsx", "A 18772-2026")</f>
-        <v/>
-      </c>
-      <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 18772-2026 karta.png", "A 18772-2026")</f>
-        <v/>
-      </c>
-      <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 18772-2026 georefererad karta.tif", "A 18772-2026")</f>
-        <v/>
-      </c>
-      <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 18772-2026 FSC-klagomål.docx", "A 18772-2026")</f>
-        <v/>
-      </c>
-      <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 18772-2026 FSC-klagomål mail.docx", "A 18772-2026")</f>
-        <v/>
-      </c>
-      <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 18772-2026 tillsynsbegäran.docx", "A 18772-2026")</f>
-        <v/>
-      </c>
-      <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 18772-2026 tillsynsbegäran mail.docx", "A 18772-2026")</f>
         <v/>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
         <v>45722</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
         <v>44603</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1481,7 +1481,7 @@
         <v>44552</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1569,7 +1569,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 7955-2023</t>
+          <t>A 25561-2025</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>44973</v>
+        <v>45803</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1599,7 +1599,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>2.9</v>
+        <v>1.6</v>
       </c>
       <c r="J11" t="n">
         <v>1</v>
@@ -1635,7 +1635,7 @@
         <v>1</v>
       </c>
       <c r="U11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
@@ -1643,38 +1643,38 @@
         </is>
       </c>
       <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 7955-2023 artfynd.xlsx", "A 7955-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 25561-2025 artfynd.xlsx", "A 25561-2025")</f>
         <v/>
       </c>
       <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 7955-2023 karta.png", "A 7955-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 25561-2025 karta.png", "A 25561-2025")</f>
         <v/>
       </c>
       <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 7955-2023 georefererad karta.tif", "A 7955-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 25561-2025 georefererad karta.tif", "A 25561-2025")</f>
         <v/>
       </c>
       <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 7955-2023 FSC-klagomål.docx", "A 7955-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 25561-2025 FSC-klagomål.docx", "A 25561-2025")</f>
         <v/>
       </c>
       <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 7955-2023 FSC-klagomål mail.docx", "A 7955-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 25561-2025 FSC-klagomål mail.docx", "A 25561-2025")</f>
         <v/>
       </c>
       <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 7955-2023 tillsynsbegäran.docx", "A 7955-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 25561-2025 tillsynsbegäran.docx", "A 25561-2025")</f>
         <v/>
       </c>
       <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 7955-2023 tillsynsbegäran mail.docx", "A 7955-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 25561-2025 tillsynsbegäran mail.docx", "A 25561-2025")</f>
         <v/>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 46438-2023</t>
+          <t>A 2409-2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1688,10 +1688,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45197</v>
+        <v>46034</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1704,7 +1704,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>0.5</v>
+        <v>14.2</v>
       </c>
       <c r="J12" t="n">
         <v>1</v>
@@ -1719,7 +1719,7 @@
         <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1728,10 +1728,10 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1744,35 +1744,39 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>Bombmurkla</t>
+          <t>Havsörn</t>
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 46438-2023 artfynd.xlsx", "A 46438-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 2409-2026 artfynd.xlsx", "A 2409-2026")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 46438-2023 karta.png", "A 46438-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 2409-2026 karta.png", "A 2409-2026")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 46438-2023 georefererad karta.tif", "A 46438-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 2409-2026 georefererad karta.tif", "A 2409-2026")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 46438-2023 FSC-klagomål.docx", "A 46438-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 2409-2026 FSC-klagomål.docx", "A 2409-2026")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 46438-2023 FSC-klagomål mail.docx", "A 46438-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 2409-2026 FSC-klagomål mail.docx", "A 2409-2026")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 46438-2023 tillsynsbegäran.docx", "A 46438-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 2409-2026 tillsynsbegäran.docx", "A 2409-2026")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 46438-2023 tillsynsbegäran mail.docx", "A 46438-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 2409-2026 tillsynsbegäran mail.docx", "A 2409-2026")</f>
+        <v/>
+      </c>
+      <c r="AE12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/fåglar/A 2409-2026 prioriterade fågelarter.docx", "A 2409-2026")</f>
         <v/>
       </c>
     </row>
@@ -1796,7 +1800,7 @@
         <v>45730</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1884,7 +1888,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 23099-2024</t>
+          <t>A 73773-2021</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1898,10 +1902,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45450</v>
+        <v>44552</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1913,16 +1917,11 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I14" t="n">
-        <v>0.7</v>
+        <v>1.9</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
@@ -1931,7 +1930,7 @@
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -1943,10 +1942,10 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
@@ -1959,35 +1958,35 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Bredbrämad bastardsvärmare</t>
+          <t>Kopparödla</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 23099-2024 artfynd.xlsx", "A 23099-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 73773-2021 artfynd.xlsx", "A 73773-2021")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 23099-2024 karta.png", "A 23099-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 73773-2021 karta.png", "A 73773-2021")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 23099-2024 georefererad karta.tif", "A 23099-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 73773-2021 georefererad karta.tif", "A 73773-2021")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 23099-2024 FSC-klagomål.docx", "A 23099-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 73773-2021 FSC-klagomål.docx", "A 73773-2021")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 23099-2024 FSC-klagomål mail.docx", "A 23099-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 73773-2021 FSC-klagomål mail.docx", "A 73773-2021")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 23099-2024 tillsynsbegäran.docx", "A 23099-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 73773-2021 tillsynsbegäran.docx", "A 73773-2021")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 23099-2024 tillsynsbegäran mail.docx", "A 23099-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 73773-2021 tillsynsbegäran mail.docx", "A 73773-2021")</f>
         <v/>
       </c>
     </row>
@@ -2011,7 +2010,7 @@
         <v>45959</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2099,7 +2098,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 2409-2026</t>
+          <t>A 23099-2024</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2113,10 +2112,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46034</v>
+        <v>45450</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2128,11 +2127,16 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I16" t="n">
-        <v>14.2</v>
+        <v>0.7</v>
       </c>
       <c r="J16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
@@ -2141,7 +2145,7 @@
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -2153,10 +2157,10 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
@@ -2165,50 +2169,46 @@
         <v>1</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Havsörn</t>
+          <t>Bredbrämad bastardsvärmare</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 2409-2026 artfynd.xlsx", "A 2409-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 23099-2024 artfynd.xlsx", "A 23099-2024")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 2409-2026 karta.png", "A 2409-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 23099-2024 karta.png", "A 23099-2024")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 2409-2026 georefererad karta.tif", "A 2409-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 23099-2024 georefererad karta.tif", "A 23099-2024")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 2409-2026 FSC-klagomål.docx", "A 2409-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 23099-2024 FSC-klagomål.docx", "A 23099-2024")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 2409-2026 FSC-klagomål mail.docx", "A 2409-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 23099-2024 FSC-klagomål mail.docx", "A 23099-2024")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 2409-2026 tillsynsbegäran.docx", "A 2409-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 23099-2024 tillsynsbegäran.docx", "A 23099-2024")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 2409-2026 tillsynsbegäran mail.docx", "A 2409-2026")</f>
-        <v/>
-      </c>
-      <c r="AE16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/fåglar/A 2409-2026 prioriterade fågelarter.docx", "A 2409-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 23099-2024 tillsynsbegäran mail.docx", "A 23099-2024")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 64098-2023</t>
+          <t>A 26637-2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2222,10 +2222,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45279</v>
+        <v>46184</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2238,7 +2238,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>0.3</v>
+        <v>5.4</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2247,10 +2247,10 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
@@ -2265,7 +2265,7 @@
         <v>1</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
@@ -2278,42 +2278,42 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Skogsalmsdvärgmal</t>
+          <t>Igelkott</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 64098-2023 artfynd.xlsx", "A 64098-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 26637-2026 artfynd.xlsx", "A 26637-2026")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 64098-2023 karta.png", "A 64098-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 26637-2026 karta.png", "A 26637-2026")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 64098-2023 georefererad karta.tif", "A 64098-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 26637-2026 georefererad karta.tif", "A 26637-2026")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 64098-2023 FSC-klagomål.docx", "A 64098-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 26637-2026 FSC-klagomål.docx", "A 26637-2026")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 64098-2023 FSC-klagomål mail.docx", "A 64098-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 26637-2026 FSC-klagomål mail.docx", "A 26637-2026")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 64098-2023 tillsynsbegäran.docx", "A 64098-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 26637-2026 tillsynsbegäran.docx", "A 26637-2026")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 64098-2023 tillsynsbegäran mail.docx", "A 64098-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 26637-2026 tillsynsbegäran mail.docx", "A 26637-2026")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 73773-2021</t>
+          <t>A 26623-2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2327,10 +2327,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>44552</v>
+        <v>46184</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2343,16 +2343,16 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>1.9</v>
+        <v>4.6</v>
       </c>
       <c r="J18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
@@ -2367,7 +2367,7 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -2379,46 +2379,46 @@
         <v>1</v>
       </c>
       <c r="U18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Kopparödla</t>
+          <t>Svartöra</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 73773-2021 artfynd.xlsx", "A 73773-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 26623-2026 artfynd.xlsx", "A 26623-2026")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 73773-2021 karta.png", "A 73773-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 26623-2026 karta.png", "A 26623-2026")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 73773-2021 georefererad karta.tif", "A 73773-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 26623-2026 georefererad karta.tif", "A 26623-2026")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 73773-2021 FSC-klagomål.docx", "A 73773-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 26623-2026 FSC-klagomål.docx", "A 26623-2026")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 73773-2021 FSC-klagomål mail.docx", "A 73773-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 26623-2026 FSC-klagomål mail.docx", "A 26623-2026")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 73773-2021 tillsynsbegäran.docx", "A 73773-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 26623-2026 tillsynsbegäran.docx", "A 26623-2026")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 73773-2021 tillsynsbegäran mail.docx", "A 73773-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 26623-2026 tillsynsbegäran mail.docx", "A 26623-2026")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 26623-2026</t>
+          <t>A 46438-2023</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2432,10 +2432,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46184</v>
+        <v>45197</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2448,22 +2448,22 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>4.6</v>
+        <v>0.5</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
         <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2475,7 +2475,7 @@
         <v>1</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
@@ -2488,35 +2488,35 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Svartöra</t>
+          <t>Bombmurkla</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 26623-2026 artfynd.xlsx", "A 26623-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 46438-2023 artfynd.xlsx", "A 46438-2023")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 26623-2026 karta.png", "A 26623-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 46438-2023 karta.png", "A 46438-2023")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 26623-2026 georefererad karta.tif", "A 26623-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 46438-2023 georefererad karta.tif", "A 46438-2023")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 26623-2026 FSC-klagomål.docx", "A 26623-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 46438-2023 FSC-klagomål.docx", "A 46438-2023")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 26623-2026 FSC-klagomål mail.docx", "A 26623-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 46438-2023 FSC-klagomål mail.docx", "A 46438-2023")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 26623-2026 tillsynsbegäran.docx", "A 26623-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 46438-2023 tillsynsbegäran.docx", "A 46438-2023")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 26623-2026 tillsynsbegäran mail.docx", "A 26623-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 46438-2023 tillsynsbegäran mail.docx", "A 46438-2023")</f>
         <v/>
       </c>
     </row>
@@ -2540,7 +2540,7 @@
         <v>45726</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2628,7 +2628,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 26637-2026</t>
+          <t>A 7955-2023</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2642,10 +2642,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46184</v>
+        <v>44973</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2658,10 +2658,10 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>5.4</v>
+        <v>2.9</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
@@ -2670,10 +2670,10 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2694,46 +2694,46 @@
         <v>1</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Igelkott</t>
+          <t>Bombmurkla</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 26637-2026 artfynd.xlsx", "A 26637-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 7955-2023 artfynd.xlsx", "A 7955-2023")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 26637-2026 karta.png", "A 26637-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 7955-2023 karta.png", "A 7955-2023")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 26637-2026 georefererad karta.tif", "A 26637-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 7955-2023 georefererad karta.tif", "A 7955-2023")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 26637-2026 FSC-klagomål.docx", "A 26637-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 7955-2023 FSC-klagomål.docx", "A 7955-2023")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 26637-2026 FSC-klagomål mail.docx", "A 26637-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 7955-2023 FSC-klagomål mail.docx", "A 7955-2023")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 26637-2026 tillsynsbegäran.docx", "A 26637-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 7955-2023 tillsynsbegäran.docx", "A 7955-2023")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 26637-2026 tillsynsbegäran mail.docx", "A 26637-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 7955-2023 tillsynsbegäran mail.docx", "A 7955-2023")</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 2062-2025</t>
+          <t>A 64098-2023</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2747,10 +2747,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45671</v>
+        <v>45279</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2763,10 +2763,10 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>1.9</v>
+        <v>0.3</v>
       </c>
       <c r="J22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
@@ -2799,50 +2799,46 @@
         <v>1</v>
       </c>
       <c r="U22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Skogsalmsdvärgmal</t>
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 2062-2025 artfynd.xlsx", "A 2062-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 64098-2023 artfynd.xlsx", "A 64098-2023")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 2062-2025 karta.png", "A 2062-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 64098-2023 karta.png", "A 64098-2023")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 2062-2025 georefererad karta.tif", "A 2062-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 64098-2023 georefererad karta.tif", "A 64098-2023")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 2062-2025 FSC-klagomål.docx", "A 2062-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 64098-2023 FSC-klagomål.docx", "A 64098-2023")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 2062-2025 FSC-klagomål mail.docx", "A 2062-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 64098-2023 FSC-klagomål mail.docx", "A 64098-2023")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 2062-2025 tillsynsbegäran.docx", "A 2062-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 64098-2023 tillsynsbegäran.docx", "A 64098-2023")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 2062-2025 tillsynsbegäran mail.docx", "A 2062-2025")</f>
-        <v/>
-      </c>
-      <c r="AE22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/fåglar/A 2062-2025 prioriterade fågelarter.docx", "A 2062-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 64098-2023 tillsynsbegäran mail.docx", "A 64098-2023")</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 25561-2025</t>
+          <t>A 2062-2025</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2856,10 +2852,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45803</v>
+        <v>45671</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2872,7 +2868,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>1.6</v>
+        <v>1.9</v>
       </c>
       <c r="J23" t="n">
         <v>1</v>
@@ -2881,13 +2877,13 @@
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M23" t="n">
         <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -2899,7 +2895,7 @@
         <v>1</v>
       </c>
       <c r="R23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
         <v>1</v>
@@ -2908,39 +2904,43 @@
         <v>1</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Bombmurkla</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 25561-2025 artfynd.xlsx", "A 25561-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 2062-2025 artfynd.xlsx", "A 2062-2025")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 25561-2025 karta.png", "A 25561-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 2062-2025 karta.png", "A 2062-2025")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 25561-2025 georefererad karta.tif", "A 25561-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 2062-2025 georefererad karta.tif", "A 2062-2025")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 25561-2025 FSC-klagomål.docx", "A 25561-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 2062-2025 FSC-klagomål.docx", "A 2062-2025")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 25561-2025 FSC-klagomål mail.docx", "A 25561-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 2062-2025 FSC-klagomål mail.docx", "A 2062-2025")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 25561-2025 tillsynsbegäran.docx", "A 25561-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 2062-2025 tillsynsbegäran.docx", "A 2062-2025")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 25561-2025 tillsynsbegäran mail.docx", "A 25561-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 2062-2025 tillsynsbegäran mail.docx", "A 2062-2025")</f>
+        <v/>
+      </c>
+      <c r="AE23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/fåglar/A 2062-2025 prioriterade fågelarter.docx", "A 2062-2025")</f>
         <v/>
       </c>
     </row>
@@ -2964,7 +2964,7 @@
         <v>44558</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3069,7 +3069,7 @@
         <v>44609</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3142,7 +3142,7 @@
         <v>44489</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3220,7 +3220,7 @@
         <v>44546</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3293,7 +3293,7 @@
         <v>44700</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3366,7 +3366,7 @@
         <v>44587</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3439,7 +3439,7 @@
         <v>44655</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3500,7 +3500,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 59700-2021</t>
+          <t>A 64105-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3514,10 +3514,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44494</v>
+        <v>45279</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3529,13 +3529,8 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I31" t="n">
-        <v>4.8</v>
+        <v>2.2</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3578,7 +3573,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 38902-2024</t>
+          <t>A 2602-2024</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3592,10 +3587,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45547</v>
+        <v>45313</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3607,13 +3602,8 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I32" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3656,7 +3646,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 50294-2023</t>
+          <t>A 59844-2022</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3670,10 +3660,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45216</v>
+        <v>44901</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3685,8 +3675,13 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I33" t="n">
-        <v>3.7</v>
+        <v>11.9</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3729,7 +3724,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 9655-2026</t>
+          <t>A 23615-2025</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3743,10 +3738,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>46070</v>
+        <v>45792</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3758,13 +3753,8 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I34" t="n">
-        <v>17.2</v>
+        <v>1.3</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3807,7 +3797,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 5264-2023</t>
+          <t>A 23627-2025</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3821,10 +3811,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44959</v>
+        <v>45792</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3837,7 +3827,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>5.8</v>
+        <v>1.7</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3880,7 +3870,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 23098-2024</t>
+          <t>A 3630-2023</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3894,10 +3884,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45450</v>
+        <v>44950</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3909,13 +3899,8 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I36" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3958,7 +3943,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 18787-2026</t>
+          <t>A 23093-2024</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3972,10 +3957,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>46128</v>
+        <v>45450</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3993,7 +3978,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>7.8</v>
+        <v>0.9</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4036,7 +4021,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 59844-2022</t>
+          <t>A 54222-2023</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4050,10 +4035,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44901</v>
+        <v>45225</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4071,7 +4056,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>11.9</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4114,7 +4099,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 18813-2026</t>
+          <t>A 7860-2024</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4128,10 +4113,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>46128</v>
+        <v>45348</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4149,7 +4134,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>56</v>
+        <v>1.9</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4192,7 +4177,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 18818-2026</t>
+          <t>A 9655-2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4206,10 +4191,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>46128</v>
+        <v>46070</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4227,7 +4212,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>17.8</v>
+        <v>17.2</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4270,7 +4255,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 54222-2023</t>
+          <t>A 27313-2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4284,10 +4269,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45225</v>
+        <v>45096</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4299,13 +4284,8 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I41" t="n">
-        <v>8.300000000000001</v>
+        <v>1.8</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4348,7 +4328,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 18778-2026</t>
+          <t>A 64114-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4362,10 +4342,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>46128</v>
+        <v>45279</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4377,13 +4357,8 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I42" t="n">
-        <v>4.5</v>
+        <v>0.4</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4426,7 +4401,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 4338-2023</t>
+          <t>A 50294-2023</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4440,10 +4415,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44953</v>
+        <v>45216</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4456,7 +4431,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>1.1</v>
+        <v>3.7</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4499,7 +4474,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 58011-2021</t>
+          <t>A 18778-2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4513,10 +4488,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44487</v>
+        <v>46128</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4534,7 +4509,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>9.199999999999999</v>
+        <v>4.5</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4577,7 +4552,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 72524-2021</t>
+          <t>A 18813-2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4591,10 +4566,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>44546</v>
+        <v>46128</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4606,8 +4581,13 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I45" t="n">
-        <v>3.6</v>
+        <v>56</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4650,7 +4630,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 64107-2023</t>
+          <t>A 18818-2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4664,10 +4644,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45279</v>
+        <v>46128</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4679,8 +4659,13 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I46" t="n">
-        <v>0.3</v>
+        <v>17.8</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4723,7 +4708,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 23093-2024</t>
+          <t>A 18787-2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4737,10 +4722,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45450</v>
+        <v>46128</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4758,7 +4743,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>0.9</v>
+        <v>7.8</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4801,7 +4786,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 27313-2023</t>
+          <t>A 58011-2021</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4815,10 +4800,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45096</v>
+        <v>44487</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4830,8 +4815,13 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I48" t="n">
-        <v>1.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4874,7 +4864,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 59377-2024</t>
+          <t>A 49622-2021</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4888,10 +4878,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45638</v>
+        <v>44455</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4904,7 +4894,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>0.6</v>
+        <v>3.8</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4964,7 +4954,7 @@
         <v>46146</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5025,7 +5015,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 51587-2023</t>
+          <t>A 64110-2023</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5039,10 +5029,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45215</v>
+        <v>45279</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5054,13 +5044,8 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I51" t="n">
-        <v>2.6</v>
+        <v>0.4</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5103,7 +5088,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 24579-2026</t>
+          <t>A 23098-2024</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5117,10 +5102,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>46170</v>
+        <v>45450</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5132,8 +5117,13 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I52" t="n">
-        <v>2.1</v>
+        <v>1</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5176,7 +5166,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 58598-2025</t>
+          <t>A 24579-2026</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5190,10 +5180,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45986</v>
+        <v>46170</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5205,13 +5195,8 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I53" t="n">
-        <v>4.5</v>
+        <v>2.1</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5271,7 +5256,7 @@
         <v>44770</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5327,7 +5312,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 26196-2026</t>
+          <t>A 58598-2025</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5337,14 +5322,14 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>46182</v>
+        <v>45986</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5356,8 +5341,13 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I55" t="n">
-        <v>53.1</v>
+        <v>4.5</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5400,7 +5390,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 26625-2026</t>
+          <t>A 26196-2026</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5410,14 +5400,14 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>46184</v>
+        <v>46182</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5430,7 +5420,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>5.3</v>
+        <v>53.1</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5473,7 +5463,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 26629-2026</t>
+          <t>A 26633-2026</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5490,7 +5480,7 @@
         <v>46184</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5503,7 +5493,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>2</v>
+        <v>0.7</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5546,7 +5536,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 26633-2026</t>
+          <t>A 26625-2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5563,7 +5553,7 @@
         <v>46184</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5576,7 +5566,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>0.7</v>
+        <v>5.3</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5619,7 +5609,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 59848-2022</t>
+          <t>A 26629-2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5633,10 +5623,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>44901</v>
+        <v>46184</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5648,13 +5638,8 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I59" t="n">
-        <v>10.7</v>
+        <v>2</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5697,7 +5682,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 49622-2021</t>
+          <t>A 3754-2026</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5711,10 +5696,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>44455</v>
+        <v>46043</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5726,8 +5711,13 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I60" t="n">
-        <v>3.8</v>
+        <v>5.1</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5770,7 +5760,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 64110-2023</t>
+          <t>A 59377-2024</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5784,10 +5774,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45279</v>
+        <v>45638</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5800,7 +5790,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5843,7 +5833,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 3754-2026</t>
+          <t>A 28735-2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5857,10 +5847,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>46043</v>
+        <v>46198</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5872,13 +5862,8 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I62" t="n">
-        <v>5.1</v>
+        <v>3.5</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5921,7 +5906,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 28797-2026</t>
+          <t>A 28740-2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5938,7 +5923,7 @@
         <v>46198</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5951,7 +5936,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>2.2</v>
+        <v>4.8</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5994,7 +5979,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 28740-2026</t>
+          <t>A 28797-2026</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6011,7 +5996,7 @@
         <v>46198</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6024,7 +6009,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>4.8</v>
+        <v>2.2</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6067,7 +6052,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 28735-2026</t>
+          <t>A 33058-2026</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6077,14 +6062,14 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>46198</v>
+        <v>46245</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6097,7 +6082,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>3.5</v>
+        <v>1.3</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6140,7 +6125,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 33058-2026</t>
+          <t>A 59402-2022</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6150,14 +6135,14 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>46245</v>
+        <v>44906</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6170,7 +6155,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>1.3</v>
+        <v>1.8</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6213,7 +6198,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 7275-2022</t>
+          <t>A 31714-2026</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6227,10 +6212,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>44606</v>
+        <v>46226</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6242,13 +6227,8 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I67" t="n">
-        <v>9.6</v>
+        <v>5</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6291,7 +6271,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 2602-2024</t>
+          <t>A 5264-2023</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6305,10 +6285,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45313</v>
+        <v>44959</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6321,7 +6301,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>0.7</v>
+        <v>5.8</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6364,7 +6344,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 59402-2022</t>
+          <t>A 51587-2023</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6378,10 +6358,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>44906</v>
+        <v>45215</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6393,8 +6373,13 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I69" t="n">
-        <v>1.8</v>
+        <v>2.6</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6437,7 +6422,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 3630-2023</t>
+          <t>A 72524-2021</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6451,10 +6436,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>44950</v>
+        <v>44546</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6467,7 +6452,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>1.4</v>
+        <v>3.6</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6510,7 +6495,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 7860-2024</t>
+          <t>A 4338-2023</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6524,10 +6509,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45348</v>
+        <v>44953</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6539,13 +6524,8 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I71" t="n">
-        <v>1.9</v>
+        <v>1.1</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6588,7 +6568,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 64105-2023</t>
+          <t>A 59848-2022</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6602,10 +6582,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45279</v>
+        <v>44901</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6617,8 +6597,13 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I72" t="n">
-        <v>2.2</v>
+        <v>10.7</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6661,7 +6646,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 64114-2023</t>
+          <t>A 59700-2021</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6675,10 +6660,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45279</v>
+        <v>44494</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6690,8 +6675,13 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I73" t="n">
-        <v>0.4</v>
+        <v>4.8</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6734,7 +6724,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 31714-2026</t>
+          <t>A 7275-2022</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6748,10 +6738,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>46226</v>
+        <v>44606</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6763,8 +6753,13 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I74" t="n">
-        <v>5</v>
+        <v>9.6</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6807,7 +6802,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 7112-2025</t>
+          <t>A 64107-2023</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6821,10 +6816,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45701</v>
+        <v>45279</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6837,7 +6832,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>2.4</v>
+        <v>0.3</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6880,7 +6875,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 23615-2025</t>
+          <t>A 7112-2025</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6894,10 +6889,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45792</v>
+        <v>45701</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6910,7 +6905,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>1.3</v>
+        <v>2.4</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6953,7 +6948,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 23627-2025</t>
+          <t>A 38902-2024</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6967,10 +6962,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45792</v>
+        <v>45547</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6982,8 +6977,13 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I77" t="n">
-        <v>1.7</v>
+        <v>0.8</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7043,7 +7043,7 @@
         <v>44558</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>

--- a/Översikt UPPLANDS-BRO.xlsx
+++ b/Översikt UPPLANDS-BRO.xlsx
@@ -601,7 +601,7 @@
         <v>44481</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -714,7 +714,7 @@
         <v>44552</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -822,7 +822,7 @@
         <v>44552</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -930,7 +930,7 @@
         <v>45232</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1025,7 +1025,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 18772-2026</t>
+          <t>A 18790-2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1042,7 +1042,7 @@
         <v>46128</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1060,16 +1060,16 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>19.5</v>
+        <v>5.5</v>
       </c>
       <c r="J6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
@@ -1084,7 +1084,7 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -1100,147 +1100,147 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
+          <t>Fläcknycklar
+Nattviol</t>
+        </is>
+      </c>
+      <c r="W6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 18790-2026 artfynd.xlsx", "A 18790-2026")</f>
+        <v/>
+      </c>
+      <c r="X6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 18790-2026 karta.png", "A 18790-2026")</f>
+        <v/>
+      </c>
+      <c r="Y6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 18790-2026 georefererad karta.tif", "A 18790-2026")</f>
+        <v/>
+      </c>
+      <c r="AA6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 18790-2026 FSC-klagomål.docx", "A 18790-2026")</f>
+        <v/>
+      </c>
+      <c r="AB6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 18790-2026 FSC-klagomål mail.docx", "A 18790-2026")</f>
+        <v/>
+      </c>
+      <c r="AC6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 18790-2026 tillsynsbegäran.docx", "A 18790-2026")</f>
+        <v/>
+      </c>
+      <c r="AD6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 18790-2026 tillsynsbegäran mail.docx", "A 18790-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>A 18772-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>46128</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>UPPLANDS-BRO</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>2</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
           <t>Svedjenäva
 Fläcknycklar</t>
         </is>
       </c>
-      <c r="W6">
+      <c r="W7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 18772-2026 artfynd.xlsx", "A 18772-2026")</f>
         <v/>
       </c>
-      <c r="X6">
+      <c r="X7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 18772-2026 karta.png", "A 18772-2026")</f>
         <v/>
       </c>
-      <c r="Y6">
+      <c r="Y7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 18772-2026 georefererad karta.tif", "A 18772-2026")</f>
         <v/>
       </c>
-      <c r="AA6">
+      <c r="AA7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 18772-2026 FSC-klagomål.docx", "A 18772-2026")</f>
         <v/>
       </c>
-      <c r="AB6">
+      <c r="AB7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 18772-2026 FSC-klagomål mail.docx", "A 18772-2026")</f>
         <v/>
       </c>
-      <c r="AC6">
+      <c r="AC7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 18772-2026 tillsynsbegäran.docx", "A 18772-2026")</f>
         <v/>
       </c>
-      <c r="AD6">
+      <c r="AD7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 18772-2026 tillsynsbegäran mail.docx", "A 18772-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>A 18790-2026</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>46128</v>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>UPPLANDS-BRO</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="J7" t="n">
-        <v>2</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
-        <v>2</v>
-      </c>
-      <c r="T7" t="n">
-        <v>2</v>
-      </c>
-      <c r="U7" t="n">
-        <v>0</v>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>Fläcknycklar
-Nattviol</t>
-        </is>
-      </c>
-      <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 18790-2026 artfynd.xlsx", "A 18790-2026")</f>
-        <v/>
-      </c>
-      <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 18790-2026 karta.png", "A 18790-2026")</f>
-        <v/>
-      </c>
-      <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 18790-2026 georefererad karta.tif", "A 18790-2026")</f>
-        <v/>
-      </c>
-      <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 18790-2026 FSC-klagomål.docx", "A 18790-2026")</f>
-        <v/>
-      </c>
-      <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 18790-2026 FSC-klagomål mail.docx", "A 18790-2026")</f>
-        <v/>
-      </c>
-      <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 18790-2026 tillsynsbegäran.docx", "A 18790-2026")</f>
-        <v/>
-      </c>
-      <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 18790-2026 tillsynsbegäran mail.docx", "A 18790-2026")</f>
         <v/>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
         <v>45722</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
         <v>44603</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1481,7 +1481,7 @@
         <v>44552</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1569,7 +1569,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 25561-2025</t>
+          <t>A 11447-2025</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1579,14 +1579,14 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45803</v>
+        <v>45726</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1599,13 +1599,13 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="J11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -1614,7 +1614,7 @@
         <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1623,10 +1623,10 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1639,42 +1639,42 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>Bombmurkla</t>
+          <t>Myskbock</t>
         </is>
       </c>
       <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 25561-2025 artfynd.xlsx", "A 25561-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 11447-2025 artfynd.xlsx", "A 11447-2025")</f>
         <v/>
       </c>
       <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 25561-2025 karta.png", "A 25561-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 11447-2025 karta.png", "A 11447-2025")</f>
         <v/>
       </c>
       <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 25561-2025 georefererad karta.tif", "A 25561-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 11447-2025 georefererad karta.tif", "A 11447-2025")</f>
         <v/>
       </c>
       <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 25561-2025 FSC-klagomål.docx", "A 25561-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 11447-2025 FSC-klagomål.docx", "A 11447-2025")</f>
         <v/>
       </c>
       <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 25561-2025 FSC-klagomål mail.docx", "A 25561-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 11447-2025 FSC-klagomål mail.docx", "A 11447-2025")</f>
         <v/>
       </c>
       <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 25561-2025 tillsynsbegäran.docx", "A 25561-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 11447-2025 tillsynsbegäran.docx", "A 11447-2025")</f>
         <v/>
       </c>
       <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 25561-2025 tillsynsbegäran mail.docx", "A 25561-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 11447-2025 tillsynsbegäran mail.docx", "A 11447-2025")</f>
         <v/>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 2409-2026</t>
+          <t>A 7955-2023</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1688,10 +1688,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46034</v>
+        <v>44973</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1704,7 +1704,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>14.2</v>
+        <v>2.9</v>
       </c>
       <c r="J12" t="n">
         <v>1</v>
@@ -1719,7 +1719,7 @@
         <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1728,10 +1728,10 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1740,43 +1740,39 @@
         <v>1</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>Havsörn</t>
+          <t>Bombmurkla</t>
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 2409-2026 artfynd.xlsx", "A 2409-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 7955-2023 artfynd.xlsx", "A 7955-2023")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 2409-2026 karta.png", "A 2409-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 7955-2023 karta.png", "A 7955-2023")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 2409-2026 georefererad karta.tif", "A 2409-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 7955-2023 georefererad karta.tif", "A 7955-2023")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 2409-2026 FSC-klagomål.docx", "A 2409-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 7955-2023 FSC-klagomål.docx", "A 7955-2023")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 2409-2026 FSC-klagomål mail.docx", "A 2409-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 7955-2023 FSC-klagomål mail.docx", "A 7955-2023")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 2409-2026 tillsynsbegäran.docx", "A 2409-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 7955-2023 tillsynsbegäran.docx", "A 7955-2023")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 2409-2026 tillsynsbegäran mail.docx", "A 2409-2026")</f>
-        <v/>
-      </c>
-      <c r="AE12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/fåglar/A 2409-2026 prioriterade fågelarter.docx", "A 2409-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 7955-2023 tillsynsbegäran mail.docx", "A 7955-2023")</f>
         <v/>
       </c>
     </row>
@@ -1800,7 +1796,7 @@
         <v>45730</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1888,7 +1884,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 73773-2021</t>
+          <t>A 46438-2023</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1902,10 +1898,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>44552</v>
+        <v>45197</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1918,7 +1914,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>1.9</v>
+        <v>0.5</v>
       </c>
       <c r="J14" t="n">
         <v>1</v>
@@ -1933,7 +1929,7 @@
         <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -1942,10 +1938,10 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
@@ -1954,39 +1950,39 @@
         <v>1</v>
       </c>
       <c r="U14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Kopparödla</t>
+          <t>Bombmurkla</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 73773-2021 artfynd.xlsx", "A 73773-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 46438-2023 artfynd.xlsx", "A 46438-2023")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 73773-2021 karta.png", "A 73773-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 46438-2023 karta.png", "A 46438-2023")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 73773-2021 georefererad karta.tif", "A 73773-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 46438-2023 georefererad karta.tif", "A 46438-2023")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 73773-2021 FSC-klagomål.docx", "A 73773-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 46438-2023 FSC-klagomål.docx", "A 46438-2023")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 73773-2021 FSC-klagomål mail.docx", "A 73773-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 46438-2023 FSC-klagomål mail.docx", "A 46438-2023")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 73773-2021 tillsynsbegäran.docx", "A 73773-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 46438-2023 tillsynsbegäran.docx", "A 46438-2023")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 73773-2021 tillsynsbegäran mail.docx", "A 73773-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 46438-2023 tillsynsbegäran mail.docx", "A 46438-2023")</f>
         <v/>
       </c>
     </row>
@@ -2010,7 +2006,7 @@
         <v>45959</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2115,7 +2111,7 @@
         <v>45450</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2208,7 +2204,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 26637-2026</t>
+          <t>A 2409-2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2222,10 +2218,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46184</v>
+        <v>46034</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2238,10 +2234,10 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>5.4</v>
+        <v>14.2</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
@@ -2250,7 +2246,7 @@
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
@@ -2262,10 +2258,10 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
@@ -2278,35 +2274,39 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Igelkott</t>
+          <t>Havsörn</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 26637-2026 artfynd.xlsx", "A 26637-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 2409-2026 artfynd.xlsx", "A 2409-2026")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 26637-2026 karta.png", "A 26637-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 2409-2026 karta.png", "A 2409-2026")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 26637-2026 georefererad karta.tif", "A 26637-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 2409-2026 georefererad karta.tif", "A 2409-2026")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 26637-2026 FSC-klagomål.docx", "A 26637-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 2409-2026 FSC-klagomål.docx", "A 2409-2026")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 26637-2026 FSC-klagomål mail.docx", "A 26637-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 2409-2026 FSC-klagomål mail.docx", "A 2409-2026")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 26637-2026 tillsynsbegäran.docx", "A 26637-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 2409-2026 tillsynsbegäran.docx", "A 2409-2026")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 26637-2026 tillsynsbegäran mail.docx", "A 26637-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 2409-2026 tillsynsbegäran mail.docx", "A 2409-2026")</f>
+        <v/>
+      </c>
+      <c r="AE17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/fåglar/A 2409-2026 prioriterade fågelarter.docx", "A 2409-2026")</f>
         <v/>
       </c>
     </row>
@@ -2330,7 +2330,7 @@
         <v>46184</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2418,7 +2418,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 46438-2023</t>
+          <t>A 26637-2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2432,10 +2432,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45197</v>
+        <v>46184</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2448,10 +2448,10 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>0.5</v>
+        <v>5.4</v>
       </c>
       <c r="J19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
@@ -2460,10 +2460,10 @@
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2488,42 +2488,42 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Bombmurkla</t>
+          <t>Igelkott</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 46438-2023 artfynd.xlsx", "A 46438-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 26637-2026 artfynd.xlsx", "A 26637-2026")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 46438-2023 karta.png", "A 46438-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 26637-2026 karta.png", "A 26637-2026")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 46438-2023 georefererad karta.tif", "A 46438-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 26637-2026 georefererad karta.tif", "A 26637-2026")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 46438-2023 FSC-klagomål.docx", "A 46438-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 26637-2026 FSC-klagomål.docx", "A 26637-2026")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 46438-2023 FSC-klagomål mail.docx", "A 46438-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 26637-2026 FSC-klagomål mail.docx", "A 26637-2026")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 46438-2023 tillsynsbegäran.docx", "A 46438-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 26637-2026 tillsynsbegäran.docx", "A 26637-2026")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 46438-2023 tillsynsbegäran mail.docx", "A 46438-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 26637-2026 tillsynsbegäran mail.docx", "A 26637-2026")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 11447-2025</t>
+          <t>A 64098-2023</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2533,14 +2533,14 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45726</v>
+        <v>45279</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2553,16 +2553,16 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>1.5</v>
+        <v>0.3</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M20" t="n">
         <v>0</v>
@@ -2577,7 +2577,7 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
@@ -2593,42 +2593,42 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>Myskbock</t>
+          <t>Skogsalmsdvärgmal</t>
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 11447-2025 artfynd.xlsx", "A 11447-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 64098-2023 artfynd.xlsx", "A 64098-2023")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 11447-2025 karta.png", "A 11447-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 64098-2023 karta.png", "A 64098-2023")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 11447-2025 georefererad karta.tif", "A 11447-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 64098-2023 georefererad karta.tif", "A 64098-2023")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 11447-2025 FSC-klagomål.docx", "A 11447-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 64098-2023 FSC-klagomål.docx", "A 64098-2023")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 11447-2025 FSC-klagomål mail.docx", "A 11447-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 64098-2023 FSC-klagomål mail.docx", "A 64098-2023")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 11447-2025 tillsynsbegäran.docx", "A 11447-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 64098-2023 tillsynsbegäran.docx", "A 64098-2023")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 11447-2025 tillsynsbegäran mail.docx", "A 11447-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 64098-2023 tillsynsbegäran mail.docx", "A 64098-2023")</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 7955-2023</t>
+          <t>A 73773-2021</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2642,10 +2642,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>44973</v>
+        <v>44552</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2658,7 +2658,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>2.9</v>
+        <v>1.9</v>
       </c>
       <c r="J21" t="n">
         <v>1</v>
@@ -2673,7 +2673,7 @@
         <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2682,10 +2682,10 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
         <v>1</v>
@@ -2698,42 +2698,42 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Bombmurkla</t>
+          <t>Kopparödla</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 7955-2023 artfynd.xlsx", "A 7955-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 73773-2021 artfynd.xlsx", "A 73773-2021")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 7955-2023 karta.png", "A 7955-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 73773-2021 karta.png", "A 73773-2021")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 7955-2023 georefererad karta.tif", "A 7955-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 73773-2021 georefererad karta.tif", "A 73773-2021")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 7955-2023 FSC-klagomål.docx", "A 7955-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 73773-2021 FSC-klagomål.docx", "A 73773-2021")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 7955-2023 FSC-klagomål mail.docx", "A 7955-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 73773-2021 FSC-klagomål mail.docx", "A 73773-2021")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 7955-2023 tillsynsbegäran.docx", "A 7955-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 73773-2021 tillsynsbegäran.docx", "A 73773-2021")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 7955-2023 tillsynsbegäran mail.docx", "A 7955-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 73773-2021 tillsynsbegäran mail.docx", "A 73773-2021")</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 64098-2023</t>
+          <t>A 2062-2025</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2747,10 +2747,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45279</v>
+        <v>45671</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2763,10 +2763,10 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>0.3</v>
+        <v>1.9</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
@@ -2799,46 +2799,50 @@
         <v>1</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>Skogsalmsdvärgmal</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 64098-2023 artfynd.xlsx", "A 64098-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 2062-2025 artfynd.xlsx", "A 2062-2025")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 64098-2023 karta.png", "A 64098-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 2062-2025 karta.png", "A 2062-2025")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 64098-2023 georefererad karta.tif", "A 64098-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 2062-2025 georefererad karta.tif", "A 2062-2025")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 64098-2023 FSC-klagomål.docx", "A 64098-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 2062-2025 FSC-klagomål.docx", "A 2062-2025")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 64098-2023 FSC-klagomål mail.docx", "A 64098-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 2062-2025 FSC-klagomål mail.docx", "A 2062-2025")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 64098-2023 tillsynsbegäran.docx", "A 64098-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 2062-2025 tillsynsbegäran.docx", "A 2062-2025")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 64098-2023 tillsynsbegäran mail.docx", "A 64098-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 2062-2025 tillsynsbegäran mail.docx", "A 2062-2025")</f>
+        <v/>
+      </c>
+      <c r="AE22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/fåglar/A 2062-2025 prioriterade fågelarter.docx", "A 2062-2025")</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 2062-2025</t>
+          <t>A 25561-2025</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2852,10 +2856,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45671</v>
+        <v>45803</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2868,7 +2872,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>1.9</v>
+        <v>1.6</v>
       </c>
       <c r="J23" t="n">
         <v>1</v>
@@ -2877,13 +2881,13 @@
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
         <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -2895,7 +2899,7 @@
         <v>1</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S23" t="n">
         <v>1</v>
@@ -2904,43 +2908,39 @@
         <v>1</v>
       </c>
       <c r="U23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Bombmurkla</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 2062-2025 artfynd.xlsx", "A 2062-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 25561-2025 artfynd.xlsx", "A 25561-2025")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 2062-2025 karta.png", "A 2062-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 25561-2025 karta.png", "A 25561-2025")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 2062-2025 georefererad karta.tif", "A 2062-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 25561-2025 georefererad karta.tif", "A 25561-2025")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 2062-2025 FSC-klagomål.docx", "A 2062-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 25561-2025 FSC-klagomål.docx", "A 25561-2025")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 2062-2025 FSC-klagomål mail.docx", "A 2062-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 25561-2025 FSC-klagomål mail.docx", "A 25561-2025")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 2062-2025 tillsynsbegäran.docx", "A 2062-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 25561-2025 tillsynsbegäran.docx", "A 25561-2025")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 2062-2025 tillsynsbegäran mail.docx", "A 2062-2025")</f>
-        <v/>
-      </c>
-      <c r="AE23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/fåglar/A 2062-2025 prioriterade fågelarter.docx", "A 2062-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 25561-2025 tillsynsbegäran mail.docx", "A 25561-2025")</f>
         <v/>
       </c>
     </row>
@@ -2964,7 +2964,7 @@
         <v>44558</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3069,7 +3069,7 @@
         <v>44609</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3142,7 +3142,7 @@
         <v>44489</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3220,7 +3220,7 @@
         <v>44546</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3293,7 +3293,7 @@
         <v>44700</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3366,7 +3366,7 @@
         <v>44587</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3439,7 +3439,7 @@
         <v>44655</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3500,7 +3500,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 64105-2023</t>
+          <t>A 59848-2022</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3514,10 +3514,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45279</v>
+        <v>44901</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3529,8 +3529,13 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I31" t="n">
-        <v>2.2</v>
+        <v>10.7</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3573,7 +3578,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 2602-2024</t>
+          <t>A 49622-2021</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3587,10 +3592,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45313</v>
+        <v>44455</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3603,7 +3608,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0.7</v>
+        <v>3.8</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3646,7 +3651,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 59844-2022</t>
+          <t>A 64110-2023</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3660,10 +3665,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44901</v>
+        <v>45279</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3675,13 +3680,8 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I33" t="n">
-        <v>11.9</v>
+        <v>0.4</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3724,7 +3724,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 23615-2025</t>
+          <t>A 59700-2021</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3738,10 +3738,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45792</v>
+        <v>44494</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3753,8 +3753,13 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I34" t="n">
-        <v>1.3</v>
+        <v>4.8</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3797,7 +3802,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 23627-2025</t>
+          <t>A 38902-2024</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3811,10 +3816,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45792</v>
+        <v>45547</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3826,8 +3831,13 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I35" t="n">
-        <v>1.7</v>
+        <v>0.8</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3870,7 +3880,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 3630-2023</t>
+          <t>A 50294-2023</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3884,10 +3894,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44950</v>
+        <v>45216</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3900,7 +3910,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>1.4</v>
+        <v>3.7</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3943,7 +3953,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 23093-2024</t>
+          <t>A 18787-2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3957,10 +3967,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45450</v>
+        <v>46128</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3978,7 +3988,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>0.9</v>
+        <v>7.8</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4021,7 +4031,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 54222-2023</t>
+          <t>A 18813-2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4035,10 +4045,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45225</v>
+        <v>46128</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4056,7 +4066,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>8.300000000000001</v>
+        <v>56</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4099,7 +4109,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 7860-2024</t>
+          <t>A 18818-2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4113,10 +4123,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45348</v>
+        <v>46128</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4134,7 +4144,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1.9</v>
+        <v>17.8</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4177,7 +4187,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 9655-2026</t>
+          <t>A 18778-2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4191,10 +4201,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>46070</v>
+        <v>46128</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4212,7 +4222,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>17.2</v>
+        <v>4.5</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4255,7 +4265,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 27313-2023</t>
+          <t>A 5264-2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4269,10 +4279,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45096</v>
+        <v>44959</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4285,7 +4295,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1.8</v>
+        <v>5.8</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4328,7 +4338,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 64114-2023</t>
+          <t>A 21206-2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4342,10 +4352,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45279</v>
+        <v>46146</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4357,8 +4367,13 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I42" t="n">
-        <v>0.4</v>
+        <v>0.9</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4401,7 +4416,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 50294-2023</t>
+          <t>A 7275-2022</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4415,10 +4430,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45216</v>
+        <v>44606</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4430,8 +4445,13 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I43" t="n">
-        <v>3.7</v>
+        <v>9.6</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4474,7 +4494,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 18778-2026</t>
+          <t>A 2602-2024</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4488,10 +4508,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>46128</v>
+        <v>45313</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4503,13 +4523,8 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I44" t="n">
-        <v>4.5</v>
+        <v>0.7</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4552,7 +4567,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 18813-2026</t>
+          <t>A 23098-2024</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4566,10 +4581,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>46128</v>
+        <v>45450</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4587,7 +4602,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>56</v>
+        <v>1</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4630,7 +4645,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 18818-2026</t>
+          <t>A 59402-2022</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4644,10 +4659,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>46128</v>
+        <v>44906</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4659,13 +4674,8 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I46" t="n">
-        <v>17.8</v>
+        <v>1.8</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4708,7 +4718,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 18787-2026</t>
+          <t>A 59844-2022</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4722,10 +4732,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>46128</v>
+        <v>44901</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4743,7 +4753,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>7.8</v>
+        <v>11.9</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4786,7 +4796,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 58011-2021</t>
+          <t>A 54222-2023</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4800,10 +4810,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>44487</v>
+        <v>45225</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4821,7 +4831,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>9.199999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4864,7 +4874,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 49622-2021</t>
+          <t>A 24579-2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4878,10 +4888,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>44455</v>
+        <v>46170</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4894,7 +4904,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>3.8</v>
+        <v>2.1</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4937,7 +4947,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 21206-2026</t>
+          <t>A 58598-2025</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4951,10 +4961,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>46146</v>
+        <v>45986</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4972,7 +4982,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>0.9</v>
+        <v>4.5</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5015,7 +5025,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 64110-2023</t>
+          <t>A 31160-2022</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5029,10 +5039,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45279</v>
+        <v>44770</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5045,7 +5055,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>0.4</v>
+        <v>3.7</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5088,7 +5098,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 23098-2024</t>
+          <t>A 26196-2026</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5098,14 +5108,14 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45450</v>
+        <v>46182</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5117,13 +5127,8 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I52" t="n">
-        <v>1</v>
+        <v>53.1</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5166,7 +5171,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 24579-2026</t>
+          <t>A 4338-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5180,10 +5185,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>46170</v>
+        <v>44953</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5196,7 +5201,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>2.1</v>
+        <v>1.1</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5239,7 +5244,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 31160-2022</t>
+          <t>A 58011-2021</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5253,10 +5258,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>44770</v>
+        <v>44487</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5268,8 +5273,13 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I54" t="n">
-        <v>3.7</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5312,7 +5322,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 58598-2025</t>
+          <t>A 26625-2026</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5326,10 +5336,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45986</v>
+        <v>46184</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5341,13 +5351,8 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I55" t="n">
-        <v>4.5</v>
+        <v>5.3</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5390,7 +5395,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 26196-2026</t>
+          <t>A 72524-2021</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5400,14 +5405,14 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>46182</v>
+        <v>44546</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5420,7 +5425,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>53.1</v>
+        <v>3.6</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5463,7 +5468,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 26633-2026</t>
+          <t>A 9655-2026</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5477,10 +5482,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>46184</v>
+        <v>46070</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5492,8 +5497,13 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I57" t="n">
-        <v>0.7</v>
+        <v>17.2</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5536,7 +5546,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 26625-2026</t>
+          <t>A 26629-2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5553,7 +5563,7 @@
         <v>46184</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5566,7 +5576,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>5.3</v>
+        <v>2</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5609,7 +5619,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 26629-2026</t>
+          <t>A 26633-2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5626,7 +5636,7 @@
         <v>46184</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5639,7 +5649,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>2</v>
+        <v>0.7</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5682,7 +5692,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 3754-2026</t>
+          <t>A 64107-2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5696,10 +5706,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>46043</v>
+        <v>45279</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5711,13 +5721,8 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I60" t="n">
-        <v>5.1</v>
+        <v>0.3</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5760,7 +5765,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 59377-2024</t>
+          <t>A 23093-2024</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5774,10 +5779,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45638</v>
+        <v>45450</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5789,8 +5794,13 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I61" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5833,7 +5843,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 28735-2026</t>
+          <t>A 3630-2023</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5847,10 +5857,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>46198</v>
+        <v>44950</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5863,7 +5873,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>3.5</v>
+        <v>1.4</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5906,7 +5916,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 28740-2026</t>
+          <t>A 7860-2024</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5920,10 +5930,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>46198</v>
+        <v>45348</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5935,8 +5945,13 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I63" t="n">
-        <v>4.8</v>
+        <v>1.9</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5979,7 +5994,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 28797-2026</t>
+          <t>A 3754-2026</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5993,10 +6008,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>46198</v>
+        <v>46043</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6008,8 +6023,13 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I64" t="n">
-        <v>2.2</v>
+        <v>5.1</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6052,7 +6072,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 33058-2026</t>
+          <t>A 27313-2023</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6062,14 +6082,14 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>46245</v>
+        <v>45096</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6082,7 +6102,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>1.3</v>
+        <v>1.8</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6125,7 +6145,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 59402-2022</t>
+          <t>A 28797-2026</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6139,10 +6159,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>44906</v>
+        <v>46198</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6155,7 +6175,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6198,7 +6218,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 31714-2026</t>
+          <t>A 28740-2026</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6212,10 +6232,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>46226</v>
+        <v>46198</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6228,7 +6248,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6271,7 +6291,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 5264-2023</t>
+          <t>A 28735-2026</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6285,10 +6305,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>44959</v>
+        <v>46198</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6301,7 +6321,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>5.8</v>
+        <v>3.5</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6344,7 +6364,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 51587-2023</t>
+          <t>A 59377-2024</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6358,10 +6378,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45215</v>
+        <v>45638</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6373,13 +6393,8 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I69" t="n">
-        <v>2.6</v>
+        <v>0.6</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6422,7 +6437,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 72524-2021</t>
+          <t>A 33058-2026</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6432,14 +6447,14 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>44546</v>
+        <v>46245</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6452,7 +6467,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>3.6</v>
+        <v>1.3</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6495,7 +6510,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 4338-2023</t>
+          <t>A 64105-2023</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6509,10 +6524,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>44953</v>
+        <v>45279</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6525,7 +6540,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>1.1</v>
+        <v>2.2</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6568,7 +6583,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 59848-2022</t>
+          <t>A 51587-2023</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6582,10 +6597,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>44901</v>
+        <v>45215</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6599,11 +6614,11 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Övriga statliga verk och myndigheter</t>
+          <t>Allmännings- och besparingsskogar</t>
         </is>
       </c>
       <c r="I72" t="n">
-        <v>10.7</v>
+        <v>2.6</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6646,7 +6661,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 59700-2021</t>
+          <t>A 64114-2023</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6660,10 +6675,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>44494</v>
+        <v>45279</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6675,13 +6690,8 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I73" t="n">
-        <v>4.8</v>
+        <v>0.4</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6724,7 +6734,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 7275-2022</t>
+          <t>A 31714-2026</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6738,10 +6748,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>44606</v>
+        <v>46226</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6753,13 +6763,8 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I74" t="n">
-        <v>9.6</v>
+        <v>5</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6802,7 +6807,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 64107-2023</t>
+          <t>A 7112-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6816,10 +6821,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45279</v>
+        <v>45701</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6832,7 +6837,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>0.3</v>
+        <v>2.4</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6875,7 +6880,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 7112-2025</t>
+          <t>A 23615-2025</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6889,10 +6894,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45701</v>
+        <v>45792</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6905,7 +6910,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>2.4</v>
+        <v>1.3</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6948,7 +6953,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 38902-2024</t>
+          <t>A 23627-2025</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6962,10 +6967,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45547</v>
+        <v>45792</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6977,13 +6982,8 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I77" t="n">
-        <v>0.8</v>
+        <v>1.7</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7043,7 +7043,7 @@
         <v>44558</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>

--- a/Översikt UPPLANDS-BRO.xlsx
+++ b/Översikt UPPLANDS-BRO.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE78"/>
+  <dimension ref="A1:AE77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>44481</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -714,7 +714,7 @@
         <v>44552</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -822,7 +822,7 @@
         <v>44552</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -930,7 +930,7 @@
         <v>45232</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1025,7 +1025,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 18790-2026</t>
+          <t>A 18772-2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1042,7 +1042,7 @@
         <v>46128</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1060,16 +1060,16 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>5.5</v>
+        <v>19.5</v>
       </c>
       <c r="J6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
@@ -1084,7 +1084,7 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -1100,147 +1100,147 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
+          <t>Svedjenäva
+Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="W6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 18772-2026 artfynd.xlsx", "A 18772-2026")</f>
+        <v/>
+      </c>
+      <c r="X6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 18772-2026 karta.png", "A 18772-2026")</f>
+        <v/>
+      </c>
+      <c r="Y6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 18772-2026 georefererad karta.tif", "A 18772-2026")</f>
+        <v/>
+      </c>
+      <c r="AA6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 18772-2026 FSC-klagomål.docx", "A 18772-2026")</f>
+        <v/>
+      </c>
+      <c r="AB6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 18772-2026 FSC-klagomål mail.docx", "A 18772-2026")</f>
+        <v/>
+      </c>
+      <c r="AC6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 18772-2026 tillsynsbegäran.docx", "A 18772-2026")</f>
+        <v/>
+      </c>
+      <c r="AD6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 18772-2026 tillsynsbegäran mail.docx", "A 18772-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>A 18790-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>46128</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>UPPLANDS-BRO</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="J7" t="n">
+        <v>2</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>2</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
           <t>Fläcknycklar
 Nattviol</t>
         </is>
       </c>
-      <c r="W6">
+      <c r="W7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 18790-2026 artfynd.xlsx", "A 18790-2026")</f>
         <v/>
       </c>
-      <c r="X6">
+      <c r="X7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 18790-2026 karta.png", "A 18790-2026")</f>
         <v/>
       </c>
-      <c r="Y6">
+      <c r="Y7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 18790-2026 georefererad karta.tif", "A 18790-2026")</f>
         <v/>
       </c>
-      <c r="AA6">
+      <c r="AA7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 18790-2026 FSC-klagomål.docx", "A 18790-2026")</f>
         <v/>
       </c>
-      <c r="AB6">
+      <c r="AB7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 18790-2026 FSC-klagomål mail.docx", "A 18790-2026")</f>
         <v/>
       </c>
-      <c r="AC6">
+      <c r="AC7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 18790-2026 tillsynsbegäran.docx", "A 18790-2026")</f>
         <v/>
       </c>
-      <c r="AD6">
+      <c r="AD7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 18790-2026 tillsynsbegäran mail.docx", "A 18790-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>A 18772-2026</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>46128</v>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>UPPLANDS-BRO</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="J7" t="n">
-        <v>1</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>1</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>1</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
-        <v>2</v>
-      </c>
-      <c r="T7" t="n">
-        <v>2</v>
-      </c>
-      <c r="U7" t="n">
-        <v>0</v>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>Svedjenäva
-Fläcknycklar</t>
-        </is>
-      </c>
-      <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 18772-2026 artfynd.xlsx", "A 18772-2026")</f>
-        <v/>
-      </c>
-      <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 18772-2026 karta.png", "A 18772-2026")</f>
-        <v/>
-      </c>
-      <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 18772-2026 georefererad karta.tif", "A 18772-2026")</f>
-        <v/>
-      </c>
-      <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 18772-2026 FSC-klagomål.docx", "A 18772-2026")</f>
-        <v/>
-      </c>
-      <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 18772-2026 FSC-klagomål mail.docx", "A 18772-2026")</f>
-        <v/>
-      </c>
-      <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 18772-2026 tillsynsbegäran.docx", "A 18772-2026")</f>
-        <v/>
-      </c>
-      <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 18772-2026 tillsynsbegäran mail.docx", "A 18772-2026")</f>
         <v/>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
         <v>45722</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
         <v>44603</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1481,7 +1481,7 @@
         <v>44552</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1569,7 +1569,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 11447-2025</t>
+          <t>A 25561-2025</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1579,14 +1579,14 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45726</v>
+        <v>45803</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1599,13 +1599,13 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -1614,7 +1614,7 @@
         <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1623,10 +1623,10 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1639,42 +1639,42 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>Myskbock</t>
+          <t>Bombmurkla</t>
         </is>
       </c>
       <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 11447-2025 artfynd.xlsx", "A 11447-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 25561-2025 artfynd.xlsx", "A 25561-2025")</f>
         <v/>
       </c>
       <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 11447-2025 karta.png", "A 11447-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 25561-2025 karta.png", "A 25561-2025")</f>
         <v/>
       </c>
       <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 11447-2025 georefererad karta.tif", "A 11447-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 25561-2025 georefererad karta.tif", "A 25561-2025")</f>
         <v/>
       </c>
       <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 11447-2025 FSC-klagomål.docx", "A 11447-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 25561-2025 FSC-klagomål.docx", "A 25561-2025")</f>
         <v/>
       </c>
       <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 11447-2025 FSC-klagomål mail.docx", "A 11447-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 25561-2025 FSC-klagomål mail.docx", "A 25561-2025")</f>
         <v/>
       </c>
       <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 11447-2025 tillsynsbegäran.docx", "A 11447-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 25561-2025 tillsynsbegäran.docx", "A 25561-2025")</f>
         <v/>
       </c>
       <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 11447-2025 tillsynsbegäran mail.docx", "A 11447-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 25561-2025 tillsynsbegäran mail.docx", "A 25561-2025")</f>
         <v/>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 7955-2023</t>
+          <t>A 2409-2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1688,10 +1688,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>44973</v>
+        <v>46034</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1704,7 +1704,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>2.9</v>
+        <v>14.2</v>
       </c>
       <c r="J12" t="n">
         <v>1</v>
@@ -1719,7 +1719,7 @@
         <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1728,10 +1728,10 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1740,39 +1740,43 @@
         <v>1</v>
       </c>
       <c r="U12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>Bombmurkla</t>
+          <t>Havsörn</t>
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 7955-2023 artfynd.xlsx", "A 7955-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 2409-2026 artfynd.xlsx", "A 2409-2026")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 7955-2023 karta.png", "A 7955-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 2409-2026 karta.png", "A 2409-2026")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 7955-2023 georefererad karta.tif", "A 7955-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 2409-2026 georefererad karta.tif", "A 2409-2026")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 7955-2023 FSC-klagomål.docx", "A 7955-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 2409-2026 FSC-klagomål.docx", "A 2409-2026")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 7955-2023 FSC-klagomål mail.docx", "A 7955-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 2409-2026 FSC-klagomål mail.docx", "A 2409-2026")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 7955-2023 tillsynsbegäran.docx", "A 7955-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 2409-2026 tillsynsbegäran.docx", "A 2409-2026")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 7955-2023 tillsynsbegäran mail.docx", "A 7955-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 2409-2026 tillsynsbegäran mail.docx", "A 2409-2026")</f>
+        <v/>
+      </c>
+      <c r="AE12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/fåglar/A 2409-2026 prioriterade fågelarter.docx", "A 2409-2026")</f>
         <v/>
       </c>
     </row>
@@ -1796,7 +1800,7 @@
         <v>45730</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1884,7 +1888,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 46438-2023</t>
+          <t>A 73773-2021</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1898,10 +1902,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45197</v>
+        <v>44552</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1914,7 +1918,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>0.5</v>
+        <v>1.9</v>
       </c>
       <c r="J14" t="n">
         <v>1</v>
@@ -1929,7 +1933,7 @@
         <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -1938,10 +1942,10 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
@@ -1950,39 +1954,39 @@
         <v>1</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Bombmurkla</t>
+          <t>Kopparödla</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 46438-2023 artfynd.xlsx", "A 46438-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 73773-2021 artfynd.xlsx", "A 73773-2021")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 46438-2023 karta.png", "A 46438-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 73773-2021 karta.png", "A 73773-2021")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 46438-2023 georefererad karta.tif", "A 46438-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 73773-2021 georefererad karta.tif", "A 73773-2021")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 46438-2023 FSC-klagomål.docx", "A 46438-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 73773-2021 FSC-klagomål.docx", "A 73773-2021")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 46438-2023 FSC-klagomål mail.docx", "A 46438-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 73773-2021 FSC-klagomål mail.docx", "A 73773-2021")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 46438-2023 tillsynsbegäran.docx", "A 46438-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 73773-2021 tillsynsbegäran.docx", "A 73773-2021")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 46438-2023 tillsynsbegäran mail.docx", "A 46438-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 73773-2021 tillsynsbegäran mail.docx", "A 73773-2021")</f>
         <v/>
       </c>
     </row>
@@ -2006,7 +2010,7 @@
         <v>45959</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2111,7 +2115,7 @@
         <v>45450</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2204,7 +2208,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 2409-2026</t>
+          <t>A 46438-2023</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2218,10 +2222,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46034</v>
+        <v>45197</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2234,7 +2238,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>14.2</v>
+        <v>0.5</v>
       </c>
       <c r="J17" t="n">
         <v>1</v>
@@ -2249,7 +2253,7 @@
         <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2258,10 +2262,10 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
@@ -2274,46 +2278,42 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Havsörn</t>
+          <t>Bombmurkla</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 2409-2026 artfynd.xlsx", "A 2409-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 46438-2023 artfynd.xlsx", "A 46438-2023")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 2409-2026 karta.png", "A 2409-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 46438-2023 karta.png", "A 46438-2023")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 2409-2026 georefererad karta.tif", "A 2409-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 46438-2023 georefererad karta.tif", "A 46438-2023")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 2409-2026 FSC-klagomål.docx", "A 2409-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 46438-2023 FSC-klagomål.docx", "A 46438-2023")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 2409-2026 FSC-klagomål mail.docx", "A 2409-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 46438-2023 FSC-klagomål mail.docx", "A 46438-2023")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 2409-2026 tillsynsbegäran.docx", "A 2409-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 46438-2023 tillsynsbegäran.docx", "A 46438-2023")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 2409-2026 tillsynsbegäran mail.docx", "A 2409-2026")</f>
-        <v/>
-      </c>
-      <c r="AE17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/fåglar/A 2409-2026 prioriterade fågelarter.docx", "A 2409-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 46438-2023 tillsynsbegäran mail.docx", "A 46438-2023")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 26623-2026</t>
+          <t>A 11447-2025</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2323,14 +2323,14 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46184</v>
+        <v>45726</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2343,16 +2343,16 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>4.6</v>
+        <v>1.5</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
@@ -2367,7 +2367,7 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -2383,42 +2383,42 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Svartöra</t>
+          <t>Myskbock</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 26623-2026 artfynd.xlsx", "A 26623-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 11447-2025 artfynd.xlsx", "A 11447-2025")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 26623-2026 karta.png", "A 26623-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 11447-2025 karta.png", "A 11447-2025")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 26623-2026 georefererad karta.tif", "A 26623-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 11447-2025 georefererad karta.tif", "A 11447-2025")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 26623-2026 FSC-klagomål.docx", "A 26623-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 11447-2025 FSC-klagomål.docx", "A 11447-2025")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 26623-2026 FSC-klagomål mail.docx", "A 26623-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 11447-2025 FSC-klagomål mail.docx", "A 11447-2025")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 26623-2026 tillsynsbegäran.docx", "A 26623-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 11447-2025 tillsynsbegäran.docx", "A 11447-2025")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 26623-2026 tillsynsbegäran mail.docx", "A 26623-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 11447-2025 tillsynsbegäran mail.docx", "A 11447-2025")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 26637-2026</t>
+          <t>A 7955-2023</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2432,10 +2432,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46184</v>
+        <v>44973</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2448,10 +2448,10 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>5.4</v>
+        <v>2.9</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
@@ -2460,10 +2460,10 @@
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2484,46 +2484,46 @@
         <v>1</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Igelkott</t>
+          <t>Bombmurkla</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 26637-2026 artfynd.xlsx", "A 26637-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 7955-2023 artfynd.xlsx", "A 7955-2023")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 26637-2026 karta.png", "A 26637-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 7955-2023 karta.png", "A 7955-2023")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 26637-2026 georefererad karta.tif", "A 26637-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 7955-2023 georefererad karta.tif", "A 7955-2023")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 26637-2026 FSC-klagomål.docx", "A 26637-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 7955-2023 FSC-klagomål.docx", "A 7955-2023")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 26637-2026 FSC-klagomål mail.docx", "A 26637-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 7955-2023 FSC-klagomål mail.docx", "A 7955-2023")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 26637-2026 tillsynsbegäran.docx", "A 26637-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 7955-2023 tillsynsbegäran.docx", "A 7955-2023")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 26637-2026 tillsynsbegäran mail.docx", "A 26637-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 7955-2023 tillsynsbegäran mail.docx", "A 7955-2023")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 64098-2023</t>
+          <t>A 26637-2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2537,10 +2537,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45279</v>
+        <v>46184</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2553,7 +2553,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>0.3</v>
+        <v>5.4</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2562,10 +2562,10 @@
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N20" t="n">
         <v>0</v>
@@ -2580,7 +2580,7 @@
         <v>1</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>
@@ -2593,42 +2593,42 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>Skogsalmsdvärgmal</t>
+          <t>Igelkott</t>
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 64098-2023 artfynd.xlsx", "A 64098-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 26637-2026 artfynd.xlsx", "A 26637-2026")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 64098-2023 karta.png", "A 64098-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 26637-2026 karta.png", "A 26637-2026")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 64098-2023 georefererad karta.tif", "A 64098-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 26637-2026 georefererad karta.tif", "A 26637-2026")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 64098-2023 FSC-klagomål.docx", "A 64098-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 26637-2026 FSC-klagomål.docx", "A 26637-2026")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 64098-2023 FSC-klagomål mail.docx", "A 64098-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 26637-2026 FSC-klagomål mail.docx", "A 26637-2026")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 64098-2023 tillsynsbegäran.docx", "A 64098-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 26637-2026 tillsynsbegäran.docx", "A 26637-2026")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 64098-2023 tillsynsbegäran mail.docx", "A 64098-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 26637-2026 tillsynsbegäran mail.docx", "A 26637-2026")</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 73773-2021</t>
+          <t>A 26623-2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2642,10 +2642,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>44552</v>
+        <v>46184</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2658,16 +2658,16 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>1.9</v>
+        <v>4.6</v>
       </c>
       <c r="J21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M21" t="n">
         <v>0</v>
@@ -2682,7 +2682,7 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R21" t="n">
         <v>0</v>
@@ -2694,46 +2694,46 @@
         <v>1</v>
       </c>
       <c r="U21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Kopparödla</t>
+          <t>Svartöra</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 73773-2021 artfynd.xlsx", "A 73773-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 26623-2026 artfynd.xlsx", "A 26623-2026")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 73773-2021 karta.png", "A 73773-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 26623-2026 karta.png", "A 26623-2026")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 73773-2021 georefererad karta.tif", "A 73773-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 26623-2026 georefererad karta.tif", "A 26623-2026")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 73773-2021 FSC-klagomål.docx", "A 73773-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 26623-2026 FSC-klagomål.docx", "A 26623-2026")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 73773-2021 FSC-klagomål mail.docx", "A 73773-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 26623-2026 FSC-klagomål mail.docx", "A 26623-2026")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 73773-2021 tillsynsbegäran.docx", "A 73773-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 26623-2026 tillsynsbegäran.docx", "A 26623-2026")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 73773-2021 tillsynsbegäran mail.docx", "A 73773-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 26623-2026 tillsynsbegäran mail.docx", "A 26623-2026")</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 2062-2025</t>
+          <t>A 64098-2023</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2747,10 +2747,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45671</v>
+        <v>45279</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2763,10 +2763,10 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>1.9</v>
+        <v>0.3</v>
       </c>
       <c r="J22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
@@ -2799,50 +2799,46 @@
         <v>1</v>
       </c>
       <c r="U22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Skogsalmsdvärgmal</t>
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 2062-2025 artfynd.xlsx", "A 2062-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 64098-2023 artfynd.xlsx", "A 64098-2023")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 2062-2025 karta.png", "A 2062-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 64098-2023 karta.png", "A 64098-2023")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 2062-2025 georefererad karta.tif", "A 2062-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 64098-2023 georefererad karta.tif", "A 64098-2023")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 2062-2025 FSC-klagomål.docx", "A 2062-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 64098-2023 FSC-klagomål.docx", "A 64098-2023")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 2062-2025 FSC-klagomål mail.docx", "A 2062-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 64098-2023 FSC-klagomål mail.docx", "A 64098-2023")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 2062-2025 tillsynsbegäran.docx", "A 2062-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 64098-2023 tillsynsbegäran.docx", "A 64098-2023")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 2062-2025 tillsynsbegäran mail.docx", "A 2062-2025")</f>
-        <v/>
-      </c>
-      <c r="AE22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/fåglar/A 2062-2025 prioriterade fågelarter.docx", "A 2062-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 64098-2023 tillsynsbegäran mail.docx", "A 64098-2023")</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 25561-2025</t>
+          <t>A 2062-2025</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2856,10 +2852,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45803</v>
+        <v>45671</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2872,7 +2868,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>1.6</v>
+        <v>1.9</v>
       </c>
       <c r="J23" t="n">
         <v>1</v>
@@ -2881,13 +2877,13 @@
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M23" t="n">
         <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -2899,7 +2895,7 @@
         <v>1</v>
       </c>
       <c r="R23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
         <v>1</v>
@@ -2908,39 +2904,43 @@
         <v>1</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Bombmurkla</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 25561-2025 artfynd.xlsx", "A 25561-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 2062-2025 artfynd.xlsx", "A 2062-2025")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 25561-2025 karta.png", "A 25561-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 2062-2025 karta.png", "A 2062-2025")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 25561-2025 georefererad karta.tif", "A 25561-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 2062-2025 georefererad karta.tif", "A 2062-2025")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 25561-2025 FSC-klagomål.docx", "A 25561-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 2062-2025 FSC-klagomål.docx", "A 2062-2025")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 25561-2025 FSC-klagomål mail.docx", "A 25561-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 2062-2025 FSC-klagomål mail.docx", "A 2062-2025")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 25561-2025 tillsynsbegäran.docx", "A 25561-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 2062-2025 tillsynsbegäran.docx", "A 2062-2025")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 25561-2025 tillsynsbegäran mail.docx", "A 25561-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 2062-2025 tillsynsbegäran mail.docx", "A 2062-2025")</f>
+        <v/>
+      </c>
+      <c r="AE23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/fåglar/A 2062-2025 prioriterade fågelarter.docx", "A 2062-2025")</f>
         <v/>
       </c>
     </row>
@@ -2964,7 +2964,7 @@
         <v>44558</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3069,7 +3069,7 @@
         <v>44609</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3142,7 +3142,7 @@
         <v>44489</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3220,7 +3220,7 @@
         <v>44546</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3293,7 +3293,7 @@
         <v>44700</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3366,7 +3366,7 @@
         <v>44587</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3439,7 +3439,7 @@
         <v>44655</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3500,7 +3500,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 59848-2022</t>
+          <t>A 64105-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3514,10 +3514,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44901</v>
+        <v>45279</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3529,13 +3529,8 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I31" t="n">
-        <v>10.7</v>
+        <v>2.2</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3578,7 +3573,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 49622-2021</t>
+          <t>A 2602-2024</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3592,10 +3587,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44455</v>
+        <v>45313</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3608,7 +3603,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>3.8</v>
+        <v>0.7</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3651,7 +3646,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 64110-2023</t>
+          <t>A 59844-2022</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3665,10 +3660,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45279</v>
+        <v>44901</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3680,8 +3675,13 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I33" t="n">
-        <v>0.4</v>
+        <v>11.9</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3724,7 +3724,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 59700-2021</t>
+          <t>A 23093-2024</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3738,10 +3738,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44494</v>
+        <v>45450</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3759,7 +3759,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>4.8</v>
+        <v>0.9</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3802,7 +3802,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 38902-2024</t>
+          <t>A 3630-2023</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3816,10 +3816,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45547</v>
+        <v>44950</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3831,13 +3831,8 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I35" t="n">
-        <v>0.8</v>
+        <v>1.4</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3880,7 +3875,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 50294-2023</t>
+          <t>A 54222-2023</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3894,10 +3889,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45216</v>
+        <v>45225</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3909,8 +3904,13 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I36" t="n">
-        <v>3.7</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3953,7 +3953,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 18787-2026</t>
+          <t>A 7860-2024</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3967,10 +3967,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>46128</v>
+        <v>45348</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3988,7 +3988,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>7.8</v>
+        <v>1.9</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4031,7 +4031,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 18813-2026</t>
+          <t>A 27313-2023</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4045,10 +4045,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>46128</v>
+        <v>45096</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4060,13 +4060,8 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I38" t="n">
-        <v>56</v>
+        <v>1.8</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4109,7 +4104,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 18818-2026</t>
+          <t>A 64114-2023</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4123,10 +4118,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>46128</v>
+        <v>45279</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4138,13 +4133,8 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I39" t="n">
-        <v>17.8</v>
+        <v>0.4</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4187,7 +4177,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 18778-2026</t>
+          <t>A 50294-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4201,10 +4191,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>46128</v>
+        <v>45216</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4216,13 +4206,8 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I40" t="n">
-        <v>4.5</v>
+        <v>3.7</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4265,7 +4250,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 5264-2023</t>
+          <t>A 58011-2021</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4279,10 +4264,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44959</v>
+        <v>44487</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4294,8 +4279,13 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I41" t="n">
-        <v>5.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4338,7 +4328,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 21206-2026</t>
+          <t>A 9655-2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4352,10 +4342,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>46146</v>
+        <v>46070</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4373,7 +4363,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>0.9</v>
+        <v>17.2</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4416,7 +4406,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 7275-2022</t>
+          <t>A 64110-2023</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4430,10 +4420,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44606</v>
+        <v>45279</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4445,13 +4435,8 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I43" t="n">
-        <v>9.6</v>
+        <v>0.4</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4494,7 +4479,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 2602-2024</t>
+          <t>A 23098-2024</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4508,10 +4493,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45313</v>
+        <v>45450</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4523,8 +4508,13 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I44" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4567,7 +4557,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 23098-2024</t>
+          <t>A 18778-2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4581,10 +4571,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45450</v>
+        <v>46128</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4602,7 +4592,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>1</v>
+        <v>4.5</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4645,7 +4635,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 59402-2022</t>
+          <t>A 18813-2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4659,10 +4649,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44906</v>
+        <v>46128</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4674,8 +4664,13 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I46" t="n">
-        <v>1.8</v>
+        <v>56</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4718,7 +4713,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 59844-2022</t>
+          <t>A 18818-2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4732,10 +4727,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>44901</v>
+        <v>46128</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4753,7 +4748,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>11.9</v>
+        <v>17.8</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4796,7 +4791,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 54222-2023</t>
+          <t>A 18787-2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4810,10 +4805,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45225</v>
+        <v>46128</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4831,7 +4826,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>8.300000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4874,7 +4869,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 24579-2026</t>
+          <t>A 59377-2024</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4888,10 +4883,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>46170</v>
+        <v>45638</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4904,7 +4899,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>2.1</v>
+        <v>0.6</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4947,7 +4942,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 58598-2025</t>
+          <t>A 59402-2022</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4961,10 +4956,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45986</v>
+        <v>44906</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4976,13 +4971,8 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I50" t="n">
-        <v>4.5</v>
+        <v>1.8</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5025,7 +5015,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 31160-2022</t>
+          <t>A 5264-2023</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5039,10 +5029,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>44770</v>
+        <v>44959</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5055,7 +5045,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>3.7</v>
+        <v>5.8</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5098,7 +5088,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 26196-2026</t>
+          <t>A 21206-2026</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5108,14 +5098,14 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>46182</v>
+        <v>46146</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5127,8 +5117,13 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I52" t="n">
-        <v>53.1</v>
+        <v>0.9</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5171,7 +5166,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 4338-2023</t>
+          <t>A 51587-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5185,10 +5180,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>44953</v>
+        <v>45215</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5200,8 +5195,13 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I53" t="n">
-        <v>1.1</v>
+        <v>2.6</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5244,7 +5244,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 58011-2021</t>
+          <t>A 72524-2021</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5258,10 +5258,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>44487</v>
+        <v>44546</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5273,13 +5273,8 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I54" t="n">
-        <v>9.199999999999999</v>
+        <v>3.6</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5322,7 +5317,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 26625-2026</t>
+          <t>A 24579-2026</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5336,10 +5331,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>46184</v>
+        <v>46170</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5352,7 +5347,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>5.3</v>
+        <v>2.1</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5395,7 +5390,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 72524-2021</t>
+          <t>A 4338-2023</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5409,10 +5404,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>44546</v>
+        <v>44953</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5425,7 +5420,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>3.6</v>
+        <v>1.1</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5468,7 +5463,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 9655-2026</t>
+          <t>A 59848-2022</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5482,10 +5477,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>46070</v>
+        <v>44901</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5503,7 +5498,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>17.2</v>
+        <v>10.7</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5546,7 +5541,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 26629-2026</t>
+          <t>A 31160-2022</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5560,10 +5555,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>46184</v>
+        <v>44770</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5576,7 +5571,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>2</v>
+        <v>3.7</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5619,7 +5614,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 26633-2026</t>
+          <t>A 58598-2025</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5633,10 +5628,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>46184</v>
+        <v>45986</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5648,8 +5643,13 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I59" t="n">
-        <v>0.7</v>
+        <v>4.5</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5692,7 +5692,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 64107-2023</t>
+          <t>A 26196-2026</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5702,14 +5702,14 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45279</v>
+        <v>46182</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5722,7 +5722,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>0.3</v>
+        <v>53.1</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5765,7 +5765,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 23093-2024</t>
+          <t>A 59700-2021</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5779,10 +5779,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45450</v>
+        <v>44494</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5800,7 +5800,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>0.9</v>
+        <v>4.8</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5843,7 +5843,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 3630-2023</t>
+          <t>A 26633-2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5857,10 +5857,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>44950</v>
+        <v>46184</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5873,7 +5873,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>1.4</v>
+        <v>0.7</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5916,7 +5916,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 7860-2024</t>
+          <t>A 26625-2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5930,10 +5930,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45348</v>
+        <v>46184</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5945,13 +5945,8 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I63" t="n">
-        <v>1.9</v>
+        <v>5.3</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5994,7 +5989,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 3754-2026</t>
+          <t>A 26629-2026</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6008,10 +6003,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>46043</v>
+        <v>46184</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6023,13 +6018,8 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I64" t="n">
-        <v>5.1</v>
+        <v>2</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6072,7 +6062,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 27313-2023</t>
+          <t>A 3754-2026</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6086,10 +6076,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45096</v>
+        <v>46043</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6101,8 +6091,13 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I65" t="n">
-        <v>1.8</v>
+        <v>5.1</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6145,7 +6140,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 28797-2026</t>
+          <t>A 28735-2026</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6162,7 +6157,7 @@
         <v>46198</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6175,7 +6170,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>2.2</v>
+        <v>3.5</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6235,7 +6230,7 @@
         <v>46198</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6291,7 +6286,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 28735-2026</t>
+          <t>A 28797-2026</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6308,7 +6303,7 @@
         <v>46198</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6321,7 +6316,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>3.5</v>
+        <v>2.2</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6364,7 +6359,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 59377-2024</t>
+          <t>A 33058-2026</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6374,14 +6369,14 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45638</v>
+        <v>46245</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6394,7 +6389,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>0.6</v>
+        <v>1.3</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6437,7 +6432,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 33058-2026</t>
+          <t>A 7275-2022</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6447,14 +6442,14 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>46245</v>
+        <v>44606</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6466,8 +6461,13 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I70" t="n">
-        <v>1.3</v>
+        <v>9.6</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6510,7 +6510,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 64105-2023</t>
+          <t>A 31714-2026</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6524,10 +6524,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45279</v>
+        <v>46226</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6540,7 +6540,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>2.2</v>
+        <v>5</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6583,7 +6583,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 51587-2023</t>
+          <t>A 64107-2023</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6597,10 +6597,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45215</v>
+        <v>45279</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6612,13 +6612,8 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I72" t="n">
-        <v>2.6</v>
+        <v>0.3</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6661,7 +6656,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 64114-2023</t>
+          <t>A 7112-2025</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6675,10 +6670,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45279</v>
+        <v>45701</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6691,7 +6686,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>0.4</v>
+        <v>2.4</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6734,7 +6729,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 31714-2026</t>
+          <t>A 38902-2024</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6748,10 +6743,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>46226</v>
+        <v>45547</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6763,8 +6758,13 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I74" t="n">
-        <v>5</v>
+        <v>0.8</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6807,7 +6807,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 7112-2025</t>
+          <t>A 23615-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6821,10 +6821,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45701</v>
+        <v>45792</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6837,7 +6837,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>2.4</v>
+        <v>1.3</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6880,7 +6880,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 23615-2025</t>
+          <t>A 23627-2025</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6897,7 +6897,7 @@
         <v>45792</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6910,7 +6910,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6950,27 +6950,27 @@
       </c>
       <c r="V76" s="2" t="inlineStr"/>
     </row>
-    <row r="77" ht="15" customHeight="1">
+    <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 23627-2025</t>
+          <t>S 10447-2021</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>avverkningsanmälan</t>
+          <t>samrådsanmälan</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45792</v>
+        <v>44558</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>1.7</v>
+        <v>4.4</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7022,79 +7022,6 @@
         <v>0</v>
       </c>
       <c r="V77" s="2" t="inlineStr"/>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>S 10447-2021</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>Annan skogsbruksåtgärd</t>
-        </is>
-      </c>
-      <c r="D78" s="1" t="n">
-        <v>44558</v>
-      </c>
-      <c r="E78" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>UPPLANDS-BRO</t>
-        </is>
-      </c>
-      <c r="I78" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="J78" t="n">
-        <v>0</v>
-      </c>
-      <c r="K78" t="n">
-        <v>0</v>
-      </c>
-      <c r="L78" t="n">
-        <v>0</v>
-      </c>
-      <c r="M78" t="n">
-        <v>0</v>
-      </c>
-      <c r="N78" t="n">
-        <v>0</v>
-      </c>
-      <c r="O78" t="n">
-        <v>0</v>
-      </c>
-      <c r="P78" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q78" t="n">
-        <v>0</v>
-      </c>
-      <c r="R78" t="n">
-        <v>0</v>
-      </c>
-      <c r="S78" t="n">
-        <v>0</v>
-      </c>
-      <c r="T78" t="n">
-        <v>0</v>
-      </c>
-      <c r="U78" t="n">
-        <v>0</v>
-      </c>
-      <c r="V78" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt UPPLANDS-BRO.xlsx
+++ b/Översikt UPPLANDS-BRO.xlsx
@@ -601,7 +601,7 @@
         <v>44481</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -714,7 +714,7 @@
         <v>44552</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -822,7 +822,7 @@
         <v>44552</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -930,7 +930,7 @@
         <v>45232</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1025,7 +1025,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 18772-2026</t>
+          <t>A 18790-2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1042,7 +1042,7 @@
         <v>46128</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1060,16 +1060,16 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>19.5</v>
+        <v>5.5</v>
       </c>
       <c r="J6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
@@ -1084,7 +1084,7 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -1100,147 +1100,147 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
+          <t>Fläcknycklar
+Nattviol</t>
+        </is>
+      </c>
+      <c r="W6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 18790-2026 artfynd.xlsx", "A 18790-2026")</f>
+        <v/>
+      </c>
+      <c r="X6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 18790-2026 karta.png", "A 18790-2026")</f>
+        <v/>
+      </c>
+      <c r="Y6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 18790-2026 georefererad karta.tif", "A 18790-2026")</f>
+        <v/>
+      </c>
+      <c r="AA6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 18790-2026 FSC-klagomål.docx", "A 18790-2026")</f>
+        <v/>
+      </c>
+      <c r="AB6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 18790-2026 FSC-klagomål mail.docx", "A 18790-2026")</f>
+        <v/>
+      </c>
+      <c r="AC6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 18790-2026 tillsynsbegäran.docx", "A 18790-2026")</f>
+        <v/>
+      </c>
+      <c r="AD6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 18790-2026 tillsynsbegäran mail.docx", "A 18790-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>A 18772-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>46128</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>UPPLANDS-BRO</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>2</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
           <t>Svedjenäva
 Fläcknycklar</t>
         </is>
       </c>
-      <c r="W6">
+      <c r="W7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 18772-2026 artfynd.xlsx", "A 18772-2026")</f>
         <v/>
       </c>
-      <c r="X6">
+      <c r="X7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 18772-2026 karta.png", "A 18772-2026")</f>
         <v/>
       </c>
-      <c r="Y6">
+      <c r="Y7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 18772-2026 georefererad karta.tif", "A 18772-2026")</f>
         <v/>
       </c>
-      <c r="AA6">
+      <c r="AA7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 18772-2026 FSC-klagomål.docx", "A 18772-2026")</f>
         <v/>
       </c>
-      <c r="AB6">
+      <c r="AB7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 18772-2026 FSC-klagomål mail.docx", "A 18772-2026")</f>
         <v/>
       </c>
-      <c r="AC6">
+      <c r="AC7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 18772-2026 tillsynsbegäran.docx", "A 18772-2026")</f>
         <v/>
       </c>
-      <c r="AD6">
+      <c r="AD7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 18772-2026 tillsynsbegäran mail.docx", "A 18772-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>A 18790-2026</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>46128</v>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>UPPLANDS-BRO</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="J7" t="n">
-        <v>2</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
-        <v>2</v>
-      </c>
-      <c r="T7" t="n">
-        <v>2</v>
-      </c>
-      <c r="U7" t="n">
-        <v>0</v>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>Fläcknycklar
-Nattviol</t>
-        </is>
-      </c>
-      <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 18790-2026 artfynd.xlsx", "A 18790-2026")</f>
-        <v/>
-      </c>
-      <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 18790-2026 karta.png", "A 18790-2026")</f>
-        <v/>
-      </c>
-      <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 18790-2026 georefererad karta.tif", "A 18790-2026")</f>
-        <v/>
-      </c>
-      <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 18790-2026 FSC-klagomål.docx", "A 18790-2026")</f>
-        <v/>
-      </c>
-      <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 18790-2026 FSC-klagomål mail.docx", "A 18790-2026")</f>
-        <v/>
-      </c>
-      <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 18790-2026 tillsynsbegäran.docx", "A 18790-2026")</f>
-        <v/>
-      </c>
-      <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 18790-2026 tillsynsbegäran mail.docx", "A 18790-2026")</f>
         <v/>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
         <v>45722</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
         <v>44603</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1481,7 +1481,7 @@
         <v>44552</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1569,7 +1569,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 25561-2025</t>
+          <t>A 7955-2023</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45803</v>
+        <v>44973</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1599,7 +1599,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>1.6</v>
+        <v>2.9</v>
       </c>
       <c r="J11" t="n">
         <v>1</v>
@@ -1635,7 +1635,7 @@
         <v>1</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
@@ -1643,38 +1643,38 @@
         </is>
       </c>
       <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 25561-2025 artfynd.xlsx", "A 25561-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 7955-2023 artfynd.xlsx", "A 7955-2023")</f>
         <v/>
       </c>
       <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 25561-2025 karta.png", "A 25561-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 7955-2023 karta.png", "A 7955-2023")</f>
         <v/>
       </c>
       <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 25561-2025 georefererad karta.tif", "A 25561-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 7955-2023 georefererad karta.tif", "A 7955-2023")</f>
         <v/>
       </c>
       <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 25561-2025 FSC-klagomål.docx", "A 25561-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 7955-2023 FSC-klagomål.docx", "A 7955-2023")</f>
         <v/>
       </c>
       <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 25561-2025 FSC-klagomål mail.docx", "A 25561-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 7955-2023 FSC-klagomål mail.docx", "A 7955-2023")</f>
         <v/>
       </c>
       <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 25561-2025 tillsynsbegäran.docx", "A 25561-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 7955-2023 tillsynsbegäran.docx", "A 7955-2023")</f>
         <v/>
       </c>
       <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 25561-2025 tillsynsbegäran mail.docx", "A 25561-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 7955-2023 tillsynsbegäran mail.docx", "A 7955-2023")</f>
         <v/>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 2409-2026</t>
+          <t>A 46438-2023</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1688,10 +1688,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46034</v>
+        <v>45197</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1704,7 +1704,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>14.2</v>
+        <v>0.5</v>
       </c>
       <c r="J12" t="n">
         <v>1</v>
@@ -1719,7 +1719,7 @@
         <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1728,10 +1728,10 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1744,39 +1744,35 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>Havsörn</t>
+          <t>Bombmurkla</t>
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 2409-2026 artfynd.xlsx", "A 2409-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 46438-2023 artfynd.xlsx", "A 46438-2023")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 2409-2026 karta.png", "A 2409-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 46438-2023 karta.png", "A 46438-2023")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 2409-2026 georefererad karta.tif", "A 2409-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 46438-2023 georefererad karta.tif", "A 46438-2023")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 2409-2026 FSC-klagomål.docx", "A 2409-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 46438-2023 FSC-klagomål.docx", "A 46438-2023")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 2409-2026 FSC-klagomål mail.docx", "A 2409-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 46438-2023 FSC-klagomål mail.docx", "A 46438-2023")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 2409-2026 tillsynsbegäran.docx", "A 2409-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 46438-2023 tillsynsbegäran.docx", "A 46438-2023")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 2409-2026 tillsynsbegäran mail.docx", "A 2409-2026")</f>
-        <v/>
-      </c>
-      <c r="AE12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/fåglar/A 2409-2026 prioriterade fågelarter.docx", "A 2409-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 46438-2023 tillsynsbegäran mail.docx", "A 46438-2023")</f>
         <v/>
       </c>
     </row>
@@ -1800,7 +1796,7 @@
         <v>45730</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1888,7 +1884,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 73773-2021</t>
+          <t>A 23099-2024</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1902,10 +1898,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>44552</v>
+        <v>45450</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1917,11 +1913,16 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I14" t="n">
-        <v>1.9</v>
+        <v>0.7</v>
       </c>
       <c r="J14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
@@ -1930,7 +1931,7 @@
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -1942,10 +1943,10 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
@@ -1958,42 +1959,42 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Kopparödla</t>
+          <t>Bredbrämad bastardsvärmare</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 73773-2021 artfynd.xlsx", "A 73773-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 23099-2024 artfynd.xlsx", "A 23099-2024")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 73773-2021 karta.png", "A 73773-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 23099-2024 karta.png", "A 23099-2024")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 73773-2021 georefererad karta.tif", "A 73773-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 23099-2024 georefererad karta.tif", "A 23099-2024")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 73773-2021 FSC-klagomål.docx", "A 73773-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 23099-2024 FSC-klagomål.docx", "A 23099-2024")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 73773-2021 FSC-klagomål mail.docx", "A 73773-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 23099-2024 FSC-klagomål mail.docx", "A 23099-2024")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 73773-2021 tillsynsbegäran.docx", "A 73773-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 23099-2024 tillsynsbegäran.docx", "A 23099-2024")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 73773-2021 tillsynsbegäran mail.docx", "A 73773-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 23099-2024 tillsynsbegäran mail.docx", "A 23099-2024")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 53357-2025</t>
+          <t>A 64098-2023</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2007,10 +2008,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45959</v>
+        <v>45279</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2023,22 +2024,22 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>2.4</v>
+        <v>0.3</v>
       </c>
       <c r="J15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M15" t="n">
         <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2050,55 +2051,55 @@
         <v>1</v>
       </c>
       <c r="R15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
         <v>1</v>
       </c>
       <c r="T15" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="U15" t="n">
         <v>0</v>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Bombmurkla</t>
+          <t>Skogsalmsdvärgmal</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 53357-2025 artfynd.xlsx", "A 53357-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 64098-2023 artfynd.xlsx", "A 64098-2023")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 53357-2025 karta.png", "A 53357-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 64098-2023 karta.png", "A 64098-2023")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 53357-2025 georefererad karta.tif", "A 53357-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 64098-2023 georefererad karta.tif", "A 64098-2023")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 53357-2025 FSC-klagomål.docx", "A 53357-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 64098-2023 FSC-klagomål.docx", "A 64098-2023")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 53357-2025 FSC-klagomål mail.docx", "A 53357-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 64098-2023 FSC-klagomål mail.docx", "A 64098-2023")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 53357-2025 tillsynsbegäran.docx", "A 53357-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 64098-2023 tillsynsbegäran.docx", "A 64098-2023")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 53357-2025 tillsynsbegäran mail.docx", "A 53357-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 64098-2023 tillsynsbegäran mail.docx", "A 64098-2023")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 23099-2024</t>
+          <t>A 26623-2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2112,10 +2113,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45450</v>
+        <v>46184</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2127,13 +2128,8 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I16" t="n">
-        <v>0.7</v>
+        <v>4.6</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -2142,10 +2138,10 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -2160,7 +2156,7 @@
         <v>1</v>
       </c>
       <c r="R16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
@@ -2169,46 +2165,46 @@
         <v>1</v>
       </c>
       <c r="U16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Bredbrämad bastardsvärmare</t>
+          <t>Svartöra</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 23099-2024 artfynd.xlsx", "A 23099-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 26623-2026 artfynd.xlsx", "A 26623-2026")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 23099-2024 karta.png", "A 23099-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 26623-2026 karta.png", "A 26623-2026")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 23099-2024 georefererad karta.tif", "A 23099-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 26623-2026 georefererad karta.tif", "A 26623-2026")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 23099-2024 FSC-klagomål.docx", "A 23099-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 26623-2026 FSC-klagomål.docx", "A 26623-2026")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 23099-2024 FSC-klagomål mail.docx", "A 23099-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 26623-2026 FSC-klagomål mail.docx", "A 26623-2026")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 23099-2024 tillsynsbegäran.docx", "A 23099-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 26623-2026 tillsynsbegäran.docx", "A 26623-2026")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 23099-2024 tillsynsbegäran mail.docx", "A 23099-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 26623-2026 tillsynsbegäran mail.docx", "A 26623-2026")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 46438-2023</t>
+          <t>A 26637-2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2222,10 +2218,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45197</v>
+        <v>46184</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2238,10 +2234,10 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>0.5</v>
+        <v>5.4</v>
       </c>
       <c r="J17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
@@ -2250,10 +2246,10 @@
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2278,42 +2274,42 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Bombmurkla</t>
+          <t>Igelkott</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 46438-2023 artfynd.xlsx", "A 46438-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 26637-2026 artfynd.xlsx", "A 26637-2026")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 46438-2023 karta.png", "A 46438-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 26637-2026 karta.png", "A 26637-2026")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 46438-2023 georefererad karta.tif", "A 46438-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 26637-2026 georefererad karta.tif", "A 26637-2026")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 46438-2023 FSC-klagomål.docx", "A 46438-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 26637-2026 FSC-klagomål.docx", "A 26637-2026")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 46438-2023 FSC-klagomål mail.docx", "A 46438-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 26637-2026 FSC-klagomål mail.docx", "A 26637-2026")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 46438-2023 tillsynsbegäran.docx", "A 46438-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 26637-2026 tillsynsbegäran.docx", "A 26637-2026")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 46438-2023 tillsynsbegäran mail.docx", "A 46438-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 26637-2026 tillsynsbegäran mail.docx", "A 26637-2026")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 11447-2025</t>
+          <t>A 53357-2025</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2323,14 +2319,14 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45726</v>
+        <v>45959</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2343,13 +2339,13 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>1.5</v>
+        <v>2.4</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
@@ -2358,7 +2354,7 @@
         <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2367,58 +2363,58 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
       </c>
       <c r="T18" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="U18" t="n">
         <v>0</v>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Myskbock</t>
+          <t>Bombmurkla</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 11447-2025 artfynd.xlsx", "A 11447-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 53357-2025 artfynd.xlsx", "A 53357-2025")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 11447-2025 karta.png", "A 11447-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 53357-2025 karta.png", "A 53357-2025")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 11447-2025 georefererad karta.tif", "A 11447-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 53357-2025 georefererad karta.tif", "A 53357-2025")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 11447-2025 FSC-klagomål.docx", "A 11447-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 53357-2025 FSC-klagomål.docx", "A 53357-2025")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 11447-2025 FSC-klagomål mail.docx", "A 11447-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 53357-2025 FSC-klagomål mail.docx", "A 53357-2025")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 11447-2025 tillsynsbegäran.docx", "A 11447-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 53357-2025 tillsynsbegäran.docx", "A 53357-2025")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 11447-2025 tillsynsbegäran mail.docx", "A 11447-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 53357-2025 tillsynsbegäran mail.docx", "A 53357-2025")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 7955-2023</t>
+          <t>A 73773-2021</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2432,10 +2428,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>44973</v>
+        <v>44552</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2448,7 +2444,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>2.9</v>
+        <v>1.9</v>
       </c>
       <c r="J19" t="n">
         <v>1</v>
@@ -2463,7 +2459,7 @@
         <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2472,10 +2468,10 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
@@ -2488,42 +2484,42 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Bombmurkla</t>
+          <t>Kopparödla</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 7955-2023 artfynd.xlsx", "A 7955-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 73773-2021 artfynd.xlsx", "A 73773-2021")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 7955-2023 karta.png", "A 7955-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 73773-2021 karta.png", "A 73773-2021")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 7955-2023 georefererad karta.tif", "A 7955-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 73773-2021 georefererad karta.tif", "A 73773-2021")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 7955-2023 FSC-klagomål.docx", "A 7955-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 73773-2021 FSC-klagomål.docx", "A 73773-2021")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 7955-2023 FSC-klagomål mail.docx", "A 7955-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 73773-2021 FSC-klagomål mail.docx", "A 73773-2021")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 7955-2023 tillsynsbegäran.docx", "A 7955-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 73773-2021 tillsynsbegäran.docx", "A 73773-2021")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 7955-2023 tillsynsbegäran mail.docx", "A 7955-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 73773-2021 tillsynsbegäran mail.docx", "A 73773-2021")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 26637-2026</t>
+          <t>A 11447-2025</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2533,14 +2529,14 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46184</v>
+        <v>45726</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2553,19 +2549,19 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>5.4</v>
+        <v>1.5</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
         <v>0</v>
@@ -2577,10 +2573,10 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>
@@ -2593,42 +2589,42 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>Igelkott</t>
+          <t>Myskbock</t>
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 26637-2026 artfynd.xlsx", "A 26637-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 11447-2025 artfynd.xlsx", "A 11447-2025")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 26637-2026 karta.png", "A 26637-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 11447-2025 karta.png", "A 11447-2025")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 26637-2026 georefererad karta.tif", "A 26637-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 11447-2025 georefererad karta.tif", "A 11447-2025")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 26637-2026 FSC-klagomål.docx", "A 26637-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 11447-2025 FSC-klagomål.docx", "A 11447-2025")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 26637-2026 FSC-klagomål mail.docx", "A 26637-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 11447-2025 FSC-klagomål mail.docx", "A 11447-2025")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 26637-2026 tillsynsbegäran.docx", "A 26637-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 11447-2025 tillsynsbegäran.docx", "A 11447-2025")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 26637-2026 tillsynsbegäran mail.docx", "A 26637-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 11447-2025 tillsynsbegäran mail.docx", "A 11447-2025")</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 26623-2026</t>
+          <t>A 2409-2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2642,10 +2638,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46184</v>
+        <v>46034</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2658,16 +2654,16 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>4.6</v>
+        <v>14.2</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
         <v>0</v>
@@ -2682,7 +2678,7 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
         <v>0</v>
@@ -2698,42 +2694,46 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Svartöra</t>
+          <t>Havsörn</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 26623-2026 artfynd.xlsx", "A 26623-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 2409-2026 artfynd.xlsx", "A 2409-2026")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 26623-2026 karta.png", "A 26623-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 2409-2026 karta.png", "A 2409-2026")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 26623-2026 georefererad karta.tif", "A 26623-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 2409-2026 georefererad karta.tif", "A 2409-2026")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 26623-2026 FSC-klagomål.docx", "A 26623-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 2409-2026 FSC-klagomål.docx", "A 2409-2026")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 26623-2026 FSC-klagomål mail.docx", "A 26623-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 2409-2026 FSC-klagomål mail.docx", "A 2409-2026")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 26623-2026 tillsynsbegäran.docx", "A 26623-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 2409-2026 tillsynsbegäran.docx", "A 2409-2026")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 26623-2026 tillsynsbegäran mail.docx", "A 26623-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 2409-2026 tillsynsbegäran mail.docx", "A 2409-2026")</f>
+        <v/>
+      </c>
+      <c r="AE21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/fåglar/A 2409-2026 prioriterade fågelarter.docx", "A 2409-2026")</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 64098-2023</t>
+          <t>A 2062-2025</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2747,10 +2747,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45279</v>
+        <v>45671</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2763,10 +2763,10 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>0.3</v>
+        <v>1.9</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
@@ -2799,46 +2799,50 @@
         <v>1</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>Skogsalmsdvärgmal</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 64098-2023 artfynd.xlsx", "A 64098-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 2062-2025 artfynd.xlsx", "A 2062-2025")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 64098-2023 karta.png", "A 64098-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 2062-2025 karta.png", "A 2062-2025")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 64098-2023 georefererad karta.tif", "A 64098-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 2062-2025 georefererad karta.tif", "A 2062-2025")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 64098-2023 FSC-klagomål.docx", "A 64098-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 2062-2025 FSC-klagomål.docx", "A 2062-2025")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 64098-2023 FSC-klagomål mail.docx", "A 64098-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 2062-2025 FSC-klagomål mail.docx", "A 2062-2025")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 64098-2023 tillsynsbegäran.docx", "A 64098-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 2062-2025 tillsynsbegäran.docx", "A 2062-2025")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 64098-2023 tillsynsbegäran mail.docx", "A 64098-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 2062-2025 tillsynsbegäran mail.docx", "A 2062-2025")</f>
+        <v/>
+      </c>
+      <c r="AE22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/fåglar/A 2062-2025 prioriterade fågelarter.docx", "A 2062-2025")</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 2062-2025</t>
+          <t>A 25561-2025</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2852,10 +2856,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45671</v>
+        <v>45803</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2868,7 +2872,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>1.9</v>
+        <v>1.6</v>
       </c>
       <c r="J23" t="n">
         <v>1</v>
@@ -2877,13 +2881,13 @@
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
         <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -2895,7 +2899,7 @@
         <v>1</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S23" t="n">
         <v>1</v>
@@ -2904,43 +2908,39 @@
         <v>1</v>
       </c>
       <c r="U23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Bombmurkla</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 2062-2025 artfynd.xlsx", "A 2062-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 25561-2025 artfynd.xlsx", "A 25561-2025")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 2062-2025 karta.png", "A 2062-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 25561-2025 karta.png", "A 25561-2025")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 2062-2025 georefererad karta.tif", "A 2062-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 25561-2025 georefererad karta.tif", "A 25561-2025")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 2062-2025 FSC-klagomål.docx", "A 2062-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 25561-2025 FSC-klagomål.docx", "A 25561-2025")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 2062-2025 FSC-klagomål mail.docx", "A 2062-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 25561-2025 FSC-klagomål mail.docx", "A 25561-2025")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 2062-2025 tillsynsbegäran.docx", "A 2062-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 25561-2025 tillsynsbegäran.docx", "A 25561-2025")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 2062-2025 tillsynsbegäran mail.docx", "A 2062-2025")</f>
-        <v/>
-      </c>
-      <c r="AE23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/fåglar/A 2062-2025 prioriterade fågelarter.docx", "A 2062-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 25561-2025 tillsynsbegäran mail.docx", "A 25561-2025")</f>
         <v/>
       </c>
     </row>
@@ -2964,7 +2964,7 @@
         <v>44558</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3069,7 +3069,7 @@
         <v>44609</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3142,7 +3142,7 @@
         <v>44489</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3220,7 +3220,7 @@
         <v>44546</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3293,7 +3293,7 @@
         <v>44700</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3366,7 +3366,7 @@
         <v>44587</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3439,7 +3439,7 @@
         <v>44655</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3500,7 +3500,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 64105-2023</t>
+          <t>A 59700-2021</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3514,10 +3514,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45279</v>
+        <v>44494</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3529,8 +3529,13 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I31" t="n">
-        <v>2.2</v>
+        <v>4.8</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3573,7 +3578,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 2602-2024</t>
+          <t>A 38902-2024</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3587,10 +3592,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45313</v>
+        <v>45547</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3602,8 +3607,13 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I32" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3646,7 +3656,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 59844-2022</t>
+          <t>A 50294-2023</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3660,10 +3670,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44901</v>
+        <v>45216</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3675,13 +3685,8 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I33" t="n">
-        <v>11.9</v>
+        <v>3.7</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3724,7 +3729,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 23093-2024</t>
+          <t>A 9655-2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3738,10 +3743,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45450</v>
+        <v>46070</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3759,7 +3764,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>0.9</v>
+        <v>17.2</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3802,7 +3807,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 3630-2023</t>
+          <t>A 5264-2023</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3816,10 +3821,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44950</v>
+        <v>44959</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3832,7 +3837,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>1.4</v>
+        <v>5.8</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3875,7 +3880,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 54222-2023</t>
+          <t>A 18787-2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3889,10 +3894,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45225</v>
+        <v>46128</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3910,7 +3915,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>8.300000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3953,7 +3958,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 7860-2024</t>
+          <t>A 18813-2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3967,10 +3972,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45348</v>
+        <v>46128</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3988,7 +3993,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>1.9</v>
+        <v>56</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4031,7 +4036,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 27313-2023</t>
+          <t>A 18818-2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4045,10 +4050,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45096</v>
+        <v>46128</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4060,8 +4065,13 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I38" t="n">
-        <v>1.8</v>
+        <v>17.8</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4104,7 +4114,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 64114-2023</t>
+          <t>A 18778-2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4118,10 +4128,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45279</v>
+        <v>46128</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4133,8 +4143,13 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I39" t="n">
-        <v>0.4</v>
+        <v>4.5</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4177,7 +4192,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 50294-2023</t>
+          <t>A 23098-2024</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4191,10 +4206,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45216</v>
+        <v>45450</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4206,8 +4221,13 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I40" t="n">
-        <v>3.7</v>
+        <v>1</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4250,7 +4270,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 58011-2021</t>
+          <t>A 59844-2022</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4264,10 +4284,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44487</v>
+        <v>44901</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4285,7 +4305,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>9.199999999999999</v>
+        <v>11.9</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4328,7 +4348,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 9655-2026</t>
+          <t>A 54222-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4342,10 +4362,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>46070</v>
+        <v>45225</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4363,7 +4383,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>17.2</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4406,7 +4426,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 64110-2023</t>
+          <t>A 21206-2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4420,10 +4440,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45279</v>
+        <v>46146</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4435,8 +4455,13 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I43" t="n">
-        <v>0.4</v>
+        <v>0.9</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4479,7 +4504,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 23098-2024</t>
+          <t>A 4338-2023</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4493,10 +4518,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45450</v>
+        <v>44953</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4508,13 +4533,8 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I44" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4557,7 +4577,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 18778-2026</t>
+          <t>A 58011-2021</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4571,10 +4591,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>46128</v>
+        <v>44487</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4592,7 +4612,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>4.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4635,7 +4655,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 18813-2026</t>
+          <t>A 72524-2021</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4649,10 +4669,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>46128</v>
+        <v>44546</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4664,13 +4684,8 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I46" t="n">
-        <v>56</v>
+        <v>3.6</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4713,7 +4728,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 18818-2026</t>
+          <t>A 64107-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4727,10 +4742,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>46128</v>
+        <v>45279</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4742,13 +4757,8 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I47" t="n">
-        <v>17.8</v>
+        <v>0.3</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4791,7 +4801,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 18787-2026</t>
+          <t>A 23093-2024</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4805,10 +4815,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>46128</v>
+        <v>45450</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4826,7 +4836,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>7.8</v>
+        <v>0.9</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4869,7 +4879,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 59377-2024</t>
+          <t>A 24579-2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4883,10 +4893,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45638</v>
+        <v>46170</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4899,7 +4909,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>0.6</v>
+        <v>2.1</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4942,7 +4952,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 59402-2022</t>
+          <t>A 27313-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4956,10 +4966,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>44906</v>
+        <v>45096</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5015,7 +5025,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 5264-2023</t>
+          <t>A 58598-2025</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5029,10 +5039,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>44959</v>
+        <v>45986</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5044,8 +5054,13 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I51" t="n">
-        <v>5.8</v>
+        <v>4.5</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5088,7 +5103,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 21206-2026</t>
+          <t>A 31160-2022</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5102,10 +5117,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>46146</v>
+        <v>44770</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5117,13 +5132,8 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I52" t="n">
-        <v>0.9</v>
+        <v>3.7</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5166,7 +5176,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 51587-2023</t>
+          <t>A 59377-2024</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5180,10 +5190,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45215</v>
+        <v>45638</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5195,13 +5205,8 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I53" t="n">
-        <v>2.6</v>
+        <v>0.6</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5244,7 +5249,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 72524-2021</t>
+          <t>A 26196-2026</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5254,14 +5259,14 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>44546</v>
+        <v>46182</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5274,7 +5279,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>3.6</v>
+        <v>53.1</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5317,7 +5322,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 24579-2026</t>
+          <t>A 26625-2026</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5331,10 +5336,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>46170</v>
+        <v>46184</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5347,7 +5352,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>2.1</v>
+        <v>5.3</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5390,7 +5395,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 4338-2023</t>
+          <t>A 26629-2026</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5404,10 +5409,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>44953</v>
+        <v>46184</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5420,7 +5425,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>1.1</v>
+        <v>2</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5463,7 +5468,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 59848-2022</t>
+          <t>A 26633-2026</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5477,10 +5482,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>44901</v>
+        <v>46184</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5492,13 +5497,8 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I57" t="n">
-        <v>10.7</v>
+        <v>0.7</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5541,7 +5541,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 31160-2022</t>
+          <t>A 3754-2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5555,10 +5555,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>44770</v>
+        <v>46043</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5570,8 +5570,13 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I58" t="n">
-        <v>3.7</v>
+        <v>5.1</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5614,7 +5619,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 58598-2025</t>
+          <t>A 28797-2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5628,10 +5633,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45986</v>
+        <v>46198</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5643,13 +5648,8 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I59" t="n">
-        <v>4.5</v>
+        <v>2.2</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5692,7 +5692,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 26196-2026</t>
+          <t>A 28740-2026</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5702,14 +5702,14 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>46182</v>
+        <v>46198</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5722,7 +5722,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>53.1</v>
+        <v>4.8</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5765,7 +5765,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 59700-2021</t>
+          <t>A 28735-2026</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5779,10 +5779,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>44494</v>
+        <v>46198</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5794,13 +5794,8 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I61" t="n">
-        <v>4.8</v>
+        <v>3.5</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5843,7 +5838,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 26633-2026</t>
+          <t>A 33058-2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5853,14 +5848,14 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>46184</v>
+        <v>46245</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5873,7 +5868,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>0.7</v>
+        <v>1.3</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5916,7 +5911,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 26625-2026</t>
+          <t>A 51587-2023</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5930,10 +5925,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>46184</v>
+        <v>45215</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5945,8 +5940,13 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I63" t="n">
-        <v>5.3</v>
+        <v>2.6</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5989,7 +5989,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 26629-2026</t>
+          <t>A 59848-2022</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6003,10 +6003,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>46184</v>
+        <v>44901</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6018,8 +6018,13 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I64" t="n">
-        <v>2</v>
+        <v>10.7</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6062,7 +6067,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 3754-2026</t>
+          <t>A 64110-2023</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6076,10 +6081,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>46043</v>
+        <v>45279</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6091,13 +6096,8 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I65" t="n">
-        <v>5.1</v>
+        <v>0.4</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6140,7 +6140,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 28735-2026</t>
+          <t>A 31714-2026</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6154,10 +6154,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>46198</v>
+        <v>46226</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6170,7 +6170,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>3.5</v>
+        <v>5</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6213,7 +6213,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 28740-2026</t>
+          <t>A 7275-2022</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6227,10 +6227,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>46198</v>
+        <v>44606</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6242,8 +6242,13 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I67" t="n">
-        <v>4.8</v>
+        <v>9.6</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6286,7 +6291,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 28797-2026</t>
+          <t>A 2602-2024</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6300,10 +6305,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>46198</v>
+        <v>45313</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6316,7 +6321,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>2.2</v>
+        <v>0.7</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6359,7 +6364,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 33058-2026</t>
+          <t>A 59402-2022</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6369,14 +6374,14 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>46245</v>
+        <v>44906</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6389,7 +6394,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1.3</v>
+        <v>1.8</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6432,7 +6437,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 7275-2022</t>
+          <t>A 3630-2023</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6446,10 +6451,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>44606</v>
+        <v>44950</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6461,13 +6466,8 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I70" t="n">
-        <v>9.6</v>
+        <v>1.4</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6510,7 +6510,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 31714-2026</t>
+          <t>A 7860-2024</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6524,10 +6524,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>46226</v>
+        <v>45348</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6539,8 +6539,13 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I71" t="n">
-        <v>5</v>
+        <v>1.9</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6583,7 +6588,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 64107-2023</t>
+          <t>A 64105-2023</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6600,7 +6605,7 @@
         <v>45279</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6613,7 +6618,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>0.3</v>
+        <v>2.2</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6656,7 +6661,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 7112-2025</t>
+          <t>A 64114-2023</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6670,10 +6675,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45701</v>
+        <v>45279</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6686,7 +6691,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>2.4</v>
+        <v>0.4</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6729,7 +6734,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 38902-2024</t>
+          <t>A 7112-2025</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6743,10 +6748,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45547</v>
+        <v>45701</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6758,13 +6763,8 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I74" t="n">
-        <v>0.8</v>
+        <v>2.4</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6824,7 +6824,7 @@
         <v>45792</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6897,7 +6897,7 @@
         <v>45792</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6970,7 +6970,7 @@
         <v>44558</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>

--- a/Översikt UPPLANDS-BRO.xlsx
+++ b/Översikt UPPLANDS-BRO.xlsx
@@ -601,7 +601,7 @@
         <v>44481</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -714,7 +714,7 @@
         <v>44552</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -822,7 +822,7 @@
         <v>44552</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -930,7 +930,7 @@
         <v>45232</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1025,7 +1025,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 18790-2026</t>
+          <t>A 10909-2025</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1039,10 +1039,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46128</v>
+        <v>45722</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1056,20 +1056,20 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Övriga statliga verk och myndigheter</t>
+          <t>Allmännings- och besparingsskogar</t>
         </is>
       </c>
       <c r="I6" t="n">
-        <v>5.5</v>
+        <v>11.2</v>
       </c>
       <c r="J6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
@@ -1084,7 +1084,7 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -1096,262 +1096,262 @@
         <v>2</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>Arommusseron
+Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="W6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 10909-2025 artfynd.xlsx", "A 10909-2025")</f>
+        <v/>
+      </c>
+      <c r="X6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 10909-2025 karta.png", "A 10909-2025")</f>
+        <v/>
+      </c>
+      <c r="Y6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 10909-2025 georefererad karta.tif", "A 10909-2025")</f>
+        <v/>
+      </c>
+      <c r="AA6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 10909-2025 FSC-klagomål.docx", "A 10909-2025")</f>
+        <v/>
+      </c>
+      <c r="AB6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 10909-2025 FSC-klagomål mail.docx", "A 10909-2025")</f>
+        <v/>
+      </c>
+      <c r="AC6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 10909-2025 tillsynsbegäran.docx", "A 10909-2025")</f>
+        <v/>
+      </c>
+      <c r="AD6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 10909-2025 tillsynsbegäran mail.docx", "A 10909-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>A 18772-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>46128</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>UPPLANDS-BRO</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>2</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>Svedjenäva
+Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="W7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 18772-2026 artfynd.xlsx", "A 18772-2026")</f>
+        <v/>
+      </c>
+      <c r="X7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 18772-2026 karta.png", "A 18772-2026")</f>
+        <v/>
+      </c>
+      <c r="Y7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 18772-2026 georefererad karta.tif", "A 18772-2026")</f>
+        <v/>
+      </c>
+      <c r="AA7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 18772-2026 FSC-klagomål.docx", "A 18772-2026")</f>
+        <v/>
+      </c>
+      <c r="AB7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 18772-2026 FSC-klagomål mail.docx", "A 18772-2026")</f>
+        <v/>
+      </c>
+      <c r="AC7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 18772-2026 tillsynsbegäran.docx", "A 18772-2026")</f>
+        <v/>
+      </c>
+      <c r="AD7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 18772-2026 tillsynsbegäran mail.docx", "A 18772-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="15" customHeight="1">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>A 18790-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D8" s="1" t="n">
+        <v>46128</v>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>UPPLANDS-BRO</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="J8" t="n">
+        <v>2</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>2</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>Fläcknycklar
 Nattviol</t>
         </is>
       </c>
-      <c r="W6">
+      <c r="W8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 18790-2026 artfynd.xlsx", "A 18790-2026")</f>
         <v/>
       </c>
-      <c r="X6">
+      <c r="X8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 18790-2026 karta.png", "A 18790-2026")</f>
         <v/>
       </c>
-      <c r="Y6">
+      <c r="Y8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 18790-2026 georefererad karta.tif", "A 18790-2026")</f>
         <v/>
       </c>
-      <c r="AA6">
+      <c r="AA8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 18790-2026 FSC-klagomål.docx", "A 18790-2026")</f>
         <v/>
       </c>
-      <c r="AB6">
+      <c r="AB8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 18790-2026 FSC-klagomål mail.docx", "A 18790-2026")</f>
         <v/>
       </c>
-      <c r="AC6">
+      <c r="AC8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 18790-2026 tillsynsbegäran.docx", "A 18790-2026")</f>
         <v/>
       </c>
-      <c r="AD6">
+      <c r="AD8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 18790-2026 tillsynsbegäran mail.docx", "A 18790-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>A 18772-2026</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>46128</v>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>UPPLANDS-BRO</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="J7" t="n">
-        <v>1</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>1</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>1</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
-        <v>2</v>
-      </c>
-      <c r="T7" t="n">
-        <v>2</v>
-      </c>
-      <c r="U7" t="n">
-        <v>0</v>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>Svedjenäva
-Fläcknycklar</t>
-        </is>
-      </c>
-      <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 18772-2026 artfynd.xlsx", "A 18772-2026")</f>
-        <v/>
-      </c>
-      <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 18772-2026 karta.png", "A 18772-2026")</f>
-        <v/>
-      </c>
-      <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 18772-2026 georefererad karta.tif", "A 18772-2026")</f>
-        <v/>
-      </c>
-      <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 18772-2026 FSC-klagomål.docx", "A 18772-2026")</f>
-        <v/>
-      </c>
-      <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 18772-2026 FSC-klagomål mail.docx", "A 18772-2026")</f>
-        <v/>
-      </c>
-      <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 18772-2026 tillsynsbegäran.docx", "A 18772-2026")</f>
-        <v/>
-      </c>
-      <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 18772-2026 tillsynsbegäran mail.docx", "A 18772-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8" ht="15" customHeight="1">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>A 10909-2025</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D8" s="1" t="n">
-        <v>45722</v>
-      </c>
-      <c r="E8" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>UPPLANDS-BRO</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
-      <c r="I8" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="J8" t="n">
-        <v>1</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>1</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>1</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" t="n">
-        <v>2</v>
-      </c>
-      <c r="T8" t="n">
-        <v>2</v>
-      </c>
-      <c r="U8" t="n">
-        <v>2</v>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>Arommusseron
-Fläcknycklar</t>
-        </is>
-      </c>
-      <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 10909-2025 artfynd.xlsx", "A 10909-2025")</f>
-        <v/>
-      </c>
-      <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 10909-2025 karta.png", "A 10909-2025")</f>
-        <v/>
-      </c>
-      <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 10909-2025 georefererad karta.tif", "A 10909-2025")</f>
-        <v/>
-      </c>
-      <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 10909-2025 FSC-klagomål.docx", "A 10909-2025")</f>
-        <v/>
-      </c>
-      <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 10909-2025 FSC-klagomål mail.docx", "A 10909-2025")</f>
-        <v/>
-      </c>
-      <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 10909-2025 tillsynsbegäran.docx", "A 10909-2025")</f>
-        <v/>
-      </c>
-      <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 10909-2025 tillsynsbegäran mail.docx", "A 10909-2025")</f>
         <v/>
       </c>
     </row>
@@ -1375,7 +1375,7 @@
         <v>44603</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1481,7 +1481,7 @@
         <v>44552</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1569,7 +1569,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 7955-2023</t>
+          <t>A 73773-2021</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>44973</v>
+        <v>44552</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1599,7 +1599,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>2.9</v>
+        <v>1.9</v>
       </c>
       <c r="J11" t="n">
         <v>1</v>
@@ -1614,7 +1614,7 @@
         <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1623,10 +1623,10 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1639,42 +1639,42 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>Bombmurkla</t>
+          <t>Kopparödla</t>
         </is>
       </c>
       <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 7955-2023 artfynd.xlsx", "A 7955-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 73773-2021 artfynd.xlsx", "A 73773-2021")</f>
         <v/>
       </c>
       <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 7955-2023 karta.png", "A 7955-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 73773-2021 karta.png", "A 73773-2021")</f>
         <v/>
       </c>
       <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 7955-2023 georefererad karta.tif", "A 7955-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 73773-2021 georefererad karta.tif", "A 73773-2021")</f>
         <v/>
       </c>
       <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 7955-2023 FSC-klagomål.docx", "A 7955-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 73773-2021 FSC-klagomål.docx", "A 73773-2021")</f>
         <v/>
       </c>
       <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 7955-2023 FSC-klagomål mail.docx", "A 7955-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 73773-2021 FSC-klagomål mail.docx", "A 73773-2021")</f>
         <v/>
       </c>
       <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 7955-2023 tillsynsbegäran.docx", "A 7955-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 73773-2021 tillsynsbegäran.docx", "A 73773-2021")</f>
         <v/>
       </c>
       <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 7955-2023 tillsynsbegäran mail.docx", "A 7955-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 73773-2021 tillsynsbegäran mail.docx", "A 73773-2021")</f>
         <v/>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 46438-2023</t>
+          <t>A 12363-2025</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1688,10 +1688,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45197</v>
+        <v>45730</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1704,13 +1704,13 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="J12" t="n">
         <v>1</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
@@ -1719,7 +1719,7 @@
         <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1728,10 +1728,10 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1744,42 +1744,42 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>Bombmurkla</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 46438-2023 artfynd.xlsx", "A 46438-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 12363-2025 artfynd.xlsx", "A 12363-2025")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 46438-2023 karta.png", "A 46438-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 12363-2025 karta.png", "A 12363-2025")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 46438-2023 georefererad karta.tif", "A 46438-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 12363-2025 georefererad karta.tif", "A 12363-2025")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 46438-2023 FSC-klagomål.docx", "A 46438-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 12363-2025 FSC-klagomål.docx", "A 12363-2025")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 46438-2023 FSC-klagomål mail.docx", "A 46438-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 12363-2025 FSC-klagomål mail.docx", "A 12363-2025")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 46438-2023 tillsynsbegäran.docx", "A 46438-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 12363-2025 tillsynsbegäran.docx", "A 12363-2025")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 46438-2023 tillsynsbegäran mail.docx", "A 46438-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 12363-2025 tillsynsbegäran mail.docx", "A 12363-2025")</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 12363-2025</t>
+          <t>A 23099-2024</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1793,10 +1793,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45730</v>
+        <v>45450</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1808,20 +1808,25 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I13" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="J13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -1833,10 +1838,10 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
@@ -1845,46 +1850,46 @@
         <v>1</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Bredbrämad bastardsvärmare</t>
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 12363-2025 artfynd.xlsx", "A 12363-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 23099-2024 artfynd.xlsx", "A 23099-2024")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 12363-2025 karta.png", "A 12363-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 23099-2024 karta.png", "A 23099-2024")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 12363-2025 georefererad karta.tif", "A 12363-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 23099-2024 georefererad karta.tif", "A 23099-2024")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 12363-2025 FSC-klagomål.docx", "A 12363-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 23099-2024 FSC-klagomål.docx", "A 23099-2024")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 12363-2025 FSC-klagomål mail.docx", "A 12363-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 23099-2024 FSC-klagomål mail.docx", "A 23099-2024")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 12363-2025 tillsynsbegäran.docx", "A 12363-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 23099-2024 tillsynsbegäran.docx", "A 23099-2024")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 12363-2025 tillsynsbegäran mail.docx", "A 12363-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 23099-2024 tillsynsbegäran mail.docx", "A 23099-2024")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 23099-2024</t>
+          <t>A 46438-2023</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1898,10 +1903,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45450</v>
+        <v>45197</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1913,16 +1918,11 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I14" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
@@ -1931,10 +1931,10 @@
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -1955,46 +1955,46 @@
         <v>1</v>
       </c>
       <c r="U14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Bredbrämad bastardsvärmare</t>
+          <t>Bombmurkla</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 23099-2024 artfynd.xlsx", "A 23099-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 46438-2023 artfynd.xlsx", "A 46438-2023")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 23099-2024 karta.png", "A 23099-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 46438-2023 karta.png", "A 46438-2023")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 23099-2024 georefererad karta.tif", "A 23099-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 46438-2023 georefererad karta.tif", "A 46438-2023")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 23099-2024 FSC-klagomål.docx", "A 23099-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 46438-2023 FSC-klagomål.docx", "A 46438-2023")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 23099-2024 FSC-klagomål mail.docx", "A 23099-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 46438-2023 FSC-klagomål mail.docx", "A 46438-2023")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 23099-2024 tillsynsbegäran.docx", "A 23099-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 46438-2023 tillsynsbegäran.docx", "A 46438-2023")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 23099-2024 tillsynsbegäran mail.docx", "A 23099-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 46438-2023 tillsynsbegäran mail.docx", "A 46438-2023")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 64098-2023</t>
+          <t>A 53357-2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2008,10 +2008,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45279</v>
+        <v>45959</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2024,22 +2024,22 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>0.3</v>
+        <v>2.4</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
         <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2051,55 +2051,55 @@
         <v>1</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S15" t="n">
         <v>1</v>
       </c>
       <c r="T15" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="U15" t="n">
         <v>0</v>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Skogsalmsdvärgmal</t>
+          <t>Bombmurkla</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 64098-2023 artfynd.xlsx", "A 64098-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 53357-2025 artfynd.xlsx", "A 53357-2025")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 64098-2023 karta.png", "A 64098-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 53357-2025 karta.png", "A 53357-2025")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 64098-2023 georefererad karta.tif", "A 64098-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 53357-2025 georefererad karta.tif", "A 53357-2025")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 64098-2023 FSC-klagomål.docx", "A 64098-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 53357-2025 FSC-klagomål.docx", "A 53357-2025")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 64098-2023 FSC-klagomål mail.docx", "A 64098-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 53357-2025 FSC-klagomål mail.docx", "A 53357-2025")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 64098-2023 tillsynsbegäran.docx", "A 64098-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 53357-2025 tillsynsbegäran.docx", "A 53357-2025")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 64098-2023 tillsynsbegäran mail.docx", "A 64098-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 53357-2025 tillsynsbegäran mail.docx", "A 53357-2025")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 26623-2026</t>
+          <t>A 11447-2025</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2109,14 +2109,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46184</v>
+        <v>45726</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2129,16 +2129,16 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>4.6</v>
+        <v>1.5</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
@@ -2153,7 +2153,7 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -2169,42 +2169,42 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Svartöra</t>
+          <t>Myskbock</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 26623-2026 artfynd.xlsx", "A 26623-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 11447-2025 artfynd.xlsx", "A 11447-2025")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 26623-2026 karta.png", "A 26623-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 11447-2025 karta.png", "A 11447-2025")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 26623-2026 georefererad karta.tif", "A 26623-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 11447-2025 georefererad karta.tif", "A 11447-2025")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 26623-2026 FSC-klagomål.docx", "A 26623-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 11447-2025 FSC-klagomål.docx", "A 11447-2025")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 26623-2026 FSC-klagomål mail.docx", "A 26623-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 11447-2025 FSC-klagomål mail.docx", "A 11447-2025")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 26623-2026 tillsynsbegäran.docx", "A 26623-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 11447-2025 tillsynsbegäran.docx", "A 11447-2025")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 26623-2026 tillsynsbegäran mail.docx", "A 26623-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 11447-2025 tillsynsbegäran mail.docx", "A 11447-2025")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 26637-2026</t>
+          <t>A 2409-2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2218,10 +2218,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46184</v>
+        <v>46034</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2234,10 +2234,10 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>5.4</v>
+        <v>14.2</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
@@ -2246,7 +2246,7 @@
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
@@ -2258,10 +2258,10 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
@@ -2274,42 +2274,46 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Igelkott</t>
+          <t>Havsörn</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 26637-2026 artfynd.xlsx", "A 26637-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 2409-2026 artfynd.xlsx", "A 2409-2026")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 26637-2026 karta.png", "A 26637-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 2409-2026 karta.png", "A 2409-2026")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 26637-2026 georefererad karta.tif", "A 26637-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 2409-2026 georefererad karta.tif", "A 2409-2026")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 26637-2026 FSC-klagomål.docx", "A 26637-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 2409-2026 FSC-klagomål.docx", "A 2409-2026")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 26637-2026 FSC-klagomål mail.docx", "A 26637-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 2409-2026 FSC-klagomål mail.docx", "A 2409-2026")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 26637-2026 tillsynsbegäran.docx", "A 26637-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 2409-2026 tillsynsbegäran.docx", "A 2409-2026")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 26637-2026 tillsynsbegäran mail.docx", "A 26637-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 2409-2026 tillsynsbegäran mail.docx", "A 2409-2026")</f>
+        <v/>
+      </c>
+      <c r="AE17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/fåglar/A 2409-2026 prioriterade fågelarter.docx", "A 2409-2026")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 53357-2025</t>
+          <t>A 7955-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2323,10 +2327,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45959</v>
+        <v>44973</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2339,7 +2343,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>2.4</v>
+        <v>2.9</v>
       </c>
       <c r="J18" t="n">
         <v>1</v>
@@ -2372,10 +2376,10 @@
         <v>1</v>
       </c>
       <c r="T18" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
@@ -2383,38 +2387,38 @@
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 53357-2025 artfynd.xlsx", "A 53357-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 7955-2023 artfynd.xlsx", "A 7955-2023")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 53357-2025 karta.png", "A 53357-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 7955-2023 karta.png", "A 7955-2023")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 53357-2025 georefererad karta.tif", "A 53357-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 7955-2023 georefererad karta.tif", "A 7955-2023")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 53357-2025 FSC-klagomål.docx", "A 53357-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 7955-2023 FSC-klagomål.docx", "A 7955-2023")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 53357-2025 FSC-klagomål mail.docx", "A 53357-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 7955-2023 FSC-klagomål mail.docx", "A 7955-2023")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 53357-2025 tillsynsbegäran.docx", "A 53357-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 7955-2023 tillsynsbegäran.docx", "A 7955-2023")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 53357-2025 tillsynsbegäran mail.docx", "A 53357-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 7955-2023 tillsynsbegäran mail.docx", "A 7955-2023")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 73773-2021</t>
+          <t>A 26637-2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2428,10 +2432,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>44552</v>
+        <v>46184</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2444,10 +2448,10 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>1.9</v>
+        <v>5.4</v>
       </c>
       <c r="J19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
@@ -2456,7 +2460,7 @@
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
@@ -2468,10 +2472,10 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
@@ -2480,46 +2484,46 @@
         <v>1</v>
       </c>
       <c r="U19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Kopparödla</t>
+          <t>Igelkott</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 73773-2021 artfynd.xlsx", "A 73773-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 26637-2026 artfynd.xlsx", "A 26637-2026")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 73773-2021 karta.png", "A 73773-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 26637-2026 karta.png", "A 26637-2026")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 73773-2021 georefererad karta.tif", "A 73773-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 26637-2026 georefererad karta.tif", "A 26637-2026")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 73773-2021 FSC-klagomål.docx", "A 73773-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 26637-2026 FSC-klagomål.docx", "A 26637-2026")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 73773-2021 FSC-klagomål mail.docx", "A 73773-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 26637-2026 FSC-klagomål mail.docx", "A 26637-2026")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 73773-2021 tillsynsbegäran.docx", "A 73773-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 26637-2026 tillsynsbegäran.docx", "A 26637-2026")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 73773-2021 tillsynsbegäran mail.docx", "A 73773-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 26637-2026 tillsynsbegäran mail.docx", "A 26637-2026")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 11447-2025</t>
+          <t>A 26623-2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2529,14 +2533,14 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45726</v>
+        <v>46184</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2549,16 +2553,16 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>1.5</v>
+        <v>4.6</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M20" t="n">
         <v>0</v>
@@ -2573,7 +2577,7 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
@@ -2589,42 +2593,42 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>Myskbock</t>
+          <t>Svartöra</t>
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 11447-2025 artfynd.xlsx", "A 11447-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 26623-2026 artfynd.xlsx", "A 26623-2026")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 11447-2025 karta.png", "A 11447-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 26623-2026 karta.png", "A 26623-2026")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 11447-2025 georefererad karta.tif", "A 11447-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 26623-2026 georefererad karta.tif", "A 26623-2026")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 11447-2025 FSC-klagomål.docx", "A 11447-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 26623-2026 FSC-klagomål.docx", "A 26623-2026")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 11447-2025 FSC-klagomål mail.docx", "A 11447-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 26623-2026 FSC-klagomål mail.docx", "A 26623-2026")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 11447-2025 tillsynsbegäran.docx", "A 11447-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 26623-2026 tillsynsbegäran.docx", "A 26623-2026")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 11447-2025 tillsynsbegäran mail.docx", "A 11447-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 26623-2026 tillsynsbegäran mail.docx", "A 26623-2026")</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 2409-2026</t>
+          <t>A 64098-2023</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2638,10 +2642,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46034</v>
+        <v>45279</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2654,16 +2658,16 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>14.2</v>
+        <v>0.3</v>
       </c>
       <c r="J21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M21" t="n">
         <v>0</v>
@@ -2678,7 +2682,7 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R21" t="n">
         <v>0</v>
@@ -2694,39 +2698,35 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Havsörn</t>
+          <t>Skogsalmsdvärgmal</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 2409-2026 artfynd.xlsx", "A 2409-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 64098-2023 artfynd.xlsx", "A 64098-2023")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 2409-2026 karta.png", "A 2409-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 64098-2023 karta.png", "A 64098-2023")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 2409-2026 georefererad karta.tif", "A 2409-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 64098-2023 georefererad karta.tif", "A 64098-2023")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 2409-2026 FSC-klagomål.docx", "A 2409-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 64098-2023 FSC-klagomål.docx", "A 64098-2023")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 2409-2026 FSC-klagomål mail.docx", "A 2409-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 64098-2023 FSC-klagomål mail.docx", "A 64098-2023")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 2409-2026 tillsynsbegäran.docx", "A 2409-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 64098-2023 tillsynsbegäran.docx", "A 64098-2023")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 2409-2026 tillsynsbegäran mail.docx", "A 2409-2026")</f>
-        <v/>
-      </c>
-      <c r="AE21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/fåglar/A 2409-2026 prioriterade fågelarter.docx", "A 2409-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 64098-2023 tillsynsbegäran mail.docx", "A 64098-2023")</f>
         <v/>
       </c>
     </row>
@@ -2750,7 +2750,7 @@
         <v>45671</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2859,7 +2859,7 @@
         <v>45803</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2964,7 +2964,7 @@
         <v>44558</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3069,7 +3069,7 @@
         <v>44609</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3142,7 +3142,7 @@
         <v>44489</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3220,7 +3220,7 @@
         <v>44546</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3293,7 +3293,7 @@
         <v>44700</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3366,7 +3366,7 @@
         <v>44587</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3439,7 +3439,7 @@
         <v>44655</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3500,7 +3500,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 59700-2021</t>
+          <t>A 2602-2024</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3514,10 +3514,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44494</v>
+        <v>45313</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3529,13 +3529,8 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I31" t="n">
-        <v>4.8</v>
+        <v>0.7</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3578,7 +3573,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 38902-2024</t>
+          <t>A 59844-2022</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3592,10 +3587,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45547</v>
+        <v>44901</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3613,7 +3608,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0.8</v>
+        <v>11.9</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3656,7 +3651,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 50294-2023</t>
+          <t>A 64105-2023</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3670,10 +3665,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45216</v>
+        <v>45279</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3686,7 +3681,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>3.7</v>
+        <v>2.2</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3729,7 +3724,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 9655-2026</t>
+          <t>A 3630-2023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3743,10 +3738,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>46070</v>
+        <v>44950</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3758,13 +3753,8 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I34" t="n">
-        <v>17.2</v>
+        <v>1.4</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3807,7 +3797,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 5264-2023</t>
+          <t>A 23093-2024</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3821,10 +3811,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44959</v>
+        <v>45450</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3836,8 +3826,13 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I35" t="n">
-        <v>5.8</v>
+        <v>0.9</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3880,7 +3875,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 18787-2026</t>
+          <t>A 54222-2023</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3894,10 +3889,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>46128</v>
+        <v>45225</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3915,7 +3910,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>7.8</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3958,7 +3953,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 18813-2026</t>
+          <t>A 7860-2024</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3972,10 +3967,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>46128</v>
+        <v>45348</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3993,7 +3988,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>56</v>
+        <v>1.9</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4036,7 +4031,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 18818-2026</t>
+          <t>A 27313-2023</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4050,10 +4045,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>46128</v>
+        <v>45096</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4065,13 +4060,8 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I38" t="n">
-        <v>17.8</v>
+        <v>1.8</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4114,7 +4104,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 18778-2026</t>
+          <t>A 64114-2023</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4128,10 +4118,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>46128</v>
+        <v>45279</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4143,13 +4133,8 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I39" t="n">
-        <v>4.5</v>
+        <v>0.4</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4192,7 +4177,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 23098-2024</t>
+          <t>A 50294-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4206,10 +4191,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45450</v>
+        <v>45216</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4221,13 +4206,8 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I40" t="n">
-        <v>1</v>
+        <v>3.7</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4270,7 +4250,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 59844-2022</t>
+          <t>A 58011-2021</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4284,10 +4264,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44901</v>
+        <v>44487</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4305,7 +4285,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>11.9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4348,7 +4328,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 54222-2023</t>
+          <t>A 21206-2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4362,10 +4342,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45225</v>
+        <v>46146</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4383,7 +4363,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>8.300000000000001</v>
+        <v>0.9</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4426,7 +4406,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 21206-2026</t>
+          <t>A 64110-2023</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4440,10 +4420,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>46146</v>
+        <v>45279</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4455,13 +4435,8 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I43" t="n">
-        <v>0.9</v>
+        <v>0.4</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4504,7 +4479,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 4338-2023</t>
+          <t>A 23098-2024</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4518,10 +4493,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44953</v>
+        <v>45450</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4533,8 +4508,13 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I44" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4577,7 +4557,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 58011-2021</t>
+          <t>A 59377-2024</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4591,10 +4571,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>44487</v>
+        <v>45638</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4606,13 +4586,8 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I45" t="n">
-        <v>9.199999999999999</v>
+        <v>0.6</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4655,7 +4630,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 72524-2021</t>
+          <t>A 59402-2022</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4669,10 +4644,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44546</v>
+        <v>44906</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4685,7 +4660,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>3.6</v>
+        <v>1.8</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4728,7 +4703,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 64107-2023</t>
+          <t>A 5264-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4742,10 +4717,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45279</v>
+        <v>44959</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4758,7 +4733,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>0.3</v>
+        <v>5.8</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4801,7 +4776,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 23093-2024</t>
+          <t>A 51587-2023</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4815,10 +4790,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45450</v>
+        <v>45215</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4832,11 +4807,11 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Övriga statliga verk och myndigheter</t>
+          <t>Allmännings- och besparingsskogar</t>
         </is>
       </c>
       <c r="I48" t="n">
-        <v>0.9</v>
+        <v>2.6</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4896,7 +4871,7 @@
         <v>46170</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4952,7 +4927,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 27313-2023</t>
+          <t>A 72524-2021</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4966,10 +4941,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45096</v>
+        <v>44546</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4982,7 +4957,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>1.8</v>
+        <v>3.6</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5025,7 +5000,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 58598-2025</t>
+          <t>A 4338-2023</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5039,10 +5014,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45986</v>
+        <v>44953</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5054,13 +5029,8 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I51" t="n">
-        <v>4.5</v>
+        <v>1.1</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5120,7 +5090,7 @@
         <v>44770</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5176,7 +5146,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 59377-2024</t>
+          <t>A 58598-2025</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5190,10 +5160,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45638</v>
+        <v>45986</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5205,8 +5175,13 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I53" t="n">
-        <v>0.6</v>
+        <v>4.5</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5249,7 +5224,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 26196-2026</t>
+          <t>A 59848-2022</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5259,14 +5234,14 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>46182</v>
+        <v>44901</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5278,8 +5253,13 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I54" t="n">
-        <v>53.1</v>
+        <v>10.7</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5322,7 +5302,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 26625-2026</t>
+          <t>A 26196-2026</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5332,14 +5312,14 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>46184</v>
+        <v>46182</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5352,7 +5332,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>5.3</v>
+        <v>53.1</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5395,7 +5375,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 26629-2026</t>
+          <t>A 9655-2026</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5409,10 +5389,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>46184</v>
+        <v>46070</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5424,8 +5404,13 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I56" t="n">
-        <v>2</v>
+        <v>17.2</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5485,7 +5470,7 @@
         <v>46184</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5541,7 +5526,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 3754-2026</t>
+          <t>A 26625-2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5555,10 +5540,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>46043</v>
+        <v>46184</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5570,13 +5555,8 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I58" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5619,7 +5599,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 28797-2026</t>
+          <t>A 26629-2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5633,10 +5613,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>46198</v>
+        <v>46184</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5649,7 +5629,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5692,7 +5672,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 28740-2026</t>
+          <t>A 59700-2021</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5706,10 +5686,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>46198</v>
+        <v>44494</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5719,6 +5699,11 @@
       <c r="G60" t="inlineStr">
         <is>
           <t>UPPLANDS-BRO</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
         </is>
       </c>
       <c r="I60" t="n">
@@ -5765,7 +5750,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 28735-2026</t>
+          <t>A 3754-2026</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5779,10 +5764,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>46198</v>
+        <v>46043</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5794,8 +5779,13 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I61" t="n">
-        <v>3.5</v>
+        <v>5.1</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5838,7 +5828,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 33058-2026</t>
+          <t>A 28735-2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5848,14 +5838,14 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>46245</v>
+        <v>46198</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5868,7 +5858,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>1.3</v>
+        <v>3.5</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5911,7 +5901,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 51587-2023</t>
+          <t>A 28740-2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5925,10 +5915,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45215</v>
+        <v>46198</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5940,13 +5930,8 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I63" t="n">
-        <v>2.6</v>
+        <v>4.8</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5989,7 +5974,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 59848-2022</t>
+          <t>A 28797-2026</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6003,10 +5988,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>44901</v>
+        <v>46198</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6018,13 +6003,8 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I64" t="n">
-        <v>10.7</v>
+        <v>2.2</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6067,7 +6047,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 64110-2023</t>
+          <t>A 18778-2026</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6081,10 +6061,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45279</v>
+        <v>46128</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6096,8 +6076,13 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I65" t="n">
-        <v>0.4</v>
+        <v>4.5</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6140,7 +6125,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 31714-2026</t>
+          <t>A 33058-2026</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6150,14 +6135,14 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>46226</v>
+        <v>46245</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6170,7 +6155,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>5</v>
+        <v>1.3</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6213,7 +6198,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 7275-2022</t>
+          <t>A 18813-2026</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6227,10 +6212,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>44606</v>
+        <v>46128</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6248,7 +6233,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>9.6</v>
+        <v>56</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6291,7 +6276,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 2602-2024</t>
+          <t>A 18818-2026</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6305,10 +6290,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45313</v>
+        <v>46128</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6320,8 +6305,13 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I68" t="n">
-        <v>0.7</v>
+        <v>17.8</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6364,7 +6354,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 59402-2022</t>
+          <t>A 18787-2026</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6378,10 +6368,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>44906</v>
+        <v>46128</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6393,8 +6383,13 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I69" t="n">
-        <v>1.8</v>
+        <v>7.8</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6437,7 +6432,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 3630-2023</t>
+          <t>A 7275-2022</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6451,10 +6446,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>44950</v>
+        <v>44606</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6466,8 +6461,13 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I70" t="n">
-        <v>1.4</v>
+        <v>9.6</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6510,7 +6510,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 7860-2024</t>
+          <t>A 64107-2023</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6524,10 +6524,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45348</v>
+        <v>45279</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6539,13 +6539,8 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I71" t="n">
-        <v>1.9</v>
+        <v>0.3</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6588,7 +6583,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 64105-2023</t>
+          <t>A 7112-2025</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6602,10 +6597,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45279</v>
+        <v>45701</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6618,7 +6613,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6661,7 +6656,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 64114-2023</t>
+          <t>A 38902-2024</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6675,10 +6670,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45279</v>
+        <v>45547</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6690,8 +6685,13 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I73" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6734,7 +6734,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 7112-2025</t>
+          <t>A 31714-2026</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6748,10 +6748,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45701</v>
+        <v>46226</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6764,7 +6764,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>2.4</v>
+        <v>5</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6824,7 +6824,7 @@
         <v>45792</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6897,7 +6897,7 @@
         <v>45792</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6970,7 +6970,7 @@
         <v>44558</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>

--- a/Översikt UPPLANDS-BRO.xlsx
+++ b/Översikt UPPLANDS-BRO.xlsx
@@ -601,7 +601,7 @@
         <v>44481</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -714,7 +714,7 @@
         <v>44552</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -822,7 +822,7 @@
         <v>44552</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -930,7 +930,7 @@
         <v>45232</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1042,7 +1042,7 @@
         <v>45722</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1153,7 +1153,7 @@
         <v>46128</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1264,7 +1264,7 @@
         <v>46128</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
         <v>44603</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1481,7 +1481,7 @@
         <v>44552</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1586,7 +1586,7 @@
         <v>44552</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>45730</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1796,7 +1796,7 @@
         <v>45450</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1906,7 +1906,7 @@
         <v>45197</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2011,7 +2011,7 @@
         <v>45959</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2116,7 +2116,7 @@
         <v>45726</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2221,7 +2221,7 @@
         <v>46034</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2330,7 +2330,7 @@
         <v>44973</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2435,7 +2435,7 @@
         <v>46184</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2540,7 +2540,7 @@
         <v>46184</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2645,7 +2645,7 @@
         <v>45279</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2750,7 +2750,7 @@
         <v>45671</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2859,7 +2859,7 @@
         <v>45803</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2964,7 +2964,7 @@
         <v>44558</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3069,7 +3069,7 @@
         <v>44609</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3142,7 +3142,7 @@
         <v>44489</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3220,7 +3220,7 @@
         <v>44546</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3293,7 +3293,7 @@
         <v>44700</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3366,7 +3366,7 @@
         <v>44587</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3439,7 +3439,7 @@
         <v>44655</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3517,7 +3517,7 @@
         <v>45313</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3590,7 +3590,7 @@
         <v>44901</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3668,7 +3668,7 @@
         <v>45279</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3741,7 +3741,7 @@
         <v>44950</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3814,7 +3814,7 @@
         <v>45450</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3892,7 +3892,7 @@
         <v>45225</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3970,7 +3970,7 @@
         <v>45348</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4048,7 +4048,7 @@
         <v>45096</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4121,7 +4121,7 @@
         <v>45279</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4194,7 +4194,7 @@
         <v>45216</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4267,7 +4267,7 @@
         <v>44487</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4345,7 +4345,7 @@
         <v>46146</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4423,7 +4423,7 @@
         <v>45279</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4496,7 +4496,7 @@
         <v>45450</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4574,7 +4574,7 @@
         <v>45638</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4647,7 +4647,7 @@
         <v>44906</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4720,7 +4720,7 @@
         <v>44959</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4793,7 +4793,7 @@
         <v>45215</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4871,7 +4871,7 @@
         <v>46170</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4944,7 +4944,7 @@
         <v>44546</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5017,7 +5017,7 @@
         <v>44953</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5090,7 +5090,7 @@
         <v>44770</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5163,7 +5163,7 @@
         <v>45986</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5241,7 +5241,7 @@
         <v>44901</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5319,7 +5319,7 @@
         <v>46182</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5392,7 +5392,7 @@
         <v>46070</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5470,7 +5470,7 @@
         <v>46184</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5543,7 +5543,7 @@
         <v>46184</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5616,7 +5616,7 @@
         <v>46184</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5689,7 +5689,7 @@
         <v>44494</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5767,7 +5767,7 @@
         <v>46043</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5845,7 +5845,7 @@
         <v>46198</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5918,7 +5918,7 @@
         <v>46198</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5991,7 +5991,7 @@
         <v>46198</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6064,7 +6064,7 @@
         <v>46128</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6142,7 +6142,7 @@
         <v>46245</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6215,7 +6215,7 @@
         <v>46128</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6293,7 +6293,7 @@
         <v>46128</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6371,7 +6371,7 @@
         <v>46128</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6449,7 +6449,7 @@
         <v>44606</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6527,7 +6527,7 @@
         <v>45279</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6600,7 +6600,7 @@
         <v>45701</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6673,7 +6673,7 @@
         <v>45547</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6751,7 +6751,7 @@
         <v>46226</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6824,7 +6824,7 @@
         <v>45792</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6897,7 +6897,7 @@
         <v>45792</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6970,7 +6970,7 @@
         <v>44558</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>

--- a/Översikt UPPLANDS-BRO.xlsx
+++ b/Översikt UPPLANDS-BRO.xlsx
@@ -601,7 +601,7 @@
         <v>44481</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -714,7 +714,7 @@
         <v>44552</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -822,7 +822,7 @@
         <v>44552</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -930,7 +930,7 @@
         <v>45232</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1042,7 +1042,7 @@
         <v>45722</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1153,7 +1153,7 @@
         <v>46128</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1264,7 +1264,7 @@
         <v>46128</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
         <v>44603</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1481,7 +1481,7 @@
         <v>44552</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1586,7 +1586,7 @@
         <v>44552</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>45730</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1779,7 +1779,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 23099-2024</t>
+          <t>A 53357-2025</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1793,10 +1793,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45450</v>
+        <v>45959</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1808,16 +1808,11 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I13" t="n">
-        <v>0.7</v>
+        <v>2.4</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
@@ -1826,10 +1821,10 @@
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -1847,49 +1842,49 @@
         <v>1</v>
       </c>
       <c r="T13" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="U13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>Bredbrämad bastardsvärmare</t>
+          <t>Bombmurkla</t>
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 23099-2024 artfynd.xlsx", "A 23099-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 53357-2025 artfynd.xlsx", "A 53357-2025")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 23099-2024 karta.png", "A 23099-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 53357-2025 karta.png", "A 53357-2025")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 23099-2024 georefererad karta.tif", "A 23099-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 53357-2025 georefererad karta.tif", "A 53357-2025")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 23099-2024 FSC-klagomål.docx", "A 23099-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 53357-2025 FSC-klagomål.docx", "A 53357-2025")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 23099-2024 FSC-klagomål mail.docx", "A 23099-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 53357-2025 FSC-klagomål mail.docx", "A 53357-2025")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 23099-2024 tillsynsbegäran.docx", "A 23099-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 53357-2025 tillsynsbegäran.docx", "A 53357-2025")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 23099-2024 tillsynsbegäran mail.docx", "A 23099-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 53357-2025 tillsynsbegäran mail.docx", "A 53357-2025")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 46438-2023</t>
+          <t>A 23099-2024</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1903,10 +1898,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45197</v>
+        <v>45450</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1918,11 +1913,16 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I14" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
@@ -1931,10 +1931,10 @@
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -1955,46 +1955,46 @@
         <v>1</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Bombmurkla</t>
+          <t>Bredbrämad bastardsvärmare</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 46438-2023 artfynd.xlsx", "A 46438-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 23099-2024 artfynd.xlsx", "A 23099-2024")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 46438-2023 karta.png", "A 46438-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 23099-2024 karta.png", "A 23099-2024")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 46438-2023 georefererad karta.tif", "A 46438-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 23099-2024 georefererad karta.tif", "A 23099-2024")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 46438-2023 FSC-klagomål.docx", "A 46438-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 23099-2024 FSC-klagomål.docx", "A 23099-2024")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 46438-2023 FSC-klagomål mail.docx", "A 46438-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 23099-2024 FSC-klagomål mail.docx", "A 23099-2024")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 46438-2023 tillsynsbegäran.docx", "A 46438-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 23099-2024 tillsynsbegäran.docx", "A 23099-2024")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 46438-2023 tillsynsbegäran mail.docx", "A 46438-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 23099-2024 tillsynsbegäran mail.docx", "A 23099-2024")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 53357-2025</t>
+          <t>A 46438-2023</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2008,10 +2008,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45959</v>
+        <v>45197</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2024,7 +2024,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>2.4</v>
+        <v>0.5</v>
       </c>
       <c r="J15" t="n">
         <v>1</v>
@@ -2057,7 +2057,7 @@
         <v>1</v>
       </c>
       <c r="T15" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="U15" t="n">
         <v>0</v>
@@ -2068,38 +2068,38 @@
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 53357-2025 artfynd.xlsx", "A 53357-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 46438-2023 artfynd.xlsx", "A 46438-2023")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 53357-2025 karta.png", "A 53357-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 46438-2023 karta.png", "A 46438-2023")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 53357-2025 georefererad karta.tif", "A 53357-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 46438-2023 georefererad karta.tif", "A 46438-2023")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 53357-2025 FSC-klagomål.docx", "A 53357-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 46438-2023 FSC-klagomål.docx", "A 46438-2023")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 53357-2025 FSC-klagomål mail.docx", "A 53357-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 46438-2023 FSC-klagomål mail.docx", "A 46438-2023")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 53357-2025 tillsynsbegäran.docx", "A 53357-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 46438-2023 tillsynsbegäran.docx", "A 46438-2023")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 53357-2025 tillsynsbegäran mail.docx", "A 53357-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 46438-2023 tillsynsbegäran mail.docx", "A 46438-2023")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 11447-2025</t>
+          <t>A 26637-2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2109,14 +2109,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45726</v>
+        <v>46184</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2129,19 +2129,19 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>1.5</v>
+        <v>5.4</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -2153,10 +2153,10 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
@@ -2169,35 +2169,35 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Myskbock</t>
+          <t>Igelkott</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 11447-2025 artfynd.xlsx", "A 11447-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 26637-2026 artfynd.xlsx", "A 26637-2026")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 11447-2025 karta.png", "A 11447-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 26637-2026 karta.png", "A 26637-2026")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 11447-2025 georefererad karta.tif", "A 11447-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 26637-2026 georefererad karta.tif", "A 26637-2026")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 11447-2025 FSC-klagomål.docx", "A 11447-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 26637-2026 FSC-klagomål.docx", "A 26637-2026")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 11447-2025 FSC-klagomål mail.docx", "A 11447-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 26637-2026 FSC-klagomål mail.docx", "A 26637-2026")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 11447-2025 tillsynsbegäran.docx", "A 11447-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 26637-2026 tillsynsbegäran.docx", "A 26637-2026")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 11447-2025 tillsynsbegäran mail.docx", "A 11447-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 26637-2026 tillsynsbegäran mail.docx", "A 26637-2026")</f>
         <v/>
       </c>
     </row>
@@ -2221,7 +2221,7 @@
         <v>46034</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2313,7 +2313,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 7955-2023</t>
+          <t>A 26623-2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2327,10 +2327,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>44973</v>
+        <v>46184</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2343,22 +2343,22 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>2.9</v>
+        <v>4.6</v>
       </c>
       <c r="J18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2370,7 +2370,7 @@
         <v>1</v>
       </c>
       <c r="R18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
@@ -2379,46 +2379,46 @@
         <v>1</v>
       </c>
       <c r="U18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Bombmurkla</t>
+          <t>Svartöra</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 7955-2023 artfynd.xlsx", "A 7955-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 26623-2026 artfynd.xlsx", "A 26623-2026")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 7955-2023 karta.png", "A 7955-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 26623-2026 karta.png", "A 26623-2026")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 7955-2023 georefererad karta.tif", "A 7955-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 26623-2026 georefererad karta.tif", "A 26623-2026")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 7955-2023 FSC-klagomål.docx", "A 7955-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 26623-2026 FSC-klagomål.docx", "A 26623-2026")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 7955-2023 FSC-klagomål mail.docx", "A 7955-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 26623-2026 FSC-klagomål mail.docx", "A 26623-2026")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 7955-2023 tillsynsbegäran.docx", "A 7955-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 26623-2026 tillsynsbegäran.docx", "A 26623-2026")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 7955-2023 tillsynsbegäran mail.docx", "A 7955-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 26623-2026 tillsynsbegäran mail.docx", "A 26623-2026")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 26637-2026</t>
+          <t>A 11447-2025</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2428,14 +2428,14 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46184</v>
+        <v>45726</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2448,19 +2448,19 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>5.4</v>
+        <v>1.5</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
@@ -2472,10 +2472,10 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
@@ -2488,42 +2488,42 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Igelkott</t>
+          <t>Myskbock</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 26637-2026 artfynd.xlsx", "A 26637-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 11447-2025 artfynd.xlsx", "A 11447-2025")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 26637-2026 karta.png", "A 26637-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 11447-2025 karta.png", "A 11447-2025")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 26637-2026 georefererad karta.tif", "A 26637-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 11447-2025 georefererad karta.tif", "A 11447-2025")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 26637-2026 FSC-klagomål.docx", "A 26637-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 11447-2025 FSC-klagomål.docx", "A 11447-2025")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 26637-2026 FSC-klagomål mail.docx", "A 26637-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 11447-2025 FSC-klagomål mail.docx", "A 11447-2025")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 26637-2026 tillsynsbegäran.docx", "A 26637-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 11447-2025 tillsynsbegäran.docx", "A 11447-2025")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 26637-2026 tillsynsbegäran mail.docx", "A 26637-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 11447-2025 tillsynsbegäran mail.docx", "A 11447-2025")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 26623-2026</t>
+          <t>A 7955-2023</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2537,10 +2537,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46184</v>
+        <v>44973</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2553,22 +2553,22 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>4.6</v>
+        <v>2.9</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
         <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2580,7 +2580,7 @@
         <v>1</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>
@@ -2589,39 +2589,39 @@
         <v>1</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>Svartöra</t>
+          <t>Bombmurkla</t>
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 26623-2026 artfynd.xlsx", "A 26623-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 7955-2023 artfynd.xlsx", "A 7955-2023")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 26623-2026 karta.png", "A 26623-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 7955-2023 karta.png", "A 7955-2023")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 26623-2026 georefererad karta.tif", "A 26623-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 7955-2023 georefererad karta.tif", "A 7955-2023")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 26623-2026 FSC-klagomål.docx", "A 26623-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 7955-2023 FSC-klagomål.docx", "A 7955-2023")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 26623-2026 FSC-klagomål mail.docx", "A 26623-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 7955-2023 FSC-klagomål mail.docx", "A 7955-2023")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 26623-2026 tillsynsbegäran.docx", "A 26623-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 7955-2023 tillsynsbegäran.docx", "A 7955-2023")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 26623-2026 tillsynsbegäran mail.docx", "A 26623-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 7955-2023 tillsynsbegäran mail.docx", "A 7955-2023")</f>
         <v/>
       </c>
     </row>
@@ -2645,7 +2645,7 @@
         <v>45279</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2750,7 +2750,7 @@
         <v>45671</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2859,7 +2859,7 @@
         <v>45803</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2964,7 +2964,7 @@
         <v>44558</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3069,7 +3069,7 @@
         <v>44609</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3142,7 +3142,7 @@
         <v>44489</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3220,7 +3220,7 @@
         <v>44546</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3293,7 +3293,7 @@
         <v>44700</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3366,7 +3366,7 @@
         <v>44587</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3439,7 +3439,7 @@
         <v>44655</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3500,7 +3500,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 2602-2024</t>
+          <t>A 64105-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3514,10 +3514,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45313</v>
+        <v>45279</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3530,7 +3530,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>0.7</v>
+        <v>2.2</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3573,7 +3573,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 59844-2022</t>
+          <t>A 2602-2024</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3587,10 +3587,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44901</v>
+        <v>45313</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3602,13 +3602,8 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I32" t="n">
-        <v>11.9</v>
+        <v>0.7</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3651,7 +3646,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 64105-2023</t>
+          <t>A 59844-2022</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3665,10 +3660,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45279</v>
+        <v>44901</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3680,8 +3675,13 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I33" t="n">
-        <v>2.2</v>
+        <v>11.9</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3724,7 +3724,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 3630-2023</t>
+          <t>A 23093-2024</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3738,10 +3738,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44950</v>
+        <v>45450</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3753,8 +3753,13 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I34" t="n">
-        <v>1.4</v>
+        <v>0.9</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3797,7 +3802,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 23093-2024</t>
+          <t>A 3630-2023</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3811,10 +3816,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45450</v>
+        <v>44950</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3826,13 +3831,8 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I35" t="n">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3892,7 +3892,7 @@
         <v>45225</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3970,7 +3970,7 @@
         <v>45348</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4048,7 +4048,7 @@
         <v>45096</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4121,7 +4121,7 @@
         <v>45279</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4194,7 +4194,7 @@
         <v>45216</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4267,7 +4267,7 @@
         <v>44487</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4345,7 +4345,7 @@
         <v>46146</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4423,7 +4423,7 @@
         <v>45279</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4496,7 +4496,7 @@
         <v>45450</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4557,7 +4557,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 59377-2024</t>
+          <t>A 24579-2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4571,10 +4571,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45638</v>
+        <v>46170</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4587,7 +4587,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.6</v>
+        <v>2.1</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4630,7 +4630,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 59402-2022</t>
+          <t>A 59377-2024</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4644,10 +4644,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44906</v>
+        <v>45638</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4660,7 +4660,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1.8</v>
+        <v>0.6</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4703,7 +4703,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 5264-2023</t>
+          <t>A 59402-2022</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4717,10 +4717,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>44959</v>
+        <v>44906</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4733,7 +4733,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>5.8</v>
+        <v>1.8</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4776,7 +4776,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 51587-2023</t>
+          <t>A 31160-2022</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4790,10 +4790,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45215</v>
+        <v>44770</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4805,13 +4805,8 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I48" t="n">
-        <v>2.6</v>
+        <v>3.7</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4854,7 +4849,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 24579-2026</t>
+          <t>A 58598-2025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4868,10 +4863,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>46170</v>
+        <v>45986</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4883,8 +4878,13 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I49" t="n">
-        <v>2.1</v>
+        <v>4.5</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4927,7 +4927,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 72524-2021</t>
+          <t>A 26196-2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4937,14 +4937,14 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>44546</v>
+        <v>46182</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4957,7 +4957,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>3.6</v>
+        <v>53.1</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5000,7 +5000,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 4338-2023</t>
+          <t>A 26633-2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5014,10 +5014,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>44953</v>
+        <v>46184</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5030,7 +5030,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5073,7 +5073,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 31160-2022</t>
+          <t>A 26625-2026</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5087,10 +5087,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>44770</v>
+        <v>46184</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5103,7 +5103,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>3.7</v>
+        <v>5.3</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5146,7 +5146,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 58598-2025</t>
+          <t>A 26629-2026</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5160,10 +5160,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45986</v>
+        <v>46184</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5175,13 +5175,8 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I53" t="n">
-        <v>4.5</v>
+        <v>2</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5224,7 +5219,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 59848-2022</t>
+          <t>A 3754-2026</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5238,10 +5233,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>44901</v>
+        <v>46043</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5259,7 +5254,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>10.7</v>
+        <v>5.1</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5302,7 +5297,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 26196-2026</t>
+          <t>A 5264-2023</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5312,14 +5307,14 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>46182</v>
+        <v>44959</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5332,7 +5327,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>53.1</v>
+        <v>5.8</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5375,7 +5370,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 9655-2026</t>
+          <t>A 28735-2026</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5389,10 +5384,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>46070</v>
+        <v>46198</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5404,13 +5399,8 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I56" t="n">
-        <v>17.2</v>
+        <v>3.5</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5453,7 +5443,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 26633-2026</t>
+          <t>A 28740-2026</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5467,10 +5457,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>46184</v>
+        <v>46198</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5483,7 +5473,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>0.7</v>
+        <v>4.8</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5526,7 +5516,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 26625-2026</t>
+          <t>A 9655-2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5540,10 +5530,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>46184</v>
+        <v>46070</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5555,8 +5545,13 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I58" t="n">
-        <v>5.3</v>
+        <v>17.2</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5599,7 +5594,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 26629-2026</t>
+          <t>A 28797-2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5613,10 +5608,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>46184</v>
+        <v>46198</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5629,7 +5624,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5672,7 +5667,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 59700-2021</t>
+          <t>A 51587-2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5686,10 +5681,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>44494</v>
+        <v>45215</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5703,11 +5698,11 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Övriga statliga verk och myndigheter</t>
+          <t>Allmännings- och besparingsskogar</t>
         </is>
       </c>
       <c r="I60" t="n">
-        <v>4.8</v>
+        <v>2.6</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5750,7 +5745,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 3754-2026</t>
+          <t>A 72524-2021</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5764,10 +5759,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>46043</v>
+        <v>44546</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5779,13 +5774,8 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I61" t="n">
-        <v>5.1</v>
+        <v>3.6</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5828,7 +5818,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 28735-2026</t>
+          <t>A 4338-2023</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5842,10 +5832,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>46198</v>
+        <v>44953</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5858,7 +5848,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>3.5</v>
+        <v>1.1</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5901,7 +5891,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 28740-2026</t>
+          <t>A 18778-2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5915,10 +5905,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>46198</v>
+        <v>46128</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5930,8 +5920,13 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I63" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5974,7 +5969,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 28797-2026</t>
+          <t>A 18813-2026</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5988,10 +5983,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>46198</v>
+        <v>46128</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6003,8 +5998,13 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I64" t="n">
-        <v>2.2</v>
+        <v>56</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6047,7 +6047,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 18778-2026</t>
+          <t>A 18818-2026</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6064,7 +6064,7 @@
         <v>46128</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6082,7 +6082,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>4.5</v>
+        <v>17.8</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6125,7 +6125,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 33058-2026</t>
+          <t>A 18787-2026</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6135,14 +6135,14 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>46245</v>
+        <v>46128</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6154,8 +6154,13 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I66" t="n">
-        <v>1.3</v>
+        <v>7.8</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6198,7 +6203,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 18813-2026</t>
+          <t>A 59848-2022</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6212,10 +6217,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>46128</v>
+        <v>44901</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6233,7 +6238,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>56</v>
+        <v>10.7</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6276,7 +6281,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 18818-2026</t>
+          <t>A 59700-2021</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6290,10 +6295,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>46128</v>
+        <v>44494</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6311,7 +6316,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>17.8</v>
+        <v>4.8</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6354,7 +6359,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 18787-2026</t>
+          <t>A 31714-2026</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6368,10 +6373,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>46128</v>
+        <v>46226</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6383,13 +6388,8 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I69" t="n">
-        <v>7.8</v>
+        <v>5</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6449,7 +6449,7 @@
         <v>44606</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6510,7 +6510,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 64107-2023</t>
+          <t>A 33058-2026</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6520,14 +6520,14 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45279</v>
+        <v>46245</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6540,7 +6540,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>0.3</v>
+        <v>1.3</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6583,7 +6583,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 7112-2025</t>
+          <t>A 64107-2023</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6597,10 +6597,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45701</v>
+        <v>45279</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6613,7 +6613,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>2.4</v>
+        <v>0.3</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6656,7 +6656,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 38902-2024</t>
+          <t>A 7112-2025</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6670,10 +6670,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45547</v>
+        <v>45701</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6685,13 +6685,8 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I73" t="n">
-        <v>0.8</v>
+        <v>2.4</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6734,7 +6729,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 31714-2026</t>
+          <t>A 38902-2024</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6748,10 +6743,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>46226</v>
+        <v>45547</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6763,8 +6758,13 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I74" t="n">
-        <v>5</v>
+        <v>0.8</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6824,7 +6824,7 @@
         <v>45792</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6897,7 +6897,7 @@
         <v>45792</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6970,7 +6970,7 @@
         <v>44558</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>

--- a/Översikt UPPLANDS-BRO.xlsx
+++ b/Översikt UPPLANDS-BRO.xlsx
@@ -601,7 +601,7 @@
         <v>44481</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -714,7 +714,7 @@
         <v>44552</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -822,7 +822,7 @@
         <v>44552</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -930,7 +930,7 @@
         <v>45232</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1025,7 +1025,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 10909-2025</t>
+          <t>A 18790-2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1039,10 +1039,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>45722</v>
+        <v>46128</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1056,20 +1056,20 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Allmännings- och besparingsskogar</t>
+          <t>Övriga statliga verk och myndigheter</t>
         </is>
       </c>
       <c r="I6" t="n">
-        <v>11.2</v>
+        <v>5.5</v>
       </c>
       <c r="J6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
@@ -1084,7 +1084,7 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -1096,262 +1096,262 @@
         <v>2</v>
       </c>
       <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>Fläcknycklar
+Nattviol</t>
+        </is>
+      </c>
+      <c r="W6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 18790-2026 artfynd.xlsx", "A 18790-2026")</f>
+        <v/>
+      </c>
+      <c r="X6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 18790-2026 karta.png", "A 18790-2026")</f>
+        <v/>
+      </c>
+      <c r="Y6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 18790-2026 georefererad karta.tif", "A 18790-2026")</f>
+        <v/>
+      </c>
+      <c r="AA6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 18790-2026 FSC-klagomål.docx", "A 18790-2026")</f>
+        <v/>
+      </c>
+      <c r="AB6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 18790-2026 FSC-klagomål mail.docx", "A 18790-2026")</f>
+        <v/>
+      </c>
+      <c r="AC6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 18790-2026 tillsynsbegäran.docx", "A 18790-2026")</f>
+        <v/>
+      </c>
+      <c r="AD6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 18790-2026 tillsynsbegäran mail.docx", "A 18790-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>A 18772-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>46128</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>UPPLANDS-BRO</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
         <v>2</v>
       </c>
-      <c r="V6" s="2" t="inlineStr">
+      <c r="T7" t="n">
+        <v>2</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>Svedjenäva
+Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="W7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 18772-2026 artfynd.xlsx", "A 18772-2026")</f>
+        <v/>
+      </c>
+      <c r="X7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 18772-2026 karta.png", "A 18772-2026")</f>
+        <v/>
+      </c>
+      <c r="Y7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 18772-2026 georefererad karta.tif", "A 18772-2026")</f>
+        <v/>
+      </c>
+      <c r="AA7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 18772-2026 FSC-klagomål.docx", "A 18772-2026")</f>
+        <v/>
+      </c>
+      <c r="AB7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 18772-2026 FSC-klagomål mail.docx", "A 18772-2026")</f>
+        <v/>
+      </c>
+      <c r="AC7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 18772-2026 tillsynsbegäran.docx", "A 18772-2026")</f>
+        <v/>
+      </c>
+      <c r="AD7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 18772-2026 tillsynsbegäran mail.docx", "A 18772-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="15" customHeight="1">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>A 10909-2025</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D8" s="1" t="n">
+        <v>45722</v>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>UPPLANDS-BRO</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="J8" t="n">
+        <v>1</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>2</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2</v>
+      </c>
+      <c r="U8" t="n">
+        <v>2</v>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>Arommusseron
 Fläcknycklar</t>
         </is>
       </c>
-      <c r="W6">
+      <c r="W8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 10909-2025 artfynd.xlsx", "A 10909-2025")</f>
         <v/>
       </c>
-      <c r="X6">
+      <c r="X8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 10909-2025 karta.png", "A 10909-2025")</f>
         <v/>
       </c>
-      <c r="Y6">
+      <c r="Y8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 10909-2025 georefererad karta.tif", "A 10909-2025")</f>
         <v/>
       </c>
-      <c r="AA6">
+      <c r="AA8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 10909-2025 FSC-klagomål.docx", "A 10909-2025")</f>
         <v/>
       </c>
-      <c r="AB6">
+      <c r="AB8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 10909-2025 FSC-klagomål mail.docx", "A 10909-2025")</f>
         <v/>
       </c>
-      <c r="AC6">
+      <c r="AC8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 10909-2025 tillsynsbegäran.docx", "A 10909-2025")</f>
         <v/>
       </c>
-      <c r="AD6">
+      <c r="AD8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 10909-2025 tillsynsbegäran mail.docx", "A 10909-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>A 18772-2026</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>46128</v>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>UPPLANDS-BRO</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="J7" t="n">
-        <v>1</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>1</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>1</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
-        <v>2</v>
-      </c>
-      <c r="T7" t="n">
-        <v>2</v>
-      </c>
-      <c r="U7" t="n">
-        <v>0</v>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>Svedjenäva
-Fläcknycklar</t>
-        </is>
-      </c>
-      <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 18772-2026 artfynd.xlsx", "A 18772-2026")</f>
-        <v/>
-      </c>
-      <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 18772-2026 karta.png", "A 18772-2026")</f>
-        <v/>
-      </c>
-      <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 18772-2026 georefererad karta.tif", "A 18772-2026")</f>
-        <v/>
-      </c>
-      <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 18772-2026 FSC-klagomål.docx", "A 18772-2026")</f>
-        <v/>
-      </c>
-      <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 18772-2026 FSC-klagomål mail.docx", "A 18772-2026")</f>
-        <v/>
-      </c>
-      <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 18772-2026 tillsynsbegäran.docx", "A 18772-2026")</f>
-        <v/>
-      </c>
-      <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 18772-2026 tillsynsbegäran mail.docx", "A 18772-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8" ht="15" customHeight="1">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>A 18790-2026</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D8" s="1" t="n">
-        <v>46128</v>
-      </c>
-      <c r="E8" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>UPPLANDS-BRO</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
-      <c r="I8" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="J8" t="n">
-        <v>2</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" t="n">
-        <v>2</v>
-      </c>
-      <c r="T8" t="n">
-        <v>2</v>
-      </c>
-      <c r="U8" t="n">
-        <v>0</v>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>Fläcknycklar
-Nattviol</t>
-        </is>
-      </c>
-      <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 18790-2026 artfynd.xlsx", "A 18790-2026")</f>
-        <v/>
-      </c>
-      <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 18790-2026 karta.png", "A 18790-2026")</f>
-        <v/>
-      </c>
-      <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 18790-2026 georefererad karta.tif", "A 18790-2026")</f>
-        <v/>
-      </c>
-      <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 18790-2026 FSC-klagomål.docx", "A 18790-2026")</f>
-        <v/>
-      </c>
-      <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 18790-2026 FSC-klagomål mail.docx", "A 18790-2026")</f>
-        <v/>
-      </c>
-      <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 18790-2026 tillsynsbegäran.docx", "A 18790-2026")</f>
-        <v/>
-      </c>
-      <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 18790-2026 tillsynsbegäran mail.docx", "A 18790-2026")</f>
         <v/>
       </c>
     </row>
@@ -1375,7 +1375,7 @@
         <v>44603</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1481,7 +1481,7 @@
         <v>44552</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1569,7 +1569,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 73773-2021</t>
+          <t>A 23099-2024</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>44552</v>
+        <v>45450</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1598,11 +1598,16 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I11" t="n">
-        <v>1.9</v>
+        <v>0.7</v>
       </c>
       <c r="J11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
@@ -1611,7 +1616,7 @@
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
@@ -1623,10 +1628,10 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1639,42 +1644,42 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>Kopparödla</t>
+          <t>Bredbrämad bastardsvärmare</t>
         </is>
       </c>
       <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 73773-2021 artfynd.xlsx", "A 73773-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 23099-2024 artfynd.xlsx", "A 23099-2024")</f>
         <v/>
       </c>
       <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 73773-2021 karta.png", "A 73773-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 23099-2024 karta.png", "A 23099-2024")</f>
         <v/>
       </c>
       <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 73773-2021 georefererad karta.tif", "A 73773-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 23099-2024 georefererad karta.tif", "A 23099-2024")</f>
         <v/>
       </c>
       <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 73773-2021 FSC-klagomål.docx", "A 73773-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 23099-2024 FSC-klagomål.docx", "A 23099-2024")</f>
         <v/>
       </c>
       <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 73773-2021 FSC-klagomål mail.docx", "A 73773-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 23099-2024 FSC-klagomål mail.docx", "A 23099-2024")</f>
         <v/>
       </c>
       <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 73773-2021 tillsynsbegäran.docx", "A 73773-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 23099-2024 tillsynsbegäran.docx", "A 23099-2024")</f>
         <v/>
       </c>
       <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 73773-2021 tillsynsbegäran mail.docx", "A 73773-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 23099-2024 tillsynsbegäran mail.docx", "A 23099-2024")</f>
         <v/>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 12363-2025</t>
+          <t>A 2062-2025</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1688,10 +1693,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45730</v>
+        <v>45671</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1704,16 +1709,16 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>0.8</v>
+        <v>1.9</v>
       </c>
       <c r="J12" t="n">
         <v>1</v>
       </c>
       <c r="K12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
@@ -1728,7 +1733,7 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -1740,46 +1745,50 @@
         <v>1</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 12363-2025 artfynd.xlsx", "A 12363-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 2062-2025 artfynd.xlsx", "A 2062-2025")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 12363-2025 karta.png", "A 12363-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 2062-2025 karta.png", "A 2062-2025")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 12363-2025 georefererad karta.tif", "A 12363-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 2062-2025 georefererad karta.tif", "A 2062-2025")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 12363-2025 FSC-klagomål.docx", "A 12363-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 2062-2025 FSC-klagomål.docx", "A 2062-2025")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 12363-2025 FSC-klagomål mail.docx", "A 12363-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 2062-2025 FSC-klagomål mail.docx", "A 2062-2025")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 12363-2025 tillsynsbegäran.docx", "A 12363-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 2062-2025 tillsynsbegäran.docx", "A 2062-2025")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 12363-2025 tillsynsbegäran mail.docx", "A 12363-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 2062-2025 tillsynsbegäran mail.docx", "A 2062-2025")</f>
+        <v/>
+      </c>
+      <c r="AE12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/fåglar/A 2062-2025 prioriterade fågelarter.docx", "A 2062-2025")</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 53357-2025</t>
+          <t>A 64098-2023</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1793,10 +1802,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45959</v>
+        <v>45279</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1809,22 +1818,22 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>2.4</v>
+        <v>0.3</v>
       </c>
       <c r="J13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -1836,55 +1845,55 @@
         <v>1</v>
       </c>
       <c r="R13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
       </c>
       <c r="T13" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="U13" t="n">
         <v>0</v>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>Bombmurkla</t>
+          <t>Skogsalmsdvärgmal</t>
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 53357-2025 artfynd.xlsx", "A 53357-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 64098-2023 artfynd.xlsx", "A 64098-2023")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 53357-2025 karta.png", "A 53357-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 64098-2023 karta.png", "A 64098-2023")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 53357-2025 georefererad karta.tif", "A 53357-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 64098-2023 georefererad karta.tif", "A 64098-2023")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 53357-2025 FSC-klagomål.docx", "A 53357-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 64098-2023 FSC-klagomål.docx", "A 64098-2023")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 53357-2025 FSC-klagomål mail.docx", "A 53357-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 64098-2023 FSC-klagomål mail.docx", "A 64098-2023")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 53357-2025 tillsynsbegäran.docx", "A 53357-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 64098-2023 tillsynsbegäran.docx", "A 64098-2023")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 53357-2025 tillsynsbegäran mail.docx", "A 53357-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 64098-2023 tillsynsbegäran mail.docx", "A 64098-2023")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 23099-2024</t>
+          <t>A 7955-2023</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1898,10 +1907,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45450</v>
+        <v>44973</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1913,16 +1922,11 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I14" t="n">
-        <v>0.7</v>
+        <v>2.9</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
@@ -1931,10 +1935,10 @@
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -1959,42 +1963,42 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Bredbrämad bastardsvärmare</t>
+          <t>Bombmurkla</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 23099-2024 artfynd.xlsx", "A 23099-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 7955-2023 artfynd.xlsx", "A 7955-2023")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 23099-2024 karta.png", "A 23099-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 7955-2023 karta.png", "A 7955-2023")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 23099-2024 georefererad karta.tif", "A 23099-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 7955-2023 georefererad karta.tif", "A 7955-2023")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 23099-2024 FSC-klagomål.docx", "A 23099-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 7955-2023 FSC-klagomål.docx", "A 7955-2023")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 23099-2024 FSC-klagomål mail.docx", "A 23099-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 7955-2023 FSC-klagomål mail.docx", "A 7955-2023")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 23099-2024 tillsynsbegäran.docx", "A 23099-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 7955-2023 tillsynsbegäran.docx", "A 7955-2023")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 23099-2024 tillsynsbegäran mail.docx", "A 23099-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 7955-2023 tillsynsbegäran mail.docx", "A 7955-2023")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 46438-2023</t>
+          <t>A 12363-2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2008,10 +2012,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45197</v>
+        <v>45730</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2024,13 +2028,13 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="J15" t="n">
         <v>1</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -2039,7 +2043,7 @@
         <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2048,10 +2052,10 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
         <v>1</v>
@@ -2064,42 +2068,42 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Bombmurkla</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 46438-2023 artfynd.xlsx", "A 46438-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 12363-2025 artfynd.xlsx", "A 12363-2025")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 46438-2023 karta.png", "A 46438-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 12363-2025 karta.png", "A 12363-2025")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 46438-2023 georefererad karta.tif", "A 46438-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 12363-2025 georefererad karta.tif", "A 12363-2025")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 46438-2023 FSC-klagomål.docx", "A 46438-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 12363-2025 FSC-klagomål.docx", "A 12363-2025")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 46438-2023 FSC-klagomål mail.docx", "A 46438-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 12363-2025 FSC-klagomål mail.docx", "A 12363-2025")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 46438-2023 tillsynsbegäran.docx", "A 46438-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 12363-2025 tillsynsbegäran.docx", "A 12363-2025")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 46438-2023 tillsynsbegäran mail.docx", "A 46438-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 12363-2025 tillsynsbegäran mail.docx", "A 12363-2025")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 26637-2026</t>
+          <t>A 25561-2025</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2113,10 +2117,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46184</v>
+        <v>45803</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2129,10 +2133,10 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>5.4</v>
+        <v>1.6</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
@@ -2141,10 +2145,10 @@
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2169,42 +2173,42 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Igelkott</t>
+          <t>Bombmurkla</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 26637-2026 artfynd.xlsx", "A 26637-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 25561-2025 artfynd.xlsx", "A 25561-2025")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 26637-2026 karta.png", "A 26637-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 25561-2025 karta.png", "A 25561-2025")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 26637-2026 georefererad karta.tif", "A 26637-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 25561-2025 georefererad karta.tif", "A 25561-2025")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 26637-2026 FSC-klagomål.docx", "A 26637-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 25561-2025 FSC-klagomål.docx", "A 25561-2025")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 26637-2026 FSC-klagomål mail.docx", "A 26637-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 25561-2025 FSC-klagomål mail.docx", "A 25561-2025")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 26637-2026 tillsynsbegäran.docx", "A 26637-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 25561-2025 tillsynsbegäran.docx", "A 25561-2025")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 26637-2026 tillsynsbegäran mail.docx", "A 26637-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 25561-2025 tillsynsbegäran mail.docx", "A 25561-2025")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 2409-2026</t>
+          <t>A 46438-2023</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2218,10 +2222,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46034</v>
+        <v>45197</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2234,7 +2238,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>14.2</v>
+        <v>0.5</v>
       </c>
       <c r="J17" t="n">
         <v>1</v>
@@ -2249,7 +2253,7 @@
         <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2258,10 +2262,10 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
@@ -2274,46 +2278,42 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Havsörn</t>
+          <t>Bombmurkla</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 2409-2026 artfynd.xlsx", "A 2409-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 46438-2023 artfynd.xlsx", "A 46438-2023")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 2409-2026 karta.png", "A 2409-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 46438-2023 karta.png", "A 46438-2023")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 2409-2026 georefererad karta.tif", "A 2409-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 46438-2023 georefererad karta.tif", "A 46438-2023")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 2409-2026 FSC-klagomål.docx", "A 2409-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 46438-2023 FSC-klagomål.docx", "A 46438-2023")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 2409-2026 FSC-klagomål mail.docx", "A 2409-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 46438-2023 FSC-klagomål mail.docx", "A 46438-2023")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 2409-2026 tillsynsbegäran.docx", "A 2409-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 46438-2023 tillsynsbegäran.docx", "A 46438-2023")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 2409-2026 tillsynsbegäran mail.docx", "A 2409-2026")</f>
-        <v/>
-      </c>
-      <c r="AE17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/fåglar/A 2409-2026 prioriterade fågelarter.docx", "A 2409-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 46438-2023 tillsynsbegäran mail.docx", "A 46438-2023")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 26623-2026</t>
+          <t>A 73773-2021</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2327,10 +2327,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46184</v>
+        <v>44552</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2343,16 +2343,16 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>4.6</v>
+        <v>1.9</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
@@ -2367,7 +2367,7 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -2379,46 +2379,46 @@
         <v>1</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Svartöra</t>
+          <t>Kopparödla</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 26623-2026 artfynd.xlsx", "A 26623-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 73773-2021 artfynd.xlsx", "A 73773-2021")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 26623-2026 karta.png", "A 26623-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 73773-2021 karta.png", "A 73773-2021")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 26623-2026 georefererad karta.tif", "A 26623-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 73773-2021 georefererad karta.tif", "A 73773-2021")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 26623-2026 FSC-klagomål.docx", "A 26623-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 73773-2021 FSC-klagomål.docx", "A 73773-2021")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 26623-2026 FSC-klagomål mail.docx", "A 26623-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 73773-2021 FSC-klagomål mail.docx", "A 73773-2021")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 26623-2026 tillsynsbegäran.docx", "A 26623-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 73773-2021 tillsynsbegäran.docx", "A 73773-2021")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 26623-2026 tillsynsbegäran mail.docx", "A 26623-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 73773-2021 tillsynsbegäran mail.docx", "A 73773-2021")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 11447-2025</t>
+          <t>A 53357-2025</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2428,14 +2428,14 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45726</v>
+        <v>45959</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2448,13 +2448,13 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>1.5</v>
+        <v>2.4</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
@@ -2463,7 +2463,7 @@
         <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2472,58 +2472,58 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
       </c>
       <c r="T19" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="U19" t="n">
         <v>0</v>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Myskbock</t>
+          <t>Bombmurkla</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 11447-2025 artfynd.xlsx", "A 11447-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 53357-2025 artfynd.xlsx", "A 53357-2025")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 11447-2025 karta.png", "A 11447-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 53357-2025 karta.png", "A 53357-2025")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 11447-2025 georefererad karta.tif", "A 11447-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 53357-2025 georefererad karta.tif", "A 53357-2025")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 11447-2025 FSC-klagomål.docx", "A 11447-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 53357-2025 FSC-klagomål.docx", "A 53357-2025")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 11447-2025 FSC-klagomål mail.docx", "A 11447-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 53357-2025 FSC-klagomål mail.docx", "A 53357-2025")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 11447-2025 tillsynsbegäran.docx", "A 11447-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 53357-2025 tillsynsbegäran.docx", "A 53357-2025")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 11447-2025 tillsynsbegäran mail.docx", "A 11447-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 53357-2025 tillsynsbegäran mail.docx", "A 53357-2025")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 7955-2023</t>
+          <t>A 2409-2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2537,10 +2537,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>44973</v>
+        <v>46034</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2553,7 +2553,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>2.9</v>
+        <v>14.2</v>
       </c>
       <c r="J20" t="n">
         <v>1</v>
@@ -2568,7 +2568,7 @@
         <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2577,10 +2577,10 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>
@@ -2589,46 +2589,50 @@
         <v>1</v>
       </c>
       <c r="U20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>Bombmurkla</t>
+          <t>Havsörn</t>
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 7955-2023 artfynd.xlsx", "A 7955-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 2409-2026 artfynd.xlsx", "A 2409-2026")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 7955-2023 karta.png", "A 7955-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 2409-2026 karta.png", "A 2409-2026")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 7955-2023 georefererad karta.tif", "A 7955-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 2409-2026 georefererad karta.tif", "A 2409-2026")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 7955-2023 FSC-klagomål.docx", "A 7955-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 2409-2026 FSC-klagomål.docx", "A 2409-2026")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 7955-2023 FSC-klagomål mail.docx", "A 7955-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 2409-2026 FSC-klagomål mail.docx", "A 2409-2026")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 7955-2023 tillsynsbegäran.docx", "A 7955-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 2409-2026 tillsynsbegäran.docx", "A 2409-2026")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 7955-2023 tillsynsbegäran mail.docx", "A 7955-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 2409-2026 tillsynsbegäran mail.docx", "A 2409-2026")</f>
+        <v/>
+      </c>
+      <c r="AE20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/fåglar/A 2409-2026 prioriterade fågelarter.docx", "A 2409-2026")</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 64098-2023</t>
+          <t>A 11447-2025</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2638,14 +2642,14 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45279</v>
+        <v>45726</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2658,16 +2662,16 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>0.3</v>
+        <v>1.5</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
         <v>0</v>
@@ -2682,7 +2686,7 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
         <v>0</v>
@@ -2698,42 +2702,42 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Skogsalmsdvärgmal</t>
+          <t>Myskbock</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 64098-2023 artfynd.xlsx", "A 64098-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 11447-2025 artfynd.xlsx", "A 11447-2025")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 64098-2023 karta.png", "A 64098-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 11447-2025 karta.png", "A 11447-2025")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 64098-2023 georefererad karta.tif", "A 64098-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 11447-2025 georefererad karta.tif", "A 11447-2025")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 64098-2023 FSC-klagomål.docx", "A 64098-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 11447-2025 FSC-klagomål.docx", "A 11447-2025")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 64098-2023 FSC-klagomål mail.docx", "A 64098-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 11447-2025 FSC-klagomål mail.docx", "A 11447-2025")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 64098-2023 tillsynsbegäran.docx", "A 64098-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 11447-2025 tillsynsbegäran.docx", "A 11447-2025")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 64098-2023 tillsynsbegäran mail.docx", "A 64098-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 11447-2025 tillsynsbegäran mail.docx", "A 11447-2025")</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 2062-2025</t>
+          <t>A 26623-2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2747,10 +2751,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45671</v>
+        <v>46184</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2763,10 +2767,10 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>1.9</v>
+        <v>4.6</v>
       </c>
       <c r="J22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
@@ -2799,50 +2803,46 @@
         <v>1</v>
       </c>
       <c r="U22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Svartöra</t>
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 2062-2025 artfynd.xlsx", "A 2062-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 26623-2026 artfynd.xlsx", "A 26623-2026")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 2062-2025 karta.png", "A 2062-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 26623-2026 karta.png", "A 26623-2026")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 2062-2025 georefererad karta.tif", "A 2062-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 26623-2026 georefererad karta.tif", "A 26623-2026")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 2062-2025 FSC-klagomål.docx", "A 2062-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 26623-2026 FSC-klagomål.docx", "A 26623-2026")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 2062-2025 FSC-klagomål mail.docx", "A 2062-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 26623-2026 FSC-klagomål mail.docx", "A 26623-2026")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 2062-2025 tillsynsbegäran.docx", "A 2062-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 26623-2026 tillsynsbegäran.docx", "A 26623-2026")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 2062-2025 tillsynsbegäran mail.docx", "A 2062-2025")</f>
-        <v/>
-      </c>
-      <c r="AE22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/fåglar/A 2062-2025 prioriterade fågelarter.docx", "A 2062-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 26623-2026 tillsynsbegäran mail.docx", "A 26623-2026")</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 25561-2025</t>
+          <t>A 26637-2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2856,10 +2856,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45803</v>
+        <v>46184</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2872,10 +2872,10 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>1.6</v>
+        <v>5.4</v>
       </c>
       <c r="J23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
@@ -2884,10 +2884,10 @@
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -2912,35 +2912,35 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Bombmurkla</t>
+          <t>Igelkott</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 25561-2025 artfynd.xlsx", "A 25561-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 26637-2026 artfynd.xlsx", "A 26637-2026")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 25561-2025 karta.png", "A 25561-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 26637-2026 karta.png", "A 26637-2026")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 25561-2025 georefererad karta.tif", "A 25561-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 26637-2026 georefererad karta.tif", "A 26637-2026")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 25561-2025 FSC-klagomål.docx", "A 25561-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 26637-2026 FSC-klagomål.docx", "A 26637-2026")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 25561-2025 FSC-klagomål mail.docx", "A 25561-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 26637-2026 FSC-klagomål mail.docx", "A 26637-2026")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 25561-2025 tillsynsbegäran.docx", "A 25561-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 26637-2026 tillsynsbegäran.docx", "A 26637-2026")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 25561-2025 tillsynsbegäran mail.docx", "A 25561-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 26637-2026 tillsynsbegäran mail.docx", "A 26637-2026")</f>
         <v/>
       </c>
     </row>
@@ -2964,7 +2964,7 @@
         <v>44558</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3069,7 +3069,7 @@
         <v>44609</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3142,7 +3142,7 @@
         <v>44489</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3220,7 +3220,7 @@
         <v>44546</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3293,7 +3293,7 @@
         <v>44700</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3366,7 +3366,7 @@
         <v>44587</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3439,7 +3439,7 @@
         <v>44655</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3500,7 +3500,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 64105-2023</t>
+          <t>A 23098-2024</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3514,10 +3514,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45279</v>
+        <v>45450</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3529,8 +3529,13 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I31" t="n">
-        <v>2.2</v>
+        <v>1</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3573,7 +3578,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 2602-2024</t>
+          <t>A 23615-2025</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3587,10 +3592,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45313</v>
+        <v>45792</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3603,7 +3608,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0.7</v>
+        <v>1.3</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3646,7 +3651,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 59844-2022</t>
+          <t>A 23627-2025</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3660,10 +3665,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44901</v>
+        <v>45792</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3675,13 +3680,8 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I33" t="n">
-        <v>11.9</v>
+        <v>1.7</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3724,7 +3724,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 23093-2024</t>
+          <t>A 59844-2022</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3738,10 +3738,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45450</v>
+        <v>44901</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3759,7 +3759,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>0.9</v>
+        <v>11.9</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3802,7 +3802,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 3630-2023</t>
+          <t>A 54222-2023</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3816,10 +3816,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44950</v>
+        <v>45225</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3831,8 +3831,13 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I35" t="n">
-        <v>1.4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3875,7 +3880,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 54222-2023</t>
+          <t>A 4338-2023</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3889,10 +3894,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45225</v>
+        <v>44953</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3904,13 +3909,8 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I36" t="n">
-        <v>8.300000000000001</v>
+        <v>1.1</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3953,7 +3953,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 7860-2024</t>
+          <t>A 58011-2021</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3967,10 +3967,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45348</v>
+        <v>44487</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3988,7 +3988,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>1.9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4031,7 +4031,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 27313-2023</t>
+          <t>A 72524-2021</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4045,10 +4045,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45096</v>
+        <v>44546</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4061,7 +4061,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>1.8</v>
+        <v>3.6</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4104,7 +4104,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 64114-2023</t>
+          <t>A 64107-2023</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4121,7 +4121,7 @@
         <v>45279</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4134,7 +4134,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4177,7 +4177,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 50294-2023</t>
+          <t>A 23093-2024</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4191,10 +4191,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45216</v>
+        <v>45450</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4206,8 +4206,13 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I40" t="n">
-        <v>3.7</v>
+        <v>0.9</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4250,7 +4255,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 58011-2021</t>
+          <t>A 59700-2021</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4264,10 +4269,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44487</v>
+        <v>44494</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4285,7 +4290,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>9.199999999999999</v>
+        <v>4.8</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4328,7 +4333,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 21206-2026</t>
+          <t>A 27313-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4342,10 +4347,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>46146</v>
+        <v>45096</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4357,13 +4362,8 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I42" t="n">
-        <v>0.9</v>
+        <v>1.8</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4406,7 +4406,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 64110-2023</t>
+          <t>A 59377-2024</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4420,10 +4420,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45279</v>
+        <v>45638</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4436,7 +4436,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4479,7 +4479,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 23098-2024</t>
+          <t>A 38902-2024</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4493,10 +4493,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45450</v>
+        <v>45547</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4514,7 +4514,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4557,7 +4557,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 24579-2026</t>
+          <t>A 50294-2023</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4571,10 +4571,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>46170</v>
+        <v>45216</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4587,7 +4587,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>2.1</v>
+        <v>3.7</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4630,7 +4630,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 59377-2024</t>
+          <t>A 5264-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4644,10 +4644,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45638</v>
+        <v>44959</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4660,7 +4660,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>0.6</v>
+        <v>5.8</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4703,7 +4703,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 59402-2022</t>
+          <t>A 51587-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4717,10 +4717,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>44906</v>
+        <v>45215</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4732,8 +4732,13 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I47" t="n">
-        <v>1.8</v>
+        <v>2.6</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4776,7 +4781,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 31160-2022</t>
+          <t>A 59848-2022</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4790,10 +4795,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>44770</v>
+        <v>44901</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4805,8 +4810,13 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I48" t="n">
-        <v>3.7</v>
+        <v>10.7</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4849,7 +4859,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 58598-2025</t>
+          <t>A 64110-2023</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4863,10 +4873,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45986</v>
+        <v>45279</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4878,13 +4888,8 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I49" t="n">
-        <v>4.5</v>
+        <v>0.4</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4927,7 +4932,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 26196-2026</t>
+          <t>A 9655-2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4937,14 +4942,14 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>46182</v>
+        <v>46070</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4956,8 +4961,13 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I50" t="n">
-        <v>53.1</v>
+        <v>17.2</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5000,7 +5010,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 26633-2026</t>
+          <t>A 33058-2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5010,14 +5020,14 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>46184</v>
+        <v>46245</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5030,7 +5040,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>0.7</v>
+        <v>1.3</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5073,7 +5083,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 26625-2026</t>
+          <t>A 7275-2022</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5087,10 +5097,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>46184</v>
+        <v>44606</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5102,8 +5112,13 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I52" t="n">
-        <v>5.3</v>
+        <v>9.6</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5146,7 +5161,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 26629-2026</t>
+          <t>A 2602-2024</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5160,10 +5175,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>46184</v>
+        <v>45313</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5176,7 +5191,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>2</v>
+        <v>0.7</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5219,7 +5234,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 3754-2026</t>
+          <t>A 59402-2022</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5233,10 +5248,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>46043</v>
+        <v>44906</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5248,13 +5263,8 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I54" t="n">
-        <v>5.1</v>
+        <v>1.8</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5297,7 +5307,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 5264-2023</t>
+          <t>A 3630-2023</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5311,10 +5321,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44959</v>
+        <v>44950</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5327,7 +5337,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>5.8</v>
+        <v>1.4</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5370,7 +5380,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 28735-2026</t>
+          <t>A 7860-2024</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5384,10 +5394,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>46198</v>
+        <v>45348</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5399,8 +5409,13 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I56" t="n">
-        <v>3.5</v>
+        <v>1.9</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5443,7 +5458,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 28740-2026</t>
+          <t>A 18787-2026</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5457,10 +5472,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>46198</v>
+        <v>46128</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5472,8 +5487,13 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I57" t="n">
-        <v>4.8</v>
+        <v>7.8</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5516,7 +5536,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 9655-2026</t>
+          <t>A 18813-2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5530,10 +5550,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>46070</v>
+        <v>46128</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5551,7 +5571,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>17.2</v>
+        <v>56</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5594,7 +5614,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 28797-2026</t>
+          <t>A 18818-2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5608,10 +5628,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>46198</v>
+        <v>46128</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5623,8 +5643,13 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I59" t="n">
-        <v>2.2</v>
+        <v>17.8</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5667,7 +5692,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 51587-2023</t>
+          <t>A 18778-2026</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5681,10 +5706,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45215</v>
+        <v>46128</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5698,11 +5723,11 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Allmännings- och besparingsskogar</t>
+          <t>Övriga statliga verk och myndigheter</t>
         </is>
       </c>
       <c r="I60" t="n">
-        <v>2.6</v>
+        <v>4.5</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5745,7 +5770,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 72524-2021</t>
+          <t>A 64105-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5759,10 +5784,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>44546</v>
+        <v>45279</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5775,7 +5800,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>3.6</v>
+        <v>2.2</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5818,7 +5843,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 4338-2023</t>
+          <t>A 64114-2023</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5832,10 +5857,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>44953</v>
+        <v>45279</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5848,7 +5873,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>1.1</v>
+        <v>0.4</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5891,7 +5916,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 18778-2026</t>
+          <t>A 21206-2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5905,10 +5930,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>46128</v>
+        <v>46146</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5926,7 +5951,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>4.5</v>
+        <v>0.9</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5969,7 +5994,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 18813-2026</t>
+          <t>A 7112-2025</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5983,10 +6008,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>46128</v>
+        <v>45701</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5998,13 +6023,8 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I64" t="n">
-        <v>56</v>
+        <v>2.4</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6047,7 +6067,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 18818-2026</t>
+          <t>A 24579-2026</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6061,10 +6081,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>46128</v>
+        <v>46170</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6076,13 +6096,8 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I65" t="n">
-        <v>17.8</v>
+        <v>2.1</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6125,7 +6140,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 18787-2026</t>
+          <t>A 58598-2025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6139,10 +6154,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>46128</v>
+        <v>45986</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6160,7 +6175,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>7.8</v>
+        <v>4.5</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6203,7 +6218,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 59848-2022</t>
+          <t>A 31160-2022</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6217,10 +6232,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>44901</v>
+        <v>44770</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6232,13 +6247,8 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I67" t="n">
-        <v>10.7</v>
+        <v>3.7</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6281,7 +6291,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 59700-2021</t>
+          <t>A 26196-2026</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6291,14 +6301,14 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>44494</v>
+        <v>46182</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6310,13 +6320,8 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I68" t="n">
-        <v>4.8</v>
+        <v>53.1</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6359,7 +6364,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 31714-2026</t>
+          <t>A 26625-2026</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6373,10 +6378,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>46226</v>
+        <v>46184</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6389,7 +6394,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6432,7 +6437,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 7275-2022</t>
+          <t>A 26629-2026</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6446,10 +6451,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>44606</v>
+        <v>46184</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6461,13 +6466,8 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I70" t="n">
-        <v>9.6</v>
+        <v>2</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6510,7 +6510,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 33058-2026</t>
+          <t>A 26633-2026</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6520,14 +6520,14 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>46245</v>
+        <v>46184</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6540,7 +6540,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>1.3</v>
+        <v>0.7</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6583,7 +6583,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 64107-2023</t>
+          <t>A 3754-2026</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6597,10 +6597,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45279</v>
+        <v>46043</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6612,8 +6612,13 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I72" t="n">
-        <v>0.3</v>
+        <v>5.1</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6656,7 +6661,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 7112-2025</t>
+          <t>A 28797-2026</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6670,10 +6675,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45701</v>
+        <v>46198</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6686,7 +6691,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6729,7 +6734,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 38902-2024</t>
+          <t>A 28740-2026</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6743,10 +6748,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45547</v>
+        <v>46198</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6758,13 +6763,8 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I74" t="n">
-        <v>0.8</v>
+        <v>4.8</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6807,7 +6807,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 23615-2025</t>
+          <t>A 28735-2026</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6821,10 +6821,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45792</v>
+        <v>46198</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6837,7 +6837,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>1.3</v>
+        <v>3.5</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6880,7 +6880,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 23627-2025</t>
+          <t>A 31714-2026</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6894,10 +6894,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45792</v>
+        <v>46226</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6910,7 +6910,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>1.7</v>
+        <v>5</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6970,7 +6970,7 @@
         <v>44558</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>

--- a/Översikt UPPLANDS-BRO.xlsx
+++ b/Översikt UPPLANDS-BRO.xlsx
@@ -601,7 +601,7 @@
         <v>44481</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -714,7 +714,7 @@
         <v>44552</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -822,7 +822,7 @@
         <v>44552</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -930,7 +930,7 @@
         <v>45232</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1025,7 +1025,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 18790-2026</t>
+          <t>A 10909-2025</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1039,10 +1039,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46128</v>
+        <v>45722</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1056,20 +1056,20 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Övriga statliga verk och myndigheter</t>
+          <t>Allmännings- och besparingsskogar</t>
         </is>
       </c>
       <c r="I6" t="n">
-        <v>5.5</v>
+        <v>11.2</v>
       </c>
       <c r="J6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
@@ -1084,7 +1084,7 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -1096,262 +1096,262 @@
         <v>2</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>Arommusseron
+Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="W6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 10909-2025 artfynd.xlsx", "A 10909-2025")</f>
+        <v/>
+      </c>
+      <c r="X6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 10909-2025 karta.png", "A 10909-2025")</f>
+        <v/>
+      </c>
+      <c r="Y6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 10909-2025 georefererad karta.tif", "A 10909-2025")</f>
+        <v/>
+      </c>
+      <c r="AA6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 10909-2025 FSC-klagomål.docx", "A 10909-2025")</f>
+        <v/>
+      </c>
+      <c r="AB6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 10909-2025 FSC-klagomål mail.docx", "A 10909-2025")</f>
+        <v/>
+      </c>
+      <c r="AC6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 10909-2025 tillsynsbegäran.docx", "A 10909-2025")</f>
+        <v/>
+      </c>
+      <c r="AD6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 10909-2025 tillsynsbegäran mail.docx", "A 10909-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>A 18772-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>46128</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>UPPLANDS-BRO</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>2</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>Svedjenäva
+Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="W7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 18772-2026 artfynd.xlsx", "A 18772-2026")</f>
+        <v/>
+      </c>
+      <c r="X7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 18772-2026 karta.png", "A 18772-2026")</f>
+        <v/>
+      </c>
+      <c r="Y7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 18772-2026 georefererad karta.tif", "A 18772-2026")</f>
+        <v/>
+      </c>
+      <c r="AA7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 18772-2026 FSC-klagomål.docx", "A 18772-2026")</f>
+        <v/>
+      </c>
+      <c r="AB7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 18772-2026 FSC-klagomål mail.docx", "A 18772-2026")</f>
+        <v/>
+      </c>
+      <c r="AC7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 18772-2026 tillsynsbegäran.docx", "A 18772-2026")</f>
+        <v/>
+      </c>
+      <c r="AD7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 18772-2026 tillsynsbegäran mail.docx", "A 18772-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="15" customHeight="1">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>A 18790-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D8" s="1" t="n">
+        <v>46128</v>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>UPPLANDS-BRO</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="J8" t="n">
+        <v>2</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>2</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>Fläcknycklar
 Nattviol</t>
         </is>
       </c>
-      <c r="W6">
+      <c r="W8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 18790-2026 artfynd.xlsx", "A 18790-2026")</f>
         <v/>
       </c>
-      <c r="X6">
+      <c r="X8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 18790-2026 karta.png", "A 18790-2026")</f>
         <v/>
       </c>
-      <c r="Y6">
+      <c r="Y8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 18790-2026 georefererad karta.tif", "A 18790-2026")</f>
         <v/>
       </c>
-      <c r="AA6">
+      <c r="AA8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 18790-2026 FSC-klagomål.docx", "A 18790-2026")</f>
         <v/>
       </c>
-      <c r="AB6">
+      <c r="AB8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 18790-2026 FSC-klagomål mail.docx", "A 18790-2026")</f>
         <v/>
       </c>
-      <c r="AC6">
+      <c r="AC8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 18790-2026 tillsynsbegäran.docx", "A 18790-2026")</f>
         <v/>
       </c>
-      <c r="AD6">
+      <c r="AD8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 18790-2026 tillsynsbegäran mail.docx", "A 18790-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>A 18772-2026</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>46128</v>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>UPPLANDS-BRO</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="J7" t="n">
-        <v>1</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>1</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>1</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
-        <v>2</v>
-      </c>
-      <c r="T7" t="n">
-        <v>2</v>
-      </c>
-      <c r="U7" t="n">
-        <v>0</v>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>Svedjenäva
-Fläcknycklar</t>
-        </is>
-      </c>
-      <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 18772-2026 artfynd.xlsx", "A 18772-2026")</f>
-        <v/>
-      </c>
-      <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 18772-2026 karta.png", "A 18772-2026")</f>
-        <v/>
-      </c>
-      <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 18772-2026 georefererad karta.tif", "A 18772-2026")</f>
-        <v/>
-      </c>
-      <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 18772-2026 FSC-klagomål.docx", "A 18772-2026")</f>
-        <v/>
-      </c>
-      <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 18772-2026 FSC-klagomål mail.docx", "A 18772-2026")</f>
-        <v/>
-      </c>
-      <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 18772-2026 tillsynsbegäran.docx", "A 18772-2026")</f>
-        <v/>
-      </c>
-      <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 18772-2026 tillsynsbegäran mail.docx", "A 18772-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8" ht="15" customHeight="1">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>A 10909-2025</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D8" s="1" t="n">
-        <v>45722</v>
-      </c>
-      <c r="E8" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>UPPLANDS-BRO</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
-      <c r="I8" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="J8" t="n">
-        <v>1</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>1</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>1</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" t="n">
-        <v>2</v>
-      </c>
-      <c r="T8" t="n">
-        <v>2</v>
-      </c>
-      <c r="U8" t="n">
-        <v>2</v>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>Arommusseron
-Fläcknycklar</t>
-        </is>
-      </c>
-      <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 10909-2025 artfynd.xlsx", "A 10909-2025")</f>
-        <v/>
-      </c>
-      <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 10909-2025 karta.png", "A 10909-2025")</f>
-        <v/>
-      </c>
-      <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 10909-2025 georefererad karta.tif", "A 10909-2025")</f>
-        <v/>
-      </c>
-      <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 10909-2025 FSC-klagomål.docx", "A 10909-2025")</f>
-        <v/>
-      </c>
-      <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 10909-2025 FSC-klagomål mail.docx", "A 10909-2025")</f>
-        <v/>
-      </c>
-      <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 10909-2025 tillsynsbegäran.docx", "A 10909-2025")</f>
-        <v/>
-      </c>
-      <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 10909-2025 tillsynsbegäran mail.docx", "A 10909-2025")</f>
         <v/>
       </c>
     </row>
@@ -1375,7 +1375,7 @@
         <v>44603</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1481,7 +1481,7 @@
         <v>44552</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1569,7 +1569,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 23099-2024</t>
+          <t>A 73773-2021</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45450</v>
+        <v>44552</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1598,16 +1598,11 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I11" t="n">
-        <v>0.7</v>
+        <v>1.9</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
@@ -1616,7 +1611,7 @@
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
@@ -1628,10 +1623,10 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1644,42 +1639,42 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>Bredbrämad bastardsvärmare</t>
+          <t>Kopparödla</t>
         </is>
       </c>
       <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 23099-2024 artfynd.xlsx", "A 23099-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 73773-2021 artfynd.xlsx", "A 73773-2021")</f>
         <v/>
       </c>
       <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 23099-2024 karta.png", "A 23099-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 73773-2021 karta.png", "A 73773-2021")</f>
         <v/>
       </c>
       <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 23099-2024 georefererad karta.tif", "A 23099-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 73773-2021 georefererad karta.tif", "A 73773-2021")</f>
         <v/>
       </c>
       <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 23099-2024 FSC-klagomål.docx", "A 23099-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 73773-2021 FSC-klagomål.docx", "A 73773-2021")</f>
         <v/>
       </c>
       <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 23099-2024 FSC-klagomål mail.docx", "A 23099-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 73773-2021 FSC-klagomål mail.docx", "A 73773-2021")</f>
         <v/>
       </c>
       <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 23099-2024 tillsynsbegäran.docx", "A 23099-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 73773-2021 tillsynsbegäran.docx", "A 73773-2021")</f>
         <v/>
       </c>
       <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 23099-2024 tillsynsbegäran mail.docx", "A 23099-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 73773-2021 tillsynsbegäran mail.docx", "A 73773-2021")</f>
         <v/>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 2062-2025</t>
+          <t>A 12363-2025</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1693,10 +1688,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45671</v>
+        <v>45730</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1709,16 +1704,16 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>1.9</v>
+        <v>0.8</v>
       </c>
       <c r="J12" t="n">
         <v>1</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
@@ -1733,7 +1728,7 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -1745,50 +1740,46 @@
         <v>1</v>
       </c>
       <c r="U12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 2062-2025 artfynd.xlsx", "A 2062-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 12363-2025 artfynd.xlsx", "A 12363-2025")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 2062-2025 karta.png", "A 2062-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 12363-2025 karta.png", "A 12363-2025")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 2062-2025 georefererad karta.tif", "A 2062-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 12363-2025 georefererad karta.tif", "A 12363-2025")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 2062-2025 FSC-klagomål.docx", "A 2062-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 12363-2025 FSC-klagomål.docx", "A 12363-2025")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 2062-2025 FSC-klagomål mail.docx", "A 2062-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 12363-2025 FSC-klagomål mail.docx", "A 12363-2025")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 2062-2025 tillsynsbegäran.docx", "A 2062-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 12363-2025 tillsynsbegäran.docx", "A 12363-2025")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 2062-2025 tillsynsbegäran mail.docx", "A 2062-2025")</f>
-        <v/>
-      </c>
-      <c r="AE12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/fåglar/A 2062-2025 prioriterade fågelarter.docx", "A 2062-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 12363-2025 tillsynsbegäran mail.docx", "A 12363-2025")</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 64098-2023</t>
+          <t>A 53357-2025</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1802,10 +1793,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45279</v>
+        <v>45959</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1818,22 +1809,22 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>0.3</v>
+        <v>2.4</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -1845,55 +1836,55 @@
         <v>1</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
       </c>
       <c r="T13" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="U13" t="n">
         <v>0</v>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>Skogsalmsdvärgmal</t>
+          <t>Bombmurkla</t>
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 64098-2023 artfynd.xlsx", "A 64098-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 53357-2025 artfynd.xlsx", "A 53357-2025")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 64098-2023 karta.png", "A 64098-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 53357-2025 karta.png", "A 53357-2025")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 64098-2023 georefererad karta.tif", "A 64098-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 53357-2025 georefererad karta.tif", "A 53357-2025")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 64098-2023 FSC-klagomål.docx", "A 64098-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 53357-2025 FSC-klagomål.docx", "A 53357-2025")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 64098-2023 FSC-klagomål mail.docx", "A 64098-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 53357-2025 FSC-klagomål mail.docx", "A 53357-2025")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 64098-2023 tillsynsbegäran.docx", "A 64098-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 53357-2025 tillsynsbegäran.docx", "A 53357-2025")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 64098-2023 tillsynsbegäran mail.docx", "A 64098-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 53357-2025 tillsynsbegäran mail.docx", "A 53357-2025")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 7955-2023</t>
+          <t>A 23099-2024</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1907,10 +1898,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>44973</v>
+        <v>45450</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1922,11 +1913,16 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I14" t="n">
-        <v>2.9</v>
+        <v>0.7</v>
       </c>
       <c r="J14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
@@ -1935,10 +1931,10 @@
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -1963,42 +1959,42 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Bombmurkla</t>
+          <t>Bredbrämad bastardsvärmare</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 7955-2023 artfynd.xlsx", "A 7955-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 23099-2024 artfynd.xlsx", "A 23099-2024")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 7955-2023 karta.png", "A 7955-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 23099-2024 karta.png", "A 23099-2024")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 7955-2023 georefererad karta.tif", "A 7955-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 23099-2024 georefererad karta.tif", "A 23099-2024")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 7955-2023 FSC-klagomål.docx", "A 7955-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 23099-2024 FSC-klagomål.docx", "A 23099-2024")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 7955-2023 FSC-klagomål mail.docx", "A 7955-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 23099-2024 FSC-klagomål mail.docx", "A 23099-2024")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 7955-2023 tillsynsbegäran.docx", "A 7955-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 23099-2024 tillsynsbegäran.docx", "A 23099-2024")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 7955-2023 tillsynsbegäran mail.docx", "A 7955-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 23099-2024 tillsynsbegäran mail.docx", "A 23099-2024")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 12363-2025</t>
+          <t>A 46438-2023</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2012,10 +2008,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45730</v>
+        <v>45197</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2028,13 +2024,13 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="J15" t="n">
         <v>1</v>
       </c>
       <c r="K15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -2043,7 +2039,7 @@
         <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2052,10 +2048,10 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S15" t="n">
         <v>1</v>
@@ -2068,42 +2064,42 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Bombmurkla</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 12363-2025 artfynd.xlsx", "A 12363-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 46438-2023 artfynd.xlsx", "A 46438-2023")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 12363-2025 karta.png", "A 12363-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 46438-2023 karta.png", "A 46438-2023")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 12363-2025 georefererad karta.tif", "A 12363-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 46438-2023 georefererad karta.tif", "A 46438-2023")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 12363-2025 FSC-klagomål.docx", "A 12363-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 46438-2023 FSC-klagomål.docx", "A 46438-2023")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 12363-2025 FSC-klagomål mail.docx", "A 12363-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 46438-2023 FSC-klagomål mail.docx", "A 46438-2023")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 12363-2025 tillsynsbegäran.docx", "A 12363-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 46438-2023 tillsynsbegäran.docx", "A 46438-2023")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 12363-2025 tillsynsbegäran mail.docx", "A 12363-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 46438-2023 tillsynsbegäran mail.docx", "A 46438-2023")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 25561-2025</t>
+          <t>A 2409-2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2117,10 +2113,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45803</v>
+        <v>46034</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2133,7 +2129,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>1.6</v>
+        <v>14.2</v>
       </c>
       <c r="J16" t="n">
         <v>1</v>
@@ -2148,7 +2144,7 @@
         <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2157,10 +2153,10 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
@@ -2173,42 +2169,46 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Bombmurkla</t>
+          <t>Havsörn</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 25561-2025 artfynd.xlsx", "A 25561-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 2409-2026 artfynd.xlsx", "A 2409-2026")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 25561-2025 karta.png", "A 25561-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 2409-2026 karta.png", "A 2409-2026")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 25561-2025 georefererad karta.tif", "A 25561-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 2409-2026 georefererad karta.tif", "A 2409-2026")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 25561-2025 FSC-klagomål.docx", "A 25561-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 2409-2026 FSC-klagomål.docx", "A 2409-2026")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 25561-2025 FSC-klagomål mail.docx", "A 25561-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 2409-2026 FSC-klagomål mail.docx", "A 2409-2026")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 25561-2025 tillsynsbegäran.docx", "A 25561-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 2409-2026 tillsynsbegäran.docx", "A 2409-2026")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 25561-2025 tillsynsbegäran mail.docx", "A 25561-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 2409-2026 tillsynsbegäran mail.docx", "A 2409-2026")</f>
+        <v/>
+      </c>
+      <c r="AE16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/fåglar/A 2409-2026 prioriterade fågelarter.docx", "A 2409-2026")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 46438-2023</t>
+          <t>A 11447-2025</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2218,14 +2218,14 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45197</v>
+        <v>45726</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2238,13 +2238,13 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="J17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
@@ -2253,7 +2253,7 @@
         <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2262,10 +2262,10 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
@@ -2278,42 +2278,42 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Bombmurkla</t>
+          <t>Myskbock</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 46438-2023 artfynd.xlsx", "A 46438-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 11447-2025 artfynd.xlsx", "A 11447-2025")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 46438-2023 karta.png", "A 46438-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 11447-2025 karta.png", "A 11447-2025")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 46438-2023 georefererad karta.tif", "A 46438-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 11447-2025 georefererad karta.tif", "A 11447-2025")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 46438-2023 FSC-klagomål.docx", "A 46438-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 11447-2025 FSC-klagomål.docx", "A 11447-2025")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 46438-2023 FSC-klagomål mail.docx", "A 46438-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 11447-2025 FSC-klagomål mail.docx", "A 11447-2025")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 46438-2023 tillsynsbegäran.docx", "A 46438-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 11447-2025 tillsynsbegäran.docx", "A 11447-2025")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 46438-2023 tillsynsbegäran mail.docx", "A 46438-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 11447-2025 tillsynsbegäran mail.docx", "A 11447-2025")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 73773-2021</t>
+          <t>A 7955-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2327,10 +2327,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>44552</v>
+        <v>44973</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2343,7 +2343,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>1.9</v>
+        <v>2.9</v>
       </c>
       <c r="J18" t="n">
         <v>1</v>
@@ -2358,7 +2358,7 @@
         <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2367,10 +2367,10 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
@@ -2383,42 +2383,42 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Kopparödla</t>
+          <t>Bombmurkla</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 73773-2021 artfynd.xlsx", "A 73773-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 7955-2023 artfynd.xlsx", "A 7955-2023")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 73773-2021 karta.png", "A 73773-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 7955-2023 karta.png", "A 7955-2023")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 73773-2021 georefererad karta.tif", "A 73773-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 7955-2023 georefererad karta.tif", "A 7955-2023")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 73773-2021 FSC-klagomål.docx", "A 73773-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 7955-2023 FSC-klagomål.docx", "A 7955-2023")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 73773-2021 FSC-klagomål mail.docx", "A 73773-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 7955-2023 FSC-klagomål mail.docx", "A 7955-2023")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 73773-2021 tillsynsbegäran.docx", "A 73773-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 7955-2023 tillsynsbegäran.docx", "A 7955-2023")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 73773-2021 tillsynsbegäran mail.docx", "A 73773-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 7955-2023 tillsynsbegäran mail.docx", "A 7955-2023")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 53357-2025</t>
+          <t>A 26637-2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2432,10 +2432,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45959</v>
+        <v>46184</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2448,10 +2448,10 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>2.4</v>
+        <v>5.4</v>
       </c>
       <c r="J19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
@@ -2460,10 +2460,10 @@
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2481,49 +2481,49 @@
         <v>1</v>
       </c>
       <c r="T19" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="U19" t="n">
         <v>0</v>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Bombmurkla</t>
+          <t>Igelkott</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 53357-2025 artfynd.xlsx", "A 53357-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 26637-2026 artfynd.xlsx", "A 26637-2026")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 53357-2025 karta.png", "A 53357-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 26637-2026 karta.png", "A 26637-2026")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 53357-2025 georefererad karta.tif", "A 53357-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 26637-2026 georefererad karta.tif", "A 26637-2026")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 53357-2025 FSC-klagomål.docx", "A 53357-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 26637-2026 FSC-klagomål.docx", "A 26637-2026")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 53357-2025 FSC-klagomål mail.docx", "A 53357-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 26637-2026 FSC-klagomål mail.docx", "A 26637-2026")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 53357-2025 tillsynsbegäran.docx", "A 53357-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 26637-2026 tillsynsbegäran.docx", "A 26637-2026")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 53357-2025 tillsynsbegäran mail.docx", "A 53357-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 26637-2026 tillsynsbegäran mail.docx", "A 26637-2026")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 2409-2026</t>
+          <t>A 26623-2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2537,10 +2537,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46034</v>
+        <v>46184</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2553,16 +2553,16 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>14.2</v>
+        <v>4.6</v>
       </c>
       <c r="J20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M20" t="n">
         <v>0</v>
@@ -2577,7 +2577,7 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
@@ -2593,46 +2593,42 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>Havsörn</t>
+          <t>Svartöra</t>
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 2409-2026 artfynd.xlsx", "A 2409-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 26623-2026 artfynd.xlsx", "A 26623-2026")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 2409-2026 karta.png", "A 2409-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 26623-2026 karta.png", "A 26623-2026")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 2409-2026 georefererad karta.tif", "A 2409-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 26623-2026 georefererad karta.tif", "A 26623-2026")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 2409-2026 FSC-klagomål.docx", "A 2409-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 26623-2026 FSC-klagomål.docx", "A 26623-2026")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 2409-2026 FSC-klagomål mail.docx", "A 2409-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 26623-2026 FSC-klagomål mail.docx", "A 26623-2026")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 2409-2026 tillsynsbegäran.docx", "A 2409-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 26623-2026 tillsynsbegäran.docx", "A 26623-2026")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 2409-2026 tillsynsbegäran mail.docx", "A 2409-2026")</f>
-        <v/>
-      </c>
-      <c r="AE20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/fåglar/A 2409-2026 prioriterade fågelarter.docx", "A 2409-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 26623-2026 tillsynsbegäran mail.docx", "A 26623-2026")</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 11447-2025</t>
+          <t>A 64098-2023</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2642,14 +2638,14 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45726</v>
+        <v>45279</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2662,16 +2658,16 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>1.5</v>
+        <v>0.3</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M21" t="n">
         <v>0</v>
@@ -2686,7 +2682,7 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R21" t="n">
         <v>0</v>
@@ -2702,42 +2698,42 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Myskbock</t>
+          <t>Skogsalmsdvärgmal</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 11447-2025 artfynd.xlsx", "A 11447-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 64098-2023 artfynd.xlsx", "A 64098-2023")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 11447-2025 karta.png", "A 11447-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 64098-2023 karta.png", "A 64098-2023")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 11447-2025 georefererad karta.tif", "A 11447-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 64098-2023 georefererad karta.tif", "A 64098-2023")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 11447-2025 FSC-klagomål.docx", "A 11447-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 64098-2023 FSC-klagomål.docx", "A 64098-2023")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 11447-2025 FSC-klagomål mail.docx", "A 11447-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 64098-2023 FSC-klagomål mail.docx", "A 64098-2023")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 11447-2025 tillsynsbegäran.docx", "A 11447-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 64098-2023 tillsynsbegäran.docx", "A 64098-2023")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 11447-2025 tillsynsbegäran mail.docx", "A 11447-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 64098-2023 tillsynsbegäran mail.docx", "A 64098-2023")</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 26623-2026</t>
+          <t>A 2062-2025</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2751,10 +2747,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46184</v>
+        <v>45671</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2767,10 +2763,10 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>4.6</v>
+        <v>1.9</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
@@ -2803,46 +2799,50 @@
         <v>1</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>Svartöra</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 26623-2026 artfynd.xlsx", "A 26623-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 2062-2025 artfynd.xlsx", "A 2062-2025")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 26623-2026 karta.png", "A 26623-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 2062-2025 karta.png", "A 2062-2025")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 26623-2026 georefererad karta.tif", "A 26623-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 2062-2025 georefererad karta.tif", "A 2062-2025")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 26623-2026 FSC-klagomål.docx", "A 26623-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 2062-2025 FSC-klagomål.docx", "A 2062-2025")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 26623-2026 FSC-klagomål mail.docx", "A 26623-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 2062-2025 FSC-klagomål mail.docx", "A 2062-2025")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 26623-2026 tillsynsbegäran.docx", "A 26623-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 2062-2025 tillsynsbegäran.docx", "A 2062-2025")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 26623-2026 tillsynsbegäran mail.docx", "A 26623-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 2062-2025 tillsynsbegäran mail.docx", "A 2062-2025")</f>
+        <v/>
+      </c>
+      <c r="AE22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/fåglar/A 2062-2025 prioriterade fågelarter.docx", "A 2062-2025")</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 26637-2026</t>
+          <t>A 25561-2025</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2856,10 +2856,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46184</v>
+        <v>45803</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2872,10 +2872,10 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>5.4</v>
+        <v>1.6</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
@@ -2884,10 +2884,10 @@
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -2912,35 +2912,35 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Igelkott</t>
+          <t>Bombmurkla</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 26637-2026 artfynd.xlsx", "A 26637-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 25561-2025 artfynd.xlsx", "A 25561-2025")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 26637-2026 karta.png", "A 26637-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 25561-2025 karta.png", "A 25561-2025")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 26637-2026 georefererad karta.tif", "A 26637-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 25561-2025 georefererad karta.tif", "A 25561-2025")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 26637-2026 FSC-klagomål.docx", "A 26637-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 25561-2025 FSC-klagomål.docx", "A 25561-2025")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 26637-2026 FSC-klagomål mail.docx", "A 26637-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 25561-2025 FSC-klagomål mail.docx", "A 25561-2025")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 26637-2026 tillsynsbegäran.docx", "A 26637-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 25561-2025 tillsynsbegäran.docx", "A 25561-2025")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 26637-2026 tillsynsbegäran mail.docx", "A 26637-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 25561-2025 tillsynsbegäran mail.docx", "A 25561-2025")</f>
         <v/>
       </c>
     </row>
@@ -2964,7 +2964,7 @@
         <v>44558</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3069,7 +3069,7 @@
         <v>44609</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3142,7 +3142,7 @@
         <v>44489</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3220,7 +3220,7 @@
         <v>44546</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3293,7 +3293,7 @@
         <v>44700</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3366,7 +3366,7 @@
         <v>44587</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3439,7 +3439,7 @@
         <v>44655</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3500,7 +3500,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 23098-2024</t>
+          <t>A 64105-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3514,10 +3514,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45450</v>
+        <v>45279</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3529,13 +3529,8 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I31" t="n">
-        <v>1</v>
+        <v>2.2</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3578,7 +3573,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 23615-2025</t>
+          <t>A 2602-2024</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3592,10 +3587,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45792</v>
+        <v>45313</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3608,7 +3603,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>1.3</v>
+        <v>0.7</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3651,7 +3646,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 23627-2025</t>
+          <t>A 59844-2022</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3665,10 +3660,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45792</v>
+        <v>44901</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3680,8 +3675,13 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I33" t="n">
-        <v>1.7</v>
+        <v>11.9</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3724,7 +3724,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 59844-2022</t>
+          <t>A 23093-2024</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3738,10 +3738,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44901</v>
+        <v>45450</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3759,7 +3759,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>11.9</v>
+        <v>0.9</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3802,7 +3802,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 54222-2023</t>
+          <t>A 3630-2023</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3816,10 +3816,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45225</v>
+        <v>44950</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3831,13 +3831,8 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I35" t="n">
-        <v>8.300000000000001</v>
+        <v>1.4</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3880,7 +3875,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 4338-2023</t>
+          <t>A 54222-2023</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3894,10 +3889,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44953</v>
+        <v>45225</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3909,8 +3904,13 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I36" t="n">
-        <v>1.1</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3953,7 +3953,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 58011-2021</t>
+          <t>A 7860-2024</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3967,10 +3967,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44487</v>
+        <v>45348</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3988,7 +3988,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>9.199999999999999</v>
+        <v>1.9</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4031,7 +4031,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 72524-2021</t>
+          <t>A 27313-2023</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4045,10 +4045,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44546</v>
+        <v>45096</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4061,7 +4061,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>3.6</v>
+        <v>1.8</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4104,7 +4104,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 64107-2023</t>
+          <t>A 64114-2023</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4121,7 +4121,7 @@
         <v>45279</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4134,7 +4134,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4177,7 +4177,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 23093-2024</t>
+          <t>A 50294-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4191,10 +4191,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45450</v>
+        <v>45216</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4206,13 +4206,8 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I40" t="n">
-        <v>0.9</v>
+        <v>3.7</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4255,7 +4250,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 59700-2021</t>
+          <t>A 58011-2021</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4269,10 +4264,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44494</v>
+        <v>44487</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4290,7 +4285,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>4.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4333,7 +4328,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 27313-2023</t>
+          <t>A 64110-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4347,10 +4342,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45096</v>
+        <v>45279</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4363,7 +4358,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1.8</v>
+        <v>0.4</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4406,7 +4401,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 59377-2024</t>
+          <t>A 23098-2024</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4420,10 +4415,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45638</v>
+        <v>45450</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4435,8 +4430,13 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I43" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4479,7 +4479,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 38902-2024</t>
+          <t>A 59377-2024</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4493,10 +4493,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45547</v>
+        <v>45638</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4508,13 +4508,8 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I44" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4557,7 +4552,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 50294-2023</t>
+          <t>A 21206-2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4571,10 +4566,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45216</v>
+        <v>46146</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4586,8 +4581,13 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I45" t="n">
-        <v>3.7</v>
+        <v>0.9</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4630,7 +4630,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 5264-2023</t>
+          <t>A 59402-2022</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4644,10 +4644,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44959</v>
+        <v>44906</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4660,7 +4660,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>5.8</v>
+        <v>1.8</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4703,7 +4703,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 51587-2023</t>
+          <t>A 5264-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4717,10 +4717,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45215</v>
+        <v>44959</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4732,13 +4732,8 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I47" t="n">
-        <v>2.6</v>
+        <v>5.8</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4781,7 +4776,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 59848-2022</t>
+          <t>A 51587-2023</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4795,10 +4790,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>44901</v>
+        <v>45215</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4812,11 +4807,11 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Övriga statliga verk och myndigheter</t>
+          <t>Allmännings- och besparingsskogar</t>
         </is>
       </c>
       <c r="I48" t="n">
-        <v>10.7</v>
+        <v>2.6</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4859,7 +4854,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 64110-2023</t>
+          <t>A 24579-2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4873,10 +4868,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45279</v>
+        <v>46170</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4889,7 +4884,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>0.4</v>
+        <v>2.1</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4949,7 +4944,7 @@
         <v>46070</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5010,7 +5005,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 33058-2026</t>
+          <t>A 31160-2022</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5020,14 +5015,14 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>46245</v>
+        <v>44770</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5040,7 +5035,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>1.3</v>
+        <v>3.7</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5083,7 +5078,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 7275-2022</t>
+          <t>A 72524-2021</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5097,10 +5092,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>44606</v>
+        <v>44546</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5112,13 +5107,8 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I52" t="n">
-        <v>9.6</v>
+        <v>3.6</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5161,7 +5151,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 2602-2024</t>
+          <t>A 58598-2025</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5175,10 +5165,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45313</v>
+        <v>45986</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5190,8 +5180,13 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I53" t="n">
-        <v>0.7</v>
+        <v>4.5</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5234,7 +5229,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 59402-2022</t>
+          <t>A 26196-2026</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5244,14 +5239,14 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>44906</v>
+        <v>46182</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5264,7 +5259,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>1.8</v>
+        <v>53.1</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5307,7 +5302,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 3630-2023</t>
+          <t>A 26633-2026</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5321,10 +5316,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44950</v>
+        <v>46184</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5337,7 +5332,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>1.4</v>
+        <v>0.7</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5380,7 +5375,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 7860-2024</t>
+          <t>A 26625-2026</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5394,10 +5389,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45348</v>
+        <v>46184</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5409,13 +5404,8 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I56" t="n">
-        <v>1.9</v>
+        <v>5.3</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5458,7 +5448,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 18787-2026</t>
+          <t>A 26629-2026</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5472,10 +5462,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>46128</v>
+        <v>46184</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5487,13 +5477,8 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I57" t="n">
-        <v>7.8</v>
+        <v>2</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5536,7 +5521,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 18813-2026</t>
+          <t>A 4338-2023</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5550,10 +5535,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>46128</v>
+        <v>44953</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5565,13 +5550,8 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I58" t="n">
-        <v>56</v>
+        <v>1.1</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5614,7 +5594,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 18818-2026</t>
+          <t>A 59848-2022</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5628,10 +5608,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>46128</v>
+        <v>44901</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5649,7 +5629,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>17.8</v>
+        <v>10.7</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5709,7 +5689,7 @@
         <v>46128</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5770,7 +5750,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 64105-2023</t>
+          <t>A 18813-2026</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5784,10 +5764,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45279</v>
+        <v>46128</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5799,8 +5779,13 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I61" t="n">
-        <v>2.2</v>
+        <v>56</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5843,7 +5828,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 64114-2023</t>
+          <t>A 18818-2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5857,10 +5842,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45279</v>
+        <v>46128</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5872,8 +5857,13 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I62" t="n">
-        <v>0.4</v>
+        <v>17.8</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5916,7 +5906,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 21206-2026</t>
+          <t>A 18787-2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5930,10 +5920,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>46146</v>
+        <v>46128</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5951,7 +5941,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>0.9</v>
+        <v>7.8</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5994,7 +5984,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 7112-2025</t>
+          <t>A 3754-2026</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6008,10 +5998,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45701</v>
+        <v>46043</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6023,8 +6013,13 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I64" t="n">
-        <v>2.4</v>
+        <v>5.1</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6067,7 +6062,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 24579-2026</t>
+          <t>A 59700-2021</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6081,10 +6076,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>46170</v>
+        <v>44494</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6096,8 +6091,13 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I65" t="n">
-        <v>2.1</v>
+        <v>4.8</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6140,7 +6140,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 58598-2025</t>
+          <t>A 28735-2026</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6154,10 +6154,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45986</v>
+        <v>46198</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6169,13 +6169,8 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I66" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6218,7 +6213,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 31160-2022</t>
+          <t>A 28740-2026</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6232,10 +6227,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>44770</v>
+        <v>46198</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6248,7 +6243,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>3.7</v>
+        <v>4.8</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6291,7 +6286,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 26196-2026</t>
+          <t>A 28797-2026</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6301,14 +6296,14 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>46182</v>
+        <v>46198</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6321,7 +6316,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>53.1</v>
+        <v>2.2</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6364,7 +6359,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 26625-2026</t>
+          <t>A 31714-2026</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6378,10 +6373,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>46184</v>
+        <v>46226</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6394,7 +6389,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6437,7 +6432,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 26629-2026</t>
+          <t>A 7275-2022</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6451,10 +6446,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>46184</v>
+        <v>44606</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6466,8 +6461,13 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I70" t="n">
-        <v>2</v>
+        <v>9.6</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6510,7 +6510,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 26633-2026</t>
+          <t>A 64107-2023</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6524,10 +6524,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>46184</v>
+        <v>45279</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6540,7 +6540,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>0.7</v>
+        <v>0.3</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6583,7 +6583,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 3754-2026</t>
+          <t>A 7112-2025</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6597,10 +6597,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>46043</v>
+        <v>45701</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6612,13 +6612,8 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I72" t="n">
-        <v>5.1</v>
+        <v>2.4</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6661,7 +6656,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 28797-2026</t>
+          <t>A 38902-2024</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6675,10 +6670,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>46198</v>
+        <v>45547</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6690,8 +6685,13 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I73" t="n">
-        <v>2.2</v>
+        <v>0.8</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6734,7 +6734,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 28740-2026</t>
+          <t>A 23615-2025</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6748,10 +6748,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>46198</v>
+        <v>45792</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6764,7 +6764,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>4.8</v>
+        <v>1.3</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6807,7 +6807,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 28735-2026</t>
+          <t>A 23627-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6821,10 +6821,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>46198</v>
+        <v>45792</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6837,7 +6837,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>3.5</v>
+        <v>1.7</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6880,7 +6880,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 31714-2026</t>
+          <t>A 33058-2026</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6890,14 +6890,14 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>46226</v>
+        <v>46245</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6910,7 +6910,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>5</v>
+        <v>1.3</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6970,7 +6970,7 @@
         <v>44558</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>

--- a/Översikt UPPLANDS-BRO.xlsx
+++ b/Översikt UPPLANDS-BRO.xlsx
@@ -601,7 +601,7 @@
         <v>44481</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -714,7 +714,7 @@
         <v>44552</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -822,7 +822,7 @@
         <v>44552</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -930,7 +930,7 @@
         <v>45232</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1025,7 +1025,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 10909-2025</t>
+          <t>A 18790-2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1039,10 +1039,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>45722</v>
+        <v>46128</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1056,20 +1056,20 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Allmännings- och besparingsskogar</t>
+          <t>Övriga statliga verk och myndigheter</t>
         </is>
       </c>
       <c r="I6" t="n">
-        <v>11.2</v>
+        <v>5.5</v>
       </c>
       <c r="J6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
@@ -1084,7 +1084,7 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -1096,262 +1096,262 @@
         <v>2</v>
       </c>
       <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>Fläcknycklar
+Nattviol</t>
+        </is>
+      </c>
+      <c r="W6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 18790-2026 artfynd.xlsx", "A 18790-2026")</f>
+        <v/>
+      </c>
+      <c r="X6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 18790-2026 karta.png", "A 18790-2026")</f>
+        <v/>
+      </c>
+      <c r="Y6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 18790-2026 georefererad karta.tif", "A 18790-2026")</f>
+        <v/>
+      </c>
+      <c r="AA6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 18790-2026 FSC-klagomål.docx", "A 18790-2026")</f>
+        <v/>
+      </c>
+      <c r="AB6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 18790-2026 FSC-klagomål mail.docx", "A 18790-2026")</f>
+        <v/>
+      </c>
+      <c r="AC6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 18790-2026 tillsynsbegäran.docx", "A 18790-2026")</f>
+        <v/>
+      </c>
+      <c r="AD6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 18790-2026 tillsynsbegäran mail.docx", "A 18790-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>A 18772-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>46128</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>UPPLANDS-BRO</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
         <v>2</v>
       </c>
-      <c r="V6" s="2" t="inlineStr">
+      <c r="T7" t="n">
+        <v>2</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>Svedjenäva
+Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="W7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 18772-2026 artfynd.xlsx", "A 18772-2026")</f>
+        <v/>
+      </c>
+      <c r="X7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 18772-2026 karta.png", "A 18772-2026")</f>
+        <v/>
+      </c>
+      <c r="Y7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 18772-2026 georefererad karta.tif", "A 18772-2026")</f>
+        <v/>
+      </c>
+      <c r="AA7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 18772-2026 FSC-klagomål.docx", "A 18772-2026")</f>
+        <v/>
+      </c>
+      <c r="AB7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 18772-2026 FSC-klagomål mail.docx", "A 18772-2026")</f>
+        <v/>
+      </c>
+      <c r="AC7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 18772-2026 tillsynsbegäran.docx", "A 18772-2026")</f>
+        <v/>
+      </c>
+      <c r="AD7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 18772-2026 tillsynsbegäran mail.docx", "A 18772-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="15" customHeight="1">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>A 10909-2025</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D8" s="1" t="n">
+        <v>45722</v>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>UPPLANDS-BRO</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="J8" t="n">
+        <v>1</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>2</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2</v>
+      </c>
+      <c r="U8" t="n">
+        <v>2</v>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>Arommusseron
 Fläcknycklar</t>
         </is>
       </c>
-      <c r="W6">
+      <c r="W8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 10909-2025 artfynd.xlsx", "A 10909-2025")</f>
         <v/>
       </c>
-      <c r="X6">
+      <c r="X8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 10909-2025 karta.png", "A 10909-2025")</f>
         <v/>
       </c>
-      <c r="Y6">
+      <c r="Y8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 10909-2025 georefererad karta.tif", "A 10909-2025")</f>
         <v/>
       </c>
-      <c r="AA6">
+      <c r="AA8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 10909-2025 FSC-klagomål.docx", "A 10909-2025")</f>
         <v/>
       </c>
-      <c r="AB6">
+      <c r="AB8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 10909-2025 FSC-klagomål mail.docx", "A 10909-2025")</f>
         <v/>
       </c>
-      <c r="AC6">
+      <c r="AC8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 10909-2025 tillsynsbegäran.docx", "A 10909-2025")</f>
         <v/>
       </c>
-      <c r="AD6">
+      <c r="AD8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 10909-2025 tillsynsbegäran mail.docx", "A 10909-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>A 18772-2026</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>46128</v>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>UPPLANDS-BRO</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="J7" t="n">
-        <v>1</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>1</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>1</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
-        <v>2</v>
-      </c>
-      <c r="T7" t="n">
-        <v>2</v>
-      </c>
-      <c r="U7" t="n">
-        <v>0</v>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>Svedjenäva
-Fläcknycklar</t>
-        </is>
-      </c>
-      <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 18772-2026 artfynd.xlsx", "A 18772-2026")</f>
-        <v/>
-      </c>
-      <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 18772-2026 karta.png", "A 18772-2026")</f>
-        <v/>
-      </c>
-      <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 18772-2026 georefererad karta.tif", "A 18772-2026")</f>
-        <v/>
-      </c>
-      <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 18772-2026 FSC-klagomål.docx", "A 18772-2026")</f>
-        <v/>
-      </c>
-      <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 18772-2026 FSC-klagomål mail.docx", "A 18772-2026")</f>
-        <v/>
-      </c>
-      <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 18772-2026 tillsynsbegäran.docx", "A 18772-2026")</f>
-        <v/>
-      </c>
-      <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 18772-2026 tillsynsbegäran mail.docx", "A 18772-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8" ht="15" customHeight="1">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>A 18790-2026</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D8" s="1" t="n">
-        <v>46128</v>
-      </c>
-      <c r="E8" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>UPPLANDS-BRO</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
-      <c r="I8" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="J8" t="n">
-        <v>2</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" t="n">
-        <v>2</v>
-      </c>
-      <c r="T8" t="n">
-        <v>2</v>
-      </c>
-      <c r="U8" t="n">
-        <v>0</v>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>Fläcknycklar
-Nattviol</t>
-        </is>
-      </c>
-      <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 18790-2026 artfynd.xlsx", "A 18790-2026")</f>
-        <v/>
-      </c>
-      <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 18790-2026 karta.png", "A 18790-2026")</f>
-        <v/>
-      </c>
-      <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 18790-2026 georefererad karta.tif", "A 18790-2026")</f>
-        <v/>
-      </c>
-      <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 18790-2026 FSC-klagomål.docx", "A 18790-2026")</f>
-        <v/>
-      </c>
-      <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 18790-2026 FSC-klagomål mail.docx", "A 18790-2026")</f>
-        <v/>
-      </c>
-      <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 18790-2026 tillsynsbegäran.docx", "A 18790-2026")</f>
-        <v/>
-      </c>
-      <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 18790-2026 tillsynsbegäran mail.docx", "A 18790-2026")</f>
         <v/>
       </c>
     </row>
@@ -1375,7 +1375,7 @@
         <v>44603</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1481,7 +1481,7 @@
         <v>44552</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1569,7 +1569,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 73773-2021</t>
+          <t>A 7955-2023</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>44552</v>
+        <v>44973</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1599,7 +1599,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>1.9</v>
+        <v>2.9</v>
       </c>
       <c r="J11" t="n">
         <v>1</v>
@@ -1614,7 +1614,7 @@
         <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1623,10 +1623,10 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1639,42 +1639,42 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>Kopparödla</t>
+          <t>Bombmurkla</t>
         </is>
       </c>
       <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 73773-2021 artfynd.xlsx", "A 73773-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 7955-2023 artfynd.xlsx", "A 7955-2023")</f>
         <v/>
       </c>
       <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 73773-2021 karta.png", "A 73773-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 7955-2023 karta.png", "A 7955-2023")</f>
         <v/>
       </c>
       <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 73773-2021 georefererad karta.tif", "A 73773-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 7955-2023 georefererad karta.tif", "A 7955-2023")</f>
         <v/>
       </c>
       <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 73773-2021 FSC-klagomål.docx", "A 73773-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 7955-2023 FSC-klagomål.docx", "A 7955-2023")</f>
         <v/>
       </c>
       <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 73773-2021 FSC-klagomål mail.docx", "A 73773-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 7955-2023 FSC-klagomål mail.docx", "A 7955-2023")</f>
         <v/>
       </c>
       <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 73773-2021 tillsynsbegäran.docx", "A 73773-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 7955-2023 tillsynsbegäran.docx", "A 7955-2023")</f>
         <v/>
       </c>
       <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 73773-2021 tillsynsbegäran mail.docx", "A 73773-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 7955-2023 tillsynsbegäran mail.docx", "A 7955-2023")</f>
         <v/>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 12363-2025</t>
+          <t>A 2409-2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1688,10 +1688,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45730</v>
+        <v>46034</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1704,13 +1704,13 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>0.8</v>
+        <v>14.2</v>
       </c>
       <c r="J12" t="n">
         <v>1</v>
       </c>
       <c r="K12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
@@ -1744,42 +1744,46 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Havsörn</t>
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 12363-2025 artfynd.xlsx", "A 12363-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 2409-2026 artfynd.xlsx", "A 2409-2026")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 12363-2025 karta.png", "A 12363-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 2409-2026 karta.png", "A 2409-2026")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 12363-2025 georefererad karta.tif", "A 12363-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 2409-2026 georefererad karta.tif", "A 2409-2026")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 12363-2025 FSC-klagomål.docx", "A 12363-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 2409-2026 FSC-klagomål.docx", "A 2409-2026")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 12363-2025 FSC-klagomål mail.docx", "A 12363-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 2409-2026 FSC-klagomål mail.docx", "A 2409-2026")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 12363-2025 tillsynsbegäran.docx", "A 12363-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 2409-2026 tillsynsbegäran.docx", "A 2409-2026")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 12363-2025 tillsynsbegäran mail.docx", "A 12363-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 2409-2026 tillsynsbegäran mail.docx", "A 2409-2026")</f>
+        <v/>
+      </c>
+      <c r="AE12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/fåglar/A 2409-2026 prioriterade fågelarter.docx", "A 2409-2026")</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 53357-2025</t>
+          <t>A 12363-2025</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1793,10 +1797,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45959</v>
+        <v>45730</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1809,13 +1813,13 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>2.4</v>
+        <v>0.8</v>
       </c>
       <c r="J13" t="n">
         <v>1</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -1824,7 +1828,7 @@
         <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -1833,58 +1837,58 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
       </c>
       <c r="T13" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="U13" t="n">
         <v>0</v>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>Bombmurkla</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 53357-2025 artfynd.xlsx", "A 53357-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 12363-2025 artfynd.xlsx", "A 12363-2025")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 53357-2025 karta.png", "A 53357-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 12363-2025 karta.png", "A 12363-2025")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 53357-2025 georefererad karta.tif", "A 53357-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 12363-2025 georefererad karta.tif", "A 12363-2025")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 53357-2025 FSC-klagomål.docx", "A 53357-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 12363-2025 FSC-klagomål.docx", "A 12363-2025")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 53357-2025 FSC-klagomål mail.docx", "A 53357-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 12363-2025 FSC-klagomål mail.docx", "A 12363-2025")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 53357-2025 tillsynsbegäran.docx", "A 53357-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 12363-2025 tillsynsbegäran.docx", "A 12363-2025")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 53357-2025 tillsynsbegäran mail.docx", "A 53357-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 12363-2025 tillsynsbegäran mail.docx", "A 12363-2025")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 23099-2024</t>
+          <t>A 25561-2025</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1898,10 +1902,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45450</v>
+        <v>45803</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1913,16 +1917,11 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I14" t="n">
-        <v>0.7</v>
+        <v>1.6</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
@@ -1931,10 +1930,10 @@
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -1955,39 +1954,39 @@
         <v>1</v>
       </c>
       <c r="U14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Bredbrämad bastardsvärmare</t>
+          <t>Bombmurkla</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 23099-2024 artfynd.xlsx", "A 23099-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 25561-2025 artfynd.xlsx", "A 25561-2025")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 23099-2024 karta.png", "A 23099-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 25561-2025 karta.png", "A 25561-2025")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 23099-2024 georefererad karta.tif", "A 23099-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 25561-2025 georefererad karta.tif", "A 25561-2025")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 23099-2024 FSC-klagomål.docx", "A 23099-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 25561-2025 FSC-klagomål.docx", "A 25561-2025")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 23099-2024 FSC-klagomål mail.docx", "A 23099-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 25561-2025 FSC-klagomål mail.docx", "A 25561-2025")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 23099-2024 tillsynsbegäran.docx", "A 23099-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 25561-2025 tillsynsbegäran.docx", "A 25561-2025")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 23099-2024 tillsynsbegäran mail.docx", "A 23099-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 25561-2025 tillsynsbegäran mail.docx", "A 25561-2025")</f>
         <v/>
       </c>
     </row>
@@ -2011,7 +2010,7 @@
         <v>45197</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2099,7 +2098,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 2409-2026</t>
+          <t>A 53357-2025</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2113,10 +2112,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46034</v>
+        <v>45959</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2129,7 +2128,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>14.2</v>
+        <v>2.4</v>
       </c>
       <c r="J16" t="n">
         <v>1</v>
@@ -2144,7 +2143,7 @@
         <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2153,62 +2152,58 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
       </c>
       <c r="T16" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="U16" t="n">
         <v>0</v>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Havsörn</t>
+          <t>Bombmurkla</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 2409-2026 artfynd.xlsx", "A 2409-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 53357-2025 artfynd.xlsx", "A 53357-2025")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 2409-2026 karta.png", "A 2409-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 53357-2025 karta.png", "A 53357-2025")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 2409-2026 georefererad karta.tif", "A 2409-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 53357-2025 georefererad karta.tif", "A 53357-2025")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 2409-2026 FSC-klagomål.docx", "A 2409-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 53357-2025 FSC-klagomål.docx", "A 53357-2025")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 2409-2026 FSC-klagomål mail.docx", "A 2409-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 53357-2025 FSC-klagomål mail.docx", "A 53357-2025")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 2409-2026 tillsynsbegäran.docx", "A 2409-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 53357-2025 tillsynsbegäran.docx", "A 53357-2025")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 2409-2026 tillsynsbegäran mail.docx", "A 2409-2026")</f>
-        <v/>
-      </c>
-      <c r="AE16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/fåglar/A 2409-2026 prioriterade fågelarter.docx", "A 2409-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 53357-2025 tillsynsbegäran mail.docx", "A 53357-2025")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 11447-2025</t>
+          <t>A 23099-2024</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2218,14 +2213,14 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45726</v>
+        <v>45450</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2237,20 +2232,25 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I17" t="n">
-        <v>1.5</v>
+        <v>0.7</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
@@ -2262,10 +2262,10 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
@@ -2274,46 +2274,46 @@
         <v>1</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Myskbock</t>
+          <t>Bredbrämad bastardsvärmare</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 11447-2025 artfynd.xlsx", "A 11447-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 23099-2024 artfynd.xlsx", "A 23099-2024")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 11447-2025 karta.png", "A 11447-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 23099-2024 karta.png", "A 23099-2024")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 11447-2025 georefererad karta.tif", "A 11447-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 23099-2024 georefererad karta.tif", "A 23099-2024")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 11447-2025 FSC-klagomål.docx", "A 11447-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 23099-2024 FSC-klagomål.docx", "A 23099-2024")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 11447-2025 FSC-klagomål mail.docx", "A 11447-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 23099-2024 FSC-klagomål mail.docx", "A 23099-2024")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 11447-2025 tillsynsbegäran.docx", "A 11447-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 23099-2024 tillsynsbegäran.docx", "A 23099-2024")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 11447-2025 tillsynsbegäran mail.docx", "A 11447-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 23099-2024 tillsynsbegäran mail.docx", "A 23099-2024")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 7955-2023</t>
+          <t>A 64098-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2327,10 +2327,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>44973</v>
+        <v>45279</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2343,22 +2343,22 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>2.9</v>
+        <v>0.3</v>
       </c>
       <c r="J18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2370,7 +2370,7 @@
         <v>1</v>
       </c>
       <c r="R18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
@@ -2379,46 +2379,46 @@
         <v>1</v>
       </c>
       <c r="U18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Bombmurkla</t>
+          <t>Skogsalmsdvärgmal</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 7955-2023 artfynd.xlsx", "A 7955-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 64098-2023 artfynd.xlsx", "A 64098-2023")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 7955-2023 karta.png", "A 7955-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 64098-2023 karta.png", "A 64098-2023")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 7955-2023 georefererad karta.tif", "A 7955-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 64098-2023 georefererad karta.tif", "A 64098-2023")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 7955-2023 FSC-klagomål.docx", "A 7955-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 64098-2023 FSC-klagomål.docx", "A 64098-2023")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 7955-2023 FSC-klagomål mail.docx", "A 7955-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 64098-2023 FSC-klagomål mail.docx", "A 64098-2023")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 7955-2023 tillsynsbegäran.docx", "A 7955-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 64098-2023 tillsynsbegäran.docx", "A 64098-2023")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 7955-2023 tillsynsbegäran mail.docx", "A 7955-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 64098-2023 tillsynsbegäran mail.docx", "A 64098-2023")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 26637-2026</t>
+          <t>A 26623-2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2435,7 +2435,7 @@
         <v>46184</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2448,7 +2448,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>5.4</v>
+        <v>4.6</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2457,10 +2457,10 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
@@ -2475,7 +2475,7 @@
         <v>1</v>
       </c>
       <c r="R19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
@@ -2488,42 +2488,42 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Igelkott</t>
+          <t>Svartöra</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 26637-2026 artfynd.xlsx", "A 26637-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 26623-2026 artfynd.xlsx", "A 26623-2026")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 26637-2026 karta.png", "A 26637-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 26623-2026 karta.png", "A 26623-2026")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 26637-2026 georefererad karta.tif", "A 26637-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 26623-2026 georefererad karta.tif", "A 26623-2026")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 26637-2026 FSC-klagomål.docx", "A 26637-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 26623-2026 FSC-klagomål.docx", "A 26623-2026")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 26637-2026 FSC-klagomål mail.docx", "A 26637-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 26623-2026 FSC-klagomål mail.docx", "A 26623-2026")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 26637-2026 tillsynsbegäran.docx", "A 26637-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 26623-2026 tillsynsbegäran.docx", "A 26623-2026")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 26637-2026 tillsynsbegäran mail.docx", "A 26637-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 26623-2026 tillsynsbegäran mail.docx", "A 26623-2026")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 26623-2026</t>
+          <t>A 26637-2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2540,7 +2540,7 @@
         <v>46184</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2553,7 +2553,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>4.6</v>
+        <v>5.4</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2562,10 +2562,10 @@
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N20" t="n">
         <v>0</v>
@@ -2580,7 +2580,7 @@
         <v>1</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>
@@ -2593,42 +2593,42 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>Svartöra</t>
+          <t>Igelkott</t>
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 26623-2026 artfynd.xlsx", "A 26623-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 26637-2026 artfynd.xlsx", "A 26637-2026")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 26623-2026 karta.png", "A 26623-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 26637-2026 karta.png", "A 26637-2026")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 26623-2026 georefererad karta.tif", "A 26623-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 26637-2026 georefererad karta.tif", "A 26637-2026")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 26623-2026 FSC-klagomål.docx", "A 26623-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 26637-2026 FSC-klagomål.docx", "A 26637-2026")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 26623-2026 FSC-klagomål mail.docx", "A 26623-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 26637-2026 FSC-klagomål mail.docx", "A 26637-2026")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 26623-2026 tillsynsbegäran.docx", "A 26623-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 26637-2026 tillsynsbegäran.docx", "A 26637-2026")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 26623-2026 tillsynsbegäran mail.docx", "A 26623-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 26637-2026 tillsynsbegäran mail.docx", "A 26637-2026")</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 64098-2023</t>
+          <t>A 73773-2021</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2642,10 +2642,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45279</v>
+        <v>44552</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2658,16 +2658,16 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>0.3</v>
+        <v>1.9</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
         <v>0</v>
@@ -2682,7 +2682,7 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
         <v>0</v>
@@ -2694,46 +2694,46 @@
         <v>1</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Skogsalmsdvärgmal</t>
+          <t>Kopparödla</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 64098-2023 artfynd.xlsx", "A 64098-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 73773-2021 artfynd.xlsx", "A 73773-2021")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 64098-2023 karta.png", "A 64098-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 73773-2021 karta.png", "A 73773-2021")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 64098-2023 georefererad karta.tif", "A 64098-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 73773-2021 georefererad karta.tif", "A 73773-2021")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 64098-2023 FSC-klagomål.docx", "A 64098-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 73773-2021 FSC-klagomål.docx", "A 73773-2021")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 64098-2023 FSC-klagomål mail.docx", "A 64098-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 73773-2021 FSC-klagomål mail.docx", "A 73773-2021")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 64098-2023 tillsynsbegäran.docx", "A 64098-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 73773-2021 tillsynsbegäran.docx", "A 73773-2021")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 64098-2023 tillsynsbegäran mail.docx", "A 64098-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 73773-2021 tillsynsbegäran mail.docx", "A 73773-2021")</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 2062-2025</t>
+          <t>A 11447-2025</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2743,14 +2743,14 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45671</v>
+        <v>45726</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2763,16 +2763,16 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>1.9</v>
+        <v>1.5</v>
       </c>
       <c r="J22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
         <v>0</v>
@@ -2787,7 +2787,7 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
         <v>0</v>
@@ -2799,50 +2799,46 @@
         <v>1</v>
       </c>
       <c r="U22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Myskbock</t>
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 2062-2025 artfynd.xlsx", "A 2062-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 11447-2025 artfynd.xlsx", "A 11447-2025")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 2062-2025 karta.png", "A 2062-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 11447-2025 karta.png", "A 11447-2025")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 2062-2025 georefererad karta.tif", "A 2062-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 11447-2025 georefererad karta.tif", "A 11447-2025")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 2062-2025 FSC-klagomål.docx", "A 2062-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 11447-2025 FSC-klagomål.docx", "A 11447-2025")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 2062-2025 FSC-klagomål mail.docx", "A 2062-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 11447-2025 FSC-klagomål mail.docx", "A 11447-2025")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 2062-2025 tillsynsbegäran.docx", "A 2062-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 11447-2025 tillsynsbegäran.docx", "A 11447-2025")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 2062-2025 tillsynsbegäran mail.docx", "A 2062-2025")</f>
-        <v/>
-      </c>
-      <c r="AE22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/fåglar/A 2062-2025 prioriterade fågelarter.docx", "A 2062-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 11447-2025 tillsynsbegäran mail.docx", "A 11447-2025")</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 25561-2025</t>
+          <t>A 2062-2025</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2856,10 +2852,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45803</v>
+        <v>45671</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2872,7 +2868,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>1.6</v>
+        <v>1.9</v>
       </c>
       <c r="J23" t="n">
         <v>1</v>
@@ -2881,13 +2877,13 @@
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M23" t="n">
         <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -2899,7 +2895,7 @@
         <v>1</v>
       </c>
       <c r="R23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
         <v>1</v>
@@ -2908,39 +2904,43 @@
         <v>1</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Bombmurkla</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 25561-2025 artfynd.xlsx", "A 25561-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 2062-2025 artfynd.xlsx", "A 2062-2025")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 25561-2025 karta.png", "A 25561-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 2062-2025 karta.png", "A 2062-2025")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 25561-2025 georefererad karta.tif", "A 25561-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 2062-2025 georefererad karta.tif", "A 2062-2025")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 25561-2025 FSC-klagomål.docx", "A 25561-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 2062-2025 FSC-klagomål.docx", "A 2062-2025")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 25561-2025 FSC-klagomål mail.docx", "A 25561-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 2062-2025 FSC-klagomål mail.docx", "A 2062-2025")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 25561-2025 tillsynsbegäran.docx", "A 25561-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 2062-2025 tillsynsbegäran.docx", "A 2062-2025")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 25561-2025 tillsynsbegäran mail.docx", "A 25561-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 2062-2025 tillsynsbegäran mail.docx", "A 2062-2025")</f>
+        <v/>
+      </c>
+      <c r="AE23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/fåglar/A 2062-2025 prioriterade fågelarter.docx", "A 2062-2025")</f>
         <v/>
       </c>
     </row>
@@ -2964,7 +2964,7 @@
         <v>44558</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3052,7 +3052,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 8261-2022</t>
+          <t>A 58663-2021</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3066,10 +3066,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>44609</v>
+        <v>44489</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3081,8 +3081,13 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I25" t="n">
-        <v>0.8</v>
+        <v>4.3</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -3125,7 +3130,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 58663-2021</t>
+          <t>A 8261-2022</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3139,10 +3144,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44489</v>
+        <v>44609</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3154,13 +3159,8 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I26" t="n">
-        <v>4.3</v>
+        <v>0.8</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -3220,7 +3220,7 @@
         <v>44546</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3293,7 +3293,7 @@
         <v>44700</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3366,7 +3366,7 @@
         <v>44587</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3439,7 +3439,7 @@
         <v>44655</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3500,7 +3500,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 64105-2023</t>
+          <t>A 59700-2021</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3514,10 +3514,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45279</v>
+        <v>44494</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3529,8 +3529,13 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I31" t="n">
-        <v>2.2</v>
+        <v>4.8</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3573,7 +3578,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 2602-2024</t>
+          <t>A 38902-2024</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3587,10 +3592,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45313</v>
+        <v>45547</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3602,8 +3607,13 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I32" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3646,7 +3656,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 59844-2022</t>
+          <t>A 50294-2023</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3660,10 +3670,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44901</v>
+        <v>45216</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3675,13 +3685,8 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I33" t="n">
-        <v>11.9</v>
+        <v>3.7</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3724,7 +3729,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 23093-2024</t>
+          <t>A 9655-2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3738,10 +3743,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45450</v>
+        <v>46070</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3759,7 +3764,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>0.9</v>
+        <v>17.2</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3802,7 +3807,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 3630-2023</t>
+          <t>A 5264-2023</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3816,10 +3821,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44950</v>
+        <v>44959</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3832,7 +3837,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>1.4</v>
+        <v>5.8</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3875,7 +3880,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 54222-2023</t>
+          <t>A 18787-2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3889,10 +3894,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45225</v>
+        <v>46128</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3910,7 +3915,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>8.300000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3953,7 +3958,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 7860-2024</t>
+          <t>A 18813-2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3967,10 +3972,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45348</v>
+        <v>46128</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3988,7 +3993,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>1.9</v>
+        <v>56</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4031,7 +4036,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 27313-2023</t>
+          <t>A 18818-2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4045,10 +4050,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45096</v>
+        <v>46128</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4060,8 +4065,13 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I38" t="n">
-        <v>1.8</v>
+        <v>17.8</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4104,7 +4114,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 64114-2023</t>
+          <t>A 18778-2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4118,10 +4128,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45279</v>
+        <v>46128</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4133,8 +4143,13 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I39" t="n">
-        <v>0.4</v>
+        <v>4.5</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4177,7 +4192,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 50294-2023</t>
+          <t>A 23098-2024</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4191,10 +4206,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45216</v>
+        <v>45450</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4206,8 +4221,13 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I40" t="n">
-        <v>3.7</v>
+        <v>1</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4250,7 +4270,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 58011-2021</t>
+          <t>A 21206-2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4264,10 +4284,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44487</v>
+        <v>46146</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4285,7 +4305,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>9.199999999999999</v>
+        <v>0.9</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4328,7 +4348,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 64110-2023</t>
+          <t>A 59844-2022</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4342,10 +4362,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45279</v>
+        <v>44901</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4357,8 +4377,13 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I42" t="n">
-        <v>0.4</v>
+        <v>11.9</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4401,7 +4426,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 23098-2024</t>
+          <t>A 54222-2023</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4415,10 +4440,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45450</v>
+        <v>45225</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4436,7 +4461,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>1</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4479,7 +4504,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 59377-2024</t>
+          <t>A 4338-2023</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4493,10 +4518,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45638</v>
+        <v>44953</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4509,7 +4534,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4552,7 +4577,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 21206-2026</t>
+          <t>A 58011-2021</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4566,10 +4591,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>46146</v>
+        <v>44487</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4587,7 +4612,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4630,7 +4655,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 59402-2022</t>
+          <t>A 72524-2021</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4644,10 +4669,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44906</v>
+        <v>44546</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4660,7 +4685,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1.8</v>
+        <v>3.6</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4703,7 +4728,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 5264-2023</t>
+          <t>A 64107-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4717,10 +4742,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>44959</v>
+        <v>45279</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4733,7 +4758,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>5.8</v>
+        <v>0.3</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4776,7 +4801,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 51587-2023</t>
+          <t>A 24579-2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4790,10 +4815,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45215</v>
+        <v>46170</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4805,13 +4830,8 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I48" t="n">
-        <v>2.6</v>
+        <v>2.1</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4854,7 +4874,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 24579-2026</t>
+          <t>A 23093-2024</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4868,10 +4888,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>46170</v>
+        <v>45450</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4883,8 +4903,13 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I49" t="n">
-        <v>2.1</v>
+        <v>0.9</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4927,7 +4952,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 9655-2026</t>
+          <t>A 58598-2025</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4941,10 +4966,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>46070</v>
+        <v>45986</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4962,7 +4987,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>17.2</v>
+        <v>4.5</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5022,7 +5047,7 @@
         <v>44770</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5078,7 +5103,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 72524-2021</t>
+          <t>A 27313-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5092,10 +5117,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>44546</v>
+        <v>45096</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5108,7 +5133,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>3.6</v>
+        <v>1.8</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5151,7 +5176,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 58598-2025</t>
+          <t>A 26196-2026</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5161,14 +5186,14 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45986</v>
+        <v>46182</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5180,13 +5205,8 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I53" t="n">
-        <v>4.5</v>
+        <v>53.1</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5229,7 +5249,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 26196-2026</t>
+          <t>A 26625-2026</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5239,14 +5259,14 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>46182</v>
+        <v>46184</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5259,7 +5279,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>53.1</v>
+        <v>5.3</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5302,7 +5322,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 26633-2026</t>
+          <t>A 59377-2024</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5316,10 +5336,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>46184</v>
+        <v>45638</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5332,7 +5352,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5375,7 +5395,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 26625-2026</t>
+          <t>A 26629-2026</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5392,7 +5412,7 @@
         <v>46184</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5405,7 +5425,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>5.3</v>
+        <v>2</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5448,7 +5468,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 26629-2026</t>
+          <t>A 26633-2026</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5465,7 +5485,7 @@
         <v>46184</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5478,7 +5498,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>2</v>
+        <v>0.7</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5521,7 +5541,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 4338-2023</t>
+          <t>A 3754-2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5535,10 +5555,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>44953</v>
+        <v>46043</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5550,8 +5570,13 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I58" t="n">
-        <v>1.1</v>
+        <v>5.1</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5594,7 +5619,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 59848-2022</t>
+          <t>A 28797-2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5608,10 +5633,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>44901</v>
+        <v>46198</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5623,13 +5648,8 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I59" t="n">
-        <v>10.7</v>
+        <v>2.2</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5672,7 +5692,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 18778-2026</t>
+          <t>A 28740-2026</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5686,10 +5706,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>46128</v>
+        <v>46198</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5701,13 +5721,8 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I60" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5750,7 +5765,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 18813-2026</t>
+          <t>A 28735-2026</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5764,10 +5779,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>46128</v>
+        <v>46198</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5779,13 +5794,8 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I61" t="n">
-        <v>56</v>
+        <v>3.5</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5828,7 +5838,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 18818-2026</t>
+          <t>A 51587-2023</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5842,10 +5852,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>46128</v>
+        <v>45215</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5859,11 +5869,11 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Övriga statliga verk och myndigheter</t>
+          <t>Allmännings- och besparingsskogar</t>
         </is>
       </c>
       <c r="I62" t="n">
-        <v>17.8</v>
+        <v>2.6</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5906,7 +5916,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 18787-2026</t>
+          <t>A 31714-2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5920,10 +5930,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>46128</v>
+        <v>46226</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5935,13 +5945,8 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I63" t="n">
-        <v>7.8</v>
+        <v>5</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5984,7 +5989,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 3754-2026</t>
+          <t>A 59848-2022</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5998,10 +6003,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>46043</v>
+        <v>44901</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6019,7 +6024,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>5.1</v>
+        <v>10.7</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6062,7 +6067,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 59700-2021</t>
+          <t>A 64110-2023</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6076,10 +6081,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>44494</v>
+        <v>45279</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6091,13 +6096,8 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I65" t="n">
-        <v>4.8</v>
+        <v>0.4</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6140,7 +6140,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 28735-2026</t>
+          <t>A 33058-2026</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6150,14 +6150,14 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>46198</v>
+        <v>46245</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6170,7 +6170,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>3.5</v>
+        <v>1.3</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6213,7 +6213,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 28740-2026</t>
+          <t>A 7275-2022</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6227,10 +6227,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>46198</v>
+        <v>44606</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6242,8 +6242,13 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I67" t="n">
-        <v>4.8</v>
+        <v>9.6</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6286,7 +6291,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 28797-2026</t>
+          <t>A 2602-2024</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6300,10 +6305,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>46198</v>
+        <v>45313</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6316,7 +6321,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>2.2</v>
+        <v>0.7</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6359,7 +6364,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 31714-2026</t>
+          <t>A 59402-2022</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6373,10 +6378,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>46226</v>
+        <v>44906</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6389,7 +6394,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>5</v>
+        <v>1.8</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6432,7 +6437,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 7275-2022</t>
+          <t>A 3630-2023</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6446,10 +6451,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>44606</v>
+        <v>44950</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6461,13 +6466,8 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I70" t="n">
-        <v>9.6</v>
+        <v>1.4</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6510,7 +6510,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 64107-2023</t>
+          <t>A 7860-2024</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6524,10 +6524,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45279</v>
+        <v>45348</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6539,8 +6539,13 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I71" t="n">
-        <v>0.3</v>
+        <v>1.9</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6583,7 +6588,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 7112-2025</t>
+          <t>A 64105-2023</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6597,10 +6602,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45701</v>
+        <v>45279</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6613,7 +6618,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6656,7 +6661,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 38902-2024</t>
+          <t>A 64114-2023</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6670,10 +6675,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45547</v>
+        <v>45279</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6685,13 +6690,8 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I73" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6734,7 +6734,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 23615-2025</t>
+          <t>A 7112-2025</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6748,10 +6748,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45792</v>
+        <v>45701</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6764,7 +6764,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>1.3</v>
+        <v>2.4</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6807,7 +6807,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 23627-2025</t>
+          <t>A 23615-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6824,7 +6824,7 @@
         <v>45792</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6837,7 +6837,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>1.7</v>
+        <v>1.3</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6880,7 +6880,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 33058-2026</t>
+          <t>A 23627-2025</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6890,14 +6890,14 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>46245</v>
+        <v>45792</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6910,7 +6910,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6970,7 +6970,7 @@
         <v>44558</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>

--- a/Översikt UPPLANDS-BRO.xlsx
+++ b/Översikt UPPLANDS-BRO.xlsx
@@ -601,7 +601,7 @@
         <v>44481</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -714,7 +714,7 @@
         <v>44552</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -822,7 +822,7 @@
         <v>44552</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -930,7 +930,7 @@
         <v>45232</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1042,7 +1042,7 @@
         <v>46128</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1153,7 +1153,7 @@
         <v>46128</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1264,7 +1264,7 @@
         <v>45722</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
         <v>44603</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1481,7 +1481,7 @@
         <v>44552</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1586,7 +1586,7 @@
         <v>44973</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>46034</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1800,7 +1800,7 @@
         <v>45730</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1905,7 +1905,7 @@
         <v>45803</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2010,7 +2010,7 @@
         <v>45197</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2115,7 +2115,7 @@
         <v>45959</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2220,7 +2220,7 @@
         <v>45450</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2330,7 +2330,7 @@
         <v>45279</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2435,7 +2435,7 @@
         <v>46184</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2540,7 +2540,7 @@
         <v>46184</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2645,7 +2645,7 @@
         <v>44552</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2750,7 +2750,7 @@
         <v>45726</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2855,7 +2855,7 @@
         <v>45671</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2964,7 +2964,7 @@
         <v>44558</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3069,7 +3069,7 @@
         <v>44489</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3147,7 +3147,7 @@
         <v>44609</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3220,7 +3220,7 @@
         <v>44546</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3293,7 +3293,7 @@
         <v>44700</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3366,7 +3366,7 @@
         <v>44587</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3439,7 +3439,7 @@
         <v>44655</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3517,7 +3517,7 @@
         <v>44494</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3595,7 +3595,7 @@
         <v>45547</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3673,7 +3673,7 @@
         <v>45216</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3746,7 +3746,7 @@
         <v>46070</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3824,7 +3824,7 @@
         <v>44959</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3897,7 +3897,7 @@
         <v>46128</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3975,7 +3975,7 @@
         <v>46128</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4053,7 +4053,7 @@
         <v>46128</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4131,7 +4131,7 @@
         <v>46128</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4209,7 +4209,7 @@
         <v>45450</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4287,7 +4287,7 @@
         <v>46146</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4365,7 +4365,7 @@
         <v>44901</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4443,7 +4443,7 @@
         <v>45225</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4521,7 +4521,7 @@
         <v>44953</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4594,7 +4594,7 @@
         <v>44487</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4672,7 +4672,7 @@
         <v>44546</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4745,7 +4745,7 @@
         <v>45279</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4818,7 +4818,7 @@
         <v>46170</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4891,7 +4891,7 @@
         <v>45450</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4969,7 +4969,7 @@
         <v>45986</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5047,7 +5047,7 @@
         <v>44770</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5120,7 +5120,7 @@
         <v>45096</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5193,7 +5193,7 @@
         <v>46182</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5266,7 +5266,7 @@
         <v>46184</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5339,7 +5339,7 @@
         <v>45638</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5412,7 +5412,7 @@
         <v>46184</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5485,7 +5485,7 @@
         <v>46184</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5558,7 +5558,7 @@
         <v>46043</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5636,7 +5636,7 @@
         <v>46198</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5709,7 +5709,7 @@
         <v>46198</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5782,7 +5782,7 @@
         <v>46198</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5855,7 +5855,7 @@
         <v>45215</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5933,7 +5933,7 @@
         <v>46226</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6006,7 +6006,7 @@
         <v>44901</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6084,7 +6084,7 @@
         <v>45279</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6157,7 +6157,7 @@
         <v>46245</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6230,7 +6230,7 @@
         <v>44606</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6308,7 +6308,7 @@
         <v>45313</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6381,7 +6381,7 @@
         <v>44906</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6454,7 +6454,7 @@
         <v>44950</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6527,7 +6527,7 @@
         <v>45348</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6605,7 +6605,7 @@
         <v>45279</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6678,7 +6678,7 @@
         <v>45279</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6751,7 +6751,7 @@
         <v>45701</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6824,7 +6824,7 @@
         <v>45792</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6897,7 +6897,7 @@
         <v>45792</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6970,7 +6970,7 @@
         <v>44558</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>

--- a/Översikt UPPLANDS-BRO.xlsx
+++ b/Översikt UPPLANDS-BRO.xlsx
@@ -601,7 +601,7 @@
         <v>44481</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -714,7 +714,7 @@
         <v>44552</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -822,7 +822,7 @@
         <v>44552</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -930,7 +930,7 @@
         <v>45232</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1042,7 +1042,7 @@
         <v>46128</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1153,7 +1153,7 @@
         <v>46128</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1264,7 +1264,7 @@
         <v>45722</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
         <v>44603</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1481,7 +1481,7 @@
         <v>44552</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1586,7 +1586,7 @@
         <v>44973</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>46034</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1800,7 +1800,7 @@
         <v>45730</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1905,7 +1905,7 @@
         <v>45803</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2010,7 +2010,7 @@
         <v>45197</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2115,7 +2115,7 @@
         <v>45959</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2220,7 +2220,7 @@
         <v>45450</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2330,7 +2330,7 @@
         <v>45279</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2435,7 +2435,7 @@
         <v>46184</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2540,7 +2540,7 @@
         <v>46184</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2645,7 +2645,7 @@
         <v>44552</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2750,7 +2750,7 @@
         <v>45726</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2855,7 +2855,7 @@
         <v>45671</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2964,7 +2964,7 @@
         <v>44558</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3069,7 +3069,7 @@
         <v>44489</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3147,7 +3147,7 @@
         <v>44609</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3220,7 +3220,7 @@
         <v>44546</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3293,7 +3293,7 @@
         <v>44700</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3366,7 +3366,7 @@
         <v>44587</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3439,7 +3439,7 @@
         <v>44655</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3517,7 +3517,7 @@
         <v>44494</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3595,7 +3595,7 @@
         <v>45547</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3673,7 +3673,7 @@
         <v>45216</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3746,7 +3746,7 @@
         <v>46070</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3824,7 +3824,7 @@
         <v>44959</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3897,7 +3897,7 @@
         <v>46128</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3975,7 +3975,7 @@
         <v>46128</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4053,7 +4053,7 @@
         <v>46128</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4131,7 +4131,7 @@
         <v>46128</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4209,7 +4209,7 @@
         <v>45450</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4287,7 +4287,7 @@
         <v>46146</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4365,7 +4365,7 @@
         <v>44901</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4443,7 +4443,7 @@
         <v>45225</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4521,7 +4521,7 @@
         <v>44953</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4594,7 +4594,7 @@
         <v>44487</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4672,7 +4672,7 @@
         <v>44546</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4745,7 +4745,7 @@
         <v>45279</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4818,7 +4818,7 @@
         <v>46170</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4891,7 +4891,7 @@
         <v>45450</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4969,7 +4969,7 @@
         <v>45986</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5047,7 +5047,7 @@
         <v>44770</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5120,7 +5120,7 @@
         <v>45096</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5193,7 +5193,7 @@
         <v>46182</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5266,7 +5266,7 @@
         <v>46184</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5339,7 +5339,7 @@
         <v>45638</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5412,7 +5412,7 @@
         <v>46184</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5485,7 +5485,7 @@
         <v>46184</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5558,7 +5558,7 @@
         <v>46043</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5636,7 +5636,7 @@
         <v>46198</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5709,7 +5709,7 @@
         <v>46198</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5782,7 +5782,7 @@
         <v>46198</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5855,7 +5855,7 @@
         <v>45215</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5933,7 +5933,7 @@
         <v>46226</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6006,7 +6006,7 @@
         <v>44901</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6084,7 +6084,7 @@
         <v>45279</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6157,7 +6157,7 @@
         <v>46245</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6230,7 +6230,7 @@
         <v>44606</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6308,7 +6308,7 @@
         <v>45313</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6381,7 +6381,7 @@
         <v>44906</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6454,7 +6454,7 @@
         <v>44950</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6527,7 +6527,7 @@
         <v>45348</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6605,7 +6605,7 @@
         <v>45279</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6678,7 +6678,7 @@
         <v>45279</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6751,7 +6751,7 @@
         <v>45701</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6824,7 +6824,7 @@
         <v>45792</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6897,7 +6897,7 @@
         <v>45792</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6970,7 +6970,7 @@
         <v>44558</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>

--- a/Översikt UPPLANDS-BRO.xlsx
+++ b/Översikt UPPLANDS-BRO.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE77"/>
+  <dimension ref="A1:AE76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>44481</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -714,7 +714,7 @@
         <v>44552</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -822,7 +822,7 @@
         <v>44552</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -930,7 +930,7 @@
         <v>45232</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1025,7 +1025,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 18790-2026</t>
+          <t>A 73773-2021</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1039,10 +1039,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46128</v>
+        <v>44552</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1054,13 +1054,8 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I6" t="n">
-        <v>5.5</v>
+        <v>1.9</v>
       </c>
       <c r="J6" t="n">
         <v>2</v>
@@ -1093,483 +1088,489 @@
         <v>2</v>
       </c>
       <c r="T6" t="n">
+        <v>3</v>
+      </c>
+      <c r="U6" t="n">
+        <v>3</v>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>Kopparödla
+Gullviva</t>
+        </is>
+      </c>
+      <c r="W6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 73773-2021 artfynd.xlsx", "A 73773-2021")</f>
+        <v/>
+      </c>
+      <c r="X6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 73773-2021 karta.png", "A 73773-2021")</f>
+        <v/>
+      </c>
+      <c r="Y6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 73773-2021 georefererad karta.tif", "A 73773-2021")</f>
+        <v/>
+      </c>
+      <c r="AA6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 73773-2021 FSC-klagomål.docx", "A 73773-2021")</f>
+        <v/>
+      </c>
+      <c r="AB6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 73773-2021 FSC-klagomål mail.docx", "A 73773-2021")</f>
+        <v/>
+      </c>
+      <c r="AC6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 73773-2021 tillsynsbegäran.docx", "A 73773-2021")</f>
+        <v/>
+      </c>
+      <c r="AD6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 73773-2021 tillsynsbegäran mail.docx", "A 73773-2021")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>A 18772-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>46128</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>UPPLANDS-BRO</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
         <v>2</v>
       </c>
-      <c r="U6" t="n">
-        <v>0</v>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
+      <c r="T7" t="n">
+        <v>2</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>Svedjenäva
+Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="W7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 18772-2026 artfynd.xlsx", "A 18772-2026")</f>
+        <v/>
+      </c>
+      <c r="X7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 18772-2026 karta.png", "A 18772-2026")</f>
+        <v/>
+      </c>
+      <c r="Y7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 18772-2026 georefererad karta.tif", "A 18772-2026")</f>
+        <v/>
+      </c>
+      <c r="AA7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 18772-2026 FSC-klagomål.docx", "A 18772-2026")</f>
+        <v/>
+      </c>
+      <c r="AB7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 18772-2026 FSC-klagomål mail.docx", "A 18772-2026")</f>
+        <v/>
+      </c>
+      <c r="AC7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 18772-2026 tillsynsbegäran.docx", "A 18772-2026")</f>
+        <v/>
+      </c>
+      <c r="AD7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 18772-2026 tillsynsbegäran mail.docx", "A 18772-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="15" customHeight="1">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>A 18790-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D8" s="1" t="n">
+        <v>46128</v>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>UPPLANDS-BRO</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="J8" t="n">
+        <v>2</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>2</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>Fläcknycklar
 Nattviol</t>
         </is>
       </c>
-      <c r="W6">
+      <c r="W8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 18790-2026 artfynd.xlsx", "A 18790-2026")</f>
         <v/>
       </c>
-      <c r="X6">
+      <c r="X8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 18790-2026 karta.png", "A 18790-2026")</f>
         <v/>
       </c>
-      <c r="Y6">
+      <c r="Y8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 18790-2026 georefererad karta.tif", "A 18790-2026")</f>
         <v/>
       </c>
-      <c r="AA6">
+      <c r="AA8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 18790-2026 FSC-klagomål.docx", "A 18790-2026")</f>
         <v/>
       </c>
-      <c r="AB6">
+      <c r="AB8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 18790-2026 FSC-klagomål mail.docx", "A 18790-2026")</f>
         <v/>
       </c>
-      <c r="AC6">
+      <c r="AC8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 18790-2026 tillsynsbegäran.docx", "A 18790-2026")</f>
         <v/>
       </c>
-      <c r="AD6">
+      <c r="AD8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 18790-2026 tillsynsbegäran mail.docx", "A 18790-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>A 18772-2026</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
+    <row r="9" ht="15" customHeight="1">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>A 10909-2025</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D7" s="1" t="n">
-        <v>46128</v>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>UPPLANDS-BRO</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="J7" t="n">
-        <v>1</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>1</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>1</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
+      <c r="D9" s="1" t="n">
+        <v>45722</v>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>UPPLANDS-BRO</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
         <v>2</v>
       </c>
-      <c r="T7" t="n">
+      <c r="T9" t="n">
         <v>2</v>
       </c>
-      <c r="U7" t="n">
-        <v>0</v>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>Svedjenäva
-Fläcknycklar</t>
-        </is>
-      </c>
-      <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 18772-2026 artfynd.xlsx", "A 18772-2026")</f>
-        <v/>
-      </c>
-      <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 18772-2026 karta.png", "A 18772-2026")</f>
-        <v/>
-      </c>
-      <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 18772-2026 georefererad karta.tif", "A 18772-2026")</f>
-        <v/>
-      </c>
-      <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 18772-2026 FSC-klagomål.docx", "A 18772-2026")</f>
-        <v/>
-      </c>
-      <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 18772-2026 FSC-klagomål mail.docx", "A 18772-2026")</f>
-        <v/>
-      </c>
-      <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 18772-2026 tillsynsbegäran.docx", "A 18772-2026")</f>
-        <v/>
-      </c>
-      <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 18772-2026 tillsynsbegäran mail.docx", "A 18772-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8" ht="15" customHeight="1">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>A 10909-2025</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D8" s="1" t="n">
-        <v>45722</v>
-      </c>
-      <c r="E8" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>UPPLANDS-BRO</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
-      <c r="I8" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="J8" t="n">
-        <v>1</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>1</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>1</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" t="n">
+      <c r="U9" t="n">
         <v>2</v>
       </c>
-      <c r="T8" t="n">
-        <v>2</v>
-      </c>
-      <c r="U8" t="n">
-        <v>2</v>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
+      <c r="V9" s="2" t="inlineStr">
         <is>
           <t>Arommusseron
 Fläcknycklar</t>
         </is>
       </c>
-      <c r="W8">
+      <c r="W9">
         <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 10909-2025 artfynd.xlsx", "A 10909-2025")</f>
         <v/>
       </c>
-      <c r="X8">
+      <c r="X9">
         <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 10909-2025 karta.png", "A 10909-2025")</f>
         <v/>
       </c>
-      <c r="Y8">
+      <c r="Y9">
         <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 10909-2025 georefererad karta.tif", "A 10909-2025")</f>
         <v/>
       </c>
-      <c r="AA8">
+      <c r="AA9">
         <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 10909-2025 FSC-klagomål.docx", "A 10909-2025")</f>
         <v/>
       </c>
-      <c r="AB8">
+      <c r="AB9">
         <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 10909-2025 FSC-klagomål mail.docx", "A 10909-2025")</f>
         <v/>
       </c>
-      <c r="AC8">
+      <c r="AC9">
         <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 10909-2025 tillsynsbegäran.docx", "A 10909-2025")</f>
         <v/>
       </c>
-      <c r="AD8">
+      <c r="AD9">
         <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 10909-2025 tillsynsbegäran mail.docx", "A 10909-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1">
-      <c r="A9" t="inlineStr">
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="inlineStr">
         <is>
           <t>S 800-2022</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>samrådsanmälan</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
-      <c r="D9" s="1" t="n">
+      <c r="D10" s="1" t="n">
         <v>44603</v>
       </c>
-      <c r="E9" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>UPPLANDS-BRO</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
+      <c r="E10" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>UPPLANDS-BRO</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
         <v>4.3</v>
       </c>
-      <c r="J9" t="n">
-        <v>1</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="n">
-        <v>1</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>1</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1</v>
-      </c>
-      <c r="S9" t="n">
+      <c r="J10" t="n">
+        <v>1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>1</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1</v>
+      </c>
+      <c r="S10" t="n">
         <v>2</v>
       </c>
-      <c r="T9" t="n">
+      <c r="T10" t="n">
         <v>7</v>
       </c>
-      <c r="U9" t="n">
-        <v>1</v>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
+      <c r="U10" t="n">
+        <v>1</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>Ask
 Mistel</t>
         </is>
       </c>
-      <c r="W9">
+      <c r="W10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/S 800-2022 artfynd.xlsx", "S 800-2022")</f>
         <v/>
       </c>
-      <c r="X9">
+      <c r="X10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/S 800-2022 karta.png", "S 800-2022")</f>
         <v/>
       </c>
-      <c r="Y9">
+      <c r="Y10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/S 800-2022 georefererad karta.tif", "S 800-2022")</f>
         <v/>
       </c>
-      <c r="AA9">
+      <c r="AA10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/S 800-2022 FSC-klagomål.docx", "S 800-2022")</f>
         <v/>
       </c>
-      <c r="AB9">
+      <c r="AB10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/S 800-2022 FSC-klagomål mail.docx", "S 800-2022")</f>
         <v/>
       </c>
-      <c r="AC9">
+      <c r="AC10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/S 800-2022 tillsynsbegäran.docx", "S 800-2022")</f>
         <v/>
       </c>
-      <c r="AD9">
+      <c r="AD10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/S 800-2022 tillsynsbegäran mail.docx", "S 800-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>A 73787-2021</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="n">
-        <v>44552</v>
-      </c>
-      <c r="E10" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>UPPLANDS-BRO</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>1</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>1</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="n">
-        <v>1</v>
-      </c>
-      <c r="T10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>Dofttaggsvamp</t>
-        </is>
-      </c>
-      <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 73787-2021 artfynd.xlsx", "A 73787-2021")</f>
-        <v/>
-      </c>
-      <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 73787-2021 karta.png", "A 73787-2021")</f>
-        <v/>
-      </c>
-      <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 73787-2021 georefererad karta.tif", "A 73787-2021")</f>
-        <v/>
-      </c>
-      <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 73787-2021 FSC-klagomål.docx", "A 73787-2021")</f>
-        <v/>
-      </c>
-      <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 73787-2021 FSC-klagomål mail.docx", "A 73787-2021")</f>
-        <v/>
-      </c>
-      <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 73787-2021 tillsynsbegäran.docx", "A 73787-2021")</f>
-        <v/>
-      </c>
-      <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 73787-2021 tillsynsbegäran mail.docx", "A 73787-2021")</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 7955-2023</t>
+          <t>A 73787-2021</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1583,10 +1584,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>44973</v>
+        <v>44552</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1599,22 +1600,22 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>2.9</v>
+        <v>4.6</v>
       </c>
       <c r="J11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1626,7 +1627,7 @@
         <v>1</v>
       </c>
       <c r="R11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1635,46 +1636,46 @@
         <v>1</v>
       </c>
       <c r="U11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>Bombmurkla</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 7955-2023 artfynd.xlsx", "A 7955-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 73787-2021 artfynd.xlsx", "A 73787-2021")</f>
         <v/>
       </c>
       <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 7955-2023 karta.png", "A 7955-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 73787-2021 karta.png", "A 73787-2021")</f>
         <v/>
       </c>
       <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 7955-2023 georefererad karta.tif", "A 7955-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 73787-2021 georefererad karta.tif", "A 73787-2021")</f>
         <v/>
       </c>
       <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 7955-2023 FSC-klagomål.docx", "A 7955-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 73787-2021 FSC-klagomål.docx", "A 73787-2021")</f>
         <v/>
       </c>
       <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 7955-2023 FSC-klagomål mail.docx", "A 7955-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 73787-2021 FSC-klagomål mail.docx", "A 73787-2021")</f>
         <v/>
       </c>
       <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 7955-2023 tillsynsbegäran.docx", "A 7955-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 73787-2021 tillsynsbegäran.docx", "A 73787-2021")</f>
         <v/>
       </c>
       <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 7955-2023 tillsynsbegäran mail.docx", "A 7955-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 73787-2021 tillsynsbegäran mail.docx", "A 73787-2021")</f>
         <v/>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 2409-2026</t>
+          <t>A 25561-2025</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1688,10 +1689,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46034</v>
+        <v>45803</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1704,7 +1705,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>14.2</v>
+        <v>1.6</v>
       </c>
       <c r="J12" t="n">
         <v>1</v>
@@ -1719,7 +1720,7 @@
         <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1728,10 +1729,10 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1744,39 +1745,35 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>Havsörn</t>
+          <t>Bombmurkla</t>
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 2409-2026 artfynd.xlsx", "A 2409-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 25561-2025 artfynd.xlsx", "A 25561-2025")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 2409-2026 karta.png", "A 2409-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 25561-2025 karta.png", "A 25561-2025")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 2409-2026 georefererad karta.tif", "A 2409-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 25561-2025 georefererad karta.tif", "A 25561-2025")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 2409-2026 FSC-klagomål.docx", "A 2409-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 25561-2025 FSC-klagomål.docx", "A 25561-2025")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 2409-2026 FSC-klagomål mail.docx", "A 2409-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 25561-2025 FSC-klagomål mail.docx", "A 25561-2025")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 2409-2026 tillsynsbegäran.docx", "A 2409-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 25561-2025 tillsynsbegäran.docx", "A 25561-2025")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 2409-2026 tillsynsbegäran mail.docx", "A 2409-2026")</f>
-        <v/>
-      </c>
-      <c r="AE12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/fåglar/A 2409-2026 prioriterade fågelarter.docx", "A 2409-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 25561-2025 tillsynsbegäran mail.docx", "A 25561-2025")</f>
         <v/>
       </c>
     </row>
@@ -1800,7 +1797,7 @@
         <v>45730</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1888,7 +1885,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 25561-2025</t>
+          <t>A 53357-2025</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1902,10 +1899,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45803</v>
+        <v>45959</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1918,7 +1915,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>1.6</v>
+        <v>2.4</v>
       </c>
       <c r="J14" t="n">
         <v>1</v>
@@ -1951,7 +1948,7 @@
         <v>1</v>
       </c>
       <c r="T14" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="U14" t="n">
         <v>0</v>
@@ -1962,38 +1959,38 @@
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 25561-2025 artfynd.xlsx", "A 25561-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 53357-2025 artfynd.xlsx", "A 53357-2025")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 25561-2025 karta.png", "A 25561-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 53357-2025 karta.png", "A 53357-2025")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 25561-2025 georefererad karta.tif", "A 25561-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 53357-2025 georefererad karta.tif", "A 53357-2025")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 25561-2025 FSC-klagomål.docx", "A 25561-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 53357-2025 FSC-klagomål.docx", "A 53357-2025")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 25561-2025 FSC-klagomål mail.docx", "A 25561-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 53357-2025 FSC-klagomål mail.docx", "A 53357-2025")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 25561-2025 tillsynsbegäran.docx", "A 25561-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 53357-2025 tillsynsbegäran.docx", "A 53357-2025")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 25561-2025 tillsynsbegäran mail.docx", "A 25561-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 53357-2025 tillsynsbegäran mail.docx", "A 53357-2025")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 46438-2023</t>
+          <t>A 23099-2024</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2007,10 +2004,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45197</v>
+        <v>45450</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2022,11 +2019,16 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I15" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
@@ -2035,10 +2037,10 @@
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2059,46 +2061,46 @@
         <v>1</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Bombmurkla</t>
+          <t>Bredbrämad bastardsvärmare</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 46438-2023 artfynd.xlsx", "A 46438-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 23099-2024 artfynd.xlsx", "A 23099-2024")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 46438-2023 karta.png", "A 46438-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 23099-2024 karta.png", "A 23099-2024")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 46438-2023 georefererad karta.tif", "A 46438-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 23099-2024 georefererad karta.tif", "A 23099-2024")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 46438-2023 FSC-klagomål.docx", "A 46438-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 23099-2024 FSC-klagomål.docx", "A 23099-2024")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 46438-2023 FSC-klagomål mail.docx", "A 46438-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 23099-2024 FSC-klagomål mail.docx", "A 23099-2024")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 46438-2023 tillsynsbegäran.docx", "A 46438-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 23099-2024 tillsynsbegäran.docx", "A 23099-2024")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 46438-2023 tillsynsbegäran mail.docx", "A 46438-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 23099-2024 tillsynsbegäran mail.docx", "A 23099-2024")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 53357-2025</t>
+          <t>A 46438-2023</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2112,10 +2114,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45959</v>
+        <v>45197</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2128,7 +2130,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>2.4</v>
+        <v>0.5</v>
       </c>
       <c r="J16" t="n">
         <v>1</v>
@@ -2161,7 +2163,7 @@
         <v>1</v>
       </c>
       <c r="T16" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="U16" t="n">
         <v>0</v>
@@ -2172,38 +2174,38 @@
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 53357-2025 artfynd.xlsx", "A 53357-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 46438-2023 artfynd.xlsx", "A 46438-2023")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 53357-2025 karta.png", "A 53357-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 46438-2023 karta.png", "A 46438-2023")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 53357-2025 georefererad karta.tif", "A 53357-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 46438-2023 georefererad karta.tif", "A 46438-2023")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 53357-2025 FSC-klagomål.docx", "A 53357-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 46438-2023 FSC-klagomål.docx", "A 46438-2023")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 53357-2025 FSC-klagomål mail.docx", "A 53357-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 46438-2023 FSC-klagomål mail.docx", "A 46438-2023")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 53357-2025 tillsynsbegäran.docx", "A 53357-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 46438-2023 tillsynsbegäran.docx", "A 46438-2023")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 53357-2025 tillsynsbegäran mail.docx", "A 53357-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 46438-2023 tillsynsbegäran mail.docx", "A 46438-2023")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 23099-2024</t>
+          <t>A 11447-2025</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2213,14 +2215,14 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45450</v>
+        <v>45726</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2232,25 +2234,20 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I17" t="n">
-        <v>0.7</v>
+        <v>1.5</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
@@ -2262,10 +2259,10 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
@@ -2274,46 +2271,46 @@
         <v>1</v>
       </c>
       <c r="U17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Bredbrämad bastardsvärmare</t>
+          <t>Myskbock</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 23099-2024 artfynd.xlsx", "A 23099-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 11447-2025 artfynd.xlsx", "A 11447-2025")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 23099-2024 karta.png", "A 23099-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 11447-2025 karta.png", "A 11447-2025")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 23099-2024 georefererad karta.tif", "A 23099-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 11447-2025 georefererad karta.tif", "A 11447-2025")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 23099-2024 FSC-klagomål.docx", "A 23099-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 11447-2025 FSC-klagomål.docx", "A 11447-2025")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 23099-2024 FSC-klagomål mail.docx", "A 23099-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 11447-2025 FSC-klagomål mail.docx", "A 11447-2025")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 23099-2024 tillsynsbegäran.docx", "A 23099-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 11447-2025 tillsynsbegäran.docx", "A 11447-2025")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 23099-2024 tillsynsbegäran mail.docx", "A 23099-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 11447-2025 tillsynsbegäran mail.docx", "A 11447-2025")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 64098-2023</t>
+          <t>A 7955-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2327,10 +2324,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45279</v>
+        <v>44973</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2343,22 +2340,22 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>0.3</v>
+        <v>2.9</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2370,7 +2367,7 @@
         <v>1</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
@@ -2379,46 +2376,46 @@
         <v>1</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Skogsalmsdvärgmal</t>
+          <t>Bombmurkla</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 64098-2023 artfynd.xlsx", "A 64098-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 7955-2023 artfynd.xlsx", "A 7955-2023")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 64098-2023 karta.png", "A 64098-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 7955-2023 karta.png", "A 7955-2023")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 64098-2023 georefererad karta.tif", "A 64098-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 7955-2023 georefererad karta.tif", "A 7955-2023")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 64098-2023 FSC-klagomål.docx", "A 64098-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 7955-2023 FSC-klagomål.docx", "A 7955-2023")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 64098-2023 FSC-klagomål mail.docx", "A 64098-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 7955-2023 FSC-klagomål mail.docx", "A 7955-2023")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 64098-2023 tillsynsbegäran.docx", "A 64098-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 7955-2023 tillsynsbegäran.docx", "A 7955-2023")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 64098-2023 tillsynsbegäran mail.docx", "A 64098-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 7955-2023 tillsynsbegäran mail.docx", "A 7955-2023")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 26623-2026</t>
+          <t>A 26196-2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2428,14 +2425,14 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46184</v>
+        <v>46182</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2448,7 +2445,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>4.6</v>
+        <v>53.1</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2457,7 +2454,7 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
         <v>0</v>
@@ -2472,7 +2469,7 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
@@ -2481,42 +2478,42 @@
         <v>1</v>
       </c>
       <c r="T19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Svartöra</t>
+          <t>Liljekonvalj</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 26623-2026 artfynd.xlsx", "A 26623-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 26196-2026 artfynd.xlsx", "A 26196-2026")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 26623-2026 karta.png", "A 26623-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 26196-2026 karta.png", "A 26196-2026")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 26623-2026 georefererad karta.tif", "A 26623-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 26196-2026 georefererad karta.tif", "A 26196-2026")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 26623-2026 FSC-klagomål.docx", "A 26623-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 26196-2026 FSC-klagomål.docx", "A 26196-2026")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 26623-2026 FSC-klagomål mail.docx", "A 26623-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 26196-2026 FSC-klagomål mail.docx", "A 26196-2026")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 26623-2026 tillsynsbegäran.docx", "A 26623-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 26196-2026 tillsynsbegäran.docx", "A 26196-2026")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 26623-2026 tillsynsbegäran mail.docx", "A 26623-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 26196-2026 tillsynsbegäran mail.docx", "A 26196-2026")</f>
         <v/>
       </c>
     </row>
@@ -2540,7 +2537,7 @@
         <v>46184</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2628,7 +2625,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 73773-2021</t>
+          <t>A 26623-2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2642,10 +2639,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>44552</v>
+        <v>46184</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2658,16 +2655,16 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>1.9</v>
+        <v>4.6</v>
       </c>
       <c r="J21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M21" t="n">
         <v>0</v>
@@ -2682,7 +2679,7 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R21" t="n">
         <v>0</v>
@@ -2694,46 +2691,46 @@
         <v>1</v>
       </c>
       <c r="U21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Kopparödla</t>
+          <t>Svartöra</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 73773-2021 artfynd.xlsx", "A 73773-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 26623-2026 artfynd.xlsx", "A 26623-2026")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 73773-2021 karta.png", "A 73773-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 26623-2026 karta.png", "A 26623-2026")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 73773-2021 georefererad karta.tif", "A 73773-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 26623-2026 georefererad karta.tif", "A 26623-2026")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 73773-2021 FSC-klagomål.docx", "A 73773-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 26623-2026 FSC-klagomål.docx", "A 26623-2026")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 73773-2021 FSC-klagomål mail.docx", "A 73773-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 26623-2026 FSC-klagomål mail.docx", "A 26623-2026")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 73773-2021 tillsynsbegäran.docx", "A 73773-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 26623-2026 tillsynsbegäran.docx", "A 26623-2026")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 73773-2021 tillsynsbegäran mail.docx", "A 73773-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 26623-2026 tillsynsbegäran mail.docx", "A 26623-2026")</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 11447-2025</t>
+          <t>A 64098-2023</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2743,14 +2740,14 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45726</v>
+        <v>45279</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2763,16 +2760,16 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>1.5</v>
+        <v>0.3</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M22" t="n">
         <v>0</v>
@@ -2787,7 +2784,7 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R22" t="n">
         <v>0</v>
@@ -2803,35 +2800,35 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>Myskbock</t>
+          <t>Skogsalmsdvärgmal</t>
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 11447-2025 artfynd.xlsx", "A 11447-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 64098-2023 artfynd.xlsx", "A 64098-2023")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 11447-2025 karta.png", "A 11447-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 64098-2023 karta.png", "A 64098-2023")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 11447-2025 georefererad karta.tif", "A 11447-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 64098-2023 georefererad karta.tif", "A 64098-2023")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 11447-2025 FSC-klagomål.docx", "A 11447-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 64098-2023 FSC-klagomål.docx", "A 64098-2023")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 11447-2025 FSC-klagomål mail.docx", "A 11447-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 64098-2023 FSC-klagomål mail.docx", "A 64098-2023")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 11447-2025 tillsynsbegäran.docx", "A 11447-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 64098-2023 tillsynsbegäran.docx", "A 64098-2023")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 11447-2025 tillsynsbegäran mail.docx", "A 11447-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 64098-2023 tillsynsbegäran mail.docx", "A 64098-2023")</f>
         <v/>
       </c>
     </row>
@@ -2855,7 +2852,7 @@
         <v>45671</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2964,7 +2961,7 @@
         <v>44558</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3052,7 +3049,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 58663-2021</t>
+          <t>A 8261-2022</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3066,10 +3063,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>44489</v>
+        <v>44609</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3081,13 +3078,8 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I25" t="n">
-        <v>4.3</v>
+        <v>0.8</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -3130,7 +3122,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 8261-2022</t>
+          <t>A 58663-2021</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3144,10 +3136,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44609</v>
+        <v>44489</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3159,8 +3151,13 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I26" t="n">
-        <v>0.8</v>
+        <v>4.3</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -3220,7 +3217,7 @@
         <v>44546</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3293,7 +3290,7 @@
         <v>44700</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3366,7 +3363,7 @@
         <v>44587</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3439,7 +3436,7 @@
         <v>44655</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3500,7 +3497,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 59700-2021</t>
+          <t>A 64105-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3514,10 +3511,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44494</v>
+        <v>45279</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3529,13 +3526,8 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I31" t="n">
-        <v>4.8</v>
+        <v>2.2</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3578,7 +3570,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 38902-2024</t>
+          <t>A 59844-2022</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3592,10 +3584,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45547</v>
+        <v>44901</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3613,7 +3605,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0.8</v>
+        <v>11.9</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3656,7 +3648,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 50294-2023</t>
+          <t>A 2602-2024</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3670,10 +3662,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45216</v>
+        <v>45313</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3686,7 +3678,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>3.7</v>
+        <v>0.7</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3729,7 +3721,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 9655-2026</t>
+          <t>A 23615-2025</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3743,10 +3735,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>46070</v>
+        <v>45792</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3758,13 +3750,8 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I34" t="n">
-        <v>17.2</v>
+        <v>1.3</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3807,7 +3794,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 5264-2023</t>
+          <t>A 23627-2025</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3821,10 +3808,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44959</v>
+        <v>45792</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3837,7 +3824,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>5.8</v>
+        <v>1.7</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3880,7 +3867,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 18787-2026</t>
+          <t>A 3630-2023</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3894,10 +3881,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>46128</v>
+        <v>44950</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3909,13 +3896,8 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I36" t="n">
-        <v>7.8</v>
+        <v>1.4</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3958,7 +3940,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 18813-2026</t>
+          <t>A 23093-2024</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3972,10 +3954,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>46128</v>
+        <v>45450</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3993,7 +3975,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>56</v>
+        <v>0.9</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4036,7 +4018,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 18818-2026</t>
+          <t>A 54222-2023</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4050,10 +4032,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>46128</v>
+        <v>45225</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4071,7 +4053,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>17.8</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4114,7 +4096,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 18778-2026</t>
+          <t>A 7860-2024</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4128,10 +4110,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>46128</v>
+        <v>45348</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4149,7 +4131,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>4.5</v>
+        <v>1.9</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4192,7 +4174,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 23098-2024</t>
+          <t>A 27313-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4206,10 +4188,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45450</v>
+        <v>45096</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4221,13 +4203,8 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I40" t="n">
-        <v>1</v>
+        <v>1.8</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4270,7 +4247,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 21206-2026</t>
+          <t>A 64114-2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4284,10 +4261,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>46146</v>
+        <v>45279</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4299,13 +4276,8 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I41" t="n">
-        <v>0.9</v>
+        <v>0.4</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4348,7 +4320,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 59844-2022</t>
+          <t>A 50294-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4362,10 +4334,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44901</v>
+        <v>45216</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4377,13 +4349,8 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I42" t="n">
-        <v>11.9</v>
+        <v>3.7</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4426,7 +4393,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 54222-2023</t>
+          <t>A 58011-2021</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4440,10 +4407,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45225</v>
+        <v>44487</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4461,7 +4428,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>8.300000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4504,7 +4471,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 4338-2023</t>
+          <t>A 9655-2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4518,10 +4485,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44953</v>
+        <v>46070</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4533,8 +4500,13 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I44" t="n">
-        <v>1.1</v>
+        <v>17.2</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4577,7 +4549,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 58011-2021</t>
+          <t>A 64110-2023</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4591,10 +4563,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>44487</v>
+        <v>45279</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4606,13 +4578,8 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I45" t="n">
-        <v>9.199999999999999</v>
+        <v>0.4</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4655,7 +4622,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 72524-2021</t>
+          <t>A 23098-2024</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4669,10 +4636,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44546</v>
+        <v>45450</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4684,8 +4651,13 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I46" t="n">
-        <v>3.6</v>
+        <v>1</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4728,7 +4700,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 64107-2023</t>
+          <t>A 18778-2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4742,10 +4714,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45279</v>
+        <v>46128</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4757,8 +4729,13 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I47" t="n">
-        <v>0.3</v>
+        <v>4.5</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4801,7 +4778,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 24579-2026</t>
+          <t>A 18813-2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4815,10 +4792,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>46170</v>
+        <v>46128</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4830,8 +4807,13 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I48" t="n">
-        <v>2.1</v>
+        <v>56</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4874,7 +4856,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 23093-2024</t>
+          <t>A 18818-2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4888,10 +4870,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45450</v>
+        <v>46128</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4909,7 +4891,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>0.9</v>
+        <v>17.8</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4952,7 +4934,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 58598-2025</t>
+          <t>A 18787-2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4966,10 +4948,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45986</v>
+        <v>46128</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4987,7 +4969,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>4.5</v>
+        <v>7.8</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5030,7 +5012,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 31160-2022</t>
+          <t>A 59377-2024</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5044,10 +5026,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>44770</v>
+        <v>45638</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5060,7 +5042,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>3.7</v>
+        <v>0.6</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5103,7 +5085,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 27313-2023</t>
+          <t>A 59402-2022</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5117,10 +5099,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45096</v>
+        <v>44906</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5176,7 +5158,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 26196-2026</t>
+          <t>A 5264-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5186,14 +5168,14 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>46182</v>
+        <v>44959</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5206,7 +5188,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>53.1</v>
+        <v>5.8</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5249,7 +5231,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 26625-2026</t>
+          <t>A 21206-2026</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5263,10 +5245,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>46184</v>
+        <v>46146</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5278,8 +5260,13 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I54" t="n">
-        <v>5.3</v>
+        <v>0.9</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5322,7 +5309,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 59377-2024</t>
+          <t>A 51587-2023</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5336,10 +5323,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45638</v>
+        <v>45215</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5351,8 +5338,13 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I55" t="n">
-        <v>0.6</v>
+        <v>2.6</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5395,7 +5387,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 26629-2026</t>
+          <t>A 72524-2021</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5409,10 +5401,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>46184</v>
+        <v>44546</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5425,7 +5417,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>2</v>
+        <v>3.6</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5468,7 +5460,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 26633-2026</t>
+          <t>A 24579-2026</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5482,10 +5474,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>46184</v>
+        <v>46170</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5498,7 +5490,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>0.7</v>
+        <v>2.1</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5541,7 +5533,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 3754-2026</t>
+          <t>A 4338-2023</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5555,10 +5547,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>46043</v>
+        <v>44953</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5570,13 +5562,8 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I58" t="n">
-        <v>5.1</v>
+        <v>1.1</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5619,7 +5606,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 28797-2026</t>
+          <t>A 31160-2022</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5633,10 +5620,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>46198</v>
+        <v>44770</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5649,7 +5636,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>2.2</v>
+        <v>3.7</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5692,7 +5679,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 28740-2026</t>
+          <t>A 58598-2025</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5706,10 +5693,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>46198</v>
+        <v>45986</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5721,8 +5708,13 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I60" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5765,7 +5757,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 28735-2026</t>
+          <t>A 59848-2022</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5779,10 +5771,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>46198</v>
+        <v>44901</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5794,8 +5786,13 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I61" t="n">
-        <v>3.5</v>
+        <v>10.7</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5838,7 +5835,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 51587-2023</t>
+          <t>A 26633-2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5852,10 +5849,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45215</v>
+        <v>46184</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5867,13 +5864,8 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I62" t="n">
-        <v>2.6</v>
+        <v>0.7</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5916,7 +5908,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 31714-2026</t>
+          <t>A 26625-2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5930,10 +5922,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>46226</v>
+        <v>46184</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5946,7 +5938,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5989,7 +5981,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 59848-2022</t>
+          <t>A 26629-2026</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6003,10 +5995,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>44901</v>
+        <v>46184</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6018,13 +6010,8 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I64" t="n">
-        <v>10.7</v>
+        <v>2</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6067,7 +6054,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 64110-2023</t>
+          <t>A 59700-2021</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6081,10 +6068,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45279</v>
+        <v>44494</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6096,8 +6083,13 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I65" t="n">
-        <v>0.4</v>
+        <v>4.8</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6140,7 +6132,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 33058-2026</t>
+          <t>A 3754-2026</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6150,14 +6142,14 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>46245</v>
+        <v>46043</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6169,8 +6161,13 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I66" t="n">
-        <v>1.3</v>
+        <v>5.1</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6213,7 +6210,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 7275-2022</t>
+          <t>A 28735-2026</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6227,10 +6224,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>44606</v>
+        <v>46198</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6242,13 +6239,8 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I67" t="n">
-        <v>9.6</v>
+        <v>3.5</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6291,7 +6283,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 2602-2024</t>
+          <t>A 28740-2026</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6305,10 +6297,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45313</v>
+        <v>46198</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6321,7 +6313,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>0.7</v>
+        <v>4.8</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6364,7 +6356,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 59402-2022</t>
+          <t>A 28797-2026</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6378,10 +6370,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>44906</v>
+        <v>46198</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6394,7 +6386,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6437,7 +6429,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 3630-2023</t>
+          <t>A 7275-2022</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6451,10 +6443,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>44950</v>
+        <v>44606</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6466,8 +6458,13 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I70" t="n">
-        <v>1.4</v>
+        <v>9.6</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6510,7 +6507,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 7860-2024</t>
+          <t>A 31714-2026</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6524,10 +6521,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45348</v>
+        <v>46226</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6539,13 +6536,8 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I71" t="n">
-        <v>1.9</v>
+        <v>5</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6588,7 +6580,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 64105-2023</t>
+          <t>A 64107-2023</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6605,7 +6597,7 @@
         <v>45279</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6618,7 +6610,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>2.2</v>
+        <v>0.3</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6661,7 +6653,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 64114-2023</t>
+          <t>A 7112-2025</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6675,10 +6667,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45279</v>
+        <v>45701</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6691,7 +6683,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>0.4</v>
+        <v>2.4</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6734,7 +6726,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 7112-2025</t>
+          <t>A 38902-2024</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6748,10 +6740,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45701</v>
+        <v>45547</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6763,8 +6755,13 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I74" t="n">
-        <v>2.4</v>
+        <v>0.8</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6807,7 +6804,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 23615-2025</t>
+          <t>A 33058-2026</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6817,14 +6814,14 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45792</v>
+        <v>46245</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6877,27 +6874,27 @@
       </c>
       <c r="V75" s="2" t="inlineStr"/>
     </row>
-    <row r="76" ht="15" customHeight="1">
+    <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 23627-2025</t>
+          <t>S 10447-2021</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>avverkningsanmälan</t>
+          <t>samrådsanmälan</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45792</v>
+        <v>44558</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6910,7 +6907,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>1.7</v>
+        <v>4.4</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6949,79 +6946,6 @@
         <v>0</v>
       </c>
       <c r="V76" s="2" t="inlineStr"/>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>S 10447-2021</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>Annan skogsbruksåtgärd</t>
-        </is>
-      </c>
-      <c r="D77" s="1" t="n">
-        <v>44558</v>
-      </c>
-      <c r="E77" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>UPPLANDS-BRO</t>
-        </is>
-      </c>
-      <c r="I77" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="J77" t="n">
-        <v>0</v>
-      </c>
-      <c r="K77" t="n">
-        <v>0</v>
-      </c>
-      <c r="L77" t="n">
-        <v>0</v>
-      </c>
-      <c r="M77" t="n">
-        <v>0</v>
-      </c>
-      <c r="N77" t="n">
-        <v>0</v>
-      </c>
-      <c r="O77" t="n">
-        <v>0</v>
-      </c>
-      <c r="P77" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q77" t="n">
-        <v>0</v>
-      </c>
-      <c r="R77" t="n">
-        <v>0</v>
-      </c>
-      <c r="S77" t="n">
-        <v>0</v>
-      </c>
-      <c r="T77" t="n">
-        <v>0</v>
-      </c>
-      <c r="U77" t="n">
-        <v>0</v>
-      </c>
-      <c r="V77" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt UPPLANDS-BRO.xlsx
+++ b/Översikt UPPLANDS-BRO.xlsx
@@ -601,7 +601,7 @@
         <v>44481</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -714,7 +714,7 @@
         <v>44552</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -822,7 +822,7 @@
         <v>44552</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -930,7 +930,7 @@
         <v>45232</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1025,7 +1025,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 73773-2021</t>
+          <t>A 18790-2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1039,10 +1039,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>44552</v>
+        <v>46128</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1054,8 +1054,13 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I6" t="n">
-        <v>1.9</v>
+        <v>5.5</v>
       </c>
       <c r="J6" t="n">
         <v>2</v>
@@ -1088,376 +1093,371 @@
         <v>2</v>
       </c>
       <c r="T6" t="n">
+        <v>2</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>Fläcknycklar
+Nattviol</t>
+        </is>
+      </c>
+      <c r="W6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 18790-2026 artfynd.xlsx", "A 18790-2026")</f>
+        <v/>
+      </c>
+      <c r="X6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 18790-2026 karta.png", "A 18790-2026")</f>
+        <v/>
+      </c>
+      <c r="Y6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 18790-2026 georefererad karta.tif", "A 18790-2026")</f>
+        <v/>
+      </c>
+      <c r="AA6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 18790-2026 FSC-klagomål.docx", "A 18790-2026")</f>
+        <v/>
+      </c>
+      <c r="AB6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 18790-2026 FSC-klagomål mail.docx", "A 18790-2026")</f>
+        <v/>
+      </c>
+      <c r="AC6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 18790-2026 tillsynsbegäran.docx", "A 18790-2026")</f>
+        <v/>
+      </c>
+      <c r="AD6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 18790-2026 tillsynsbegäran mail.docx", "A 18790-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>A 18772-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>46128</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>UPPLANDS-BRO</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>2</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>Svedjenäva
+Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="W7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 18772-2026 artfynd.xlsx", "A 18772-2026")</f>
+        <v/>
+      </c>
+      <c r="X7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 18772-2026 karta.png", "A 18772-2026")</f>
+        <v/>
+      </c>
+      <c r="Y7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 18772-2026 georefererad karta.tif", "A 18772-2026")</f>
+        <v/>
+      </c>
+      <c r="AA7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 18772-2026 FSC-klagomål.docx", "A 18772-2026")</f>
+        <v/>
+      </c>
+      <c r="AB7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 18772-2026 FSC-klagomål mail.docx", "A 18772-2026")</f>
+        <v/>
+      </c>
+      <c r="AC7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 18772-2026 tillsynsbegäran.docx", "A 18772-2026")</f>
+        <v/>
+      </c>
+      <c r="AD7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 18772-2026 tillsynsbegäran mail.docx", "A 18772-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="15" customHeight="1">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>A 10909-2025</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D8" s="1" t="n">
+        <v>45722</v>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>UPPLANDS-BRO</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="J8" t="n">
+        <v>1</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>2</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2</v>
+      </c>
+      <c r="U8" t="n">
+        <v>2</v>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>Arommusseron
+Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="W8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 10909-2025 artfynd.xlsx", "A 10909-2025")</f>
+        <v/>
+      </c>
+      <c r="X8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 10909-2025 karta.png", "A 10909-2025")</f>
+        <v/>
+      </c>
+      <c r="Y8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 10909-2025 georefererad karta.tif", "A 10909-2025")</f>
+        <v/>
+      </c>
+      <c r="AA8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 10909-2025 FSC-klagomål.docx", "A 10909-2025")</f>
+        <v/>
+      </c>
+      <c r="AB8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 10909-2025 FSC-klagomål mail.docx", "A 10909-2025")</f>
+        <v/>
+      </c>
+      <c r="AC8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 10909-2025 tillsynsbegäran.docx", "A 10909-2025")</f>
+        <v/>
+      </c>
+      <c r="AD8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 10909-2025 tillsynsbegäran mail.docx", "A 10909-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="15" customHeight="1">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>A 73773-2021</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D9" s="1" t="n">
+        <v>44552</v>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>UPPLANDS-BRO</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="J9" t="n">
+        <v>2</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>2</v>
+      </c>
+      <c r="T9" t="n">
         <v>3</v>
       </c>
-      <c r="U6" t="n">
+      <c r="U9" t="n">
         <v>3</v>
       </c>
-      <c r="V6" s="2" t="inlineStr">
+      <c r="V9" s="2" t="inlineStr">
         <is>
           <t>Kopparödla
 Gullviva</t>
         </is>
       </c>
-      <c r="W6">
+      <c r="W9">
         <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 73773-2021 artfynd.xlsx", "A 73773-2021")</f>
         <v/>
       </c>
-      <c r="X6">
+      <c r="X9">
         <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 73773-2021 karta.png", "A 73773-2021")</f>
         <v/>
       </c>
-      <c r="Y6">
+      <c r="Y9">
         <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 73773-2021 georefererad karta.tif", "A 73773-2021")</f>
         <v/>
       </c>
-      <c r="AA6">
+      <c r="AA9">
         <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 73773-2021 FSC-klagomål.docx", "A 73773-2021")</f>
         <v/>
       </c>
-      <c r="AB6">
+      <c r="AB9">
         <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 73773-2021 FSC-klagomål mail.docx", "A 73773-2021")</f>
         <v/>
       </c>
-      <c r="AC6">
+      <c r="AC9">
         <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 73773-2021 tillsynsbegäran.docx", "A 73773-2021")</f>
         <v/>
       </c>
-      <c r="AD6">
+      <c r="AD9">
         <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 73773-2021 tillsynsbegäran mail.docx", "A 73773-2021")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>A 18772-2026</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>46128</v>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>46294</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>UPPLANDS-BRO</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="J7" t="n">
-        <v>1</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>1</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>1</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
-        <v>2</v>
-      </c>
-      <c r="T7" t="n">
-        <v>2</v>
-      </c>
-      <c r="U7" t="n">
-        <v>0</v>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>Svedjenäva
-Fläcknycklar</t>
-        </is>
-      </c>
-      <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 18772-2026 artfynd.xlsx", "A 18772-2026")</f>
-        <v/>
-      </c>
-      <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 18772-2026 karta.png", "A 18772-2026")</f>
-        <v/>
-      </c>
-      <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 18772-2026 georefererad karta.tif", "A 18772-2026")</f>
-        <v/>
-      </c>
-      <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 18772-2026 FSC-klagomål.docx", "A 18772-2026")</f>
-        <v/>
-      </c>
-      <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 18772-2026 FSC-klagomål mail.docx", "A 18772-2026")</f>
-        <v/>
-      </c>
-      <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 18772-2026 tillsynsbegäran.docx", "A 18772-2026")</f>
-        <v/>
-      </c>
-      <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 18772-2026 tillsynsbegäran mail.docx", "A 18772-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8" ht="15" customHeight="1">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>A 18790-2026</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D8" s="1" t="n">
-        <v>46128</v>
-      </c>
-      <c r="E8" s="1" t="n">
-        <v>46294</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>UPPLANDS-BRO</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
-      <c r="I8" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="J8" t="n">
-        <v>2</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" t="n">
-        <v>2</v>
-      </c>
-      <c r="T8" t="n">
-        <v>2</v>
-      </c>
-      <c r="U8" t="n">
-        <v>0</v>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>Fläcknycklar
-Nattviol</t>
-        </is>
-      </c>
-      <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 18790-2026 artfynd.xlsx", "A 18790-2026")</f>
-        <v/>
-      </c>
-      <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 18790-2026 karta.png", "A 18790-2026")</f>
-        <v/>
-      </c>
-      <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 18790-2026 georefererad karta.tif", "A 18790-2026")</f>
-        <v/>
-      </c>
-      <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 18790-2026 FSC-klagomål.docx", "A 18790-2026")</f>
-        <v/>
-      </c>
-      <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 18790-2026 FSC-klagomål mail.docx", "A 18790-2026")</f>
-        <v/>
-      </c>
-      <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 18790-2026 tillsynsbegäran.docx", "A 18790-2026")</f>
-        <v/>
-      </c>
-      <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 18790-2026 tillsynsbegäran mail.docx", "A 18790-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9" ht="15" customHeight="1">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>A 10909-2025</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D9" s="1" t="n">
-        <v>45722</v>
-      </c>
-      <c r="E9" s="1" t="n">
-        <v>46294</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>UPPLANDS-BRO</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="J9" t="n">
-        <v>1</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>1</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>1</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" t="n">
-        <v>2</v>
-      </c>
-      <c r="T9" t="n">
-        <v>2</v>
-      </c>
-      <c r="U9" t="n">
-        <v>2</v>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>Arommusseron
-Fläcknycklar</t>
-        </is>
-      </c>
-      <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 10909-2025 artfynd.xlsx", "A 10909-2025")</f>
-        <v/>
-      </c>
-      <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 10909-2025 karta.png", "A 10909-2025")</f>
-        <v/>
-      </c>
-      <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 10909-2025 georefererad karta.tif", "A 10909-2025")</f>
-        <v/>
-      </c>
-      <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 10909-2025 FSC-klagomål.docx", "A 10909-2025")</f>
-        <v/>
-      </c>
-      <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 10909-2025 FSC-klagomål mail.docx", "A 10909-2025")</f>
-        <v/>
-      </c>
-      <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 10909-2025 tillsynsbegäran.docx", "A 10909-2025")</f>
-        <v/>
-      </c>
-      <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 10909-2025 tillsynsbegäran mail.docx", "A 10909-2025")</f>
         <v/>
       </c>
     </row>
@@ -1481,7 +1481,7 @@
         <v>44603</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1587,7 +1587,7 @@
         <v>44552</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1675,7 +1675,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 25561-2025</t>
+          <t>A 7955-2023</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1689,10 +1689,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45803</v>
+        <v>44973</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1705,7 +1705,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>1.6</v>
+        <v>2.9</v>
       </c>
       <c r="J12" t="n">
         <v>1</v>
@@ -1741,7 +1741,7 @@
         <v>1</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
@@ -1749,38 +1749,38 @@
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 25561-2025 artfynd.xlsx", "A 25561-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 7955-2023 artfynd.xlsx", "A 7955-2023")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 25561-2025 karta.png", "A 25561-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 7955-2023 karta.png", "A 7955-2023")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 25561-2025 georefererad karta.tif", "A 25561-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 7955-2023 georefererad karta.tif", "A 7955-2023")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 25561-2025 FSC-klagomål.docx", "A 25561-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 7955-2023 FSC-klagomål.docx", "A 7955-2023")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 25561-2025 FSC-klagomål mail.docx", "A 25561-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 7955-2023 FSC-klagomål mail.docx", "A 7955-2023")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 25561-2025 tillsynsbegäran.docx", "A 25561-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 7955-2023 tillsynsbegäran.docx", "A 7955-2023")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 25561-2025 tillsynsbegäran mail.docx", "A 25561-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 7955-2023 tillsynsbegäran mail.docx", "A 7955-2023")</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 12363-2025</t>
+          <t>A 25561-2025</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1794,10 +1794,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45730</v>
+        <v>45803</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1810,13 +1810,13 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>0.8</v>
+        <v>1.6</v>
       </c>
       <c r="J13" t="n">
         <v>1</v>
       </c>
       <c r="K13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -1825,7 +1825,7 @@
         <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -1834,10 +1834,10 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
@@ -1850,42 +1850,42 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Bombmurkla</t>
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 12363-2025 artfynd.xlsx", "A 12363-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 25561-2025 artfynd.xlsx", "A 25561-2025")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 12363-2025 karta.png", "A 12363-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 25561-2025 karta.png", "A 25561-2025")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 12363-2025 georefererad karta.tif", "A 12363-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 25561-2025 georefererad karta.tif", "A 25561-2025")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 12363-2025 FSC-klagomål.docx", "A 12363-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 25561-2025 FSC-klagomål.docx", "A 25561-2025")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 12363-2025 FSC-klagomål mail.docx", "A 12363-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 25561-2025 FSC-klagomål mail.docx", "A 25561-2025")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 12363-2025 tillsynsbegäran.docx", "A 12363-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 25561-2025 tillsynsbegäran.docx", "A 25561-2025")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 12363-2025 tillsynsbegäran mail.docx", "A 12363-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 25561-2025 tillsynsbegäran mail.docx", "A 25561-2025")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 53357-2025</t>
+          <t>A 12363-2025</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1899,10 +1899,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45959</v>
+        <v>45730</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1915,13 +1915,13 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>2.4</v>
+        <v>0.8</v>
       </c>
       <c r="J14" t="n">
         <v>1</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
@@ -1930,7 +1930,7 @@
         <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -1939,58 +1939,58 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
       </c>
       <c r="T14" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="U14" t="n">
         <v>0</v>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Bombmurkla</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 53357-2025 artfynd.xlsx", "A 53357-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 12363-2025 artfynd.xlsx", "A 12363-2025")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 53357-2025 karta.png", "A 53357-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 12363-2025 karta.png", "A 12363-2025")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 53357-2025 georefererad karta.tif", "A 53357-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 12363-2025 georefererad karta.tif", "A 12363-2025")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 53357-2025 FSC-klagomål.docx", "A 53357-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 12363-2025 FSC-klagomål.docx", "A 12363-2025")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 53357-2025 FSC-klagomål mail.docx", "A 53357-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 12363-2025 FSC-klagomål mail.docx", "A 12363-2025")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 53357-2025 tillsynsbegäran.docx", "A 53357-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 12363-2025 tillsynsbegäran.docx", "A 12363-2025")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 53357-2025 tillsynsbegäran mail.docx", "A 53357-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 12363-2025 tillsynsbegäran mail.docx", "A 12363-2025")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 23099-2024</t>
+          <t>A 46438-2023</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2004,10 +2004,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45450</v>
+        <v>45197</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2019,16 +2019,11 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I15" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
@@ -2037,10 +2032,10 @@
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2061,46 +2056,46 @@
         <v>1</v>
       </c>
       <c r="U15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Bredbrämad bastardsvärmare</t>
+          <t>Bombmurkla</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 23099-2024 artfynd.xlsx", "A 23099-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 46438-2023 artfynd.xlsx", "A 46438-2023")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 23099-2024 karta.png", "A 23099-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 46438-2023 karta.png", "A 46438-2023")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 23099-2024 georefererad karta.tif", "A 23099-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 46438-2023 georefererad karta.tif", "A 46438-2023")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 23099-2024 FSC-klagomål.docx", "A 23099-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 46438-2023 FSC-klagomål.docx", "A 46438-2023")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 23099-2024 FSC-klagomål mail.docx", "A 23099-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 46438-2023 FSC-klagomål mail.docx", "A 46438-2023")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 23099-2024 tillsynsbegäran.docx", "A 23099-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 46438-2023 tillsynsbegäran.docx", "A 46438-2023")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 23099-2024 tillsynsbegäran mail.docx", "A 23099-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 46438-2023 tillsynsbegäran mail.docx", "A 46438-2023")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 46438-2023</t>
+          <t>A 53357-2025</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2114,10 +2109,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45197</v>
+        <v>45959</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2130,7 +2125,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>0.5</v>
+        <v>2.4</v>
       </c>
       <c r="J16" t="n">
         <v>1</v>
@@ -2163,7 +2158,7 @@
         <v>1</v>
       </c>
       <c r="T16" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="U16" t="n">
         <v>0</v>
@@ -2174,38 +2169,38 @@
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 46438-2023 artfynd.xlsx", "A 46438-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 53357-2025 artfynd.xlsx", "A 53357-2025")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 46438-2023 karta.png", "A 46438-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 53357-2025 karta.png", "A 53357-2025")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 46438-2023 georefererad karta.tif", "A 46438-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 53357-2025 georefererad karta.tif", "A 53357-2025")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 46438-2023 FSC-klagomål.docx", "A 46438-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 53357-2025 FSC-klagomål.docx", "A 53357-2025")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 46438-2023 FSC-klagomål mail.docx", "A 46438-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 53357-2025 FSC-klagomål mail.docx", "A 53357-2025")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 46438-2023 tillsynsbegäran.docx", "A 46438-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 53357-2025 tillsynsbegäran.docx", "A 53357-2025")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 46438-2023 tillsynsbegäran mail.docx", "A 46438-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 53357-2025 tillsynsbegäran mail.docx", "A 53357-2025")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 11447-2025</t>
+          <t>A 23099-2024</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2215,14 +2210,14 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45726</v>
+        <v>45450</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2234,20 +2229,25 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I17" t="n">
-        <v>1.5</v>
+        <v>0.7</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
@@ -2259,10 +2259,10 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
@@ -2271,46 +2271,46 @@
         <v>1</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Myskbock</t>
+          <t>Bredbrämad bastardsvärmare</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 11447-2025 artfynd.xlsx", "A 11447-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 23099-2024 artfynd.xlsx", "A 23099-2024")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 11447-2025 karta.png", "A 11447-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 23099-2024 karta.png", "A 23099-2024")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 11447-2025 georefererad karta.tif", "A 11447-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 23099-2024 georefererad karta.tif", "A 23099-2024")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 11447-2025 FSC-klagomål.docx", "A 11447-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 23099-2024 FSC-klagomål.docx", "A 23099-2024")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 11447-2025 FSC-klagomål mail.docx", "A 11447-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 23099-2024 FSC-klagomål mail.docx", "A 23099-2024")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 11447-2025 tillsynsbegäran.docx", "A 11447-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 23099-2024 tillsynsbegäran.docx", "A 23099-2024")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 11447-2025 tillsynsbegäran mail.docx", "A 11447-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 23099-2024 tillsynsbegäran mail.docx", "A 23099-2024")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 7955-2023</t>
+          <t>A 64098-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2324,10 +2324,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>44973</v>
+        <v>45279</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2340,22 +2340,22 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>2.9</v>
+        <v>0.3</v>
       </c>
       <c r="J18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2367,7 +2367,7 @@
         <v>1</v>
       </c>
       <c r="R18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
@@ -2376,39 +2376,39 @@
         <v>1</v>
       </c>
       <c r="U18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Bombmurkla</t>
+          <t>Skogsalmsdvärgmal</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 7955-2023 artfynd.xlsx", "A 7955-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 64098-2023 artfynd.xlsx", "A 64098-2023")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 7955-2023 karta.png", "A 7955-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 64098-2023 karta.png", "A 64098-2023")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 7955-2023 georefererad karta.tif", "A 7955-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 64098-2023 georefererad karta.tif", "A 64098-2023")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 7955-2023 FSC-klagomål.docx", "A 7955-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 64098-2023 FSC-klagomål.docx", "A 64098-2023")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 7955-2023 FSC-klagomål mail.docx", "A 7955-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 64098-2023 FSC-klagomål mail.docx", "A 64098-2023")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 7955-2023 tillsynsbegäran.docx", "A 7955-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 64098-2023 tillsynsbegäran.docx", "A 64098-2023")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 7955-2023 tillsynsbegäran mail.docx", "A 7955-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 64098-2023 tillsynsbegäran mail.docx", "A 64098-2023")</f>
         <v/>
       </c>
     </row>
@@ -2432,7 +2432,7 @@
         <v>46182</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2520,7 +2520,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 26637-2026</t>
+          <t>A 11447-2025</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2530,14 +2530,14 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46184</v>
+        <v>45726</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2550,19 +2550,19 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>5.4</v>
+        <v>1.5</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
         <v>0</v>
@@ -2574,10 +2574,10 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>
@@ -2590,35 +2590,35 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>Igelkott</t>
+          <t>Myskbock</t>
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 26637-2026 artfynd.xlsx", "A 26637-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 11447-2025 artfynd.xlsx", "A 11447-2025")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 26637-2026 karta.png", "A 26637-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 11447-2025 karta.png", "A 11447-2025")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 26637-2026 georefererad karta.tif", "A 26637-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 11447-2025 georefererad karta.tif", "A 11447-2025")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 26637-2026 FSC-klagomål.docx", "A 26637-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 11447-2025 FSC-klagomål.docx", "A 11447-2025")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 26637-2026 FSC-klagomål mail.docx", "A 26637-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 11447-2025 FSC-klagomål mail.docx", "A 11447-2025")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 26637-2026 tillsynsbegäran.docx", "A 26637-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 11447-2025 tillsynsbegäran.docx", "A 11447-2025")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 26637-2026 tillsynsbegäran mail.docx", "A 26637-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 11447-2025 tillsynsbegäran mail.docx", "A 11447-2025")</f>
         <v/>
       </c>
     </row>
@@ -2642,7 +2642,7 @@
         <v>46184</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2730,7 +2730,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 64098-2023</t>
+          <t>A 26637-2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2744,10 +2744,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45279</v>
+        <v>46184</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2760,7 +2760,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>0.3</v>
+        <v>5.4</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2769,10 +2769,10 @@
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N22" t="n">
         <v>0</v>
@@ -2787,7 +2787,7 @@
         <v>1</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S22" t="n">
         <v>1</v>
@@ -2800,35 +2800,35 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>Skogsalmsdvärgmal</t>
+          <t>Igelkott</t>
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 64098-2023 artfynd.xlsx", "A 64098-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 26637-2026 artfynd.xlsx", "A 26637-2026")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 64098-2023 karta.png", "A 64098-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 26637-2026 karta.png", "A 26637-2026")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 64098-2023 georefererad karta.tif", "A 64098-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 26637-2026 georefererad karta.tif", "A 26637-2026")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 64098-2023 FSC-klagomål.docx", "A 64098-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 26637-2026 FSC-klagomål.docx", "A 26637-2026")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 64098-2023 FSC-klagomål mail.docx", "A 64098-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 26637-2026 FSC-klagomål mail.docx", "A 26637-2026")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 64098-2023 tillsynsbegäran.docx", "A 64098-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 26637-2026 tillsynsbegäran.docx", "A 26637-2026")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 64098-2023 tillsynsbegäran mail.docx", "A 64098-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 26637-2026 tillsynsbegäran mail.docx", "A 26637-2026")</f>
         <v/>
       </c>
     </row>
@@ -2852,7 +2852,7 @@
         <v>45671</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2961,7 +2961,7 @@
         <v>44558</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3066,7 +3066,7 @@
         <v>44609</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3139,7 +3139,7 @@
         <v>44489</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3217,7 +3217,7 @@
         <v>44546</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3290,7 +3290,7 @@
         <v>44700</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3363,7 +3363,7 @@
         <v>44587</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3436,7 +3436,7 @@
         <v>44655</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3497,7 +3497,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 64105-2023</t>
+          <t>A 23615-2025</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3511,10 +3511,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45279</v>
+        <v>45792</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3527,7 +3527,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>2.2</v>
+        <v>1.3</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3570,7 +3570,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 59844-2022</t>
+          <t>A 23627-2025</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3584,10 +3584,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44901</v>
+        <v>45792</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3599,13 +3599,8 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I32" t="n">
-        <v>11.9</v>
+        <v>1.7</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3648,7 +3643,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 2602-2024</t>
+          <t>A 59700-2021</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3662,10 +3657,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45313</v>
+        <v>44494</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3677,8 +3672,13 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I33" t="n">
-        <v>0.7</v>
+        <v>4.8</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3721,7 +3721,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 23615-2025</t>
+          <t>A 38902-2024</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3735,10 +3735,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45792</v>
+        <v>45547</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3750,8 +3750,13 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I34" t="n">
-        <v>1.3</v>
+        <v>0.8</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3794,7 +3799,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 23627-2025</t>
+          <t>A 50294-2023</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3808,10 +3813,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45792</v>
+        <v>45216</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3824,7 +3829,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>1.7</v>
+        <v>3.7</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3867,7 +3872,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 3630-2023</t>
+          <t>A 5264-2023</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3881,10 +3886,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44950</v>
+        <v>44959</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3897,7 +3902,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>1.4</v>
+        <v>5.8</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3940,7 +3945,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 23093-2024</t>
+          <t>A 9655-2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3954,10 +3959,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45450</v>
+        <v>46070</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3975,7 +3980,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>0.9</v>
+        <v>17.2</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4018,7 +4023,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 54222-2023</t>
+          <t>A 23098-2024</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4032,10 +4037,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45225</v>
+        <v>45450</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4053,7 +4058,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>8.300000000000001</v>
+        <v>1</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4096,7 +4101,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 7860-2024</t>
+          <t>A 59844-2022</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4110,10 +4115,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45348</v>
+        <v>44901</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4131,7 +4136,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1.9</v>
+        <v>11.9</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4174,7 +4179,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 27313-2023</t>
+          <t>A 54222-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4188,10 +4193,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45096</v>
+        <v>45225</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4203,8 +4208,13 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I40" t="n">
-        <v>1.8</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4247,7 +4257,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 64114-2023</t>
+          <t>A 18787-2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4261,10 +4271,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45279</v>
+        <v>46128</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4276,8 +4286,13 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I41" t="n">
-        <v>0.4</v>
+        <v>7.8</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4320,7 +4335,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 50294-2023</t>
+          <t>A 18813-2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4334,10 +4349,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45216</v>
+        <v>46128</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4349,8 +4364,13 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I42" t="n">
-        <v>3.7</v>
+        <v>56</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4393,7 +4413,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 58011-2021</t>
+          <t>A 18818-2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4407,10 +4427,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44487</v>
+        <v>46128</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4428,7 +4448,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>9.199999999999999</v>
+        <v>17.8</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4471,7 +4491,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 9655-2026</t>
+          <t>A 18778-2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4485,10 +4505,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>46070</v>
+        <v>46128</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4506,7 +4526,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>17.2</v>
+        <v>4.5</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4549,7 +4569,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 64110-2023</t>
+          <t>A 4338-2023</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4563,10 +4583,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45279</v>
+        <v>44953</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4579,7 +4599,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.4</v>
+        <v>1.1</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4622,7 +4642,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 23098-2024</t>
+          <t>A 58011-2021</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4636,10 +4656,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45450</v>
+        <v>44487</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4657,7 +4677,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4700,7 +4720,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 18778-2026</t>
+          <t>A 72524-2021</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4714,10 +4734,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>46128</v>
+        <v>44546</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4729,13 +4749,8 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I47" t="n">
-        <v>4.5</v>
+        <v>3.6</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4778,7 +4793,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 18813-2026</t>
+          <t>A 64107-2023</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4792,10 +4807,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>46128</v>
+        <v>45279</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4807,13 +4822,8 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I48" t="n">
-        <v>56</v>
+        <v>0.3</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4856,7 +4866,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 18818-2026</t>
+          <t>A 23093-2024</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4870,10 +4880,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>46128</v>
+        <v>45450</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4891,7 +4901,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>17.8</v>
+        <v>0.9</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4934,7 +4944,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 18787-2026</t>
+          <t>A 27313-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4948,10 +4958,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>46128</v>
+        <v>45096</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4963,13 +4973,8 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I50" t="n">
-        <v>7.8</v>
+        <v>1.8</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5029,7 +5034,7 @@
         <v>45638</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5085,7 +5090,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 59402-2022</t>
+          <t>A 21206-2026</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5099,10 +5104,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>44906</v>
+        <v>46146</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5114,8 +5119,13 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I52" t="n">
-        <v>1.8</v>
+        <v>0.9</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5158,7 +5168,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 5264-2023</t>
+          <t>A 51587-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5172,10 +5182,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>44959</v>
+        <v>45215</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5187,8 +5197,13 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I53" t="n">
-        <v>5.8</v>
+        <v>2.6</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5231,7 +5246,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 21206-2026</t>
+          <t>A 24579-2026</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5245,10 +5260,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>46146</v>
+        <v>46170</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5260,13 +5275,8 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I54" t="n">
-        <v>0.9</v>
+        <v>2.1</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5309,7 +5319,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 51587-2023</t>
+          <t>A 58598-2025</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5323,10 +5333,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45215</v>
+        <v>45986</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5340,11 +5350,11 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Allmännings- och besparingsskogar</t>
+          <t>Övriga statliga verk och myndigheter</t>
         </is>
       </c>
       <c r="I55" t="n">
-        <v>2.6</v>
+        <v>4.5</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5387,7 +5397,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 72524-2021</t>
+          <t>A 31160-2022</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5401,10 +5411,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>44546</v>
+        <v>44770</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5417,7 +5427,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5460,7 +5470,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 24579-2026</t>
+          <t>A 26625-2026</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5474,10 +5484,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>46170</v>
+        <v>46184</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5490,7 +5500,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>2.1</v>
+        <v>5.3</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5533,7 +5543,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 4338-2023</t>
+          <t>A 26629-2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5547,10 +5557,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>44953</v>
+        <v>46184</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5563,7 +5573,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>1.1</v>
+        <v>2</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5606,7 +5616,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 31160-2022</t>
+          <t>A 26633-2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5620,10 +5630,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>44770</v>
+        <v>46184</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5636,7 +5646,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>3.7</v>
+        <v>0.7</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5679,7 +5689,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 58598-2025</t>
+          <t>A 59848-2022</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5693,10 +5703,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45986</v>
+        <v>44901</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5714,7 +5724,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>4.5</v>
+        <v>10.7</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5757,7 +5767,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 59848-2022</t>
+          <t>A 64110-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5771,10 +5781,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>44901</v>
+        <v>45279</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5786,13 +5796,8 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I61" t="n">
-        <v>10.7</v>
+        <v>0.4</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5835,7 +5840,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 26633-2026</t>
+          <t>A 3754-2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5849,10 +5854,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>46184</v>
+        <v>46043</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5864,8 +5869,13 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I62" t="n">
-        <v>0.7</v>
+        <v>5.1</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5908,7 +5918,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 26625-2026</t>
+          <t>A 28797-2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5922,10 +5932,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>46184</v>
+        <v>46198</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5938,7 +5948,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>5.3</v>
+        <v>2.2</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5981,7 +5991,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 26629-2026</t>
+          <t>A 28740-2026</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5995,10 +6005,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>46184</v>
+        <v>46198</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6011,7 +6021,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>2</v>
+        <v>4.8</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6054,7 +6064,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 59700-2021</t>
+          <t>A 28735-2026</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6068,10 +6078,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>44494</v>
+        <v>46198</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6083,13 +6093,8 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I65" t="n">
-        <v>4.8</v>
+        <v>3.5</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6132,7 +6137,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 3754-2026</t>
+          <t>A 7275-2022</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6146,10 +6151,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>46043</v>
+        <v>44606</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6167,7 +6172,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>5.1</v>
+        <v>9.6</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6210,7 +6215,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 28735-2026</t>
+          <t>A 2602-2024</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6224,10 +6229,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>46198</v>
+        <v>45313</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6240,7 +6245,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>3.5</v>
+        <v>0.7</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6283,7 +6288,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 28740-2026</t>
+          <t>A 59402-2022</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6297,10 +6302,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>46198</v>
+        <v>44906</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6313,7 +6318,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>4.8</v>
+        <v>1.8</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6356,7 +6361,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 28797-2026</t>
+          <t>A 3630-2023</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6370,10 +6375,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>46198</v>
+        <v>44950</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6386,7 +6391,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>2.2</v>
+        <v>1.4</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6429,7 +6434,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 7275-2022</t>
+          <t>A 7860-2024</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6443,10 +6448,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>44606</v>
+        <v>45348</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6464,7 +6469,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>9.6</v>
+        <v>1.9</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6524,7 +6529,7 @@
         <v>46226</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6580,7 +6585,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 64107-2023</t>
+          <t>A 64105-2023</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6597,7 +6602,7 @@
         <v>45279</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6610,7 +6615,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>0.3</v>
+        <v>2.2</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6653,7 +6658,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 7112-2025</t>
+          <t>A 64114-2023</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6667,10 +6672,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45701</v>
+        <v>45279</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6683,7 +6688,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>2.4</v>
+        <v>0.4</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6726,7 +6731,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 38902-2024</t>
+          <t>A 33058-2026</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6736,14 +6741,14 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45547</v>
+        <v>46245</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6755,13 +6760,8 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I74" t="n">
-        <v>0.8</v>
+        <v>1.3</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6804,7 +6804,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 33058-2026</t>
+          <t>A 7112-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6814,14 +6814,14 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>46245</v>
+        <v>45701</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6834,7 +6834,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>1.3</v>
+        <v>2.4</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6894,7 +6894,7 @@
         <v>44558</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>

--- a/Översikt UPPLANDS-BRO.xlsx
+++ b/Översikt UPPLANDS-BRO.xlsx
@@ -601,7 +601,7 @@
         <v>44481</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -714,7 +714,7 @@
         <v>44552</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -822,7 +822,7 @@
         <v>44552</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -930,7 +930,7 @@
         <v>45232</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1025,7 +1025,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 18790-2026</t>
+          <t>A 73773-2021</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1039,10 +1039,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46128</v>
+        <v>44552</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1054,13 +1054,8 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I6" t="n">
-        <v>5.5</v>
+        <v>1.9</v>
       </c>
       <c r="J6" t="n">
         <v>2</v>
@@ -1093,371 +1088,376 @@
         <v>2</v>
       </c>
       <c r="T6" t="n">
+        <v>3</v>
+      </c>
+      <c r="U6" t="n">
+        <v>3</v>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>Kopparödla
+Gullviva</t>
+        </is>
+      </c>
+      <c r="W6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 73773-2021 artfynd.xlsx", "A 73773-2021")</f>
+        <v/>
+      </c>
+      <c r="X6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 73773-2021 karta.png", "A 73773-2021")</f>
+        <v/>
+      </c>
+      <c r="Y6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 73773-2021 georefererad karta.tif", "A 73773-2021")</f>
+        <v/>
+      </c>
+      <c r="AA6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 73773-2021 FSC-klagomål.docx", "A 73773-2021")</f>
+        <v/>
+      </c>
+      <c r="AB6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 73773-2021 FSC-klagomål mail.docx", "A 73773-2021")</f>
+        <v/>
+      </c>
+      <c r="AC6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 73773-2021 tillsynsbegäran.docx", "A 73773-2021")</f>
+        <v/>
+      </c>
+      <c r="AD6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 73773-2021 tillsynsbegäran mail.docx", "A 73773-2021")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>A 18772-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>46128</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>UPPLANDS-BRO</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
         <v>2</v>
       </c>
-      <c r="U6" t="n">
-        <v>0</v>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
+      <c r="T7" t="n">
+        <v>2</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>Svedjenäva
+Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="W7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 18772-2026 artfynd.xlsx", "A 18772-2026")</f>
+        <v/>
+      </c>
+      <c r="X7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 18772-2026 karta.png", "A 18772-2026")</f>
+        <v/>
+      </c>
+      <c r="Y7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 18772-2026 georefererad karta.tif", "A 18772-2026")</f>
+        <v/>
+      </c>
+      <c r="AA7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 18772-2026 FSC-klagomål.docx", "A 18772-2026")</f>
+        <v/>
+      </c>
+      <c r="AB7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 18772-2026 FSC-klagomål mail.docx", "A 18772-2026")</f>
+        <v/>
+      </c>
+      <c r="AC7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 18772-2026 tillsynsbegäran.docx", "A 18772-2026")</f>
+        <v/>
+      </c>
+      <c r="AD7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 18772-2026 tillsynsbegäran mail.docx", "A 18772-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="15" customHeight="1">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>A 18790-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D8" s="1" t="n">
+        <v>46128</v>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>UPPLANDS-BRO</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="J8" t="n">
+        <v>2</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>2</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>Fläcknycklar
 Nattviol</t>
         </is>
       </c>
-      <c r="W6">
+      <c r="W8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 18790-2026 artfynd.xlsx", "A 18790-2026")</f>
         <v/>
       </c>
-      <c r="X6">
+      <c r="X8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 18790-2026 karta.png", "A 18790-2026")</f>
         <v/>
       </c>
-      <c r="Y6">
+      <c r="Y8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 18790-2026 georefererad karta.tif", "A 18790-2026")</f>
         <v/>
       </c>
-      <c r="AA6">
+      <c r="AA8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 18790-2026 FSC-klagomål.docx", "A 18790-2026")</f>
         <v/>
       </c>
-      <c r="AB6">
+      <c r="AB8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 18790-2026 FSC-klagomål mail.docx", "A 18790-2026")</f>
         <v/>
       </c>
-      <c r="AC6">
+      <c r="AC8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 18790-2026 tillsynsbegäran.docx", "A 18790-2026")</f>
         <v/>
       </c>
-      <c r="AD6">
+      <c r="AD8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 18790-2026 tillsynsbegäran mail.docx", "A 18790-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>A 18772-2026</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
+    <row r="9" ht="15" customHeight="1">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>A 10909-2025</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D7" s="1" t="n">
-        <v>46128</v>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>46295</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>UPPLANDS-BRO</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="J7" t="n">
-        <v>1</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>1</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>1</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
+      <c r="D9" s="1" t="n">
+        <v>45722</v>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>UPPLANDS-BRO</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
         <v>2</v>
       </c>
-      <c r="T7" t="n">
+      <c r="T9" t="n">
         <v>2</v>
       </c>
-      <c r="U7" t="n">
-        <v>0</v>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>Svedjenäva
-Fläcknycklar</t>
-        </is>
-      </c>
-      <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 18772-2026 artfynd.xlsx", "A 18772-2026")</f>
-        <v/>
-      </c>
-      <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 18772-2026 karta.png", "A 18772-2026")</f>
-        <v/>
-      </c>
-      <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 18772-2026 georefererad karta.tif", "A 18772-2026")</f>
-        <v/>
-      </c>
-      <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 18772-2026 FSC-klagomål.docx", "A 18772-2026")</f>
-        <v/>
-      </c>
-      <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 18772-2026 FSC-klagomål mail.docx", "A 18772-2026")</f>
-        <v/>
-      </c>
-      <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 18772-2026 tillsynsbegäran.docx", "A 18772-2026")</f>
-        <v/>
-      </c>
-      <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 18772-2026 tillsynsbegäran mail.docx", "A 18772-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8" ht="15" customHeight="1">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>A 10909-2025</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D8" s="1" t="n">
-        <v>45722</v>
-      </c>
-      <c r="E8" s="1" t="n">
-        <v>46295</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>UPPLANDS-BRO</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
-      <c r="I8" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="J8" t="n">
-        <v>1</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>1</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>1</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" t="n">
+      <c r="U9" t="n">
         <v>2</v>
       </c>
-      <c r="T8" t="n">
-        <v>2</v>
-      </c>
-      <c r="U8" t="n">
-        <v>2</v>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
+      <c r="V9" s="2" t="inlineStr">
         <is>
           <t>Arommusseron
 Fläcknycklar</t>
         </is>
       </c>
-      <c r="W8">
+      <c r="W9">
         <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 10909-2025 artfynd.xlsx", "A 10909-2025")</f>
         <v/>
       </c>
-      <c r="X8">
+      <c r="X9">
         <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 10909-2025 karta.png", "A 10909-2025")</f>
         <v/>
       </c>
-      <c r="Y8">
+      <c r="Y9">
         <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 10909-2025 georefererad karta.tif", "A 10909-2025")</f>
         <v/>
       </c>
-      <c r="AA8">
+      <c r="AA9">
         <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 10909-2025 FSC-klagomål.docx", "A 10909-2025")</f>
         <v/>
       </c>
-      <c r="AB8">
+      <c r="AB9">
         <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 10909-2025 FSC-klagomål mail.docx", "A 10909-2025")</f>
         <v/>
       </c>
-      <c r="AC8">
+      <c r="AC9">
         <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 10909-2025 tillsynsbegäran.docx", "A 10909-2025")</f>
         <v/>
       </c>
-      <c r="AD8">
+      <c r="AD9">
         <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 10909-2025 tillsynsbegäran mail.docx", "A 10909-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9" ht="15" customHeight="1">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>A 73773-2021</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D9" s="1" t="n">
-        <v>44552</v>
-      </c>
-      <c r="E9" s="1" t="n">
-        <v>46295</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>UPPLANDS-BRO</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="J9" t="n">
-        <v>2</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" t="n">
-        <v>2</v>
-      </c>
-      <c r="T9" t="n">
-        <v>3</v>
-      </c>
-      <c r="U9" t="n">
-        <v>3</v>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>Kopparödla
-Gullviva</t>
-        </is>
-      </c>
-      <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 73773-2021 artfynd.xlsx", "A 73773-2021")</f>
-        <v/>
-      </c>
-      <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 73773-2021 karta.png", "A 73773-2021")</f>
-        <v/>
-      </c>
-      <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 73773-2021 georefererad karta.tif", "A 73773-2021")</f>
-        <v/>
-      </c>
-      <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 73773-2021 FSC-klagomål.docx", "A 73773-2021")</f>
-        <v/>
-      </c>
-      <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 73773-2021 FSC-klagomål mail.docx", "A 73773-2021")</f>
-        <v/>
-      </c>
-      <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 73773-2021 tillsynsbegäran.docx", "A 73773-2021")</f>
-        <v/>
-      </c>
-      <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 73773-2021 tillsynsbegäran mail.docx", "A 73773-2021")</f>
         <v/>
       </c>
     </row>
@@ -1481,7 +1481,7 @@
         <v>44603</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1587,7 +1587,7 @@
         <v>44552</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1675,7 +1675,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 7955-2023</t>
+          <t>A 11447-2025</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1685,14 +1685,14 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>44973</v>
+        <v>45726</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1705,13 +1705,13 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>2.9</v>
+        <v>1.5</v>
       </c>
       <c r="J12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
@@ -1720,7 +1720,7 @@
         <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1729,10 +1729,10 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1741,46 +1741,46 @@
         <v>1</v>
       </c>
       <c r="U12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>Bombmurkla</t>
+          <t>Myskbock</t>
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 7955-2023 artfynd.xlsx", "A 7955-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 11447-2025 artfynd.xlsx", "A 11447-2025")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 7955-2023 karta.png", "A 7955-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 11447-2025 karta.png", "A 11447-2025")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 7955-2023 georefererad karta.tif", "A 7955-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 11447-2025 georefererad karta.tif", "A 11447-2025")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 7955-2023 FSC-klagomål.docx", "A 7955-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 11447-2025 FSC-klagomål.docx", "A 11447-2025")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 7955-2023 FSC-klagomål mail.docx", "A 7955-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 11447-2025 FSC-klagomål mail.docx", "A 11447-2025")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 7955-2023 tillsynsbegäran.docx", "A 7955-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 11447-2025 tillsynsbegäran.docx", "A 11447-2025")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 7955-2023 tillsynsbegäran mail.docx", "A 7955-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 11447-2025 tillsynsbegäran mail.docx", "A 11447-2025")</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 25561-2025</t>
+          <t>A 7955-2023</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1794,10 +1794,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45803</v>
+        <v>44973</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1810,7 +1810,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>1.6</v>
+        <v>2.9</v>
       </c>
       <c r="J13" t="n">
         <v>1</v>
@@ -1846,7 +1846,7 @@
         <v>1</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
@@ -1854,38 +1854,38 @@
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 25561-2025 artfynd.xlsx", "A 25561-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 7955-2023 artfynd.xlsx", "A 7955-2023")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 25561-2025 karta.png", "A 25561-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 7955-2023 karta.png", "A 7955-2023")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 25561-2025 georefererad karta.tif", "A 25561-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 7955-2023 georefererad karta.tif", "A 7955-2023")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 25561-2025 FSC-klagomål.docx", "A 25561-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 7955-2023 FSC-klagomål.docx", "A 7955-2023")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 25561-2025 FSC-klagomål mail.docx", "A 25561-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 7955-2023 FSC-klagomål mail.docx", "A 7955-2023")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 25561-2025 tillsynsbegäran.docx", "A 25561-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 7955-2023 tillsynsbegäran.docx", "A 7955-2023")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 25561-2025 tillsynsbegäran mail.docx", "A 25561-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 7955-2023 tillsynsbegäran mail.docx", "A 7955-2023")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 12363-2025</t>
+          <t>A 64098-2023</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1899,10 +1899,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45730</v>
+        <v>45279</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1915,16 +1915,16 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>0.8</v>
+        <v>0.3</v>
       </c>
       <c r="J14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
@@ -1939,7 +1939,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -1955,42 +1955,42 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Skogsalmsdvärgmal</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 12363-2025 artfynd.xlsx", "A 12363-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 64098-2023 artfynd.xlsx", "A 64098-2023")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 12363-2025 karta.png", "A 12363-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 64098-2023 karta.png", "A 64098-2023")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 12363-2025 georefererad karta.tif", "A 12363-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 64098-2023 georefererad karta.tif", "A 64098-2023")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 12363-2025 FSC-klagomål.docx", "A 12363-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 64098-2023 FSC-klagomål.docx", "A 64098-2023")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 12363-2025 FSC-klagomål mail.docx", "A 12363-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 64098-2023 FSC-klagomål mail.docx", "A 64098-2023")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 12363-2025 tillsynsbegäran.docx", "A 12363-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 64098-2023 tillsynsbegäran.docx", "A 64098-2023")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 12363-2025 tillsynsbegäran mail.docx", "A 12363-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 64098-2023 tillsynsbegäran mail.docx", "A 64098-2023")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 46438-2023</t>
+          <t>A 2062-2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2004,10 +2004,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45197</v>
+        <v>45671</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2020,7 +2020,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>0.5</v>
+        <v>1.9</v>
       </c>
       <c r="J15" t="n">
         <v>1</v>
@@ -2029,13 +2029,13 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M15" t="n">
         <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2047,7 +2047,7 @@
         <v>1</v>
       </c>
       <c r="R15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
         <v>1</v>
@@ -2056,46 +2056,50 @@
         <v>1</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Bombmurkla</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 46438-2023 artfynd.xlsx", "A 46438-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 2062-2025 artfynd.xlsx", "A 2062-2025")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 46438-2023 karta.png", "A 46438-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 2062-2025 karta.png", "A 2062-2025")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 46438-2023 georefererad karta.tif", "A 46438-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 2062-2025 georefererad karta.tif", "A 2062-2025")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 46438-2023 FSC-klagomål.docx", "A 46438-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 2062-2025 FSC-klagomål.docx", "A 2062-2025")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 46438-2023 FSC-klagomål mail.docx", "A 46438-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 2062-2025 FSC-klagomål mail.docx", "A 2062-2025")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 46438-2023 tillsynsbegäran.docx", "A 46438-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 2062-2025 tillsynsbegäran.docx", "A 2062-2025")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 46438-2023 tillsynsbegäran mail.docx", "A 46438-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 2062-2025 tillsynsbegäran mail.docx", "A 2062-2025")</f>
+        <v/>
+      </c>
+      <c r="AE15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/fåglar/A 2062-2025 prioriterade fågelarter.docx", "A 2062-2025")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 53357-2025</t>
+          <t>A 23099-2024</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2109,10 +2113,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45959</v>
+        <v>45450</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2124,11 +2128,16 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I16" t="n">
-        <v>2.4</v>
+        <v>0.7</v>
       </c>
       <c r="J16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
@@ -2137,10 +2146,10 @@
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2158,49 +2167,49 @@
         <v>1</v>
       </c>
       <c r="T16" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Bombmurkla</t>
+          <t>Bredbrämad bastardsvärmare</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 53357-2025 artfynd.xlsx", "A 53357-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 23099-2024 artfynd.xlsx", "A 23099-2024")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 53357-2025 karta.png", "A 53357-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 23099-2024 karta.png", "A 23099-2024")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 53357-2025 georefererad karta.tif", "A 53357-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 23099-2024 georefererad karta.tif", "A 23099-2024")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 53357-2025 FSC-klagomål.docx", "A 53357-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 23099-2024 FSC-klagomål.docx", "A 23099-2024")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 53357-2025 FSC-klagomål mail.docx", "A 53357-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 23099-2024 FSC-klagomål mail.docx", "A 23099-2024")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 53357-2025 tillsynsbegäran.docx", "A 53357-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 23099-2024 tillsynsbegäran.docx", "A 23099-2024")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 53357-2025 tillsynsbegäran mail.docx", "A 53357-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 23099-2024 tillsynsbegäran mail.docx", "A 23099-2024")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 23099-2024</t>
+          <t>A 25561-2025</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2214,10 +2223,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45450</v>
+        <v>45803</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2229,16 +2238,11 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I17" t="n">
-        <v>0.7</v>
+        <v>1.6</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
@@ -2247,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2271,46 +2275,46 @@
         <v>1</v>
       </c>
       <c r="U17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Bredbrämad bastardsvärmare</t>
+          <t>Bombmurkla</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 23099-2024 artfynd.xlsx", "A 23099-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 25561-2025 artfynd.xlsx", "A 25561-2025")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 23099-2024 karta.png", "A 23099-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 25561-2025 karta.png", "A 25561-2025")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 23099-2024 georefererad karta.tif", "A 23099-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 25561-2025 georefererad karta.tif", "A 25561-2025")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 23099-2024 FSC-klagomål.docx", "A 23099-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 25561-2025 FSC-klagomål.docx", "A 25561-2025")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 23099-2024 FSC-klagomål mail.docx", "A 23099-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 25561-2025 FSC-klagomål mail.docx", "A 25561-2025")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 23099-2024 tillsynsbegäran.docx", "A 23099-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 25561-2025 tillsynsbegäran.docx", "A 25561-2025")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 23099-2024 tillsynsbegäran mail.docx", "A 23099-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 25561-2025 tillsynsbegäran mail.docx", "A 25561-2025")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 64098-2023</t>
+          <t>A 46438-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2324,10 +2328,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45279</v>
+        <v>45197</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2340,22 +2344,22 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2367,7 +2371,7 @@
         <v>1</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
@@ -2380,42 +2384,42 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Skogsalmsdvärgmal</t>
+          <t>Bombmurkla</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 64098-2023 artfynd.xlsx", "A 64098-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 46438-2023 artfynd.xlsx", "A 46438-2023")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 64098-2023 karta.png", "A 64098-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 46438-2023 karta.png", "A 46438-2023")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 64098-2023 georefererad karta.tif", "A 64098-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 46438-2023 georefererad karta.tif", "A 46438-2023")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 64098-2023 FSC-klagomål.docx", "A 64098-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 46438-2023 FSC-klagomål.docx", "A 46438-2023")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 64098-2023 FSC-klagomål mail.docx", "A 64098-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 46438-2023 FSC-klagomål mail.docx", "A 46438-2023")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 64098-2023 tillsynsbegäran.docx", "A 64098-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 46438-2023 tillsynsbegäran.docx", "A 46438-2023")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 64098-2023 tillsynsbegäran mail.docx", "A 64098-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 46438-2023 tillsynsbegäran mail.docx", "A 46438-2023")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 26196-2026</t>
+          <t>A 53357-2025</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2425,14 +2429,14 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46182</v>
+        <v>45959</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2445,10 +2449,10 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>53.1</v>
+        <v>2.4</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
@@ -2460,7 +2464,7 @@
         <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2469,58 +2473,58 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
       </c>
       <c r="T19" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="U19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Liljekonvalj</t>
+          <t>Bombmurkla</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 26196-2026 artfynd.xlsx", "A 26196-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 53357-2025 artfynd.xlsx", "A 53357-2025")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 26196-2026 karta.png", "A 26196-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 53357-2025 karta.png", "A 53357-2025")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 26196-2026 georefererad karta.tif", "A 26196-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 53357-2025 georefererad karta.tif", "A 53357-2025")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 26196-2026 FSC-klagomål.docx", "A 26196-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 53357-2025 FSC-klagomål.docx", "A 53357-2025")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 26196-2026 FSC-klagomål mail.docx", "A 26196-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 53357-2025 FSC-klagomål mail.docx", "A 53357-2025")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 26196-2026 tillsynsbegäran.docx", "A 26196-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 53357-2025 tillsynsbegäran.docx", "A 53357-2025")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 26196-2026 tillsynsbegäran mail.docx", "A 26196-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 53357-2025 tillsynsbegäran mail.docx", "A 53357-2025")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 11447-2025</t>
+          <t>A 12363-2025</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2530,14 +2534,14 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45726</v>
+        <v>45730</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2550,10 +2554,10 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K20" t="n">
         <v>1</v>
@@ -2590,42 +2594,42 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>Myskbock</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 11447-2025 artfynd.xlsx", "A 11447-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 12363-2025 artfynd.xlsx", "A 12363-2025")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 11447-2025 karta.png", "A 11447-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 12363-2025 karta.png", "A 12363-2025")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 11447-2025 georefererad karta.tif", "A 11447-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 12363-2025 georefererad karta.tif", "A 12363-2025")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 11447-2025 FSC-klagomål.docx", "A 11447-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 12363-2025 FSC-klagomål.docx", "A 12363-2025")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 11447-2025 FSC-klagomål mail.docx", "A 11447-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 12363-2025 FSC-klagomål mail.docx", "A 12363-2025")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 11447-2025 tillsynsbegäran.docx", "A 11447-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 12363-2025 tillsynsbegäran.docx", "A 12363-2025")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 11447-2025 tillsynsbegäran mail.docx", "A 11447-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 12363-2025 tillsynsbegäran mail.docx", "A 12363-2025")</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 26623-2026</t>
+          <t>A 26196-2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2635,14 +2639,14 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46184</v>
+        <v>46182</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2655,7 +2659,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>4.6</v>
+        <v>53.1</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2664,7 +2668,7 @@
         <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
         <v>0</v>
@@ -2679,7 +2683,7 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
         <v>0</v>
@@ -2688,42 +2692,42 @@
         <v>1</v>
       </c>
       <c r="T21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Svartöra</t>
+          <t>Liljekonvalj</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 26623-2026 artfynd.xlsx", "A 26623-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 26196-2026 artfynd.xlsx", "A 26196-2026")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 26623-2026 karta.png", "A 26623-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 26196-2026 karta.png", "A 26196-2026")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 26623-2026 georefererad karta.tif", "A 26623-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 26196-2026 georefererad karta.tif", "A 26196-2026")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 26623-2026 FSC-klagomål.docx", "A 26623-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 26196-2026 FSC-klagomål.docx", "A 26196-2026")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 26623-2026 FSC-klagomål mail.docx", "A 26623-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 26196-2026 FSC-klagomål mail.docx", "A 26196-2026")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 26623-2026 tillsynsbegäran.docx", "A 26623-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 26196-2026 tillsynsbegäran.docx", "A 26196-2026")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 26623-2026 tillsynsbegäran mail.docx", "A 26623-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 26196-2026 tillsynsbegäran mail.docx", "A 26196-2026")</f>
         <v/>
       </c>
     </row>
@@ -2747,7 +2751,7 @@
         <v>46184</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2835,7 +2839,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 2062-2025</t>
+          <t>A 26623-2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2849,10 +2853,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45671</v>
+        <v>46184</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2865,10 +2869,10 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>1.9</v>
+        <v>4.6</v>
       </c>
       <c r="J23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
@@ -2901,43 +2905,39 @@
         <v>1</v>
       </c>
       <c r="U23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Svartöra</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 2062-2025 artfynd.xlsx", "A 2062-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 26623-2026 artfynd.xlsx", "A 26623-2026")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 2062-2025 karta.png", "A 2062-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 26623-2026 karta.png", "A 26623-2026")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 2062-2025 georefererad karta.tif", "A 2062-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 26623-2026 georefererad karta.tif", "A 26623-2026")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 2062-2025 FSC-klagomål.docx", "A 2062-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 26623-2026 FSC-klagomål.docx", "A 26623-2026")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 2062-2025 FSC-klagomål mail.docx", "A 2062-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 26623-2026 FSC-klagomål mail.docx", "A 26623-2026")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 2062-2025 tillsynsbegäran.docx", "A 2062-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 26623-2026 tillsynsbegäran.docx", "A 26623-2026")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 2062-2025 tillsynsbegäran mail.docx", "A 2062-2025")</f>
-        <v/>
-      </c>
-      <c r="AE23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/fåglar/A 2062-2025 prioriterade fågelarter.docx", "A 2062-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 26623-2026 tillsynsbegäran mail.docx", "A 26623-2026")</f>
         <v/>
       </c>
     </row>
@@ -2961,7 +2961,7 @@
         <v>44558</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3066,7 +3066,7 @@
         <v>44609</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3139,7 +3139,7 @@
         <v>44489</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3217,7 +3217,7 @@
         <v>44546</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3273,7 +3273,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 20604-2022</t>
+          <t>A 3838-2022</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3287,10 +3287,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44700</v>
+        <v>44587</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3303,7 +3303,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>2</v>
+        <v>2.9</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3346,7 +3346,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 3838-2022</t>
+          <t>A 20604-2022</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3360,10 +3360,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44587</v>
+        <v>44700</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3376,7 +3376,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>2.9</v>
+        <v>2</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3436,7 +3436,7 @@
         <v>44655</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3497,7 +3497,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 23615-2025</t>
+          <t>A 64105-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3511,10 +3511,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45792</v>
+        <v>45279</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3527,7 +3527,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>1.3</v>
+        <v>2.2</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3570,7 +3570,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 23627-2025</t>
+          <t>A 5264-2023</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3584,10 +3584,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45792</v>
+        <v>44959</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3600,7 +3600,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>1.7</v>
+        <v>5.8</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3643,7 +3643,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 59700-2021</t>
+          <t>A 27313-2023</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3657,10 +3657,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44494</v>
+        <v>45096</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3672,13 +3672,8 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I33" t="n">
-        <v>4.8</v>
+        <v>1.8</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3721,7 +3716,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 38902-2024</t>
+          <t>A 64114-2023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3735,10 +3730,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45547</v>
+        <v>45279</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3750,13 +3745,8 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I34" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3816,7 +3806,7 @@
         <v>45216</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3872,7 +3862,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 5264-2023</t>
+          <t>A 2602-2024</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3886,10 +3876,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44959</v>
+        <v>45313</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3902,7 +3892,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>5.8</v>
+        <v>0.7</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3945,7 +3935,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 9655-2026</t>
+          <t>A 51587-2023</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3959,10 +3949,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>46070</v>
+        <v>45215</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3976,11 +3966,11 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Övriga statliga verk och myndigheter</t>
+          <t>Allmännings- och besparingsskogar</t>
         </is>
       </c>
       <c r="I37" t="n">
-        <v>17.2</v>
+        <v>2.6</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4023,7 +4013,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 23098-2024</t>
+          <t>A 7275-2022</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4037,10 +4027,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45450</v>
+        <v>44606</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4058,7 +4048,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>1</v>
+        <v>9.6</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4118,7 +4108,7 @@
         <v>44901</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4179,7 +4169,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 54222-2023</t>
+          <t>A 58011-2021</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4193,10 +4183,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45225</v>
+        <v>44487</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4214,7 +4204,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>8.300000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4257,7 +4247,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 18787-2026</t>
+          <t>A 72524-2021</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4271,10 +4261,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>46128</v>
+        <v>44546</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4286,13 +4276,8 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I41" t="n">
-        <v>7.8</v>
+        <v>3.6</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4335,7 +4320,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 18813-2026</t>
+          <t>A 4338-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4349,10 +4334,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>46128</v>
+        <v>44953</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4364,13 +4349,8 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I42" t="n">
-        <v>56</v>
+        <v>1.1</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4413,7 +4393,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 18818-2026</t>
+          <t>A 64107-2023</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4427,10 +4407,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>46128</v>
+        <v>45279</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4442,13 +4422,8 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I43" t="n">
-        <v>17.8</v>
+        <v>0.3</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4491,7 +4466,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 18778-2026</t>
+          <t>A 7112-2025</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4505,10 +4480,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>46128</v>
+        <v>45701</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4520,13 +4495,8 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I44" t="n">
-        <v>4.5</v>
+        <v>2.4</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4569,7 +4539,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 4338-2023</t>
+          <t>A 59848-2022</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4583,10 +4553,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>44953</v>
+        <v>44901</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4598,8 +4568,13 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I45" t="n">
-        <v>1.1</v>
+        <v>10.7</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4642,7 +4617,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 58011-2021</t>
+          <t>A 38902-2024</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4656,10 +4631,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44487</v>
+        <v>45547</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4677,7 +4652,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>9.199999999999999</v>
+        <v>0.8</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4720,7 +4695,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 72524-2021</t>
+          <t>A 59700-2021</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4734,10 +4709,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>44546</v>
+        <v>44494</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4749,8 +4724,13 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I47" t="n">
-        <v>3.6</v>
+        <v>4.8</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4793,7 +4773,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 64107-2023</t>
+          <t>A 23615-2025</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4807,10 +4787,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45279</v>
+        <v>45792</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4823,7 +4803,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>0.3</v>
+        <v>1.3</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4866,7 +4846,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 23093-2024</t>
+          <t>A 23627-2025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4880,10 +4860,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45450</v>
+        <v>45792</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4895,13 +4875,8 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I49" t="n">
-        <v>0.9</v>
+        <v>1.7</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4944,7 +4919,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 27313-2023</t>
+          <t>A 3630-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4958,10 +4933,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45096</v>
+        <v>44950</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4974,7 +4949,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>1.8</v>
+        <v>1.4</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5017,7 +4992,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 59377-2024</t>
+          <t>A 23093-2024</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5031,10 +5006,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45638</v>
+        <v>45450</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5046,8 +5021,13 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I51" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5090,7 +5070,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 21206-2026</t>
+          <t>A 64110-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5104,10 +5084,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>46146</v>
+        <v>45279</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5119,13 +5099,8 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I52" t="n">
-        <v>0.9</v>
+        <v>0.4</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5168,7 +5143,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 51587-2023</t>
+          <t>A 23098-2024</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5182,10 +5157,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45215</v>
+        <v>45450</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5199,11 +5174,11 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Allmännings- och besparingsskogar</t>
+          <t>Övriga statliga verk och myndigheter</t>
         </is>
       </c>
       <c r="I53" t="n">
-        <v>2.6</v>
+        <v>1</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5246,7 +5221,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 24579-2026</t>
+          <t>A 54222-2023</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5260,10 +5235,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>46170</v>
+        <v>45225</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5275,8 +5250,13 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I54" t="n">
-        <v>2.1</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5319,7 +5299,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 58598-2025</t>
+          <t>A 59377-2024</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5333,10 +5313,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45986</v>
+        <v>45638</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5348,13 +5328,8 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I55" t="n">
-        <v>4.5</v>
+        <v>0.6</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5397,7 +5372,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 31160-2022</t>
+          <t>A 7860-2024</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5411,10 +5386,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>44770</v>
+        <v>45348</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5426,8 +5401,13 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I56" t="n">
-        <v>3.7</v>
+        <v>1.9</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5470,7 +5450,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 26625-2026</t>
+          <t>A 59402-2022</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5484,10 +5464,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>46184</v>
+        <v>44906</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5500,7 +5480,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>5.3</v>
+        <v>1.8</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5543,7 +5523,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 26629-2026</t>
+          <t>A 9655-2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5557,10 +5537,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>46184</v>
+        <v>46070</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5572,8 +5552,13 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I58" t="n">
-        <v>2</v>
+        <v>17.2</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5616,7 +5601,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 26633-2026</t>
+          <t>A 18778-2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5630,10 +5615,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>46184</v>
+        <v>46128</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5645,8 +5630,13 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I59" t="n">
-        <v>0.7</v>
+        <v>4.5</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5689,7 +5679,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 59848-2022</t>
+          <t>A 18813-2026</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5703,10 +5693,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>44901</v>
+        <v>46128</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5724,7 +5714,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>10.7</v>
+        <v>56</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5767,7 +5757,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 64110-2023</t>
+          <t>A 18818-2026</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5781,10 +5771,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45279</v>
+        <v>46128</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5796,8 +5786,13 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I61" t="n">
-        <v>0.4</v>
+        <v>17.8</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5840,7 +5835,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 3754-2026</t>
+          <t>A 18787-2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5854,10 +5849,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>46043</v>
+        <v>46128</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5875,7 +5870,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>5.1</v>
+        <v>7.8</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5918,7 +5913,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 28797-2026</t>
+          <t>A 21206-2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5932,10 +5927,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>46198</v>
+        <v>46146</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5947,8 +5942,13 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I63" t="n">
-        <v>2.2</v>
+        <v>0.9</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5991,7 +5991,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 28740-2026</t>
+          <t>A 24579-2026</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6005,10 +6005,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>46198</v>
+        <v>46170</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6021,7 +6021,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>4.8</v>
+        <v>2.1</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6064,7 +6064,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 28735-2026</t>
+          <t>A 31160-2022</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6078,10 +6078,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>46198</v>
+        <v>44770</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6094,7 +6094,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6137,7 +6137,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 7275-2022</t>
+          <t>A 58598-2025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6151,10 +6151,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>44606</v>
+        <v>45986</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6172,7 +6172,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>9.6</v>
+        <v>4.5</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6215,7 +6215,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 2602-2024</t>
+          <t>A 26633-2026</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6229,10 +6229,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45313</v>
+        <v>46184</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6288,7 +6288,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 59402-2022</t>
+          <t>A 26625-2026</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6302,10 +6302,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>44906</v>
+        <v>46184</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6318,7 +6318,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>1.8</v>
+        <v>5.3</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6361,7 +6361,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 3630-2023</t>
+          <t>A 26629-2026</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6375,10 +6375,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>44950</v>
+        <v>46184</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6391,7 +6391,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1.4</v>
+        <v>2</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6434,7 +6434,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 7860-2024</t>
+          <t>A 3754-2026</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6448,10 +6448,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45348</v>
+        <v>46043</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6469,7 +6469,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>1.9</v>
+        <v>5.1</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6512,7 +6512,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 31714-2026</t>
+          <t>A 28735-2026</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6526,10 +6526,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>46226</v>
+        <v>46198</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6542,7 +6542,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>5</v>
+        <v>3.5</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6585,7 +6585,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 64105-2023</t>
+          <t>A 28740-2026</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6599,10 +6599,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45279</v>
+        <v>46198</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6615,7 +6615,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>2.2</v>
+        <v>4.8</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6658,7 +6658,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 64114-2023</t>
+          <t>A 28797-2026</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6672,10 +6672,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45279</v>
+        <v>46198</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6688,7 +6688,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>0.4</v>
+        <v>2.2</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6731,7 +6731,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 33058-2026</t>
+          <t>A 31714-2026</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6741,14 +6741,14 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>46245</v>
+        <v>46226</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6761,7 +6761,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>1.3</v>
+        <v>5</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6804,7 +6804,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 7112-2025</t>
+          <t>A 33058-2026</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6814,14 +6814,14 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45701</v>
+        <v>46245</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6834,7 +6834,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>2.4</v>
+        <v>1.3</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6894,7 +6894,7 @@
         <v>44558</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>

--- a/Översikt UPPLANDS-BRO.xlsx
+++ b/Översikt UPPLANDS-BRO.xlsx
@@ -601,7 +601,7 @@
         <v>44481</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -714,7 +714,7 @@
         <v>44552</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -822,7 +822,7 @@
         <v>44552</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -930,7 +930,7 @@
         <v>45232</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1025,7 +1025,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 73773-2021</t>
+          <t>A 18790-2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1039,10 +1039,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>44552</v>
+        <v>46128</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1054,8 +1054,13 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I6" t="n">
-        <v>1.9</v>
+        <v>5.5</v>
       </c>
       <c r="J6" t="n">
         <v>2</v>
@@ -1088,376 +1093,371 @@
         <v>2</v>
       </c>
       <c r="T6" t="n">
+        <v>2</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>Fläcknycklar
+Nattviol</t>
+        </is>
+      </c>
+      <c r="W6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 18790-2026 artfynd.xlsx", "A 18790-2026")</f>
+        <v/>
+      </c>
+      <c r="X6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 18790-2026 karta.png", "A 18790-2026")</f>
+        <v/>
+      </c>
+      <c r="Y6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 18790-2026 georefererad karta.tif", "A 18790-2026")</f>
+        <v/>
+      </c>
+      <c r="AA6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 18790-2026 FSC-klagomål.docx", "A 18790-2026")</f>
+        <v/>
+      </c>
+      <c r="AB6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 18790-2026 FSC-klagomål mail.docx", "A 18790-2026")</f>
+        <v/>
+      </c>
+      <c r="AC6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 18790-2026 tillsynsbegäran.docx", "A 18790-2026")</f>
+        <v/>
+      </c>
+      <c r="AD6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 18790-2026 tillsynsbegäran mail.docx", "A 18790-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>A 18772-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>46128</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>46297</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>UPPLANDS-BRO</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>2</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>Svedjenäva
+Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="W7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 18772-2026 artfynd.xlsx", "A 18772-2026")</f>
+        <v/>
+      </c>
+      <c r="X7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 18772-2026 karta.png", "A 18772-2026")</f>
+        <v/>
+      </c>
+      <c r="Y7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 18772-2026 georefererad karta.tif", "A 18772-2026")</f>
+        <v/>
+      </c>
+      <c r="AA7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 18772-2026 FSC-klagomål.docx", "A 18772-2026")</f>
+        <v/>
+      </c>
+      <c r="AB7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 18772-2026 FSC-klagomål mail.docx", "A 18772-2026")</f>
+        <v/>
+      </c>
+      <c r="AC7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 18772-2026 tillsynsbegäran.docx", "A 18772-2026")</f>
+        <v/>
+      </c>
+      <c r="AD7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 18772-2026 tillsynsbegäran mail.docx", "A 18772-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="15" customHeight="1">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>A 10909-2025</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D8" s="1" t="n">
+        <v>45722</v>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>46297</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>UPPLANDS-BRO</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="J8" t="n">
+        <v>1</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>2</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2</v>
+      </c>
+      <c r="U8" t="n">
+        <v>2</v>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>Arommusseron
+Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="W8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 10909-2025 artfynd.xlsx", "A 10909-2025")</f>
+        <v/>
+      </c>
+      <c r="X8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 10909-2025 karta.png", "A 10909-2025")</f>
+        <v/>
+      </c>
+      <c r="Y8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 10909-2025 georefererad karta.tif", "A 10909-2025")</f>
+        <v/>
+      </c>
+      <c r="AA8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 10909-2025 FSC-klagomål.docx", "A 10909-2025")</f>
+        <v/>
+      </c>
+      <c r="AB8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 10909-2025 FSC-klagomål mail.docx", "A 10909-2025")</f>
+        <v/>
+      </c>
+      <c r="AC8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 10909-2025 tillsynsbegäran.docx", "A 10909-2025")</f>
+        <v/>
+      </c>
+      <c r="AD8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 10909-2025 tillsynsbegäran mail.docx", "A 10909-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="15" customHeight="1">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>A 73773-2021</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D9" s="1" t="n">
+        <v>44552</v>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>46297</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>UPPLANDS-BRO</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="J9" t="n">
+        <v>2</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>2</v>
+      </c>
+      <c r="T9" t="n">
         <v>3</v>
       </c>
-      <c r="U6" t="n">
+      <c r="U9" t="n">
         <v>3</v>
       </c>
-      <c r="V6" s="2" t="inlineStr">
+      <c r="V9" s="2" t="inlineStr">
         <is>
           <t>Kopparödla
 Gullviva</t>
         </is>
       </c>
-      <c r="W6">
+      <c r="W9">
         <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 73773-2021 artfynd.xlsx", "A 73773-2021")</f>
         <v/>
       </c>
-      <c r="X6">
+      <c r="X9">
         <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 73773-2021 karta.png", "A 73773-2021")</f>
         <v/>
       </c>
-      <c r="Y6">
+      <c r="Y9">
         <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 73773-2021 georefererad karta.tif", "A 73773-2021")</f>
         <v/>
       </c>
-      <c r="AA6">
+      <c r="AA9">
         <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 73773-2021 FSC-klagomål.docx", "A 73773-2021")</f>
         <v/>
       </c>
-      <c r="AB6">
+      <c r="AB9">
         <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 73773-2021 FSC-klagomål mail.docx", "A 73773-2021")</f>
         <v/>
       </c>
-      <c r="AC6">
+      <c r="AC9">
         <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 73773-2021 tillsynsbegäran.docx", "A 73773-2021")</f>
         <v/>
       </c>
-      <c r="AD6">
+      <c r="AD9">
         <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 73773-2021 tillsynsbegäran mail.docx", "A 73773-2021")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>A 18772-2026</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>46128</v>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>46296</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>UPPLANDS-BRO</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="J7" t="n">
-        <v>1</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>1</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>1</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
-        <v>2</v>
-      </c>
-      <c r="T7" t="n">
-        <v>2</v>
-      </c>
-      <c r="U7" t="n">
-        <v>0</v>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>Svedjenäva
-Fläcknycklar</t>
-        </is>
-      </c>
-      <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 18772-2026 artfynd.xlsx", "A 18772-2026")</f>
-        <v/>
-      </c>
-      <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 18772-2026 karta.png", "A 18772-2026")</f>
-        <v/>
-      </c>
-      <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 18772-2026 georefererad karta.tif", "A 18772-2026")</f>
-        <v/>
-      </c>
-      <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 18772-2026 FSC-klagomål.docx", "A 18772-2026")</f>
-        <v/>
-      </c>
-      <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 18772-2026 FSC-klagomål mail.docx", "A 18772-2026")</f>
-        <v/>
-      </c>
-      <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 18772-2026 tillsynsbegäran.docx", "A 18772-2026")</f>
-        <v/>
-      </c>
-      <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 18772-2026 tillsynsbegäran mail.docx", "A 18772-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8" ht="15" customHeight="1">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>A 18790-2026</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D8" s="1" t="n">
-        <v>46128</v>
-      </c>
-      <c r="E8" s="1" t="n">
-        <v>46296</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>UPPLANDS-BRO</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
-      <c r="I8" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="J8" t="n">
-        <v>2</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" t="n">
-        <v>2</v>
-      </c>
-      <c r="T8" t="n">
-        <v>2</v>
-      </c>
-      <c r="U8" t="n">
-        <v>0</v>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>Fläcknycklar
-Nattviol</t>
-        </is>
-      </c>
-      <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 18790-2026 artfynd.xlsx", "A 18790-2026")</f>
-        <v/>
-      </c>
-      <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 18790-2026 karta.png", "A 18790-2026")</f>
-        <v/>
-      </c>
-      <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 18790-2026 georefererad karta.tif", "A 18790-2026")</f>
-        <v/>
-      </c>
-      <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 18790-2026 FSC-klagomål.docx", "A 18790-2026")</f>
-        <v/>
-      </c>
-      <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 18790-2026 FSC-klagomål mail.docx", "A 18790-2026")</f>
-        <v/>
-      </c>
-      <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 18790-2026 tillsynsbegäran.docx", "A 18790-2026")</f>
-        <v/>
-      </c>
-      <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 18790-2026 tillsynsbegäran mail.docx", "A 18790-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9" ht="15" customHeight="1">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>A 10909-2025</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D9" s="1" t="n">
-        <v>45722</v>
-      </c>
-      <c r="E9" s="1" t="n">
-        <v>46296</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>UPPLANDS-BRO</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="J9" t="n">
-        <v>1</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>1</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>1</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" t="n">
-        <v>2</v>
-      </c>
-      <c r="T9" t="n">
-        <v>2</v>
-      </c>
-      <c r="U9" t="n">
-        <v>2</v>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>Arommusseron
-Fläcknycklar</t>
-        </is>
-      </c>
-      <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 10909-2025 artfynd.xlsx", "A 10909-2025")</f>
-        <v/>
-      </c>
-      <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 10909-2025 karta.png", "A 10909-2025")</f>
-        <v/>
-      </c>
-      <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 10909-2025 georefererad karta.tif", "A 10909-2025")</f>
-        <v/>
-      </c>
-      <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 10909-2025 FSC-klagomål.docx", "A 10909-2025")</f>
-        <v/>
-      </c>
-      <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 10909-2025 FSC-klagomål mail.docx", "A 10909-2025")</f>
-        <v/>
-      </c>
-      <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 10909-2025 tillsynsbegäran.docx", "A 10909-2025")</f>
-        <v/>
-      </c>
-      <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 10909-2025 tillsynsbegäran mail.docx", "A 10909-2025")</f>
         <v/>
       </c>
     </row>
@@ -1481,7 +1481,7 @@
         <v>44603</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1587,7 +1587,7 @@
         <v>44552</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1675,7 +1675,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 11447-2025</t>
+          <t>A 7955-2023</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1685,14 +1685,14 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45726</v>
+        <v>44973</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1705,13 +1705,13 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>1.5</v>
+        <v>2.9</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
@@ -1720,7 +1720,7 @@
         <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1729,10 +1729,10 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1741,46 +1741,46 @@
         <v>1</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>Myskbock</t>
+          <t>Bombmurkla</t>
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 11447-2025 artfynd.xlsx", "A 11447-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 7955-2023 artfynd.xlsx", "A 7955-2023")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 11447-2025 karta.png", "A 11447-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 7955-2023 karta.png", "A 7955-2023")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 11447-2025 georefererad karta.tif", "A 11447-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 7955-2023 georefererad karta.tif", "A 7955-2023")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 11447-2025 FSC-klagomål.docx", "A 11447-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 7955-2023 FSC-klagomål.docx", "A 7955-2023")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 11447-2025 FSC-klagomål mail.docx", "A 11447-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 7955-2023 FSC-klagomål mail.docx", "A 7955-2023")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 11447-2025 tillsynsbegäran.docx", "A 11447-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 7955-2023 tillsynsbegäran.docx", "A 7955-2023")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 11447-2025 tillsynsbegäran mail.docx", "A 11447-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 7955-2023 tillsynsbegäran mail.docx", "A 7955-2023")</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 7955-2023</t>
+          <t>A 12363-2025</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1794,10 +1794,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>44973</v>
+        <v>45730</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1810,13 +1810,13 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>2.9</v>
+        <v>0.8</v>
       </c>
       <c r="J13" t="n">
         <v>1</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -1825,7 +1825,7 @@
         <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -1834,10 +1834,10 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
@@ -1846,46 +1846,46 @@
         <v>1</v>
       </c>
       <c r="U13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>Bombmurkla</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 7955-2023 artfynd.xlsx", "A 7955-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 12363-2025 artfynd.xlsx", "A 12363-2025")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 7955-2023 karta.png", "A 7955-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 12363-2025 karta.png", "A 12363-2025")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 7955-2023 georefererad karta.tif", "A 7955-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 12363-2025 georefererad karta.tif", "A 12363-2025")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 7955-2023 FSC-klagomål.docx", "A 7955-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 12363-2025 FSC-klagomål.docx", "A 12363-2025")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 7955-2023 FSC-klagomål mail.docx", "A 7955-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 12363-2025 FSC-klagomål mail.docx", "A 12363-2025")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 7955-2023 tillsynsbegäran.docx", "A 7955-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 12363-2025 tillsynsbegäran.docx", "A 12363-2025")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 7955-2023 tillsynsbegäran mail.docx", "A 7955-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 12363-2025 tillsynsbegäran mail.docx", "A 12363-2025")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 64098-2023</t>
+          <t>A 25561-2025</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1899,10 +1899,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45279</v>
+        <v>45803</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1915,22 +1915,22 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>0.3</v>
+        <v>1.6</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -1942,7 +1942,7 @@
         <v>1</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
@@ -1955,42 +1955,42 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Skogsalmsdvärgmal</t>
+          <t>Bombmurkla</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 64098-2023 artfynd.xlsx", "A 64098-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 25561-2025 artfynd.xlsx", "A 25561-2025")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 64098-2023 karta.png", "A 64098-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 25561-2025 karta.png", "A 25561-2025")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 64098-2023 georefererad karta.tif", "A 64098-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 25561-2025 georefererad karta.tif", "A 25561-2025")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 64098-2023 FSC-klagomål.docx", "A 64098-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 25561-2025 FSC-klagomål.docx", "A 25561-2025")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 64098-2023 FSC-klagomål mail.docx", "A 64098-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 25561-2025 FSC-klagomål mail.docx", "A 25561-2025")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 64098-2023 tillsynsbegäran.docx", "A 64098-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 25561-2025 tillsynsbegäran.docx", "A 25561-2025")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 64098-2023 tillsynsbegäran mail.docx", "A 64098-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 25561-2025 tillsynsbegäran mail.docx", "A 25561-2025")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 2062-2025</t>
+          <t>A 46438-2023</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2004,10 +2004,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45671</v>
+        <v>45197</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2020,7 +2020,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>1.9</v>
+        <v>0.5</v>
       </c>
       <c r="J15" t="n">
         <v>1</v>
@@ -2029,13 +2029,13 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
         <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2047,7 +2047,7 @@
         <v>1</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S15" t="n">
         <v>1</v>
@@ -2056,50 +2056,46 @@
         <v>1</v>
       </c>
       <c r="U15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Bombmurkla</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 2062-2025 artfynd.xlsx", "A 2062-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 46438-2023 artfynd.xlsx", "A 46438-2023")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 2062-2025 karta.png", "A 2062-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 46438-2023 karta.png", "A 46438-2023")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 2062-2025 georefererad karta.tif", "A 2062-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 46438-2023 georefererad karta.tif", "A 46438-2023")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 2062-2025 FSC-klagomål.docx", "A 2062-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 46438-2023 FSC-klagomål.docx", "A 46438-2023")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 2062-2025 FSC-klagomål mail.docx", "A 2062-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 46438-2023 FSC-klagomål mail.docx", "A 46438-2023")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 2062-2025 tillsynsbegäran.docx", "A 2062-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 46438-2023 tillsynsbegäran.docx", "A 46438-2023")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 2062-2025 tillsynsbegäran mail.docx", "A 2062-2025")</f>
-        <v/>
-      </c>
-      <c r="AE15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/fåglar/A 2062-2025 prioriterade fågelarter.docx", "A 2062-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 46438-2023 tillsynsbegäran mail.docx", "A 46438-2023")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 23099-2024</t>
+          <t>A 53357-2025</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2113,10 +2109,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45450</v>
+        <v>45959</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2128,16 +2124,11 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I16" t="n">
-        <v>0.7</v>
+        <v>2.4</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
@@ -2146,10 +2137,10 @@
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2167,49 +2158,49 @@
         <v>1</v>
       </c>
       <c r="T16" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="U16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Bredbrämad bastardsvärmare</t>
+          <t>Bombmurkla</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 23099-2024 artfynd.xlsx", "A 23099-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 53357-2025 artfynd.xlsx", "A 53357-2025")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 23099-2024 karta.png", "A 23099-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 53357-2025 karta.png", "A 53357-2025")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 23099-2024 georefererad karta.tif", "A 23099-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 53357-2025 georefererad karta.tif", "A 53357-2025")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 23099-2024 FSC-klagomål.docx", "A 23099-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 53357-2025 FSC-klagomål.docx", "A 53357-2025")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 23099-2024 FSC-klagomål mail.docx", "A 23099-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 53357-2025 FSC-klagomål mail.docx", "A 53357-2025")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 23099-2024 tillsynsbegäran.docx", "A 23099-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 53357-2025 tillsynsbegäran.docx", "A 53357-2025")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 23099-2024 tillsynsbegäran mail.docx", "A 23099-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 53357-2025 tillsynsbegäran mail.docx", "A 53357-2025")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 25561-2025</t>
+          <t>A 23099-2024</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2223,10 +2214,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45803</v>
+        <v>45450</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2238,11 +2229,16 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I17" t="n">
-        <v>1.6</v>
+        <v>0.7</v>
       </c>
       <c r="J17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
@@ -2251,10 +2247,10 @@
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2275,46 +2271,46 @@
         <v>1</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Bombmurkla</t>
+          <t>Bredbrämad bastardsvärmare</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 25561-2025 artfynd.xlsx", "A 25561-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 23099-2024 artfynd.xlsx", "A 23099-2024")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 25561-2025 karta.png", "A 25561-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 23099-2024 karta.png", "A 23099-2024")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 25561-2025 georefererad karta.tif", "A 25561-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 23099-2024 georefererad karta.tif", "A 23099-2024")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 25561-2025 FSC-klagomål.docx", "A 25561-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 23099-2024 FSC-klagomål.docx", "A 23099-2024")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 25561-2025 FSC-klagomål mail.docx", "A 25561-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 23099-2024 FSC-klagomål mail.docx", "A 23099-2024")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 25561-2025 tillsynsbegäran.docx", "A 25561-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 23099-2024 tillsynsbegäran.docx", "A 23099-2024")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 25561-2025 tillsynsbegäran mail.docx", "A 25561-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 23099-2024 tillsynsbegäran mail.docx", "A 23099-2024")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 46438-2023</t>
+          <t>A 64098-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2328,10 +2324,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45197</v>
+        <v>45279</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2344,22 +2340,22 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="J18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2371,7 +2367,7 @@
         <v>1</v>
       </c>
       <c r="R18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
@@ -2384,42 +2380,42 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Bombmurkla</t>
+          <t>Skogsalmsdvärgmal</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 46438-2023 artfynd.xlsx", "A 46438-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 64098-2023 artfynd.xlsx", "A 64098-2023")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 46438-2023 karta.png", "A 46438-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 64098-2023 karta.png", "A 64098-2023")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 46438-2023 georefererad karta.tif", "A 46438-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 64098-2023 georefererad karta.tif", "A 64098-2023")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 46438-2023 FSC-klagomål.docx", "A 46438-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 64098-2023 FSC-klagomål.docx", "A 64098-2023")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 46438-2023 FSC-klagomål mail.docx", "A 46438-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 64098-2023 FSC-klagomål mail.docx", "A 64098-2023")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 46438-2023 tillsynsbegäran.docx", "A 46438-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 64098-2023 tillsynsbegäran.docx", "A 64098-2023")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 46438-2023 tillsynsbegäran mail.docx", "A 46438-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 64098-2023 tillsynsbegäran mail.docx", "A 64098-2023")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 53357-2025</t>
+          <t>A 26196-2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2429,14 +2425,14 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45959</v>
+        <v>46182</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2449,10 +2445,10 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>2.4</v>
+        <v>53.1</v>
       </c>
       <c r="J19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
@@ -2464,7 +2460,7 @@
         <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2473,58 +2469,58 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
       </c>
       <c r="T19" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Bombmurkla</t>
+          <t>Liljekonvalj</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 53357-2025 artfynd.xlsx", "A 53357-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 26196-2026 artfynd.xlsx", "A 26196-2026")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 53357-2025 karta.png", "A 53357-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 26196-2026 karta.png", "A 26196-2026")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 53357-2025 georefererad karta.tif", "A 53357-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 26196-2026 georefererad karta.tif", "A 26196-2026")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 53357-2025 FSC-klagomål.docx", "A 53357-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 26196-2026 FSC-klagomål.docx", "A 26196-2026")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 53357-2025 FSC-klagomål mail.docx", "A 53357-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 26196-2026 FSC-klagomål mail.docx", "A 26196-2026")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 53357-2025 tillsynsbegäran.docx", "A 53357-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 26196-2026 tillsynsbegäran.docx", "A 26196-2026")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 53357-2025 tillsynsbegäran mail.docx", "A 53357-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 26196-2026 tillsynsbegäran mail.docx", "A 26196-2026")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 12363-2025</t>
+          <t>A 26623-2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2538,10 +2534,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45730</v>
+        <v>46184</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2554,16 +2550,16 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>0.8</v>
+        <v>4.6</v>
       </c>
       <c r="J20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M20" t="n">
         <v>0</v>
@@ -2578,7 +2574,7 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
@@ -2594,42 +2590,42 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Svartöra</t>
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 12363-2025 artfynd.xlsx", "A 12363-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 26623-2026 artfynd.xlsx", "A 26623-2026")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 12363-2025 karta.png", "A 12363-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 26623-2026 karta.png", "A 26623-2026")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 12363-2025 georefererad karta.tif", "A 12363-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 26623-2026 georefererad karta.tif", "A 26623-2026")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 12363-2025 FSC-klagomål.docx", "A 12363-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 26623-2026 FSC-klagomål.docx", "A 26623-2026")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 12363-2025 FSC-klagomål mail.docx", "A 12363-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 26623-2026 FSC-klagomål mail.docx", "A 26623-2026")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 12363-2025 tillsynsbegäran.docx", "A 12363-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 26623-2026 tillsynsbegäran.docx", "A 26623-2026")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 12363-2025 tillsynsbegäran mail.docx", "A 12363-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 26623-2026 tillsynsbegäran mail.docx", "A 26623-2026")</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 26196-2026</t>
+          <t>A 26637-2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2639,14 +2635,14 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46182</v>
+        <v>46184</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2659,7 +2655,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>53.1</v>
+        <v>5.4</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2671,7 +2667,7 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N21" t="n">
         <v>0</v>
@@ -2683,58 +2679,58 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S21" t="n">
         <v>1</v>
       </c>
       <c r="T21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Liljekonvalj</t>
+          <t>Igelkott</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 26196-2026 artfynd.xlsx", "A 26196-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 26637-2026 artfynd.xlsx", "A 26637-2026")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 26196-2026 karta.png", "A 26196-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 26637-2026 karta.png", "A 26637-2026")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 26196-2026 georefererad karta.tif", "A 26196-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 26637-2026 georefererad karta.tif", "A 26637-2026")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 26196-2026 FSC-klagomål.docx", "A 26196-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 26637-2026 FSC-klagomål.docx", "A 26637-2026")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 26196-2026 FSC-klagomål mail.docx", "A 26196-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 26637-2026 FSC-klagomål mail.docx", "A 26637-2026")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 26196-2026 tillsynsbegäran.docx", "A 26196-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 26637-2026 tillsynsbegäran.docx", "A 26637-2026")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 26196-2026 tillsynsbegäran mail.docx", "A 26196-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 26637-2026 tillsynsbegäran mail.docx", "A 26637-2026")</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 26637-2026</t>
+          <t>A 11447-2025</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2744,14 +2740,14 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46184</v>
+        <v>45726</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2764,19 +2760,19 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>5.4</v>
+        <v>1.5</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
         <v>0</v>
@@ -2788,10 +2784,10 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
         <v>1</v>
@@ -2804,42 +2800,42 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>Igelkott</t>
+          <t>Myskbock</t>
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 26637-2026 artfynd.xlsx", "A 26637-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 11447-2025 artfynd.xlsx", "A 11447-2025")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 26637-2026 karta.png", "A 26637-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 11447-2025 karta.png", "A 11447-2025")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 26637-2026 georefererad karta.tif", "A 26637-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 11447-2025 georefererad karta.tif", "A 11447-2025")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 26637-2026 FSC-klagomål.docx", "A 26637-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 11447-2025 FSC-klagomål.docx", "A 11447-2025")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 26637-2026 FSC-klagomål mail.docx", "A 26637-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 11447-2025 FSC-klagomål mail.docx", "A 11447-2025")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 26637-2026 tillsynsbegäran.docx", "A 26637-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 11447-2025 tillsynsbegäran.docx", "A 11447-2025")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 26637-2026 tillsynsbegäran mail.docx", "A 26637-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 11447-2025 tillsynsbegäran mail.docx", "A 11447-2025")</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 26623-2026</t>
+          <t>A 2062-2025</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2853,10 +2849,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46184</v>
+        <v>45671</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2869,10 +2865,10 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>4.6</v>
+        <v>1.9</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
@@ -2905,39 +2901,43 @@
         <v>1</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Svartöra</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 26623-2026 artfynd.xlsx", "A 26623-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 2062-2025 artfynd.xlsx", "A 2062-2025")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 26623-2026 karta.png", "A 26623-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 2062-2025 karta.png", "A 2062-2025")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 26623-2026 georefererad karta.tif", "A 26623-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 2062-2025 georefererad karta.tif", "A 2062-2025")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 26623-2026 FSC-klagomål.docx", "A 26623-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 2062-2025 FSC-klagomål.docx", "A 2062-2025")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 26623-2026 FSC-klagomål mail.docx", "A 26623-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 2062-2025 FSC-klagomål mail.docx", "A 2062-2025")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 26623-2026 tillsynsbegäran.docx", "A 26623-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 2062-2025 tillsynsbegäran.docx", "A 2062-2025")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 26623-2026 tillsynsbegäran mail.docx", "A 26623-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 2062-2025 tillsynsbegäran mail.docx", "A 2062-2025")</f>
+        <v/>
+      </c>
+      <c r="AE23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/fåglar/A 2062-2025 prioriterade fågelarter.docx", "A 2062-2025")</f>
         <v/>
       </c>
     </row>
@@ -2961,7 +2961,7 @@
         <v>44558</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3066,7 +3066,7 @@
         <v>44609</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3139,7 +3139,7 @@
         <v>44489</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3217,7 +3217,7 @@
         <v>44546</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3273,7 +3273,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 3838-2022</t>
+          <t>A 20604-2022</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3287,10 +3287,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44587</v>
+        <v>44700</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3303,7 +3303,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>2.9</v>
+        <v>2</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3346,7 +3346,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 20604-2022</t>
+          <t>A 3838-2022</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3360,10 +3360,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44700</v>
+        <v>44587</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3376,7 +3376,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>2</v>
+        <v>2.9</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3436,7 +3436,7 @@
         <v>44655</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3497,7 +3497,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 64105-2023</t>
+          <t>A 23615-2025</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3511,10 +3511,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45279</v>
+        <v>45792</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3527,7 +3527,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>2.2</v>
+        <v>1.3</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3570,7 +3570,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 5264-2023</t>
+          <t>A 23627-2025</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3584,10 +3584,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44959</v>
+        <v>45792</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3600,7 +3600,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>5.8</v>
+        <v>1.7</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3643,7 +3643,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 27313-2023</t>
+          <t>A 59700-2021</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3657,10 +3657,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45096</v>
+        <v>44494</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3672,8 +3672,13 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I33" t="n">
-        <v>1.8</v>
+        <v>4.8</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3716,7 +3721,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 64114-2023</t>
+          <t>A 9655-2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3730,10 +3735,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45279</v>
+        <v>46070</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3745,8 +3750,13 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I34" t="n">
-        <v>0.4</v>
+        <v>17.2</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3789,7 +3799,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 50294-2023</t>
+          <t>A 38902-2024</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3803,10 +3813,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45216</v>
+        <v>45547</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3818,8 +3828,13 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I35" t="n">
-        <v>3.7</v>
+        <v>0.8</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3862,7 +3877,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 2602-2024</t>
+          <t>A 50294-2023</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3876,10 +3891,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45313</v>
+        <v>45216</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3892,7 +3907,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>0.7</v>
+        <v>3.7</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3935,7 +3950,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 51587-2023</t>
+          <t>A 5264-2023</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3949,10 +3964,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45215</v>
+        <v>44959</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3964,13 +3979,8 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I37" t="n">
-        <v>2.6</v>
+        <v>5.8</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4013,7 +4023,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 7275-2022</t>
+          <t>A 18787-2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4027,10 +4037,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44606</v>
+        <v>46128</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4048,7 +4058,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>9.6</v>
+        <v>7.8</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4091,7 +4101,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 59844-2022</t>
+          <t>A 18813-2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4105,10 +4115,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44901</v>
+        <v>46128</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4126,7 +4136,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>11.9</v>
+        <v>56</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4169,7 +4179,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 58011-2021</t>
+          <t>A 18818-2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4183,10 +4193,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44487</v>
+        <v>46128</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4204,7 +4214,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>9.199999999999999</v>
+        <v>17.8</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4247,7 +4257,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 72524-2021</t>
+          <t>A 18778-2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4261,10 +4271,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44546</v>
+        <v>46128</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4276,8 +4286,13 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I41" t="n">
-        <v>3.6</v>
+        <v>4.5</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4320,7 +4335,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 4338-2023</t>
+          <t>A 23098-2024</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4334,10 +4349,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44953</v>
+        <v>45450</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4349,8 +4364,13 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I42" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4393,7 +4413,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 64107-2023</t>
+          <t>A 59844-2022</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4407,10 +4427,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45279</v>
+        <v>44901</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4422,8 +4442,13 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I43" t="n">
-        <v>0.3</v>
+        <v>11.9</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4466,7 +4491,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 7112-2025</t>
+          <t>A 21206-2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4480,10 +4505,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45701</v>
+        <v>46146</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4495,8 +4520,13 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I44" t="n">
-        <v>2.4</v>
+        <v>0.9</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4539,7 +4569,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 59848-2022</t>
+          <t>A 54222-2023</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4553,10 +4583,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>44901</v>
+        <v>45225</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4574,7 +4604,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>10.7</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4617,7 +4647,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 38902-2024</t>
+          <t>A 4338-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4631,10 +4661,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45547</v>
+        <v>44953</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4646,13 +4676,8 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I46" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4695,7 +4720,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 59700-2021</t>
+          <t>A 58011-2021</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4709,10 +4734,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>44494</v>
+        <v>44487</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4730,7 +4755,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>4.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4773,7 +4798,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 23615-2025</t>
+          <t>A 72524-2021</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4787,10 +4812,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45792</v>
+        <v>44546</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4803,7 +4828,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>1.3</v>
+        <v>3.6</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4846,7 +4871,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 23627-2025</t>
+          <t>A 64107-2023</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4860,10 +4885,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45792</v>
+        <v>45279</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4876,7 +4901,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>1.7</v>
+        <v>0.3</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4919,7 +4944,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 3630-2023</t>
+          <t>A 23093-2024</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4933,10 +4958,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>44950</v>
+        <v>45450</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4948,8 +4973,13 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I50" t="n">
-        <v>1.4</v>
+        <v>0.9</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4992,7 +5022,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 23093-2024</t>
+          <t>A 24579-2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5006,10 +5036,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45450</v>
+        <v>46170</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5021,13 +5051,8 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I51" t="n">
-        <v>0.9</v>
+        <v>2.1</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5070,7 +5095,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 64110-2023</t>
+          <t>A 27313-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5084,10 +5109,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45279</v>
+        <v>45096</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5100,7 +5125,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>0.4</v>
+        <v>1.8</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5143,7 +5168,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 23098-2024</t>
+          <t>A 59377-2024</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5157,10 +5182,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45450</v>
+        <v>45638</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5172,13 +5197,8 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I53" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5221,7 +5241,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 54222-2023</t>
+          <t>A 58598-2025</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5235,10 +5255,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45225</v>
+        <v>45986</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5256,7 +5276,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>8.300000000000001</v>
+        <v>4.5</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5299,7 +5319,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 59377-2024</t>
+          <t>A 31160-2022</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5313,10 +5333,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45638</v>
+        <v>44770</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5329,7 +5349,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>0.6</v>
+        <v>3.7</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5372,7 +5392,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 7860-2024</t>
+          <t>A 26625-2026</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5386,10 +5406,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45348</v>
+        <v>46184</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5401,13 +5421,8 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I56" t="n">
-        <v>1.9</v>
+        <v>5.3</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5450,7 +5465,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 59402-2022</t>
+          <t>A 26629-2026</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5464,10 +5479,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>44906</v>
+        <v>46184</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5480,7 +5495,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5523,7 +5538,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 9655-2026</t>
+          <t>A 26633-2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5537,10 +5552,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>46070</v>
+        <v>46184</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5552,13 +5567,8 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I58" t="n">
-        <v>17.2</v>
+        <v>0.7</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5601,7 +5611,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 18778-2026</t>
+          <t>A 3754-2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5615,10 +5625,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>46128</v>
+        <v>46043</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5636,7 +5646,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>4.5</v>
+        <v>5.1</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5679,7 +5689,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 18813-2026</t>
+          <t>A 28797-2026</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5693,10 +5703,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>46128</v>
+        <v>46198</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5708,13 +5718,8 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I60" t="n">
-        <v>56</v>
+        <v>2.2</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5757,7 +5762,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 18818-2026</t>
+          <t>A 28740-2026</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5771,10 +5776,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>46128</v>
+        <v>46198</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5786,13 +5791,8 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I61" t="n">
-        <v>17.8</v>
+        <v>4.8</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5835,7 +5835,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 18787-2026</t>
+          <t>A 28735-2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5849,10 +5849,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>46128</v>
+        <v>46198</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5864,13 +5864,8 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I62" t="n">
-        <v>7.8</v>
+        <v>3.5</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5913,7 +5908,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 21206-2026</t>
+          <t>A 51587-2023</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5927,10 +5922,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>46146</v>
+        <v>45215</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5944,11 +5939,11 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Övriga statliga verk och myndigheter</t>
+          <t>Allmännings- och besparingsskogar</t>
         </is>
       </c>
       <c r="I63" t="n">
-        <v>0.9</v>
+        <v>2.6</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5991,7 +5986,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 24579-2026</t>
+          <t>A 59848-2022</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6005,10 +6000,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>46170</v>
+        <v>44901</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6020,8 +6015,13 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I64" t="n">
-        <v>2.1</v>
+        <v>10.7</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6064,7 +6064,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 31160-2022</t>
+          <t>A 31714-2026</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6078,10 +6078,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>44770</v>
+        <v>46226</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6094,7 +6094,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>3.7</v>
+        <v>5</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6137,7 +6137,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 58598-2025</t>
+          <t>A 64110-2023</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6151,10 +6151,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45986</v>
+        <v>45279</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6166,13 +6166,8 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I66" t="n">
-        <v>4.5</v>
+        <v>0.4</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6215,7 +6210,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 26633-2026</t>
+          <t>A 7275-2022</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6229,10 +6224,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>46184</v>
+        <v>44606</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6244,8 +6239,13 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I67" t="n">
-        <v>0.7</v>
+        <v>9.6</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6288,7 +6288,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 26625-2026</t>
+          <t>A 2602-2024</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6302,10 +6302,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>46184</v>
+        <v>45313</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6318,7 +6318,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>5.3</v>
+        <v>0.7</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6361,7 +6361,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 26629-2026</t>
+          <t>A 59402-2022</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6375,10 +6375,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>46184</v>
+        <v>44906</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6391,7 +6391,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6434,7 +6434,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 3754-2026</t>
+          <t>A 33058-2026</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6444,14 +6444,14 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>46043</v>
+        <v>46245</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6463,13 +6463,8 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I70" t="n">
-        <v>5.1</v>
+        <v>1.3</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6512,7 +6507,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 28735-2026</t>
+          <t>A 3630-2023</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6526,10 +6521,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>46198</v>
+        <v>44950</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6542,7 +6537,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>3.5</v>
+        <v>1.4</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6585,7 +6580,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 28740-2026</t>
+          <t>A 7860-2024</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6599,10 +6594,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>46198</v>
+        <v>45348</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6614,8 +6609,13 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I72" t="n">
-        <v>4.8</v>
+        <v>1.9</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6658,7 +6658,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 28797-2026</t>
+          <t>A 64105-2023</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6672,10 +6672,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>46198</v>
+        <v>45279</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6731,7 +6731,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 31714-2026</t>
+          <t>A 64114-2023</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6745,10 +6745,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>46226</v>
+        <v>45279</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6761,7 +6761,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>5</v>
+        <v>0.4</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6804,7 +6804,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 33058-2026</t>
+          <t>A 7112-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6814,14 +6814,14 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>46245</v>
+        <v>45701</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6834,7 +6834,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>1.3</v>
+        <v>2.4</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6894,7 +6894,7 @@
         <v>44558</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>

--- a/Översikt UPPLANDS-BRO.xlsx
+++ b/Översikt UPPLANDS-BRO.xlsx
@@ -601,7 +601,7 @@
         <v>44481</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -714,7 +714,7 @@
         <v>44552</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -822,7 +822,7 @@
         <v>44552</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -930,7 +930,7 @@
         <v>45232</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1025,7 +1025,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 18790-2026</t>
+          <t>A 73773-2021</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1039,10 +1039,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46128</v>
+        <v>44552</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1054,13 +1054,8 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I6" t="n">
-        <v>5.5</v>
+        <v>1.9</v>
       </c>
       <c r="J6" t="n">
         <v>2</v>
@@ -1093,371 +1088,376 @@
         <v>2</v>
       </c>
       <c r="T6" t="n">
+        <v>3</v>
+      </c>
+      <c r="U6" t="n">
+        <v>3</v>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>Kopparödla
+Gullviva</t>
+        </is>
+      </c>
+      <c r="W6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 73773-2021 artfynd.xlsx", "A 73773-2021")</f>
+        <v/>
+      </c>
+      <c r="X6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 73773-2021 karta.png", "A 73773-2021")</f>
+        <v/>
+      </c>
+      <c r="Y6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 73773-2021 georefererad karta.tif", "A 73773-2021")</f>
+        <v/>
+      </c>
+      <c r="AA6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 73773-2021 FSC-klagomål.docx", "A 73773-2021")</f>
+        <v/>
+      </c>
+      <c r="AB6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 73773-2021 FSC-klagomål mail.docx", "A 73773-2021")</f>
+        <v/>
+      </c>
+      <c r="AC6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 73773-2021 tillsynsbegäran.docx", "A 73773-2021")</f>
+        <v/>
+      </c>
+      <c r="AD6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 73773-2021 tillsynsbegäran mail.docx", "A 73773-2021")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>A 18772-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>46128</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>46298</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>UPPLANDS-BRO</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
         <v>2</v>
       </c>
-      <c r="U6" t="n">
-        <v>0</v>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
+      <c r="T7" t="n">
+        <v>2</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>Svedjenäva
+Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="W7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 18772-2026 artfynd.xlsx", "A 18772-2026")</f>
+        <v/>
+      </c>
+      <c r="X7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 18772-2026 karta.png", "A 18772-2026")</f>
+        <v/>
+      </c>
+      <c r="Y7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 18772-2026 georefererad karta.tif", "A 18772-2026")</f>
+        <v/>
+      </c>
+      <c r="AA7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 18772-2026 FSC-klagomål.docx", "A 18772-2026")</f>
+        <v/>
+      </c>
+      <c r="AB7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 18772-2026 FSC-klagomål mail.docx", "A 18772-2026")</f>
+        <v/>
+      </c>
+      <c r="AC7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 18772-2026 tillsynsbegäran.docx", "A 18772-2026")</f>
+        <v/>
+      </c>
+      <c r="AD7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 18772-2026 tillsynsbegäran mail.docx", "A 18772-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="15" customHeight="1">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>A 18790-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D8" s="1" t="n">
+        <v>46128</v>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>46298</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>UPPLANDS-BRO</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="J8" t="n">
+        <v>2</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>2</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>Fläcknycklar
 Nattviol</t>
         </is>
       </c>
-      <c r="W6">
+      <c r="W8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 18790-2026 artfynd.xlsx", "A 18790-2026")</f>
         <v/>
       </c>
-      <c r="X6">
+      <c r="X8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 18790-2026 karta.png", "A 18790-2026")</f>
         <v/>
       </c>
-      <c r="Y6">
+      <c r="Y8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 18790-2026 georefererad karta.tif", "A 18790-2026")</f>
         <v/>
       </c>
-      <c r="AA6">
+      <c r="AA8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 18790-2026 FSC-klagomål.docx", "A 18790-2026")</f>
         <v/>
       </c>
-      <c r="AB6">
+      <c r="AB8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 18790-2026 FSC-klagomål mail.docx", "A 18790-2026")</f>
         <v/>
       </c>
-      <c r="AC6">
+      <c r="AC8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 18790-2026 tillsynsbegäran.docx", "A 18790-2026")</f>
         <v/>
       </c>
-      <c r="AD6">
+      <c r="AD8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 18790-2026 tillsynsbegäran mail.docx", "A 18790-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>A 18772-2026</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
+    <row r="9" ht="15" customHeight="1">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>A 10909-2025</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D7" s="1" t="n">
-        <v>46128</v>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>46297</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>UPPLANDS-BRO</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="J7" t="n">
-        <v>1</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>1</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>1</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
+      <c r="D9" s="1" t="n">
+        <v>45722</v>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>46298</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>UPPLANDS-BRO</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
         <v>2</v>
       </c>
-      <c r="T7" t="n">
+      <c r="T9" t="n">
         <v>2</v>
       </c>
-      <c r="U7" t="n">
-        <v>0</v>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>Svedjenäva
-Fläcknycklar</t>
-        </is>
-      </c>
-      <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 18772-2026 artfynd.xlsx", "A 18772-2026")</f>
-        <v/>
-      </c>
-      <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 18772-2026 karta.png", "A 18772-2026")</f>
-        <v/>
-      </c>
-      <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 18772-2026 georefererad karta.tif", "A 18772-2026")</f>
-        <v/>
-      </c>
-      <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 18772-2026 FSC-klagomål.docx", "A 18772-2026")</f>
-        <v/>
-      </c>
-      <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 18772-2026 FSC-klagomål mail.docx", "A 18772-2026")</f>
-        <v/>
-      </c>
-      <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 18772-2026 tillsynsbegäran.docx", "A 18772-2026")</f>
-        <v/>
-      </c>
-      <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 18772-2026 tillsynsbegäran mail.docx", "A 18772-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8" ht="15" customHeight="1">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>A 10909-2025</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D8" s="1" t="n">
-        <v>45722</v>
-      </c>
-      <c r="E8" s="1" t="n">
-        <v>46297</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>UPPLANDS-BRO</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
-      <c r="I8" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="J8" t="n">
-        <v>1</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>1</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>1</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" t="n">
+      <c r="U9" t="n">
         <v>2</v>
       </c>
-      <c r="T8" t="n">
-        <v>2</v>
-      </c>
-      <c r="U8" t="n">
-        <v>2</v>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
+      <c r="V9" s="2" t="inlineStr">
         <is>
           <t>Arommusseron
 Fläcknycklar</t>
         </is>
       </c>
-      <c r="W8">
+      <c r="W9">
         <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 10909-2025 artfynd.xlsx", "A 10909-2025")</f>
         <v/>
       </c>
-      <c r="X8">
+      <c r="X9">
         <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 10909-2025 karta.png", "A 10909-2025")</f>
         <v/>
       </c>
-      <c r="Y8">
+      <c r="Y9">
         <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 10909-2025 georefererad karta.tif", "A 10909-2025")</f>
         <v/>
       </c>
-      <c r="AA8">
+      <c r="AA9">
         <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 10909-2025 FSC-klagomål.docx", "A 10909-2025")</f>
         <v/>
       </c>
-      <c r="AB8">
+      <c r="AB9">
         <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 10909-2025 FSC-klagomål mail.docx", "A 10909-2025")</f>
         <v/>
       </c>
-      <c r="AC8">
+      <c r="AC9">
         <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 10909-2025 tillsynsbegäran.docx", "A 10909-2025")</f>
         <v/>
       </c>
-      <c r="AD8">
+      <c r="AD9">
         <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 10909-2025 tillsynsbegäran mail.docx", "A 10909-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9" ht="15" customHeight="1">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>A 73773-2021</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D9" s="1" t="n">
-        <v>44552</v>
-      </c>
-      <c r="E9" s="1" t="n">
-        <v>46297</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>UPPLANDS-BRO</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="J9" t="n">
-        <v>2</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" t="n">
-        <v>2</v>
-      </c>
-      <c r="T9" t="n">
-        <v>3</v>
-      </c>
-      <c r="U9" t="n">
-        <v>3</v>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>Kopparödla
-Gullviva</t>
-        </is>
-      </c>
-      <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 73773-2021 artfynd.xlsx", "A 73773-2021")</f>
-        <v/>
-      </c>
-      <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 73773-2021 karta.png", "A 73773-2021")</f>
-        <v/>
-      </c>
-      <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 73773-2021 georefererad karta.tif", "A 73773-2021")</f>
-        <v/>
-      </c>
-      <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 73773-2021 FSC-klagomål.docx", "A 73773-2021")</f>
-        <v/>
-      </c>
-      <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 73773-2021 FSC-klagomål mail.docx", "A 73773-2021")</f>
-        <v/>
-      </c>
-      <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 73773-2021 tillsynsbegäran.docx", "A 73773-2021")</f>
-        <v/>
-      </c>
-      <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 73773-2021 tillsynsbegäran mail.docx", "A 73773-2021")</f>
         <v/>
       </c>
     </row>
@@ -1481,7 +1481,7 @@
         <v>44603</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1587,7 +1587,7 @@
         <v>44552</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1675,7 +1675,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 7955-2023</t>
+          <t>A 12363-2025</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1689,10 +1689,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>44973</v>
+        <v>45730</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1705,13 +1705,13 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>2.9</v>
+        <v>0.8</v>
       </c>
       <c r="J12" t="n">
         <v>1</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
@@ -1720,7 +1720,7 @@
         <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1729,10 +1729,10 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1741,46 +1741,46 @@
         <v>1</v>
       </c>
       <c r="U12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>Bombmurkla</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 7955-2023 artfynd.xlsx", "A 7955-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 12363-2025 artfynd.xlsx", "A 12363-2025")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 7955-2023 karta.png", "A 7955-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 12363-2025 karta.png", "A 12363-2025")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 7955-2023 georefererad karta.tif", "A 7955-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 12363-2025 georefererad karta.tif", "A 12363-2025")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 7955-2023 FSC-klagomål.docx", "A 7955-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 12363-2025 FSC-klagomål.docx", "A 12363-2025")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 7955-2023 FSC-klagomål mail.docx", "A 7955-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 12363-2025 FSC-klagomål mail.docx", "A 12363-2025")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 7955-2023 tillsynsbegäran.docx", "A 7955-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 12363-2025 tillsynsbegäran.docx", "A 12363-2025")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 7955-2023 tillsynsbegäran mail.docx", "A 7955-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 12363-2025 tillsynsbegäran mail.docx", "A 12363-2025")</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 12363-2025</t>
+          <t>A 25561-2025</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1794,10 +1794,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45730</v>
+        <v>45803</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1810,13 +1810,13 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>0.8</v>
+        <v>1.6</v>
       </c>
       <c r="J13" t="n">
         <v>1</v>
       </c>
       <c r="K13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -1825,7 +1825,7 @@
         <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -1834,10 +1834,10 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
@@ -1850,42 +1850,42 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Bombmurkla</t>
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 12363-2025 artfynd.xlsx", "A 12363-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 25561-2025 artfynd.xlsx", "A 25561-2025")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 12363-2025 karta.png", "A 12363-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 25561-2025 karta.png", "A 25561-2025")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 12363-2025 georefererad karta.tif", "A 12363-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 25561-2025 georefererad karta.tif", "A 25561-2025")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 12363-2025 FSC-klagomål.docx", "A 12363-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 25561-2025 FSC-klagomål.docx", "A 25561-2025")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 12363-2025 FSC-klagomål mail.docx", "A 12363-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 25561-2025 FSC-klagomål mail.docx", "A 25561-2025")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 12363-2025 tillsynsbegäran.docx", "A 12363-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 25561-2025 tillsynsbegäran.docx", "A 25561-2025")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 12363-2025 tillsynsbegäran mail.docx", "A 12363-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 25561-2025 tillsynsbegäran mail.docx", "A 25561-2025")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 25561-2025</t>
+          <t>A 53357-2025</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1899,10 +1899,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45803</v>
+        <v>45959</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>1.6</v>
+        <v>2.4</v>
       </c>
       <c r="J14" t="n">
         <v>1</v>
@@ -1948,7 +1948,7 @@
         <v>1</v>
       </c>
       <c r="T14" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="U14" t="n">
         <v>0</v>
@@ -1959,38 +1959,38 @@
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 25561-2025 artfynd.xlsx", "A 25561-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 53357-2025 artfynd.xlsx", "A 53357-2025")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 25561-2025 karta.png", "A 25561-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 53357-2025 karta.png", "A 53357-2025")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 25561-2025 georefererad karta.tif", "A 25561-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 53357-2025 georefererad karta.tif", "A 53357-2025")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 25561-2025 FSC-klagomål.docx", "A 25561-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 53357-2025 FSC-klagomål.docx", "A 53357-2025")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 25561-2025 FSC-klagomål mail.docx", "A 25561-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 53357-2025 FSC-klagomål mail.docx", "A 53357-2025")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 25561-2025 tillsynsbegäran.docx", "A 25561-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 53357-2025 tillsynsbegäran.docx", "A 53357-2025")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 25561-2025 tillsynsbegäran mail.docx", "A 25561-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 53357-2025 tillsynsbegäran mail.docx", "A 53357-2025")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 46438-2023</t>
+          <t>A 23099-2024</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2004,10 +2004,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45197</v>
+        <v>45450</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2019,11 +2019,16 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I15" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
@@ -2032,10 +2037,10 @@
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2056,46 +2061,46 @@
         <v>1</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Bombmurkla</t>
+          <t>Bredbrämad bastardsvärmare</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 46438-2023 artfynd.xlsx", "A 46438-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 23099-2024 artfynd.xlsx", "A 23099-2024")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 46438-2023 karta.png", "A 46438-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 23099-2024 karta.png", "A 23099-2024")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 46438-2023 georefererad karta.tif", "A 46438-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 23099-2024 georefererad karta.tif", "A 23099-2024")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 46438-2023 FSC-klagomål.docx", "A 46438-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 23099-2024 FSC-klagomål.docx", "A 23099-2024")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 46438-2023 FSC-klagomål mail.docx", "A 46438-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 23099-2024 FSC-klagomål mail.docx", "A 23099-2024")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 46438-2023 tillsynsbegäran.docx", "A 46438-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 23099-2024 tillsynsbegäran.docx", "A 23099-2024")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 46438-2023 tillsynsbegäran mail.docx", "A 46438-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 23099-2024 tillsynsbegäran mail.docx", "A 23099-2024")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 53357-2025</t>
+          <t>A 46438-2023</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2109,10 +2114,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45959</v>
+        <v>45197</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2125,7 +2130,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>2.4</v>
+        <v>0.5</v>
       </c>
       <c r="J16" t="n">
         <v>1</v>
@@ -2158,7 +2163,7 @@
         <v>1</v>
       </c>
       <c r="T16" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="U16" t="n">
         <v>0</v>
@@ -2169,38 +2174,38 @@
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 53357-2025 artfynd.xlsx", "A 53357-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 46438-2023 artfynd.xlsx", "A 46438-2023")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 53357-2025 karta.png", "A 53357-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 46438-2023 karta.png", "A 46438-2023")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 53357-2025 georefererad karta.tif", "A 53357-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 46438-2023 georefererad karta.tif", "A 46438-2023")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 53357-2025 FSC-klagomål.docx", "A 53357-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 46438-2023 FSC-klagomål.docx", "A 46438-2023")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 53357-2025 FSC-klagomål mail.docx", "A 53357-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 46438-2023 FSC-klagomål mail.docx", "A 46438-2023")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 53357-2025 tillsynsbegäran.docx", "A 53357-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 46438-2023 tillsynsbegäran.docx", "A 46438-2023")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 53357-2025 tillsynsbegäran mail.docx", "A 53357-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 46438-2023 tillsynsbegäran mail.docx", "A 46438-2023")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 23099-2024</t>
+          <t>A 26196-2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2210,14 +2215,14 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45450</v>
+        <v>46182</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2229,13 +2234,8 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I17" t="n">
-        <v>0.7</v>
+        <v>53.1</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2247,7 +2247,7 @@
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
@@ -2259,58 +2259,58 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
       </c>
       <c r="T17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Bredbrämad bastardsvärmare</t>
+          <t>Liljekonvalj</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 23099-2024 artfynd.xlsx", "A 23099-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 26196-2026 artfynd.xlsx", "A 26196-2026")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 23099-2024 karta.png", "A 23099-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 26196-2026 karta.png", "A 26196-2026")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 23099-2024 georefererad karta.tif", "A 23099-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 26196-2026 georefererad karta.tif", "A 26196-2026")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 23099-2024 FSC-klagomål.docx", "A 23099-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 26196-2026 FSC-klagomål.docx", "A 26196-2026")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 23099-2024 FSC-klagomål mail.docx", "A 23099-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 26196-2026 FSC-klagomål mail.docx", "A 26196-2026")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 23099-2024 tillsynsbegäran.docx", "A 23099-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 26196-2026 tillsynsbegäran.docx", "A 26196-2026")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 23099-2024 tillsynsbegäran mail.docx", "A 23099-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 26196-2026 tillsynsbegäran mail.docx", "A 26196-2026")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 64098-2023</t>
+          <t>A 26637-2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2324,10 +2324,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45279</v>
+        <v>46184</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2340,7 +2340,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>0.3</v>
+        <v>5.4</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2349,10 +2349,10 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
@@ -2367,7 +2367,7 @@
         <v>1</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
@@ -2380,42 +2380,42 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Skogsalmsdvärgmal</t>
+          <t>Igelkott</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 64098-2023 artfynd.xlsx", "A 64098-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 26637-2026 artfynd.xlsx", "A 26637-2026")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 64098-2023 karta.png", "A 64098-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 26637-2026 karta.png", "A 26637-2026")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 64098-2023 georefererad karta.tif", "A 64098-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 26637-2026 georefererad karta.tif", "A 26637-2026")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 64098-2023 FSC-klagomål.docx", "A 64098-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 26637-2026 FSC-klagomål.docx", "A 26637-2026")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 64098-2023 FSC-klagomål mail.docx", "A 64098-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 26637-2026 FSC-klagomål mail.docx", "A 26637-2026")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 64098-2023 tillsynsbegäran.docx", "A 64098-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 26637-2026 tillsynsbegäran.docx", "A 26637-2026")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 64098-2023 tillsynsbegäran mail.docx", "A 64098-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 26637-2026 tillsynsbegäran mail.docx", "A 26637-2026")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 26196-2026</t>
+          <t>A 26623-2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2425,14 +2425,14 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46182</v>
+        <v>46184</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2445,7 +2445,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>53.1</v>
+        <v>4.6</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2454,7 +2454,7 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M19" t="n">
         <v>0</v>
@@ -2469,7 +2469,7 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
@@ -2478,49 +2478,49 @@
         <v>1</v>
       </c>
       <c r="T19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Liljekonvalj</t>
+          <t>Svartöra</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 26196-2026 artfynd.xlsx", "A 26196-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 26623-2026 artfynd.xlsx", "A 26623-2026")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 26196-2026 karta.png", "A 26196-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 26623-2026 karta.png", "A 26623-2026")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 26196-2026 georefererad karta.tif", "A 26196-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 26623-2026 georefererad karta.tif", "A 26623-2026")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 26196-2026 FSC-klagomål.docx", "A 26196-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 26623-2026 FSC-klagomål.docx", "A 26623-2026")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 26196-2026 FSC-klagomål mail.docx", "A 26196-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 26623-2026 FSC-klagomål mail.docx", "A 26623-2026")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 26196-2026 tillsynsbegäran.docx", "A 26196-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 26623-2026 tillsynsbegäran.docx", "A 26623-2026")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 26196-2026 tillsynsbegäran mail.docx", "A 26196-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 26623-2026 tillsynsbegäran mail.docx", "A 26623-2026")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 26623-2026</t>
+          <t>A 11447-2025</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2530,14 +2530,14 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46184</v>
+        <v>45726</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2550,16 +2550,16 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>4.6</v>
+        <v>1.5</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
         <v>0</v>
@@ -2574,7 +2574,7 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
@@ -2590,42 +2590,42 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>Svartöra</t>
+          <t>Myskbock</t>
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 26623-2026 artfynd.xlsx", "A 26623-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 11447-2025 artfynd.xlsx", "A 11447-2025")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 26623-2026 karta.png", "A 26623-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 11447-2025 karta.png", "A 11447-2025")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 26623-2026 georefererad karta.tif", "A 26623-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 11447-2025 georefererad karta.tif", "A 11447-2025")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 26623-2026 FSC-klagomål.docx", "A 26623-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 11447-2025 FSC-klagomål.docx", "A 11447-2025")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 26623-2026 FSC-klagomål mail.docx", "A 26623-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 11447-2025 FSC-klagomål mail.docx", "A 11447-2025")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 26623-2026 tillsynsbegäran.docx", "A 26623-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 11447-2025 tillsynsbegäran.docx", "A 11447-2025")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 26623-2026 tillsynsbegäran mail.docx", "A 26623-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 11447-2025 tillsynsbegäran mail.docx", "A 11447-2025")</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 26637-2026</t>
+          <t>A 7955-2023</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2639,10 +2639,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46184</v>
+        <v>44973</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2655,10 +2655,10 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>5.4</v>
+        <v>2.9</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
@@ -2667,10 +2667,10 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2691,46 +2691,46 @@
         <v>1</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Igelkott</t>
+          <t>Bombmurkla</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 26637-2026 artfynd.xlsx", "A 26637-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 7955-2023 artfynd.xlsx", "A 7955-2023")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 26637-2026 karta.png", "A 26637-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 7955-2023 karta.png", "A 7955-2023")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 26637-2026 georefererad karta.tif", "A 26637-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 7955-2023 georefererad karta.tif", "A 7955-2023")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 26637-2026 FSC-klagomål.docx", "A 26637-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 7955-2023 FSC-klagomål.docx", "A 7955-2023")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 26637-2026 FSC-klagomål mail.docx", "A 26637-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 7955-2023 FSC-klagomål mail.docx", "A 7955-2023")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 26637-2026 tillsynsbegäran.docx", "A 26637-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 7955-2023 tillsynsbegäran.docx", "A 7955-2023")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 26637-2026 tillsynsbegäran mail.docx", "A 26637-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 7955-2023 tillsynsbegäran mail.docx", "A 7955-2023")</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 11447-2025</t>
+          <t>A 64098-2023</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2740,14 +2740,14 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45726</v>
+        <v>45279</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2760,16 +2760,16 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>1.5</v>
+        <v>0.3</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M22" t="n">
         <v>0</v>
@@ -2784,7 +2784,7 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R22" t="n">
         <v>0</v>
@@ -2800,35 +2800,35 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>Myskbock</t>
+          <t>Skogsalmsdvärgmal</t>
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 11447-2025 artfynd.xlsx", "A 11447-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 64098-2023 artfynd.xlsx", "A 64098-2023")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 11447-2025 karta.png", "A 11447-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 64098-2023 karta.png", "A 64098-2023")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 11447-2025 georefererad karta.tif", "A 11447-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 64098-2023 georefererad karta.tif", "A 64098-2023")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 11447-2025 FSC-klagomål.docx", "A 11447-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 64098-2023 FSC-klagomål.docx", "A 64098-2023")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 11447-2025 FSC-klagomål mail.docx", "A 11447-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 64098-2023 FSC-klagomål mail.docx", "A 64098-2023")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 11447-2025 tillsynsbegäran.docx", "A 11447-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 64098-2023 tillsynsbegäran.docx", "A 64098-2023")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 11447-2025 tillsynsbegäran mail.docx", "A 11447-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 64098-2023 tillsynsbegäran mail.docx", "A 64098-2023")</f>
         <v/>
       </c>
     </row>
@@ -2852,7 +2852,7 @@
         <v>45671</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2961,7 +2961,7 @@
         <v>44558</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3066,7 +3066,7 @@
         <v>44609</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3139,7 +3139,7 @@
         <v>44489</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3217,7 +3217,7 @@
         <v>44546</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3290,7 +3290,7 @@
         <v>44700</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3363,7 +3363,7 @@
         <v>44587</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3436,7 +3436,7 @@
         <v>44655</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3497,7 +3497,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 23615-2025</t>
+          <t>A 64105-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3511,10 +3511,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45792</v>
+        <v>45279</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3527,7 +3527,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>1.3</v>
+        <v>2.2</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3570,7 +3570,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 23627-2025</t>
+          <t>A 2602-2024</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3584,10 +3584,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45792</v>
+        <v>45313</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3600,7 +3600,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>1.7</v>
+        <v>0.7</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3643,7 +3643,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 59700-2021</t>
+          <t>A 59844-2022</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3657,10 +3657,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44494</v>
+        <v>44901</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3678,7 +3678,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>4.8</v>
+        <v>11.9</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3721,7 +3721,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 9655-2026</t>
+          <t>A 3630-2023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3735,10 +3735,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>46070</v>
+        <v>44950</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3750,13 +3750,8 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I34" t="n">
-        <v>17.2</v>
+        <v>1.4</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3799,7 +3794,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 38902-2024</t>
+          <t>A 23093-2024</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3813,10 +3808,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45547</v>
+        <v>45450</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3834,7 +3829,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3877,7 +3872,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 50294-2023</t>
+          <t>A 23615-2025</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3891,10 +3886,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45216</v>
+        <v>45792</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3907,7 +3902,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>3.7</v>
+        <v>1.3</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3950,7 +3945,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 5264-2023</t>
+          <t>A 54222-2023</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3964,10 +3959,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44959</v>
+        <v>45225</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3979,8 +3974,13 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I37" t="n">
-        <v>5.8</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4023,7 +4023,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 18787-2026</t>
+          <t>A 23627-2025</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4037,10 +4037,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>46128</v>
+        <v>45792</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4052,13 +4052,8 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I38" t="n">
-        <v>7.8</v>
+        <v>1.7</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4101,7 +4096,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 18813-2026</t>
+          <t>A 7860-2024</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4115,10 +4110,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>46128</v>
+        <v>45348</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4136,7 +4131,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>56</v>
+        <v>1.9</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4179,7 +4174,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 18818-2026</t>
+          <t>A 9655-2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4193,10 +4188,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>46128</v>
+        <v>46070</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4214,7 +4209,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>17.8</v>
+        <v>17.2</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4257,7 +4252,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 18778-2026</t>
+          <t>A 27313-2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4271,10 +4266,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>46128</v>
+        <v>45096</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4286,13 +4281,8 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I41" t="n">
-        <v>4.5</v>
+        <v>1.8</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4335,7 +4325,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 23098-2024</t>
+          <t>A 64114-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4349,10 +4339,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45450</v>
+        <v>45279</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4364,13 +4354,8 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I42" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4413,7 +4398,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 59844-2022</t>
+          <t>A 50294-2023</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4427,10 +4412,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44901</v>
+        <v>45216</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4442,13 +4427,8 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I43" t="n">
-        <v>11.9</v>
+        <v>3.7</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4491,7 +4471,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 21206-2026</t>
+          <t>A 58011-2021</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4505,10 +4485,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>46146</v>
+        <v>44487</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4526,7 +4506,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4569,7 +4549,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 54222-2023</t>
+          <t>A 18778-2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4583,10 +4563,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45225</v>
+        <v>46128</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4604,7 +4584,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>8.300000000000001</v>
+        <v>4.5</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4647,7 +4627,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 4338-2023</t>
+          <t>A 18813-2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4661,10 +4641,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44953</v>
+        <v>46128</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4676,8 +4656,13 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I46" t="n">
-        <v>1.1</v>
+        <v>56</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4720,7 +4705,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 58011-2021</t>
+          <t>A 18818-2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4734,10 +4719,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>44487</v>
+        <v>46128</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4755,7 +4740,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>9.199999999999999</v>
+        <v>17.8</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4798,7 +4783,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 72524-2021</t>
+          <t>A 18787-2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4812,10 +4797,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>44546</v>
+        <v>46128</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4827,8 +4812,13 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I48" t="n">
-        <v>3.6</v>
+        <v>7.8</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4871,7 +4861,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 64107-2023</t>
+          <t>A 64110-2023</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4888,7 +4878,7 @@
         <v>45279</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4901,7 +4891,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4944,7 +4934,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 23093-2024</t>
+          <t>A 23098-2024</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4961,7 +4951,7 @@
         <v>45450</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4979,7 +4969,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5022,7 +5012,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 24579-2026</t>
+          <t>A 21206-2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5036,10 +5026,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>46170</v>
+        <v>46146</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5051,8 +5041,13 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I51" t="n">
-        <v>2.1</v>
+        <v>0.9</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5095,7 +5090,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 27313-2023</t>
+          <t>A 59377-2024</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5109,10 +5104,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45096</v>
+        <v>45638</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5125,7 +5120,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>1.8</v>
+        <v>0.6</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5168,7 +5163,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 59377-2024</t>
+          <t>A 59402-2022</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5182,10 +5177,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45638</v>
+        <v>44906</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5198,7 +5193,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>0.6</v>
+        <v>1.8</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5241,7 +5236,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 58598-2025</t>
+          <t>A 24579-2026</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5255,10 +5250,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45986</v>
+        <v>46170</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5270,13 +5265,8 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I54" t="n">
-        <v>4.5</v>
+        <v>2.1</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5336,7 +5326,7 @@
         <v>44770</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5392,7 +5382,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 26625-2026</t>
+          <t>A 58598-2025</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5406,10 +5396,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>46184</v>
+        <v>45986</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5421,8 +5411,13 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I56" t="n">
-        <v>5.3</v>
+        <v>4.5</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5465,7 +5460,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 26629-2026</t>
+          <t>A 5264-2023</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5479,10 +5474,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>46184</v>
+        <v>44959</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5495,7 +5490,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>2</v>
+        <v>5.8</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5555,7 +5550,7 @@
         <v>46184</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5611,7 +5606,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 3754-2026</t>
+          <t>A 26625-2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5625,10 +5620,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>46043</v>
+        <v>46184</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5640,13 +5635,8 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I59" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5689,7 +5679,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 28797-2026</t>
+          <t>A 26629-2026</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5703,10 +5693,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>46198</v>
+        <v>46184</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5719,7 +5709,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5762,7 +5752,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 28740-2026</t>
+          <t>A 3754-2026</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5776,10 +5766,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>46198</v>
+        <v>46043</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5791,8 +5781,13 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I61" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5835,7 +5830,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 28735-2026</t>
+          <t>A 51587-2023</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5849,10 +5844,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>46198</v>
+        <v>45215</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5864,8 +5859,13 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I62" t="n">
-        <v>3.5</v>
+        <v>2.6</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5908,7 +5908,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 51587-2023</t>
+          <t>A 28735-2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5922,10 +5922,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45215</v>
+        <v>46198</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5937,13 +5937,8 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I63" t="n">
-        <v>2.6</v>
+        <v>3.5</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5986,7 +5981,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 59848-2022</t>
+          <t>A 28740-2026</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6000,10 +5995,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>44901</v>
+        <v>46198</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6015,13 +6010,8 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I64" t="n">
-        <v>10.7</v>
+        <v>4.8</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6064,7 +6054,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 31714-2026</t>
+          <t>A 28797-2026</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6078,10 +6068,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>46226</v>
+        <v>46198</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6094,7 +6084,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>5</v>
+        <v>2.2</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6137,7 +6127,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 64110-2023</t>
+          <t>A 72524-2021</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6151,10 +6141,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45279</v>
+        <v>44546</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6167,7 +6157,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>0.4</v>
+        <v>3.6</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6210,7 +6200,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 7275-2022</t>
+          <t>A 4338-2023</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6224,10 +6214,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>44606</v>
+        <v>44953</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6239,13 +6229,8 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I67" t="n">
-        <v>9.6</v>
+        <v>1.1</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6288,7 +6273,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 2602-2024</t>
+          <t>A 59848-2022</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6302,10 +6287,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45313</v>
+        <v>44901</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6317,8 +6302,13 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I68" t="n">
-        <v>0.7</v>
+        <v>10.7</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6361,7 +6351,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 59402-2022</t>
+          <t>A 31714-2026</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6375,10 +6365,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>44906</v>
+        <v>46226</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6391,7 +6381,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1.8</v>
+        <v>5</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6434,7 +6424,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 33058-2026</t>
+          <t>A 59700-2021</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6444,14 +6434,14 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>46245</v>
+        <v>44494</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6463,8 +6453,13 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I70" t="n">
-        <v>1.3</v>
+        <v>4.8</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6507,7 +6502,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 3630-2023</t>
+          <t>A 33058-2026</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6517,14 +6512,14 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>44950</v>
+        <v>46245</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6537,7 +6532,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6580,7 +6575,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 7860-2024</t>
+          <t>A 7275-2022</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6594,10 +6589,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45348</v>
+        <v>44606</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6615,7 +6610,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>1.9</v>
+        <v>9.6</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6658,7 +6653,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 64105-2023</t>
+          <t>A 64107-2023</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6675,7 +6670,7 @@
         <v>45279</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6688,7 +6683,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>2.2</v>
+        <v>0.3</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6731,7 +6726,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 64114-2023</t>
+          <t>A 7112-2025</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6745,10 +6740,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45279</v>
+        <v>45701</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6761,7 +6756,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>0.4</v>
+        <v>2.4</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6804,7 +6799,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 7112-2025</t>
+          <t>A 38902-2024</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6818,10 +6813,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45701</v>
+        <v>45547</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6833,8 +6828,13 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I75" t="n">
-        <v>2.4</v>
+        <v>0.8</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6894,7 +6894,7 @@
         <v>44558</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>

--- a/Översikt UPPLANDS-BRO.xlsx
+++ b/Översikt UPPLANDS-BRO.xlsx
@@ -601,7 +601,7 @@
         <v>44481</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -714,7 +714,7 @@
         <v>44552</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -822,7 +822,7 @@
         <v>44552</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -930,7 +930,7 @@
         <v>45232</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1042,7 +1042,7 @@
         <v>44552</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1148,7 +1148,7 @@
         <v>46128</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1259,7 +1259,7 @@
         <v>46128</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1370,7 +1370,7 @@
         <v>45722</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1481,7 +1481,7 @@
         <v>44603</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1587,7 +1587,7 @@
         <v>44552</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1692,7 +1692,7 @@
         <v>45730</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1797,7 +1797,7 @@
         <v>45803</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1902,7 +1902,7 @@
         <v>45959</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2007,7 +2007,7 @@
         <v>45450</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2117,7 +2117,7 @@
         <v>45197</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2222,7 +2222,7 @@
         <v>46182</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2327,7 +2327,7 @@
         <v>46184</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2432,7 +2432,7 @@
         <v>46184</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2537,7 +2537,7 @@
         <v>45726</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2642,7 +2642,7 @@
         <v>44973</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2747,7 +2747,7 @@
         <v>45279</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2852,7 +2852,7 @@
         <v>45671</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2961,7 +2961,7 @@
         <v>44558</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3066,7 +3066,7 @@
         <v>44609</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3139,7 +3139,7 @@
         <v>44489</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3217,7 +3217,7 @@
         <v>44546</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3290,7 +3290,7 @@
         <v>44700</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3363,7 +3363,7 @@
         <v>44587</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3436,7 +3436,7 @@
         <v>44655</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3514,7 +3514,7 @@
         <v>45279</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3587,7 +3587,7 @@
         <v>45313</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3660,7 +3660,7 @@
         <v>44901</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
         <v>44950</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3811,7 +3811,7 @@
         <v>45450</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3889,7 +3889,7 @@
         <v>45792</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3962,7 +3962,7 @@
         <v>45225</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4040,7 +4040,7 @@
         <v>45792</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4113,7 +4113,7 @@
         <v>45348</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4191,7 +4191,7 @@
         <v>46070</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4269,7 +4269,7 @@
         <v>45096</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4342,7 +4342,7 @@
         <v>45279</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4415,7 +4415,7 @@
         <v>45216</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4488,7 +4488,7 @@
         <v>44487</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4566,7 +4566,7 @@
         <v>46128</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4644,7 +4644,7 @@
         <v>46128</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4722,7 +4722,7 @@
         <v>46128</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4800,7 +4800,7 @@
         <v>46128</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4878,7 +4878,7 @@
         <v>45279</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4951,7 +4951,7 @@
         <v>45450</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5029,7 +5029,7 @@
         <v>46146</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5107,7 +5107,7 @@
         <v>45638</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5180,7 +5180,7 @@
         <v>44906</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5253,7 +5253,7 @@
         <v>46170</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5326,7 +5326,7 @@
         <v>44770</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5399,7 +5399,7 @@
         <v>45986</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5477,7 +5477,7 @@
         <v>44959</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5550,7 +5550,7 @@
         <v>46184</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5623,7 +5623,7 @@
         <v>46184</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5696,7 +5696,7 @@
         <v>46184</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5769,7 +5769,7 @@
         <v>46043</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5847,7 +5847,7 @@
         <v>45215</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5925,7 +5925,7 @@
         <v>46198</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5998,7 +5998,7 @@
         <v>46198</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6071,7 +6071,7 @@
         <v>46198</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6144,7 +6144,7 @@
         <v>44546</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6217,7 +6217,7 @@
         <v>44953</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6290,7 +6290,7 @@
         <v>44901</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6368,7 +6368,7 @@
         <v>46226</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6441,7 +6441,7 @@
         <v>44494</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6519,7 +6519,7 @@
         <v>46245</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6592,7 +6592,7 @@
         <v>44606</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6670,7 +6670,7 @@
         <v>45279</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6743,7 +6743,7 @@
         <v>45701</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6816,7 +6816,7 @@
         <v>45547</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6894,7 +6894,7 @@
         <v>44558</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>

--- a/Översikt UPPLANDS-BRO.xlsx
+++ b/Översikt UPPLANDS-BRO.xlsx
@@ -601,7 +601,7 @@
         <v>44481</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -714,7 +714,7 @@
         <v>44552</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -822,7 +822,7 @@
         <v>44552</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -930,7 +930,7 @@
         <v>45232</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1042,7 +1042,7 @@
         <v>44552</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1148,7 +1148,7 @@
         <v>46128</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1259,7 +1259,7 @@
         <v>46128</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1370,7 +1370,7 @@
         <v>45722</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1481,7 +1481,7 @@
         <v>44603</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1587,7 +1587,7 @@
         <v>44552</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1692,7 +1692,7 @@
         <v>45730</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1797,7 +1797,7 @@
         <v>45803</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1902,7 +1902,7 @@
         <v>45959</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2007,7 +2007,7 @@
         <v>45450</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2117,7 +2117,7 @@
         <v>45197</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2222,7 +2222,7 @@
         <v>46182</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2327,7 +2327,7 @@
         <v>46184</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2432,7 +2432,7 @@
         <v>46184</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2537,7 +2537,7 @@
         <v>45726</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2642,7 +2642,7 @@
         <v>44973</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2747,7 +2747,7 @@
         <v>45279</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2852,7 +2852,7 @@
         <v>45671</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2961,7 +2961,7 @@
         <v>44558</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3066,7 +3066,7 @@
         <v>44609</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3139,7 +3139,7 @@
         <v>44489</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3217,7 +3217,7 @@
         <v>44546</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3290,7 +3290,7 @@
         <v>44700</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3363,7 +3363,7 @@
         <v>44587</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3436,7 +3436,7 @@
         <v>44655</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3514,7 +3514,7 @@
         <v>45279</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3587,7 +3587,7 @@
         <v>45313</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3660,7 +3660,7 @@
         <v>44901</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
         <v>44950</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3811,7 +3811,7 @@
         <v>45450</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3889,7 +3889,7 @@
         <v>45792</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3962,7 +3962,7 @@
         <v>45225</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4040,7 +4040,7 @@
         <v>45792</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4113,7 +4113,7 @@
         <v>45348</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4191,7 +4191,7 @@
         <v>46070</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4269,7 +4269,7 @@
         <v>45096</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4342,7 +4342,7 @@
         <v>45279</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4415,7 +4415,7 @@
         <v>45216</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4488,7 +4488,7 @@
         <v>44487</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4566,7 +4566,7 @@
         <v>46128</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4644,7 +4644,7 @@
         <v>46128</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4722,7 +4722,7 @@
         <v>46128</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4800,7 +4800,7 @@
         <v>46128</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4878,7 +4878,7 @@
         <v>45279</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4951,7 +4951,7 @@
         <v>45450</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5029,7 +5029,7 @@
         <v>46146</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5107,7 +5107,7 @@
         <v>45638</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5180,7 +5180,7 @@
         <v>44906</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5253,7 +5253,7 @@
         <v>46170</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5326,7 +5326,7 @@
         <v>44770</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5399,7 +5399,7 @@
         <v>45986</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5477,7 +5477,7 @@
         <v>44959</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5550,7 +5550,7 @@
         <v>46184</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5623,7 +5623,7 @@
         <v>46184</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5696,7 +5696,7 @@
         <v>46184</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5769,7 +5769,7 @@
         <v>46043</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5847,7 +5847,7 @@
         <v>45215</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5925,7 +5925,7 @@
         <v>46198</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5998,7 +5998,7 @@
         <v>46198</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6071,7 +6071,7 @@
         <v>46198</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6144,7 +6144,7 @@
         <v>44546</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6217,7 +6217,7 @@
         <v>44953</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6290,7 +6290,7 @@
         <v>44901</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6368,7 +6368,7 @@
         <v>46226</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6441,7 +6441,7 @@
         <v>44494</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6519,7 +6519,7 @@
         <v>46245</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6592,7 +6592,7 @@
         <v>44606</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6670,7 +6670,7 @@
         <v>45279</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6743,7 +6743,7 @@
         <v>45701</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6816,7 +6816,7 @@
         <v>45547</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6894,7 +6894,7 @@
         <v>44558</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>

--- a/Översikt UPPLANDS-BRO.xlsx
+++ b/Översikt UPPLANDS-BRO.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE76"/>
+  <dimension ref="A1:AE75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>44481</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -714,7 +714,7 @@
         <v>44552</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -822,7 +822,7 @@
         <v>44552</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -930,7 +930,7 @@
         <v>45232</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1025,7 +1025,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 73773-2021</t>
+          <t>A 18790-2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1039,10 +1039,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>44552</v>
+        <v>46128</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1054,8 +1054,13 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I6" t="n">
-        <v>1.9</v>
+        <v>5.5</v>
       </c>
       <c r="J6" t="n">
         <v>2</v>
@@ -1088,376 +1093,371 @@
         <v>2</v>
       </c>
       <c r="T6" t="n">
+        <v>2</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>Fläcknycklar
+Nattviol</t>
+        </is>
+      </c>
+      <c r="W6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 18790-2026 artfynd.xlsx", "A 18790-2026")</f>
+        <v/>
+      </c>
+      <c r="X6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 18790-2026 karta.png", "A 18790-2026")</f>
+        <v/>
+      </c>
+      <c r="Y6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 18790-2026 georefererad karta.tif", "A 18790-2026")</f>
+        <v/>
+      </c>
+      <c r="AA6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 18790-2026 FSC-klagomål.docx", "A 18790-2026")</f>
+        <v/>
+      </c>
+      <c r="AB6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 18790-2026 FSC-klagomål mail.docx", "A 18790-2026")</f>
+        <v/>
+      </c>
+      <c r="AC6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 18790-2026 tillsynsbegäran.docx", "A 18790-2026")</f>
+        <v/>
+      </c>
+      <c r="AD6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 18790-2026 tillsynsbegäran mail.docx", "A 18790-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>A 18772-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>46128</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>46301</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>UPPLANDS-BRO</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>2</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>Svedjenäva
+Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="W7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 18772-2026 artfynd.xlsx", "A 18772-2026")</f>
+        <v/>
+      </c>
+      <c r="X7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 18772-2026 karta.png", "A 18772-2026")</f>
+        <v/>
+      </c>
+      <c r="Y7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 18772-2026 georefererad karta.tif", "A 18772-2026")</f>
+        <v/>
+      </c>
+      <c r="AA7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 18772-2026 FSC-klagomål.docx", "A 18772-2026")</f>
+        <v/>
+      </c>
+      <c r="AB7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 18772-2026 FSC-klagomål mail.docx", "A 18772-2026")</f>
+        <v/>
+      </c>
+      <c r="AC7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 18772-2026 tillsynsbegäran.docx", "A 18772-2026")</f>
+        <v/>
+      </c>
+      <c r="AD7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 18772-2026 tillsynsbegäran mail.docx", "A 18772-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="15" customHeight="1">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>A 10909-2025</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D8" s="1" t="n">
+        <v>45722</v>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>46301</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>UPPLANDS-BRO</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="J8" t="n">
+        <v>1</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>2</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2</v>
+      </c>
+      <c r="U8" t="n">
+        <v>2</v>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>Arommusseron
+Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="W8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 10909-2025 artfynd.xlsx", "A 10909-2025")</f>
+        <v/>
+      </c>
+      <c r="X8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 10909-2025 karta.png", "A 10909-2025")</f>
+        <v/>
+      </c>
+      <c r="Y8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 10909-2025 georefererad karta.tif", "A 10909-2025")</f>
+        <v/>
+      </c>
+      <c r="AA8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 10909-2025 FSC-klagomål.docx", "A 10909-2025")</f>
+        <v/>
+      </c>
+      <c r="AB8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 10909-2025 FSC-klagomål mail.docx", "A 10909-2025")</f>
+        <v/>
+      </c>
+      <c r="AC8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 10909-2025 tillsynsbegäran.docx", "A 10909-2025")</f>
+        <v/>
+      </c>
+      <c r="AD8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 10909-2025 tillsynsbegäran mail.docx", "A 10909-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="15" customHeight="1">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>A 73773-2021</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D9" s="1" t="n">
+        <v>44552</v>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>46301</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>UPPLANDS-BRO</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="J9" t="n">
+        <v>2</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>2</v>
+      </c>
+      <c r="T9" t="n">
         <v>3</v>
       </c>
-      <c r="U6" t="n">
+      <c r="U9" t="n">
         <v>3</v>
       </c>
-      <c r="V6" s="2" t="inlineStr">
+      <c r="V9" s="2" t="inlineStr">
         <is>
           <t>Kopparödla
 Gullviva</t>
         </is>
       </c>
-      <c r="W6">
+      <c r="W9">
         <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 73773-2021 artfynd.xlsx", "A 73773-2021")</f>
         <v/>
       </c>
-      <c r="X6">
+      <c r="X9">
         <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 73773-2021 karta.png", "A 73773-2021")</f>
         <v/>
       </c>
-      <c r="Y6">
+      <c r="Y9">
         <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 73773-2021 georefererad karta.tif", "A 73773-2021")</f>
         <v/>
       </c>
-      <c r="AA6">
+      <c r="AA9">
         <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 73773-2021 FSC-klagomål.docx", "A 73773-2021")</f>
         <v/>
       </c>
-      <c r="AB6">
+      <c r="AB9">
         <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 73773-2021 FSC-klagomål mail.docx", "A 73773-2021")</f>
         <v/>
       </c>
-      <c r="AC6">
+      <c r="AC9">
         <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 73773-2021 tillsynsbegäran.docx", "A 73773-2021")</f>
         <v/>
       </c>
-      <c r="AD6">
+      <c r="AD9">
         <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 73773-2021 tillsynsbegäran mail.docx", "A 73773-2021")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>A 18772-2026</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>46128</v>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>46300</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>UPPLANDS-BRO</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="J7" t="n">
-        <v>1</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>1</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>1</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
-        <v>2</v>
-      </c>
-      <c r="T7" t="n">
-        <v>2</v>
-      </c>
-      <c r="U7" t="n">
-        <v>0</v>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>Svedjenäva
-Fläcknycklar</t>
-        </is>
-      </c>
-      <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 18772-2026 artfynd.xlsx", "A 18772-2026")</f>
-        <v/>
-      </c>
-      <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 18772-2026 karta.png", "A 18772-2026")</f>
-        <v/>
-      </c>
-      <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 18772-2026 georefererad karta.tif", "A 18772-2026")</f>
-        <v/>
-      </c>
-      <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 18772-2026 FSC-klagomål.docx", "A 18772-2026")</f>
-        <v/>
-      </c>
-      <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 18772-2026 FSC-klagomål mail.docx", "A 18772-2026")</f>
-        <v/>
-      </c>
-      <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 18772-2026 tillsynsbegäran.docx", "A 18772-2026")</f>
-        <v/>
-      </c>
-      <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 18772-2026 tillsynsbegäran mail.docx", "A 18772-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8" ht="15" customHeight="1">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>A 18790-2026</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D8" s="1" t="n">
-        <v>46128</v>
-      </c>
-      <c r="E8" s="1" t="n">
-        <v>46300</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>UPPLANDS-BRO</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
-      <c r="I8" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="J8" t="n">
-        <v>2</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" t="n">
-        <v>2</v>
-      </c>
-      <c r="T8" t="n">
-        <v>2</v>
-      </c>
-      <c r="U8" t="n">
-        <v>0</v>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>Fläcknycklar
-Nattviol</t>
-        </is>
-      </c>
-      <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 18790-2026 artfynd.xlsx", "A 18790-2026")</f>
-        <v/>
-      </c>
-      <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 18790-2026 karta.png", "A 18790-2026")</f>
-        <v/>
-      </c>
-      <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 18790-2026 georefererad karta.tif", "A 18790-2026")</f>
-        <v/>
-      </c>
-      <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 18790-2026 FSC-klagomål.docx", "A 18790-2026")</f>
-        <v/>
-      </c>
-      <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 18790-2026 FSC-klagomål mail.docx", "A 18790-2026")</f>
-        <v/>
-      </c>
-      <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 18790-2026 tillsynsbegäran.docx", "A 18790-2026")</f>
-        <v/>
-      </c>
-      <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 18790-2026 tillsynsbegäran mail.docx", "A 18790-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9" ht="15" customHeight="1">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>A 10909-2025</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D9" s="1" t="n">
-        <v>45722</v>
-      </c>
-      <c r="E9" s="1" t="n">
-        <v>46300</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>UPPLANDS-BRO</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="J9" t="n">
-        <v>1</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>1</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>1</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" t="n">
-        <v>2</v>
-      </c>
-      <c r="T9" t="n">
-        <v>2</v>
-      </c>
-      <c r="U9" t="n">
-        <v>2</v>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>Arommusseron
-Fläcknycklar</t>
-        </is>
-      </c>
-      <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 10909-2025 artfynd.xlsx", "A 10909-2025")</f>
-        <v/>
-      </c>
-      <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 10909-2025 karta.png", "A 10909-2025")</f>
-        <v/>
-      </c>
-      <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 10909-2025 georefererad karta.tif", "A 10909-2025")</f>
-        <v/>
-      </c>
-      <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 10909-2025 FSC-klagomål.docx", "A 10909-2025")</f>
-        <v/>
-      </c>
-      <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 10909-2025 FSC-klagomål mail.docx", "A 10909-2025")</f>
-        <v/>
-      </c>
-      <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 10909-2025 tillsynsbegäran.docx", "A 10909-2025")</f>
-        <v/>
-      </c>
-      <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 10909-2025 tillsynsbegäran mail.docx", "A 10909-2025")</f>
         <v/>
       </c>
     </row>
@@ -1481,7 +1481,7 @@
         <v>44603</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1587,7 +1587,7 @@
         <v>44552</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1675,7 +1675,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 12363-2025</t>
+          <t>A 7955-2023</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1689,10 +1689,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45730</v>
+        <v>44973</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1705,13 +1705,13 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>0.8</v>
+        <v>2.9</v>
       </c>
       <c r="J12" t="n">
         <v>1</v>
       </c>
       <c r="K12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
@@ -1720,7 +1720,7 @@
         <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1729,10 +1729,10 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1741,46 +1741,46 @@
         <v>1</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Bombmurkla</t>
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 12363-2025 artfynd.xlsx", "A 12363-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 7955-2023 artfynd.xlsx", "A 7955-2023")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 12363-2025 karta.png", "A 12363-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 7955-2023 karta.png", "A 7955-2023")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 12363-2025 georefererad karta.tif", "A 12363-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 7955-2023 georefererad karta.tif", "A 7955-2023")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 12363-2025 FSC-klagomål.docx", "A 12363-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 7955-2023 FSC-klagomål.docx", "A 7955-2023")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 12363-2025 FSC-klagomål mail.docx", "A 12363-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 7955-2023 FSC-klagomål mail.docx", "A 7955-2023")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 12363-2025 tillsynsbegäran.docx", "A 12363-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 7955-2023 tillsynsbegäran.docx", "A 7955-2023")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 12363-2025 tillsynsbegäran mail.docx", "A 12363-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 7955-2023 tillsynsbegäran mail.docx", "A 7955-2023")</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 25561-2025</t>
+          <t>A 46438-2023</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1794,10 +1794,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45803</v>
+        <v>45197</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1810,7 +1810,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>1.6</v>
+        <v>0.5</v>
       </c>
       <c r="J13" t="n">
         <v>1</v>
@@ -1854,38 +1854,38 @@
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 25561-2025 artfynd.xlsx", "A 25561-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 46438-2023 artfynd.xlsx", "A 46438-2023")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 25561-2025 karta.png", "A 25561-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 46438-2023 karta.png", "A 46438-2023")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 25561-2025 georefererad karta.tif", "A 25561-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 46438-2023 georefererad karta.tif", "A 46438-2023")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 25561-2025 FSC-klagomål.docx", "A 25561-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 46438-2023 FSC-klagomål.docx", "A 46438-2023")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 25561-2025 FSC-klagomål mail.docx", "A 25561-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 46438-2023 FSC-klagomål mail.docx", "A 46438-2023")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 25561-2025 tillsynsbegäran.docx", "A 25561-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 46438-2023 tillsynsbegäran.docx", "A 46438-2023")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 25561-2025 tillsynsbegäran mail.docx", "A 25561-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 46438-2023 tillsynsbegäran mail.docx", "A 46438-2023")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 53357-2025</t>
+          <t>A 12363-2025</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1899,10 +1899,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45959</v>
+        <v>45730</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1915,13 +1915,13 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>2.4</v>
+        <v>0.8</v>
       </c>
       <c r="J14" t="n">
         <v>1</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
@@ -1930,7 +1930,7 @@
         <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -1939,58 +1939,58 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
       </c>
       <c r="T14" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="U14" t="n">
         <v>0</v>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Bombmurkla</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 53357-2025 artfynd.xlsx", "A 53357-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 12363-2025 artfynd.xlsx", "A 12363-2025")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 53357-2025 karta.png", "A 53357-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 12363-2025 karta.png", "A 12363-2025")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 53357-2025 georefererad karta.tif", "A 53357-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 12363-2025 georefererad karta.tif", "A 12363-2025")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 53357-2025 FSC-klagomål.docx", "A 53357-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 12363-2025 FSC-klagomål.docx", "A 12363-2025")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 53357-2025 FSC-klagomål mail.docx", "A 53357-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 12363-2025 FSC-klagomål mail.docx", "A 12363-2025")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 53357-2025 tillsynsbegäran.docx", "A 53357-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 12363-2025 tillsynsbegäran.docx", "A 12363-2025")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 53357-2025 tillsynsbegäran mail.docx", "A 53357-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 12363-2025 tillsynsbegäran mail.docx", "A 12363-2025")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 23099-2024</t>
+          <t>A 53357-2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2004,10 +2004,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45450</v>
+        <v>45959</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2019,16 +2019,11 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I15" t="n">
-        <v>0.7</v>
+        <v>2.4</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
@@ -2037,10 +2032,10 @@
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2058,49 +2053,49 @@
         <v>1</v>
       </c>
       <c r="T15" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="U15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Bredbrämad bastardsvärmare</t>
+          <t>Bombmurkla</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 23099-2024 artfynd.xlsx", "A 23099-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 53357-2025 artfynd.xlsx", "A 53357-2025")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 23099-2024 karta.png", "A 23099-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 53357-2025 karta.png", "A 53357-2025")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 23099-2024 georefererad karta.tif", "A 23099-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 53357-2025 georefererad karta.tif", "A 53357-2025")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 23099-2024 FSC-klagomål.docx", "A 23099-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 53357-2025 FSC-klagomål.docx", "A 53357-2025")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 23099-2024 FSC-klagomål mail.docx", "A 23099-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 53357-2025 FSC-klagomål mail.docx", "A 53357-2025")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 23099-2024 tillsynsbegäran.docx", "A 23099-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 53357-2025 tillsynsbegäran.docx", "A 53357-2025")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 23099-2024 tillsynsbegäran mail.docx", "A 23099-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 53357-2025 tillsynsbegäran mail.docx", "A 53357-2025")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 46438-2023</t>
+          <t>A 23099-2024</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2114,10 +2109,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45197</v>
+        <v>45450</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2129,11 +2124,16 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I16" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
@@ -2142,10 +2142,10 @@
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2166,46 +2166,46 @@
         <v>1</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Bombmurkla</t>
+          <t>Bredbrämad bastardsvärmare</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 46438-2023 artfynd.xlsx", "A 46438-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 23099-2024 artfynd.xlsx", "A 23099-2024")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 46438-2023 karta.png", "A 46438-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 23099-2024 karta.png", "A 23099-2024")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 46438-2023 georefererad karta.tif", "A 46438-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 23099-2024 georefererad karta.tif", "A 23099-2024")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 46438-2023 FSC-klagomål.docx", "A 46438-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 23099-2024 FSC-klagomål.docx", "A 23099-2024")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 46438-2023 FSC-klagomål mail.docx", "A 46438-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 23099-2024 FSC-klagomål mail.docx", "A 23099-2024")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 46438-2023 tillsynsbegäran.docx", "A 46438-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 23099-2024 tillsynsbegäran.docx", "A 23099-2024")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 46438-2023 tillsynsbegäran mail.docx", "A 46438-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 23099-2024 tillsynsbegäran mail.docx", "A 23099-2024")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 26196-2026</t>
+          <t>A 64098-2023</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2215,14 +2215,14 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46182</v>
+        <v>45279</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2235,7 +2235,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>53.1</v>
+        <v>0.3</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2244,7 +2244,7 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M17" t="n">
         <v>0</v>
@@ -2259,7 +2259,7 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -2268,49 +2268,49 @@
         <v>1</v>
       </c>
       <c r="T17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Liljekonvalj</t>
+          <t>Skogsalmsdvärgmal</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 26196-2026 artfynd.xlsx", "A 26196-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 64098-2023 artfynd.xlsx", "A 64098-2023")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 26196-2026 karta.png", "A 26196-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 64098-2023 karta.png", "A 64098-2023")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 26196-2026 georefererad karta.tif", "A 26196-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 64098-2023 georefererad karta.tif", "A 64098-2023")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 26196-2026 FSC-klagomål.docx", "A 26196-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 64098-2023 FSC-klagomål.docx", "A 64098-2023")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 26196-2026 FSC-klagomål mail.docx", "A 26196-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 64098-2023 FSC-klagomål mail.docx", "A 64098-2023")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 26196-2026 tillsynsbegäran.docx", "A 26196-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 64098-2023 tillsynsbegäran.docx", "A 64098-2023")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 26196-2026 tillsynsbegäran mail.docx", "A 26196-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 64098-2023 tillsynsbegäran mail.docx", "A 64098-2023")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 26637-2026</t>
+          <t>A 26196-2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2320,14 +2320,14 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46184</v>
+        <v>46182</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2340,7 +2340,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>5.4</v>
+        <v>53.1</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2352,7 +2352,7 @@
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
@@ -2364,51 +2364,51 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
       </c>
       <c r="T18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Igelkott</t>
+          <t>Liljekonvalj</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 26637-2026 artfynd.xlsx", "A 26637-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 26196-2026 artfynd.xlsx", "A 26196-2026")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 26637-2026 karta.png", "A 26637-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 26196-2026 karta.png", "A 26196-2026")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 26637-2026 georefererad karta.tif", "A 26637-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 26196-2026 georefererad karta.tif", "A 26196-2026")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 26637-2026 FSC-klagomål.docx", "A 26637-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 26196-2026 FSC-klagomål.docx", "A 26196-2026")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 26637-2026 FSC-klagomål mail.docx", "A 26637-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 26196-2026 FSC-klagomål mail.docx", "A 26196-2026")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 26637-2026 tillsynsbegäran.docx", "A 26637-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 26196-2026 tillsynsbegäran.docx", "A 26196-2026")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 26637-2026 tillsynsbegäran mail.docx", "A 26637-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 26196-2026 tillsynsbegäran mail.docx", "A 26196-2026")</f>
         <v/>
       </c>
     </row>
@@ -2432,7 +2432,7 @@
         <v>46184</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2537,7 +2537,7 @@
         <v>45726</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2625,7 +2625,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 7955-2023</t>
+          <t>A 26637-2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2639,10 +2639,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>44973</v>
+        <v>46184</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2655,10 +2655,10 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>2.9</v>
+        <v>5.4</v>
       </c>
       <c r="J21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
@@ -2667,10 +2667,10 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2691,46 +2691,46 @@
         <v>1</v>
       </c>
       <c r="U21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Bombmurkla</t>
+          <t>Igelkott</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 7955-2023 artfynd.xlsx", "A 7955-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 26637-2026 artfynd.xlsx", "A 26637-2026")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 7955-2023 karta.png", "A 7955-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 26637-2026 karta.png", "A 26637-2026")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 7955-2023 georefererad karta.tif", "A 7955-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 26637-2026 georefererad karta.tif", "A 26637-2026")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 7955-2023 FSC-klagomål.docx", "A 7955-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 26637-2026 FSC-klagomål.docx", "A 26637-2026")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 7955-2023 FSC-klagomål mail.docx", "A 7955-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 26637-2026 FSC-klagomål mail.docx", "A 26637-2026")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 7955-2023 tillsynsbegäran.docx", "A 7955-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 26637-2026 tillsynsbegäran.docx", "A 26637-2026")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 7955-2023 tillsynsbegäran mail.docx", "A 7955-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 26637-2026 tillsynsbegäran mail.docx", "A 26637-2026")</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 64098-2023</t>
+          <t>A 2062-2025</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2744,10 +2744,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45279</v>
+        <v>45671</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2760,10 +2760,10 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>0.3</v>
+        <v>1.9</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
@@ -2796,46 +2796,50 @@
         <v>1</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>Skogsalmsdvärgmal</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 64098-2023 artfynd.xlsx", "A 64098-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 2062-2025 artfynd.xlsx", "A 2062-2025")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 64098-2023 karta.png", "A 64098-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 2062-2025 karta.png", "A 2062-2025")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 64098-2023 georefererad karta.tif", "A 64098-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 2062-2025 georefererad karta.tif", "A 2062-2025")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 64098-2023 FSC-klagomål.docx", "A 64098-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 2062-2025 FSC-klagomål.docx", "A 2062-2025")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 64098-2023 FSC-klagomål mail.docx", "A 64098-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 2062-2025 FSC-klagomål mail.docx", "A 2062-2025")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 64098-2023 tillsynsbegäran.docx", "A 64098-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 2062-2025 tillsynsbegäran.docx", "A 2062-2025")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 64098-2023 tillsynsbegäran mail.docx", "A 64098-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 2062-2025 tillsynsbegäran mail.docx", "A 2062-2025")</f>
+        <v/>
+      </c>
+      <c r="AE22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/fåglar/A 2062-2025 prioriterade fågelarter.docx", "A 2062-2025")</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 2062-2025</t>
+          <t>A 25561-2025</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2849,10 +2853,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45671</v>
+        <v>45803</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2865,7 +2869,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>1.9</v>
+        <v>1.6</v>
       </c>
       <c r="J23" t="n">
         <v>1</v>
@@ -2874,13 +2878,13 @@
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
         <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -2892,7 +2896,7 @@
         <v>1</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S23" t="n">
         <v>1</v>
@@ -2901,43 +2905,39 @@
         <v>1</v>
       </c>
       <c r="U23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Bombmurkla</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 2062-2025 artfynd.xlsx", "A 2062-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 25561-2025 artfynd.xlsx", "A 25561-2025")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 2062-2025 karta.png", "A 2062-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 25561-2025 karta.png", "A 25561-2025")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 2062-2025 georefererad karta.tif", "A 2062-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 25561-2025 georefererad karta.tif", "A 25561-2025")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 2062-2025 FSC-klagomål.docx", "A 2062-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 25561-2025 FSC-klagomål.docx", "A 25561-2025")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 2062-2025 FSC-klagomål mail.docx", "A 2062-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 25561-2025 FSC-klagomål mail.docx", "A 25561-2025")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 2062-2025 tillsynsbegäran.docx", "A 2062-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 25561-2025 tillsynsbegäran.docx", "A 25561-2025")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 2062-2025 tillsynsbegäran mail.docx", "A 2062-2025")</f>
-        <v/>
-      </c>
-      <c r="AE23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/fåglar/A 2062-2025 prioriterade fågelarter.docx", "A 2062-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 25561-2025 tillsynsbegäran mail.docx", "A 25561-2025")</f>
         <v/>
       </c>
     </row>
@@ -2961,7 +2961,7 @@
         <v>44558</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3066,7 +3066,7 @@
         <v>44609</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3139,7 +3139,7 @@
         <v>44489</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3217,7 +3217,7 @@
         <v>44546</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3290,7 +3290,7 @@
         <v>44700</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3363,7 +3363,7 @@
         <v>44587</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3436,7 +3436,7 @@
         <v>44655</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3497,7 +3497,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 64105-2023</t>
+          <t>A 59700-2021</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3511,10 +3511,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45279</v>
+        <v>44494</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3526,8 +3526,13 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I31" t="n">
-        <v>2.2</v>
+        <v>4.8</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3570,7 +3575,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 2602-2024</t>
+          <t>A 38902-2024</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3584,10 +3589,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45313</v>
+        <v>45547</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3599,8 +3604,13 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I32" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3643,7 +3653,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 59844-2022</t>
+          <t>A 50294-2023</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3657,10 +3667,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44901</v>
+        <v>45216</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3672,13 +3682,8 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I33" t="n">
-        <v>11.9</v>
+        <v>3.7</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3721,7 +3726,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 3630-2023</t>
+          <t>A 5264-2023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3735,10 +3740,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44950</v>
+        <v>44959</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3751,7 +3756,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>1.4</v>
+        <v>5.8</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3794,7 +3799,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 23093-2024</t>
+          <t>A 9655-2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3808,10 +3813,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45450</v>
+        <v>46070</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3829,7 +3834,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>0.9</v>
+        <v>17.2</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3872,7 +3877,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 23615-2025</t>
+          <t>A 23098-2024</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3886,10 +3891,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45792</v>
+        <v>45450</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3901,8 +3906,13 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I36" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3945,7 +3955,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 54222-2023</t>
+          <t>A 18787-2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3959,10 +3969,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45225</v>
+        <v>46128</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3980,7 +3990,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>8.300000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4023,7 +4033,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 23627-2025</t>
+          <t>A 18813-2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4037,10 +4047,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45792</v>
+        <v>46128</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4052,8 +4062,13 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I38" t="n">
-        <v>1.7</v>
+        <v>56</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4096,7 +4111,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 7860-2024</t>
+          <t>A 18818-2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4110,10 +4125,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45348</v>
+        <v>46128</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4131,7 +4146,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1.9</v>
+        <v>17.8</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4174,7 +4189,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 9655-2026</t>
+          <t>A 18778-2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4188,10 +4203,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>46070</v>
+        <v>46128</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4209,7 +4224,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>17.2</v>
+        <v>4.5</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4252,7 +4267,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 27313-2023</t>
+          <t>A 59844-2022</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4266,10 +4281,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45096</v>
+        <v>44901</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4281,8 +4296,13 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I41" t="n">
-        <v>1.8</v>
+        <v>11.9</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4325,7 +4345,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 64114-2023</t>
+          <t>A 54222-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4339,10 +4359,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45279</v>
+        <v>45225</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4354,8 +4374,13 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I42" t="n">
-        <v>0.4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4398,7 +4423,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 50294-2023</t>
+          <t>A 4338-2023</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4412,10 +4437,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45216</v>
+        <v>44953</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4428,7 +4453,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>3.7</v>
+        <v>1.1</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4488,7 +4513,7 @@
         <v>44487</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4549,7 +4574,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 18778-2026</t>
+          <t>A 72524-2021</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4563,10 +4588,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>46128</v>
+        <v>44546</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4578,13 +4603,8 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I45" t="n">
-        <v>4.5</v>
+        <v>3.6</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4627,7 +4647,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 18813-2026</t>
+          <t>A 64107-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4641,10 +4661,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>46128</v>
+        <v>45279</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4656,13 +4676,8 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I46" t="n">
-        <v>56</v>
+        <v>0.3</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4705,7 +4720,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 18818-2026</t>
+          <t>A 23093-2024</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4719,10 +4734,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>46128</v>
+        <v>45450</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4740,7 +4755,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>17.8</v>
+        <v>0.9</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4783,7 +4798,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 18787-2026</t>
+          <t>A 27313-2023</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4797,10 +4812,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>46128</v>
+        <v>45096</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4812,13 +4827,8 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I48" t="n">
-        <v>7.8</v>
+        <v>1.8</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4861,7 +4871,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 64110-2023</t>
+          <t>A 59377-2024</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4875,10 +4885,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45279</v>
+        <v>45638</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4891,7 +4901,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4934,7 +4944,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 23098-2024</t>
+          <t>A 21206-2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4948,10 +4958,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45450</v>
+        <v>46146</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4969,7 +4979,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5012,7 +5022,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 21206-2026</t>
+          <t>A 24579-2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5026,10 +5036,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>46146</v>
+        <v>46170</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5041,13 +5051,8 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I51" t="n">
-        <v>0.9</v>
+        <v>2.1</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5090,7 +5095,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 59377-2024</t>
+          <t>A 58598-2025</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5104,10 +5109,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45638</v>
+        <v>45986</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5119,8 +5124,13 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I52" t="n">
-        <v>0.6</v>
+        <v>4.5</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5163,7 +5173,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 59402-2022</t>
+          <t>A 31160-2022</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5177,10 +5187,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>44906</v>
+        <v>44770</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5193,7 +5203,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>1.8</v>
+        <v>3.7</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5236,7 +5246,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 24579-2026</t>
+          <t>A 51587-2023</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5250,10 +5260,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>46170</v>
+        <v>45215</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5265,8 +5275,13 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I54" t="n">
-        <v>2.1</v>
+        <v>2.6</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5309,7 +5324,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 31160-2022</t>
+          <t>A 26625-2026</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5323,10 +5338,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44770</v>
+        <v>46184</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5339,7 +5354,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>3.7</v>
+        <v>5.3</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5382,7 +5397,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 58598-2025</t>
+          <t>A 26633-2026</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5396,10 +5411,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45986</v>
+        <v>46184</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5411,13 +5426,8 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I56" t="n">
-        <v>4.5</v>
+        <v>0.7</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5460,7 +5470,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 5264-2023</t>
+          <t>A 3754-2026</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5474,10 +5484,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>44959</v>
+        <v>46043</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5489,8 +5499,13 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I57" t="n">
-        <v>5.8</v>
+        <v>5.1</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5533,7 +5548,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 26633-2026</t>
+          <t>A 28797-2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5547,10 +5562,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>46184</v>
+        <v>46198</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5563,7 +5578,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>0.7</v>
+        <v>2.2</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5606,7 +5621,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 26625-2026</t>
+          <t>A 28740-2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5620,10 +5635,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>46184</v>
+        <v>46198</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5636,7 +5651,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>5.3</v>
+        <v>4.8</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5679,7 +5694,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 26629-2026</t>
+          <t>A 59848-2022</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5693,10 +5708,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>46184</v>
+        <v>44901</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5708,8 +5723,13 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I60" t="n">
-        <v>2</v>
+        <v>10.7</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5752,7 +5772,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 3754-2026</t>
+          <t>A 28735-2026</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5766,10 +5786,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>46043</v>
+        <v>46198</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5781,13 +5801,8 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I61" t="n">
-        <v>5.1</v>
+        <v>3.5</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5830,7 +5845,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 51587-2023</t>
+          <t>A 64110-2023</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5844,10 +5859,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45215</v>
+        <v>45279</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5859,13 +5874,8 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I62" t="n">
-        <v>2.6</v>
+        <v>0.4</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5908,7 +5918,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 28735-2026</t>
+          <t>A 7275-2022</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5922,10 +5932,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>46198</v>
+        <v>44606</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5937,8 +5947,13 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I63" t="n">
-        <v>3.5</v>
+        <v>9.6</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5981,7 +5996,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 28740-2026</t>
+          <t>A 2602-2024</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5995,10 +6010,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>46198</v>
+        <v>45313</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6011,7 +6026,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>4.8</v>
+        <v>0.7</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6054,7 +6069,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 28797-2026</t>
+          <t>A 59402-2022</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6068,10 +6083,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>46198</v>
+        <v>44906</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6084,7 +6099,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6127,7 +6142,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 72524-2021</t>
+          <t>A 31714-2026</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6141,10 +6156,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>44546</v>
+        <v>46226</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6157,7 +6172,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>3.6</v>
+        <v>5</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6200,7 +6215,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 4338-2023</t>
+          <t>A 3630-2023</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6214,10 +6229,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>44953</v>
+        <v>44950</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6230,7 +6245,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6273,7 +6288,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 59848-2022</t>
+          <t>A 7860-2024</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6287,10 +6302,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>44901</v>
+        <v>45348</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6308,7 +6323,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>10.7</v>
+        <v>1.9</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6351,7 +6366,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 31714-2026</t>
+          <t>A 64105-2023</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6365,10 +6380,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>46226</v>
+        <v>45279</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6381,7 +6396,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>5</v>
+        <v>2.2</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6424,7 +6439,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 59700-2021</t>
+          <t>A 33058-2026</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6434,14 +6449,14 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>44494</v>
+        <v>46245</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6453,13 +6468,8 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I70" t="n">
-        <v>4.8</v>
+        <v>1.3</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6502,7 +6512,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 33058-2026</t>
+          <t>A 64114-2023</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6512,14 +6522,14 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>46245</v>
+        <v>45279</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6532,7 +6542,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>1.3</v>
+        <v>0.4</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6575,7 +6585,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 7275-2022</t>
+          <t>A 7112-2025</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6589,10 +6599,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>44606</v>
+        <v>45701</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6604,13 +6614,8 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I72" t="n">
-        <v>9.6</v>
+        <v>2.4</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6653,7 +6658,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 64107-2023</t>
+          <t>A 23615-2025</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6667,10 +6672,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45279</v>
+        <v>45792</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6683,7 +6688,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>0.3</v>
+        <v>1.3</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6726,7 +6731,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 7112-2025</t>
+          <t>A 23627-2025</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6740,10 +6745,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45701</v>
+        <v>45792</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6756,7 +6761,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>2.4</v>
+        <v>1.7</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6796,27 +6801,27 @@
       </c>
       <c r="V74" s="2" t="inlineStr"/>
     </row>
-    <row r="75" ht="15" customHeight="1">
+    <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 38902-2024</t>
+          <t>S 10447-2021</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>avverkningsanmälan</t>
+          <t>samrådsanmälan</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45547</v>
+        <v>44558</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6828,13 +6833,8 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I75" t="n">
-        <v>0.8</v>
+        <v>4.4</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6873,79 +6873,6 @@
         <v>0</v>
       </c>
       <c r="V75" s="2" t="inlineStr"/>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>S 10447-2021</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>Annan skogsbruksåtgärd</t>
-        </is>
-      </c>
-      <c r="D76" s="1" t="n">
-        <v>44558</v>
-      </c>
-      <c r="E76" s="1" t="n">
-        <v>46300</v>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>UPPLANDS-BRO</t>
-        </is>
-      </c>
-      <c r="I76" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="J76" t="n">
-        <v>0</v>
-      </c>
-      <c r="K76" t="n">
-        <v>0</v>
-      </c>
-      <c r="L76" t="n">
-        <v>0</v>
-      </c>
-      <c r="M76" t="n">
-        <v>0</v>
-      </c>
-      <c r="N76" t="n">
-        <v>0</v>
-      </c>
-      <c r="O76" t="n">
-        <v>0</v>
-      </c>
-      <c r="P76" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q76" t="n">
-        <v>0</v>
-      </c>
-      <c r="R76" t="n">
-        <v>0</v>
-      </c>
-      <c r="S76" t="n">
-        <v>0</v>
-      </c>
-      <c r="T76" t="n">
-        <v>0</v>
-      </c>
-      <c r="U76" t="n">
-        <v>0</v>
-      </c>
-      <c r="V76" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt UPPLANDS-BRO.xlsx
+++ b/Översikt UPPLANDS-BRO.xlsx
@@ -601,7 +601,7 @@
         <v>44481</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -714,7 +714,7 @@
         <v>44552</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -822,7 +822,7 @@
         <v>44552</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -930,7 +930,7 @@
         <v>45232</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1025,7 +1025,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 18790-2026</t>
+          <t>A 73773-2021</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1039,10 +1039,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46128</v>
+        <v>44552</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1054,13 +1054,8 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I6" t="n">
-        <v>5.5</v>
+        <v>1.9</v>
       </c>
       <c r="J6" t="n">
         <v>2</v>
@@ -1093,371 +1088,376 @@
         <v>2</v>
       </c>
       <c r="T6" t="n">
+        <v>3</v>
+      </c>
+      <c r="U6" t="n">
+        <v>3</v>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>Kopparödla
+Gullviva</t>
+        </is>
+      </c>
+      <c r="W6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 73773-2021 artfynd.xlsx", "A 73773-2021")</f>
+        <v/>
+      </c>
+      <c r="X6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 73773-2021 karta.png", "A 73773-2021")</f>
+        <v/>
+      </c>
+      <c r="Y6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 73773-2021 georefererad karta.tif", "A 73773-2021")</f>
+        <v/>
+      </c>
+      <c r="AA6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 73773-2021 FSC-klagomål.docx", "A 73773-2021")</f>
+        <v/>
+      </c>
+      <c r="AB6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 73773-2021 FSC-klagomål mail.docx", "A 73773-2021")</f>
+        <v/>
+      </c>
+      <c r="AC6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 73773-2021 tillsynsbegäran.docx", "A 73773-2021")</f>
+        <v/>
+      </c>
+      <c r="AD6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 73773-2021 tillsynsbegäran mail.docx", "A 73773-2021")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>A 18772-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>46128</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>46302</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>UPPLANDS-BRO</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
         <v>2</v>
       </c>
-      <c r="U6" t="n">
-        <v>0</v>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
+      <c r="T7" t="n">
+        <v>2</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>Svedjenäva
+Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="W7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 18772-2026 artfynd.xlsx", "A 18772-2026")</f>
+        <v/>
+      </c>
+      <c r="X7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 18772-2026 karta.png", "A 18772-2026")</f>
+        <v/>
+      </c>
+      <c r="Y7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 18772-2026 georefererad karta.tif", "A 18772-2026")</f>
+        <v/>
+      </c>
+      <c r="AA7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 18772-2026 FSC-klagomål.docx", "A 18772-2026")</f>
+        <v/>
+      </c>
+      <c r="AB7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 18772-2026 FSC-klagomål mail.docx", "A 18772-2026")</f>
+        <v/>
+      </c>
+      <c r="AC7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 18772-2026 tillsynsbegäran.docx", "A 18772-2026")</f>
+        <v/>
+      </c>
+      <c r="AD7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 18772-2026 tillsynsbegäran mail.docx", "A 18772-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="15" customHeight="1">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>A 18790-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D8" s="1" t="n">
+        <v>46128</v>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>46302</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>UPPLANDS-BRO</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="J8" t="n">
+        <v>2</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>2</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>Fläcknycklar
 Nattviol</t>
         </is>
       </c>
-      <c r="W6">
+      <c r="W8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 18790-2026 artfynd.xlsx", "A 18790-2026")</f>
         <v/>
       </c>
-      <c r="X6">
+      <c r="X8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 18790-2026 karta.png", "A 18790-2026")</f>
         <v/>
       </c>
-      <c r="Y6">
+      <c r="Y8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 18790-2026 georefererad karta.tif", "A 18790-2026")</f>
         <v/>
       </c>
-      <c r="AA6">
+      <c r="AA8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 18790-2026 FSC-klagomål.docx", "A 18790-2026")</f>
         <v/>
       </c>
-      <c r="AB6">
+      <c r="AB8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 18790-2026 FSC-klagomål mail.docx", "A 18790-2026")</f>
         <v/>
       </c>
-      <c r="AC6">
+      <c r="AC8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 18790-2026 tillsynsbegäran.docx", "A 18790-2026")</f>
         <v/>
       </c>
-      <c r="AD6">
+      <c r="AD8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 18790-2026 tillsynsbegäran mail.docx", "A 18790-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>A 18772-2026</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
+    <row r="9" ht="15" customHeight="1">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>A 10909-2025</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D7" s="1" t="n">
-        <v>46128</v>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>46301</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>UPPLANDS-BRO</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="J7" t="n">
-        <v>1</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>1</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>1</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
+      <c r="D9" s="1" t="n">
+        <v>45722</v>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>46302</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>UPPLANDS-BRO</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
         <v>2</v>
       </c>
-      <c r="T7" t="n">
+      <c r="T9" t="n">
         <v>2</v>
       </c>
-      <c r="U7" t="n">
-        <v>0</v>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>Svedjenäva
-Fläcknycklar</t>
-        </is>
-      </c>
-      <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 18772-2026 artfynd.xlsx", "A 18772-2026")</f>
-        <v/>
-      </c>
-      <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 18772-2026 karta.png", "A 18772-2026")</f>
-        <v/>
-      </c>
-      <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 18772-2026 georefererad karta.tif", "A 18772-2026")</f>
-        <v/>
-      </c>
-      <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 18772-2026 FSC-klagomål.docx", "A 18772-2026")</f>
-        <v/>
-      </c>
-      <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 18772-2026 FSC-klagomål mail.docx", "A 18772-2026")</f>
-        <v/>
-      </c>
-      <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 18772-2026 tillsynsbegäran.docx", "A 18772-2026")</f>
-        <v/>
-      </c>
-      <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 18772-2026 tillsynsbegäran mail.docx", "A 18772-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8" ht="15" customHeight="1">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>A 10909-2025</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D8" s="1" t="n">
-        <v>45722</v>
-      </c>
-      <c r="E8" s="1" t="n">
-        <v>46301</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>UPPLANDS-BRO</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
-      <c r="I8" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="J8" t="n">
-        <v>1</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>1</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>1</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" t="n">
+      <c r="U9" t="n">
         <v>2</v>
       </c>
-      <c r="T8" t="n">
-        <v>2</v>
-      </c>
-      <c r="U8" t="n">
-        <v>2</v>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
+      <c r="V9" s="2" t="inlineStr">
         <is>
           <t>Arommusseron
 Fläcknycklar</t>
         </is>
       </c>
-      <c r="W8">
+      <c r="W9">
         <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 10909-2025 artfynd.xlsx", "A 10909-2025")</f>
         <v/>
       </c>
-      <c r="X8">
+      <c r="X9">
         <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 10909-2025 karta.png", "A 10909-2025")</f>
         <v/>
       </c>
-      <c r="Y8">
+      <c r="Y9">
         <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 10909-2025 georefererad karta.tif", "A 10909-2025")</f>
         <v/>
       </c>
-      <c r="AA8">
+      <c r="AA9">
         <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 10909-2025 FSC-klagomål.docx", "A 10909-2025")</f>
         <v/>
       </c>
-      <c r="AB8">
+      <c r="AB9">
         <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 10909-2025 FSC-klagomål mail.docx", "A 10909-2025")</f>
         <v/>
       </c>
-      <c r="AC8">
+      <c r="AC9">
         <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 10909-2025 tillsynsbegäran.docx", "A 10909-2025")</f>
         <v/>
       </c>
-      <c r="AD8">
+      <c r="AD9">
         <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 10909-2025 tillsynsbegäran mail.docx", "A 10909-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9" ht="15" customHeight="1">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>A 73773-2021</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D9" s="1" t="n">
-        <v>44552</v>
-      </c>
-      <c r="E9" s="1" t="n">
-        <v>46301</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>UPPLANDS-BRO</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="J9" t="n">
-        <v>2</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" t="n">
-        <v>2</v>
-      </c>
-      <c r="T9" t="n">
-        <v>3</v>
-      </c>
-      <c r="U9" t="n">
-        <v>3</v>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>Kopparödla
-Gullviva</t>
-        </is>
-      </c>
-      <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 73773-2021 artfynd.xlsx", "A 73773-2021")</f>
-        <v/>
-      </c>
-      <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 73773-2021 karta.png", "A 73773-2021")</f>
-        <v/>
-      </c>
-      <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 73773-2021 georefererad karta.tif", "A 73773-2021")</f>
-        <v/>
-      </c>
-      <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 73773-2021 FSC-klagomål.docx", "A 73773-2021")</f>
-        <v/>
-      </c>
-      <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 73773-2021 FSC-klagomål mail.docx", "A 73773-2021")</f>
-        <v/>
-      </c>
-      <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 73773-2021 tillsynsbegäran.docx", "A 73773-2021")</f>
-        <v/>
-      </c>
-      <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 73773-2021 tillsynsbegäran mail.docx", "A 73773-2021")</f>
         <v/>
       </c>
     </row>
@@ -1481,7 +1481,7 @@
         <v>44603</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1587,7 +1587,7 @@
         <v>44552</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1675,7 +1675,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 7955-2023</t>
+          <t>A 25561-2025</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1689,10 +1689,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>44973</v>
+        <v>45803</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1705,7 +1705,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>2.9</v>
+        <v>1.6</v>
       </c>
       <c r="J12" t="n">
         <v>1</v>
@@ -1741,7 +1741,7 @@
         <v>1</v>
       </c>
       <c r="U12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
@@ -1749,38 +1749,38 @@
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 7955-2023 artfynd.xlsx", "A 7955-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 25561-2025 artfynd.xlsx", "A 25561-2025")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 7955-2023 karta.png", "A 7955-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 25561-2025 karta.png", "A 25561-2025")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 7955-2023 georefererad karta.tif", "A 7955-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 25561-2025 georefererad karta.tif", "A 25561-2025")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 7955-2023 FSC-klagomål.docx", "A 7955-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 25561-2025 FSC-klagomål.docx", "A 25561-2025")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 7955-2023 FSC-klagomål mail.docx", "A 7955-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 25561-2025 FSC-klagomål mail.docx", "A 25561-2025")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 7955-2023 tillsynsbegäran.docx", "A 7955-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 25561-2025 tillsynsbegäran.docx", "A 25561-2025")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 7955-2023 tillsynsbegäran mail.docx", "A 7955-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 25561-2025 tillsynsbegäran mail.docx", "A 25561-2025")</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 46438-2023</t>
+          <t>A 12363-2025</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1794,10 +1794,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45197</v>
+        <v>45730</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1810,13 +1810,13 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="J13" t="n">
         <v>1</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -1825,7 +1825,7 @@
         <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -1834,10 +1834,10 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
@@ -1850,42 +1850,42 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>Bombmurkla</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 46438-2023 artfynd.xlsx", "A 46438-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 12363-2025 artfynd.xlsx", "A 12363-2025")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 46438-2023 karta.png", "A 46438-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 12363-2025 karta.png", "A 12363-2025")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 46438-2023 georefererad karta.tif", "A 46438-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 12363-2025 georefererad karta.tif", "A 12363-2025")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 46438-2023 FSC-klagomål.docx", "A 46438-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 12363-2025 FSC-klagomål.docx", "A 12363-2025")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 46438-2023 FSC-klagomål mail.docx", "A 46438-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 12363-2025 FSC-klagomål mail.docx", "A 12363-2025")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 46438-2023 tillsynsbegäran.docx", "A 46438-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 12363-2025 tillsynsbegäran.docx", "A 12363-2025")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 46438-2023 tillsynsbegäran mail.docx", "A 46438-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 12363-2025 tillsynsbegäran mail.docx", "A 12363-2025")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 12363-2025</t>
+          <t>A 53357-2025</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1899,10 +1899,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45730</v>
+        <v>45959</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1915,13 +1915,13 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>0.8</v>
+        <v>2.4</v>
       </c>
       <c r="J14" t="n">
         <v>1</v>
       </c>
       <c r="K14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
@@ -1930,7 +1930,7 @@
         <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -1939,58 +1939,58 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
       </c>
       <c r="T14" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="U14" t="n">
         <v>0</v>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Bombmurkla</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 12363-2025 artfynd.xlsx", "A 12363-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 53357-2025 artfynd.xlsx", "A 53357-2025")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 12363-2025 karta.png", "A 12363-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 53357-2025 karta.png", "A 53357-2025")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 12363-2025 georefererad karta.tif", "A 12363-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 53357-2025 georefererad karta.tif", "A 53357-2025")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 12363-2025 FSC-klagomål.docx", "A 12363-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 53357-2025 FSC-klagomål.docx", "A 53357-2025")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 12363-2025 FSC-klagomål mail.docx", "A 12363-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 53357-2025 FSC-klagomål mail.docx", "A 53357-2025")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 12363-2025 tillsynsbegäran.docx", "A 12363-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 53357-2025 tillsynsbegäran.docx", "A 53357-2025")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 12363-2025 tillsynsbegäran mail.docx", "A 12363-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 53357-2025 tillsynsbegäran mail.docx", "A 53357-2025")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 53357-2025</t>
+          <t>A 26196-2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2000,14 +2000,14 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45959</v>
+        <v>46182</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2020,10 +2020,10 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>2.4</v>
+        <v>53.1</v>
       </c>
       <c r="J15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
@@ -2035,7 +2035,7 @@
         <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2044,58 +2044,58 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
         <v>1</v>
       </c>
       <c r="T15" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Bombmurkla</t>
+          <t>Liljekonvalj</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 53357-2025 artfynd.xlsx", "A 53357-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 26196-2026 artfynd.xlsx", "A 26196-2026")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 53357-2025 karta.png", "A 53357-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 26196-2026 karta.png", "A 26196-2026")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 53357-2025 georefererad karta.tif", "A 53357-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 26196-2026 georefererad karta.tif", "A 26196-2026")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 53357-2025 FSC-klagomål.docx", "A 53357-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 26196-2026 FSC-klagomål.docx", "A 26196-2026")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 53357-2025 FSC-klagomål mail.docx", "A 53357-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 26196-2026 FSC-klagomål mail.docx", "A 26196-2026")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 53357-2025 tillsynsbegäran.docx", "A 53357-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 26196-2026 tillsynsbegäran.docx", "A 26196-2026")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 53357-2025 tillsynsbegäran mail.docx", "A 53357-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 26196-2026 tillsynsbegäran mail.docx", "A 26196-2026")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 23099-2024</t>
+          <t>A 26623-2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2109,10 +2109,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45450</v>
+        <v>46184</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2124,13 +2124,8 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I16" t="n">
-        <v>0.7</v>
+        <v>4.6</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -2139,10 +2134,10 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -2157,7 +2152,7 @@
         <v>1</v>
       </c>
       <c r="R16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
@@ -2166,46 +2161,46 @@
         <v>1</v>
       </c>
       <c r="U16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Bredbrämad bastardsvärmare</t>
+          <t>Svartöra</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 23099-2024 artfynd.xlsx", "A 23099-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 26623-2026 artfynd.xlsx", "A 26623-2026")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 23099-2024 karta.png", "A 23099-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 26623-2026 karta.png", "A 26623-2026")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 23099-2024 georefererad karta.tif", "A 23099-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 26623-2026 georefererad karta.tif", "A 26623-2026")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 23099-2024 FSC-klagomål.docx", "A 23099-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 26623-2026 FSC-klagomål.docx", "A 26623-2026")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 23099-2024 FSC-klagomål mail.docx", "A 23099-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 26623-2026 FSC-klagomål mail.docx", "A 26623-2026")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 23099-2024 tillsynsbegäran.docx", "A 23099-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 26623-2026 tillsynsbegäran.docx", "A 26623-2026")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 23099-2024 tillsynsbegäran mail.docx", "A 23099-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 26623-2026 tillsynsbegäran mail.docx", "A 26623-2026")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 64098-2023</t>
+          <t>A 23099-2024</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2219,10 +2214,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45279</v>
+        <v>45450</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2234,8 +2229,13 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I17" t="n">
-        <v>0.3</v>
+        <v>0.7</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2244,10 +2244,10 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
@@ -2262,7 +2262,7 @@
         <v>1</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
@@ -2271,46 +2271,46 @@
         <v>1</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Skogsalmsdvärgmal</t>
+          <t>Bredbrämad bastardsvärmare</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 64098-2023 artfynd.xlsx", "A 64098-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 23099-2024 artfynd.xlsx", "A 23099-2024")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 64098-2023 karta.png", "A 64098-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 23099-2024 karta.png", "A 23099-2024")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 64098-2023 georefererad karta.tif", "A 64098-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 23099-2024 georefererad karta.tif", "A 23099-2024")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 64098-2023 FSC-klagomål.docx", "A 64098-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 23099-2024 FSC-klagomål.docx", "A 23099-2024")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 64098-2023 FSC-klagomål mail.docx", "A 64098-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 23099-2024 FSC-klagomål mail.docx", "A 23099-2024")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 64098-2023 tillsynsbegäran.docx", "A 64098-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 23099-2024 tillsynsbegäran.docx", "A 23099-2024")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 64098-2023 tillsynsbegäran mail.docx", "A 64098-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 23099-2024 tillsynsbegäran mail.docx", "A 23099-2024")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 26196-2026</t>
+          <t>A 46438-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2320,14 +2320,14 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46182</v>
+        <v>45197</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2340,10 +2340,10 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>53.1</v>
+        <v>0.5</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
@@ -2355,7 +2355,7 @@
         <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2364,58 +2364,58 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
       </c>
       <c r="T18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Liljekonvalj</t>
+          <t>Bombmurkla</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 26196-2026 artfynd.xlsx", "A 26196-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 46438-2023 artfynd.xlsx", "A 46438-2023")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 26196-2026 karta.png", "A 26196-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 46438-2023 karta.png", "A 46438-2023")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 26196-2026 georefererad karta.tif", "A 26196-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 46438-2023 georefererad karta.tif", "A 46438-2023")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 26196-2026 FSC-klagomål.docx", "A 26196-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 46438-2023 FSC-klagomål.docx", "A 46438-2023")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 26196-2026 FSC-klagomål mail.docx", "A 26196-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 46438-2023 FSC-klagomål mail.docx", "A 46438-2023")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 26196-2026 tillsynsbegäran.docx", "A 26196-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 46438-2023 tillsynsbegäran.docx", "A 46438-2023")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 26196-2026 tillsynsbegäran mail.docx", "A 26196-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 46438-2023 tillsynsbegäran mail.docx", "A 46438-2023")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 26623-2026</t>
+          <t>A 11447-2025</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2425,14 +2425,14 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46184</v>
+        <v>45726</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2445,16 +2445,16 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>4.6</v>
+        <v>1.5</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
         <v>0</v>
@@ -2469,7 +2469,7 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
@@ -2485,42 +2485,42 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Svartöra</t>
+          <t>Myskbock</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 26623-2026 artfynd.xlsx", "A 26623-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 11447-2025 artfynd.xlsx", "A 11447-2025")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 26623-2026 karta.png", "A 26623-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 11447-2025 karta.png", "A 11447-2025")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 26623-2026 georefererad karta.tif", "A 26623-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 11447-2025 georefererad karta.tif", "A 11447-2025")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 26623-2026 FSC-klagomål.docx", "A 26623-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 11447-2025 FSC-klagomål.docx", "A 11447-2025")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 26623-2026 FSC-klagomål mail.docx", "A 26623-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 11447-2025 FSC-klagomål mail.docx", "A 11447-2025")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 26623-2026 tillsynsbegäran.docx", "A 26623-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 11447-2025 tillsynsbegäran.docx", "A 11447-2025")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 26623-2026 tillsynsbegäran mail.docx", "A 26623-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 11447-2025 tillsynsbegäran mail.docx", "A 11447-2025")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 11447-2025</t>
+          <t>A 7955-2023</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2530,14 +2530,14 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45726</v>
+        <v>44973</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2550,13 +2550,13 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>1.5</v>
+        <v>2.9</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
@@ -2565,7 +2565,7 @@
         <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2574,10 +2574,10 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>
@@ -2586,39 +2586,39 @@
         <v>1</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>Myskbock</t>
+          <t>Bombmurkla</t>
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 11447-2025 artfynd.xlsx", "A 11447-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 7955-2023 artfynd.xlsx", "A 7955-2023")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 11447-2025 karta.png", "A 11447-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 7955-2023 karta.png", "A 7955-2023")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 11447-2025 georefererad karta.tif", "A 11447-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 7955-2023 georefererad karta.tif", "A 7955-2023")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 11447-2025 FSC-klagomål.docx", "A 11447-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 7955-2023 FSC-klagomål.docx", "A 7955-2023")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 11447-2025 FSC-klagomål mail.docx", "A 11447-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 7955-2023 FSC-klagomål mail.docx", "A 7955-2023")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 11447-2025 tillsynsbegäran.docx", "A 11447-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 7955-2023 tillsynsbegäran.docx", "A 7955-2023")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 11447-2025 tillsynsbegäran mail.docx", "A 11447-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 7955-2023 tillsynsbegäran mail.docx", "A 7955-2023")</f>
         <v/>
       </c>
     </row>
@@ -2642,7 +2642,7 @@
         <v>46184</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2730,7 +2730,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 2062-2025</t>
+          <t>A 64098-2023</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2744,10 +2744,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45671</v>
+        <v>45279</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2760,10 +2760,10 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>1.9</v>
+        <v>0.3</v>
       </c>
       <c r="J22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
@@ -2796,50 +2796,46 @@
         <v>1</v>
       </c>
       <c r="U22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Skogsalmsdvärgmal</t>
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 2062-2025 artfynd.xlsx", "A 2062-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 64098-2023 artfynd.xlsx", "A 64098-2023")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 2062-2025 karta.png", "A 2062-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 64098-2023 karta.png", "A 64098-2023")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 2062-2025 georefererad karta.tif", "A 2062-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 64098-2023 georefererad karta.tif", "A 64098-2023")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 2062-2025 FSC-klagomål.docx", "A 2062-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 64098-2023 FSC-klagomål.docx", "A 64098-2023")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 2062-2025 FSC-klagomål mail.docx", "A 2062-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 64098-2023 FSC-klagomål mail.docx", "A 64098-2023")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 2062-2025 tillsynsbegäran.docx", "A 2062-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 64098-2023 tillsynsbegäran.docx", "A 64098-2023")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 2062-2025 tillsynsbegäran mail.docx", "A 2062-2025")</f>
-        <v/>
-      </c>
-      <c r="AE22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/fåglar/A 2062-2025 prioriterade fågelarter.docx", "A 2062-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 64098-2023 tillsynsbegäran mail.docx", "A 64098-2023")</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 25561-2025</t>
+          <t>A 2062-2025</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2853,10 +2849,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45803</v>
+        <v>45671</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2869,7 +2865,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>1.6</v>
+        <v>1.9</v>
       </c>
       <c r="J23" t="n">
         <v>1</v>
@@ -2878,13 +2874,13 @@
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M23" t="n">
         <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -2896,7 +2892,7 @@
         <v>1</v>
       </c>
       <c r="R23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
         <v>1</v>
@@ -2905,39 +2901,43 @@
         <v>1</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Bombmurkla</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 25561-2025 artfynd.xlsx", "A 25561-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 2062-2025 artfynd.xlsx", "A 2062-2025")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 25561-2025 karta.png", "A 25561-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 2062-2025 karta.png", "A 2062-2025")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 25561-2025 georefererad karta.tif", "A 25561-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 2062-2025 georefererad karta.tif", "A 2062-2025")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 25561-2025 FSC-klagomål.docx", "A 25561-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 2062-2025 FSC-klagomål.docx", "A 2062-2025")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 25561-2025 FSC-klagomål mail.docx", "A 25561-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 2062-2025 FSC-klagomål mail.docx", "A 2062-2025")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 25561-2025 tillsynsbegäran.docx", "A 25561-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 2062-2025 tillsynsbegäran.docx", "A 2062-2025")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 25561-2025 tillsynsbegäran mail.docx", "A 25561-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 2062-2025 tillsynsbegäran mail.docx", "A 2062-2025")</f>
+        <v/>
+      </c>
+      <c r="AE23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/fåglar/A 2062-2025 prioriterade fågelarter.docx", "A 2062-2025")</f>
         <v/>
       </c>
     </row>
@@ -2961,7 +2961,7 @@
         <v>44558</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3066,7 +3066,7 @@
         <v>44609</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3139,7 +3139,7 @@
         <v>44489</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3217,7 +3217,7 @@
         <v>44546</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3290,7 +3290,7 @@
         <v>44700</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3363,7 +3363,7 @@
         <v>44587</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3436,7 +3436,7 @@
         <v>44655</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3497,7 +3497,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 59700-2021</t>
+          <t>A 64105-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3511,10 +3511,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44494</v>
+        <v>45279</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3526,13 +3526,8 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I31" t="n">
-        <v>4.8</v>
+        <v>2.2</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3575,7 +3570,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 38902-2024</t>
+          <t>A 2602-2024</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3589,10 +3584,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45547</v>
+        <v>45313</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3604,13 +3599,8 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I32" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3653,7 +3643,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 50294-2023</t>
+          <t>A 59844-2022</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3667,10 +3657,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45216</v>
+        <v>44901</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3682,8 +3672,13 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I33" t="n">
-        <v>3.7</v>
+        <v>11.9</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3726,7 +3721,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 5264-2023</t>
+          <t>A 23093-2024</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3740,10 +3735,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44959</v>
+        <v>45450</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3755,8 +3750,13 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I34" t="n">
-        <v>5.8</v>
+        <v>0.9</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3799,7 +3799,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 9655-2026</t>
+          <t>A 3630-2023</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3813,10 +3813,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>46070</v>
+        <v>44950</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3828,13 +3828,8 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I35" t="n">
-        <v>17.2</v>
+        <v>1.4</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3877,7 +3872,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 23098-2024</t>
+          <t>A 54222-2023</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3891,10 +3886,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45450</v>
+        <v>45225</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3912,7 +3907,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>1</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3955,7 +3950,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 18787-2026</t>
+          <t>A 7860-2024</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3969,10 +3964,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>46128</v>
+        <v>45348</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3990,7 +3985,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>7.8</v>
+        <v>1.9</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4033,7 +4028,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 18813-2026</t>
+          <t>A 9655-2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4047,10 +4042,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>46128</v>
+        <v>46070</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4068,7 +4063,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>56</v>
+        <v>17.2</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4111,7 +4106,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 18818-2026</t>
+          <t>A 27313-2023</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4125,10 +4120,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>46128</v>
+        <v>45096</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4140,13 +4135,8 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I39" t="n">
-        <v>17.8</v>
+        <v>1.8</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4189,7 +4179,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 18778-2026</t>
+          <t>A 64114-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4203,10 +4193,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>46128</v>
+        <v>45279</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4218,13 +4208,8 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I40" t="n">
-        <v>4.5</v>
+        <v>0.4</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4267,7 +4252,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 59844-2022</t>
+          <t>A 50294-2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4281,10 +4266,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44901</v>
+        <v>45216</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4296,13 +4281,8 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I41" t="n">
-        <v>11.9</v>
+        <v>3.7</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4345,7 +4325,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 54222-2023</t>
+          <t>A 18778-2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4359,10 +4339,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45225</v>
+        <v>46128</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4380,7 +4360,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>8.300000000000001</v>
+        <v>4.5</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4423,7 +4403,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 4338-2023</t>
+          <t>A 58011-2021</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4437,10 +4417,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44953</v>
+        <v>44487</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4452,8 +4432,13 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I43" t="n">
-        <v>1.1</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4496,7 +4481,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 58011-2021</t>
+          <t>A 18813-2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4510,10 +4495,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44487</v>
+        <v>46128</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4531,7 +4516,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>9.199999999999999</v>
+        <v>56</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4574,7 +4559,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 72524-2021</t>
+          <t>A 18818-2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4588,10 +4573,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>44546</v>
+        <v>46128</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4603,8 +4588,13 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I45" t="n">
-        <v>3.6</v>
+        <v>17.8</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4647,7 +4637,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 64107-2023</t>
+          <t>A 18787-2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4661,10 +4651,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45279</v>
+        <v>46128</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4676,8 +4666,13 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I46" t="n">
-        <v>0.3</v>
+        <v>7.8</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4720,7 +4715,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 23093-2024</t>
+          <t>A 21206-2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4734,10 +4729,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45450</v>
+        <v>46146</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4798,7 +4793,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 27313-2023</t>
+          <t>A 24579-2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4812,10 +4807,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45096</v>
+        <v>46170</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4828,7 +4823,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4871,7 +4866,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 59377-2024</t>
+          <t>A 31160-2022</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4885,10 +4880,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45638</v>
+        <v>44770</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4901,7 +4896,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>0.6</v>
+        <v>3.7</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4944,7 +4939,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 21206-2026</t>
+          <t>A 58598-2025</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4958,10 +4953,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>46146</v>
+        <v>45986</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4979,7 +4974,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>0.9</v>
+        <v>4.5</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5022,7 +5017,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 24579-2026</t>
+          <t>A 26633-2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5036,10 +5031,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>46170</v>
+        <v>46184</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5052,7 +5047,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>2.1</v>
+        <v>0.7</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5095,7 +5090,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 58598-2025</t>
+          <t>A 26625-2026</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5109,10 +5104,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45986</v>
+        <v>46184</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5124,13 +5119,8 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I52" t="n">
-        <v>4.5</v>
+        <v>5.3</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5173,7 +5163,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 31160-2022</t>
+          <t>A 3754-2026</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5187,10 +5177,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>44770</v>
+        <v>46043</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5202,8 +5192,13 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I53" t="n">
-        <v>3.7</v>
+        <v>5.1</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5246,7 +5241,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 51587-2023</t>
+          <t>A 64110-2023</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5260,10 +5255,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45215</v>
+        <v>45279</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5275,13 +5270,8 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I54" t="n">
-        <v>2.6</v>
+        <v>0.4</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5324,7 +5314,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 26625-2026</t>
+          <t>A 23098-2024</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5338,10 +5328,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>46184</v>
+        <v>45450</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5353,8 +5343,13 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I55" t="n">
-        <v>5.3</v>
+        <v>1</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5397,7 +5392,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 26633-2026</t>
+          <t>A 28735-2026</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5411,10 +5406,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>46184</v>
+        <v>46198</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5427,7 +5422,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>0.7</v>
+        <v>3.5</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5470,7 +5465,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 3754-2026</t>
+          <t>A 28740-2026</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5484,10 +5479,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>46043</v>
+        <v>46198</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5499,13 +5494,8 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I57" t="n">
-        <v>5.1</v>
+        <v>4.8</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5565,7 +5555,7 @@
         <v>46198</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5621,7 +5611,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 28740-2026</t>
+          <t>A 59377-2024</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5635,10 +5625,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>46198</v>
+        <v>45638</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5651,7 +5641,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>4.8</v>
+        <v>0.6</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5694,7 +5684,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 59848-2022</t>
+          <t>A 59402-2022</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5708,10 +5698,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>44901</v>
+        <v>44906</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5723,13 +5713,8 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I60" t="n">
-        <v>10.7</v>
+        <v>1.8</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5772,7 +5757,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 28735-2026</t>
+          <t>A 5264-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5786,10 +5771,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>46198</v>
+        <v>44959</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5802,7 +5787,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>3.5</v>
+        <v>5.8</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5845,7 +5830,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 64110-2023</t>
+          <t>A 31714-2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5859,10 +5844,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45279</v>
+        <v>46226</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5875,7 +5860,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>0.4</v>
+        <v>5</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5918,7 +5903,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 7275-2022</t>
+          <t>A 51587-2023</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5932,10 +5917,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>44606</v>
+        <v>45215</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5949,11 +5934,11 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Övriga statliga verk och myndigheter</t>
+          <t>Allmännings- och besparingsskogar</t>
         </is>
       </c>
       <c r="I63" t="n">
-        <v>9.6</v>
+        <v>2.6</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5996,7 +5981,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 2602-2024</t>
+          <t>A 72524-2021</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6010,10 +5995,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45313</v>
+        <v>44546</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6026,7 +6011,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>0.7</v>
+        <v>3.6</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6069,7 +6054,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 59402-2022</t>
+          <t>A 4338-2023</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6083,10 +6068,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>44906</v>
+        <v>44953</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6099,7 +6084,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>1.8</v>
+        <v>1.1</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6142,7 +6127,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 31714-2026</t>
+          <t>A 59848-2022</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6156,10 +6141,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>46226</v>
+        <v>44901</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6171,8 +6156,13 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I66" t="n">
-        <v>5</v>
+        <v>10.7</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6215,7 +6205,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 3630-2023</t>
+          <t>A 33058-2026</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6225,14 +6215,14 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>44950</v>
+        <v>46245</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6245,7 +6235,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6288,7 +6278,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 7860-2024</t>
+          <t>A 59700-2021</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6302,10 +6292,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45348</v>
+        <v>44494</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6323,7 +6313,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>1.9</v>
+        <v>4.8</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6366,7 +6356,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 64105-2023</t>
+          <t>A 7275-2022</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6380,10 +6370,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45279</v>
+        <v>44606</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6395,8 +6385,13 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I69" t="n">
-        <v>2.2</v>
+        <v>9.6</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6439,7 +6434,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 33058-2026</t>
+          <t>A 64107-2023</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6449,14 +6444,14 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>46245</v>
+        <v>45279</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6469,7 +6464,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>1.3</v>
+        <v>0.3</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6512,7 +6507,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 64114-2023</t>
+          <t>A 7112-2025</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6526,10 +6521,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45279</v>
+        <v>45701</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6542,7 +6537,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>0.4</v>
+        <v>2.4</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6585,7 +6580,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 7112-2025</t>
+          <t>A 38902-2024</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6599,10 +6594,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45701</v>
+        <v>45547</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6614,8 +6609,13 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I72" t="n">
-        <v>2.4</v>
+        <v>0.8</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6675,7 +6675,7 @@
         <v>45792</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6748,7 +6748,7 @@
         <v>45792</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6821,7 +6821,7 @@
         <v>44558</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>

--- a/Översikt UPPLANDS-BRO.xlsx
+++ b/Översikt UPPLANDS-BRO.xlsx
@@ -601,7 +601,7 @@
         <v>44481</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -714,7 +714,7 @@
         <v>44552</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -822,7 +822,7 @@
         <v>44552</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -930,7 +930,7 @@
         <v>45232</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1042,7 +1042,7 @@
         <v>44552</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 18772-2026</t>
+          <t>A 18790-2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1148,7 +1148,7 @@
         <v>46128</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1166,16 +1166,16 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>19.5</v>
+        <v>5.5</v>
       </c>
       <c r="J7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -1190,7 +1190,7 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -1206,147 +1206,147 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
+          <t>Fläcknycklar
+Nattviol</t>
+        </is>
+      </c>
+      <c r="W7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 18790-2026 artfynd.xlsx", "A 18790-2026")</f>
+        <v/>
+      </c>
+      <c r="X7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 18790-2026 karta.png", "A 18790-2026")</f>
+        <v/>
+      </c>
+      <c r="Y7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 18790-2026 georefererad karta.tif", "A 18790-2026")</f>
+        <v/>
+      </c>
+      <c r="AA7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 18790-2026 FSC-klagomål.docx", "A 18790-2026")</f>
+        <v/>
+      </c>
+      <c r="AB7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 18790-2026 FSC-klagomål mail.docx", "A 18790-2026")</f>
+        <v/>
+      </c>
+      <c r="AC7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 18790-2026 tillsynsbegäran.docx", "A 18790-2026")</f>
+        <v/>
+      </c>
+      <c r="AD7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 18790-2026 tillsynsbegäran mail.docx", "A 18790-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="15" customHeight="1">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>A 18772-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D8" s="1" t="n">
+        <v>46128</v>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>46303</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>UPPLANDS-BRO</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="J8" t="n">
+        <v>1</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>2</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
           <t>Svedjenäva
 Fläcknycklar</t>
         </is>
       </c>
-      <c r="W7">
+      <c r="W8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 18772-2026 artfynd.xlsx", "A 18772-2026")</f>
         <v/>
       </c>
-      <c r="X7">
+      <c r="X8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 18772-2026 karta.png", "A 18772-2026")</f>
         <v/>
       </c>
-      <c r="Y7">
+      <c r="Y8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 18772-2026 georefererad karta.tif", "A 18772-2026")</f>
         <v/>
       </c>
-      <c r="AA7">
+      <c r="AA8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 18772-2026 FSC-klagomål.docx", "A 18772-2026")</f>
         <v/>
       </c>
-      <c r="AB7">
+      <c r="AB8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 18772-2026 FSC-klagomål mail.docx", "A 18772-2026")</f>
         <v/>
       </c>
-      <c r="AC7">
+      <c r="AC8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 18772-2026 tillsynsbegäran.docx", "A 18772-2026")</f>
         <v/>
       </c>
-      <c r="AD7">
+      <c r="AD8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 18772-2026 tillsynsbegäran mail.docx", "A 18772-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8" ht="15" customHeight="1">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>A 18790-2026</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D8" s="1" t="n">
-        <v>46128</v>
-      </c>
-      <c r="E8" s="1" t="n">
-        <v>46302</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>UPPLANDS-BRO</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
-      <c r="I8" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="J8" t="n">
-        <v>2</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" t="n">
-        <v>2</v>
-      </c>
-      <c r="T8" t="n">
-        <v>2</v>
-      </c>
-      <c r="U8" t="n">
-        <v>0</v>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>Fläcknycklar
-Nattviol</t>
-        </is>
-      </c>
-      <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 18790-2026 artfynd.xlsx", "A 18790-2026")</f>
-        <v/>
-      </c>
-      <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 18790-2026 karta.png", "A 18790-2026")</f>
-        <v/>
-      </c>
-      <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 18790-2026 georefererad karta.tif", "A 18790-2026")</f>
-        <v/>
-      </c>
-      <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 18790-2026 FSC-klagomål.docx", "A 18790-2026")</f>
-        <v/>
-      </c>
-      <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 18790-2026 FSC-klagomål mail.docx", "A 18790-2026")</f>
-        <v/>
-      </c>
-      <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 18790-2026 tillsynsbegäran.docx", "A 18790-2026")</f>
-        <v/>
-      </c>
-      <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 18790-2026 tillsynsbegäran mail.docx", "A 18790-2026")</f>
         <v/>
       </c>
     </row>
@@ -1370,7 +1370,7 @@
         <v>45722</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1481,7 +1481,7 @@
         <v>44603</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1570,7 +1570,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 73787-2021</t>
+          <t>A 23099-2024</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1584,10 +1584,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>44552</v>
+        <v>45450</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1599,8 +1599,13 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I11" t="n">
-        <v>4.6</v>
+        <v>0.7</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1609,10 +1614,10 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
@@ -1627,7 +1632,7 @@
         <v>1</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1636,46 +1641,46 @@
         <v>1</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Bredbrämad bastardsvärmare</t>
         </is>
       </c>
       <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 73787-2021 artfynd.xlsx", "A 73787-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 23099-2024 artfynd.xlsx", "A 23099-2024")</f>
         <v/>
       </c>
       <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 73787-2021 karta.png", "A 73787-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 23099-2024 karta.png", "A 23099-2024")</f>
         <v/>
       </c>
       <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 73787-2021 georefererad karta.tif", "A 73787-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 23099-2024 georefererad karta.tif", "A 23099-2024")</f>
         <v/>
       </c>
       <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 73787-2021 FSC-klagomål.docx", "A 73787-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 23099-2024 FSC-klagomål.docx", "A 23099-2024")</f>
         <v/>
       </c>
       <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 73787-2021 FSC-klagomål mail.docx", "A 73787-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 23099-2024 FSC-klagomål mail.docx", "A 23099-2024")</f>
         <v/>
       </c>
       <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 73787-2021 tillsynsbegäran.docx", "A 73787-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 23099-2024 tillsynsbegäran.docx", "A 23099-2024")</f>
         <v/>
       </c>
       <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 73787-2021 tillsynsbegäran mail.docx", "A 73787-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 23099-2024 tillsynsbegäran mail.docx", "A 23099-2024")</f>
         <v/>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 25561-2025</t>
+          <t>A 73787-2021</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1689,10 +1694,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45803</v>
+        <v>44552</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1705,22 +1710,22 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>1.6</v>
+        <v>4.6</v>
       </c>
       <c r="J12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1732,7 +1737,7 @@
         <v>1</v>
       </c>
       <c r="R12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1745,42 +1750,42 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>Bombmurkla</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 25561-2025 artfynd.xlsx", "A 25561-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 73787-2021 artfynd.xlsx", "A 73787-2021")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 25561-2025 karta.png", "A 25561-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 73787-2021 karta.png", "A 73787-2021")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 25561-2025 georefererad karta.tif", "A 25561-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 73787-2021 georefererad karta.tif", "A 73787-2021")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 25561-2025 FSC-klagomål.docx", "A 25561-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 73787-2021 FSC-klagomål.docx", "A 73787-2021")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 25561-2025 FSC-klagomål mail.docx", "A 25561-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 73787-2021 FSC-klagomål mail.docx", "A 73787-2021")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 25561-2025 tillsynsbegäran.docx", "A 25561-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 73787-2021 tillsynsbegäran.docx", "A 73787-2021")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 25561-2025 tillsynsbegäran mail.docx", "A 25561-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 73787-2021 tillsynsbegäran mail.docx", "A 73787-2021")</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 12363-2025</t>
+          <t>A 2062-2025</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1794,10 +1799,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45730</v>
+        <v>45671</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1810,16 +1815,16 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>0.8</v>
+        <v>1.9</v>
       </c>
       <c r="J13" t="n">
         <v>1</v>
       </c>
       <c r="K13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
@@ -1834,7 +1839,7 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -1846,46 +1851,50 @@
         <v>1</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 12363-2025 artfynd.xlsx", "A 12363-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 2062-2025 artfynd.xlsx", "A 2062-2025")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 12363-2025 karta.png", "A 12363-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 2062-2025 karta.png", "A 2062-2025")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 12363-2025 georefererad karta.tif", "A 12363-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 2062-2025 georefererad karta.tif", "A 2062-2025")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 12363-2025 FSC-klagomål.docx", "A 12363-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 2062-2025 FSC-klagomål.docx", "A 2062-2025")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 12363-2025 FSC-klagomål mail.docx", "A 12363-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 2062-2025 FSC-klagomål mail.docx", "A 2062-2025")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 12363-2025 tillsynsbegäran.docx", "A 12363-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 2062-2025 tillsynsbegäran.docx", "A 2062-2025")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 12363-2025 tillsynsbegäran mail.docx", "A 12363-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 2062-2025 tillsynsbegäran mail.docx", "A 2062-2025")</f>
+        <v/>
+      </c>
+      <c r="AE13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/fåglar/A 2062-2025 prioriterade fågelarter.docx", "A 2062-2025")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 53357-2025</t>
+          <t>A 12363-2025</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1899,10 +1908,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45959</v>
+        <v>45730</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1915,13 +1924,13 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>2.4</v>
+        <v>0.8</v>
       </c>
       <c r="J14" t="n">
         <v>1</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
@@ -1930,7 +1939,7 @@
         <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -1939,58 +1948,58 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
       </c>
       <c r="T14" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="U14" t="n">
         <v>0</v>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Bombmurkla</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 53357-2025 artfynd.xlsx", "A 53357-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 12363-2025 artfynd.xlsx", "A 12363-2025")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 53357-2025 karta.png", "A 53357-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 12363-2025 karta.png", "A 12363-2025")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 53357-2025 georefererad karta.tif", "A 53357-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 12363-2025 georefererad karta.tif", "A 12363-2025")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 53357-2025 FSC-klagomål.docx", "A 53357-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 12363-2025 FSC-klagomål.docx", "A 12363-2025")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 53357-2025 FSC-klagomål mail.docx", "A 53357-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 12363-2025 FSC-klagomål mail.docx", "A 12363-2025")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 53357-2025 tillsynsbegäran.docx", "A 53357-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 12363-2025 tillsynsbegäran.docx", "A 12363-2025")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 53357-2025 tillsynsbegäran mail.docx", "A 53357-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 12363-2025 tillsynsbegäran mail.docx", "A 12363-2025")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 26196-2026</t>
+          <t>A 25561-2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2000,14 +2009,14 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46182</v>
+        <v>45803</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2020,10 +2029,10 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>53.1</v>
+        <v>1.6</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
@@ -2035,7 +2044,7 @@
         <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2044,58 +2053,58 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S15" t="n">
         <v>1</v>
       </c>
       <c r="T15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Liljekonvalj</t>
+          <t>Bombmurkla</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 26196-2026 artfynd.xlsx", "A 26196-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 25561-2025 artfynd.xlsx", "A 25561-2025")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 26196-2026 karta.png", "A 26196-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 25561-2025 karta.png", "A 25561-2025")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 26196-2026 georefererad karta.tif", "A 26196-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 25561-2025 georefererad karta.tif", "A 25561-2025")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 26196-2026 FSC-klagomål.docx", "A 26196-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 25561-2025 FSC-klagomål.docx", "A 25561-2025")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 26196-2026 FSC-klagomål mail.docx", "A 26196-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 25561-2025 FSC-klagomål mail.docx", "A 25561-2025")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 26196-2026 tillsynsbegäran.docx", "A 26196-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 25561-2025 tillsynsbegäran.docx", "A 25561-2025")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 26196-2026 tillsynsbegäran mail.docx", "A 26196-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 25561-2025 tillsynsbegäran mail.docx", "A 25561-2025")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 26623-2026</t>
+          <t>A 64098-2023</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2109,10 +2118,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46184</v>
+        <v>45279</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2125,7 +2134,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>4.6</v>
+        <v>0.3</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -2165,42 +2174,42 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Svartöra</t>
+          <t>Skogsalmsdvärgmal</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 26623-2026 artfynd.xlsx", "A 26623-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 64098-2023 artfynd.xlsx", "A 64098-2023")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 26623-2026 karta.png", "A 26623-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 64098-2023 karta.png", "A 64098-2023")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 26623-2026 georefererad karta.tif", "A 26623-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 64098-2023 georefererad karta.tif", "A 64098-2023")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 26623-2026 FSC-klagomål.docx", "A 26623-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 64098-2023 FSC-klagomål.docx", "A 64098-2023")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 26623-2026 FSC-klagomål mail.docx", "A 26623-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 64098-2023 FSC-klagomål mail.docx", "A 64098-2023")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 26623-2026 tillsynsbegäran.docx", "A 26623-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 64098-2023 tillsynsbegäran.docx", "A 64098-2023")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 26623-2026 tillsynsbegäran mail.docx", "A 26623-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 64098-2023 tillsynsbegäran mail.docx", "A 64098-2023")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 23099-2024</t>
+          <t>A 7955-2023</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2214,10 +2223,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45450</v>
+        <v>44973</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2229,16 +2238,11 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I17" t="n">
-        <v>0.7</v>
+        <v>2.9</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
@@ -2247,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2275,42 +2279,42 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Bredbrämad bastardsvärmare</t>
+          <t>Bombmurkla</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 23099-2024 artfynd.xlsx", "A 23099-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 7955-2023 artfynd.xlsx", "A 7955-2023")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 23099-2024 karta.png", "A 23099-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 7955-2023 karta.png", "A 7955-2023")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 23099-2024 georefererad karta.tif", "A 23099-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 7955-2023 georefererad karta.tif", "A 7955-2023")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 23099-2024 FSC-klagomål.docx", "A 23099-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 7955-2023 FSC-klagomål.docx", "A 7955-2023")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 23099-2024 FSC-klagomål mail.docx", "A 23099-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 7955-2023 FSC-klagomål mail.docx", "A 7955-2023")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 23099-2024 tillsynsbegäran.docx", "A 23099-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 7955-2023 tillsynsbegäran.docx", "A 7955-2023")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 23099-2024 tillsynsbegäran mail.docx", "A 23099-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 7955-2023 tillsynsbegäran mail.docx", "A 7955-2023")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 46438-2023</t>
+          <t>A 53357-2025</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2324,10 +2328,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45197</v>
+        <v>45959</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2340,7 +2344,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>0.5</v>
+        <v>2.4</v>
       </c>
       <c r="J18" t="n">
         <v>1</v>
@@ -2373,7 +2377,7 @@
         <v>1</v>
       </c>
       <c r="T18" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="U18" t="n">
         <v>0</v>
@@ -2384,38 +2388,38 @@
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 46438-2023 artfynd.xlsx", "A 46438-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 53357-2025 artfynd.xlsx", "A 53357-2025")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 46438-2023 karta.png", "A 46438-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 53357-2025 karta.png", "A 53357-2025")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 46438-2023 georefererad karta.tif", "A 46438-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 53357-2025 georefererad karta.tif", "A 53357-2025")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 46438-2023 FSC-klagomål.docx", "A 46438-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 53357-2025 FSC-klagomål.docx", "A 53357-2025")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 46438-2023 FSC-klagomål mail.docx", "A 46438-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 53357-2025 FSC-klagomål mail.docx", "A 53357-2025")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 46438-2023 tillsynsbegäran.docx", "A 46438-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 53357-2025 tillsynsbegäran.docx", "A 53357-2025")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 46438-2023 tillsynsbegäran mail.docx", "A 46438-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 53357-2025 tillsynsbegäran mail.docx", "A 53357-2025")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 11447-2025</t>
+          <t>A 46438-2023</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2425,14 +2429,14 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45726</v>
+        <v>45197</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2445,13 +2449,13 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
@@ -2460,7 +2464,7 @@
         <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2469,10 +2473,10 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
@@ -2485,42 +2489,42 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Myskbock</t>
+          <t>Bombmurkla</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 11447-2025 artfynd.xlsx", "A 11447-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 46438-2023 artfynd.xlsx", "A 46438-2023")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 11447-2025 karta.png", "A 11447-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 46438-2023 karta.png", "A 46438-2023")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 11447-2025 georefererad karta.tif", "A 11447-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 46438-2023 georefererad karta.tif", "A 46438-2023")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 11447-2025 FSC-klagomål.docx", "A 11447-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 46438-2023 FSC-klagomål.docx", "A 46438-2023")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 11447-2025 FSC-klagomål mail.docx", "A 11447-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 46438-2023 FSC-klagomål mail.docx", "A 46438-2023")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 11447-2025 tillsynsbegäran.docx", "A 11447-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 46438-2023 tillsynsbegäran.docx", "A 46438-2023")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 11447-2025 tillsynsbegäran mail.docx", "A 11447-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 46438-2023 tillsynsbegäran mail.docx", "A 46438-2023")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 7955-2023</t>
+          <t>A 11447-2025</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2530,14 +2534,14 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>44973</v>
+        <v>45726</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2550,13 +2554,13 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>2.9</v>
+        <v>1.5</v>
       </c>
       <c r="J20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
@@ -2565,7 +2569,7 @@
         <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2574,10 +2578,10 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>
@@ -2586,46 +2590,46 @@
         <v>1</v>
       </c>
       <c r="U20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>Bombmurkla</t>
+          <t>Myskbock</t>
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 7955-2023 artfynd.xlsx", "A 7955-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 11447-2025 artfynd.xlsx", "A 11447-2025")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 7955-2023 karta.png", "A 7955-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 11447-2025 karta.png", "A 11447-2025")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 7955-2023 georefererad karta.tif", "A 7955-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 11447-2025 georefererad karta.tif", "A 11447-2025")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 7955-2023 FSC-klagomål.docx", "A 7955-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 11447-2025 FSC-klagomål.docx", "A 11447-2025")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 7955-2023 FSC-klagomål mail.docx", "A 7955-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 11447-2025 FSC-klagomål mail.docx", "A 11447-2025")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 7955-2023 tillsynsbegäran.docx", "A 7955-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 11447-2025 tillsynsbegäran.docx", "A 11447-2025")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 7955-2023 tillsynsbegäran mail.docx", "A 7955-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 11447-2025 tillsynsbegäran mail.docx", "A 11447-2025")</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 26637-2026</t>
+          <t>A 26196-2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2635,14 +2639,14 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46184</v>
+        <v>46182</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2655,7 +2659,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>5.4</v>
+        <v>53.1</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2667,7 +2671,7 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
         <v>0</v>
@@ -2679,58 +2683,58 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
         <v>1</v>
       </c>
       <c r="T21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Igelkott</t>
+          <t>Liljekonvalj</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 26637-2026 artfynd.xlsx", "A 26637-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 26196-2026 artfynd.xlsx", "A 26196-2026")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 26637-2026 karta.png", "A 26637-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 26196-2026 karta.png", "A 26196-2026")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 26637-2026 georefererad karta.tif", "A 26637-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 26196-2026 georefererad karta.tif", "A 26196-2026")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 26637-2026 FSC-klagomål.docx", "A 26637-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 26196-2026 FSC-klagomål.docx", "A 26196-2026")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 26637-2026 FSC-klagomål mail.docx", "A 26637-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 26196-2026 FSC-klagomål mail.docx", "A 26196-2026")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 26637-2026 tillsynsbegäran.docx", "A 26637-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 26196-2026 tillsynsbegäran.docx", "A 26196-2026")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 26637-2026 tillsynsbegäran mail.docx", "A 26637-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 26196-2026 tillsynsbegäran mail.docx", "A 26196-2026")</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 64098-2023</t>
+          <t>A 26623-2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2744,10 +2748,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45279</v>
+        <v>46184</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2760,7 +2764,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>0.3</v>
+        <v>4.6</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2800,42 +2804,42 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>Skogsalmsdvärgmal</t>
+          <t>Svartöra</t>
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 64098-2023 artfynd.xlsx", "A 64098-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 26623-2026 artfynd.xlsx", "A 26623-2026")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 64098-2023 karta.png", "A 64098-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 26623-2026 karta.png", "A 26623-2026")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 64098-2023 georefererad karta.tif", "A 64098-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 26623-2026 georefererad karta.tif", "A 26623-2026")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 64098-2023 FSC-klagomål.docx", "A 64098-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 26623-2026 FSC-klagomål.docx", "A 26623-2026")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 64098-2023 FSC-klagomål mail.docx", "A 64098-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 26623-2026 FSC-klagomål mail.docx", "A 26623-2026")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 64098-2023 tillsynsbegäran.docx", "A 64098-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 26623-2026 tillsynsbegäran.docx", "A 26623-2026")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 64098-2023 tillsynsbegäran mail.docx", "A 64098-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 26623-2026 tillsynsbegäran mail.docx", "A 26623-2026")</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 2062-2025</t>
+          <t>A 26637-2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2849,10 +2853,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45671</v>
+        <v>46184</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2865,19 +2869,19 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>1.9</v>
+        <v>5.4</v>
       </c>
       <c r="J23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N23" t="n">
         <v>0</v>
@@ -2892,7 +2896,7 @@
         <v>1</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S23" t="n">
         <v>1</v>
@@ -2901,43 +2905,39 @@
         <v>1</v>
       </c>
       <c r="U23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Igelkott</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 2062-2025 artfynd.xlsx", "A 2062-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 26637-2026 artfynd.xlsx", "A 26637-2026")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 2062-2025 karta.png", "A 2062-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 26637-2026 karta.png", "A 26637-2026")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 2062-2025 georefererad karta.tif", "A 2062-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 26637-2026 georefererad karta.tif", "A 26637-2026")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 2062-2025 FSC-klagomål.docx", "A 2062-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 26637-2026 FSC-klagomål.docx", "A 26637-2026")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 2062-2025 FSC-klagomål mail.docx", "A 2062-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 26637-2026 FSC-klagomål mail.docx", "A 26637-2026")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 2062-2025 tillsynsbegäran.docx", "A 2062-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 26637-2026 tillsynsbegäran.docx", "A 26637-2026")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 2062-2025 tillsynsbegäran mail.docx", "A 2062-2025")</f>
-        <v/>
-      </c>
-      <c r="AE23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/fåglar/A 2062-2025 prioriterade fågelarter.docx", "A 2062-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 26637-2026 tillsynsbegäran mail.docx", "A 26637-2026")</f>
         <v/>
       </c>
     </row>
@@ -2961,7 +2961,7 @@
         <v>44558</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3066,7 +3066,7 @@
         <v>44609</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3139,7 +3139,7 @@
         <v>44489</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3217,7 +3217,7 @@
         <v>44546</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3290,7 +3290,7 @@
         <v>44700</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3363,7 +3363,7 @@
         <v>44587</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3419,7 +3419,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 14719-2022</t>
+          <t>A 23098-2024</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3433,10 +3433,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>44655</v>
+        <v>45450</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3450,11 +3450,11 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Allmännings- och besparingsskogar</t>
+          <t>Övriga statliga verk och myndigheter</t>
         </is>
       </c>
       <c r="I30" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3497,7 +3497,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 64105-2023</t>
+          <t>A 14719-2022</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3511,10 +3511,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45279</v>
+        <v>44655</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3526,8 +3526,13 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I31" t="n">
-        <v>2.2</v>
+        <v>1.2</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3570,7 +3575,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 2602-2024</t>
+          <t>A 7112-2025</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3584,10 +3589,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45313</v>
+        <v>45701</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3600,7 +3605,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0.7</v>
+        <v>2.4</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3660,7 +3665,7 @@
         <v>44901</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3721,7 +3726,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 23093-2024</t>
+          <t>A 54222-2023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3735,10 +3740,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45450</v>
+        <v>45225</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3756,7 +3761,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>0.9</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3799,7 +3804,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 3630-2023</t>
+          <t>A 23615-2025</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3813,10 +3818,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44950</v>
+        <v>45792</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3829,7 +3834,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3872,7 +3877,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 54222-2023</t>
+          <t>A 23627-2025</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3886,10 +3891,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45225</v>
+        <v>45792</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3901,13 +3906,8 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I36" t="n">
-        <v>8.300000000000001</v>
+        <v>1.7</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3950,7 +3950,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 7860-2024</t>
+          <t>A 4338-2023</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3964,10 +3964,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45348</v>
+        <v>44953</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3979,13 +3979,8 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I37" t="n">
-        <v>1.9</v>
+        <v>1.1</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4028,7 +4023,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 9655-2026</t>
+          <t>A 58011-2021</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4042,10 +4037,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>46070</v>
+        <v>44487</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4063,7 +4058,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>17.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4106,7 +4101,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 27313-2023</t>
+          <t>A 72524-2021</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4120,10 +4115,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45096</v>
+        <v>44546</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4136,7 +4131,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1.8</v>
+        <v>3.6</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4179,7 +4174,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 64114-2023</t>
+          <t>A 64107-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4196,7 +4191,7 @@
         <v>45279</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4209,7 +4204,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4252,7 +4247,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 50294-2023</t>
+          <t>A 23093-2024</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4266,10 +4261,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45216</v>
+        <v>45450</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4281,8 +4276,13 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I41" t="n">
-        <v>3.7</v>
+        <v>0.9</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4325,7 +4325,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 18778-2026</t>
+          <t>A 59700-2021</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4339,10 +4339,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>46128</v>
+        <v>44494</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4360,7 +4360,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4403,7 +4403,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 58011-2021</t>
+          <t>A 27313-2023</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4417,10 +4417,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44487</v>
+        <v>45096</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4432,13 +4432,8 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I43" t="n">
-        <v>9.199999999999999</v>
+        <v>1.8</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4481,7 +4476,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 18813-2026</t>
+          <t>A 59377-2024</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4495,10 +4490,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>46128</v>
+        <v>45638</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4510,13 +4505,8 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I44" t="n">
-        <v>56</v>
+        <v>0.6</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4559,7 +4549,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 18818-2026</t>
+          <t>A 38902-2024</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4573,10 +4563,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>46128</v>
+        <v>45547</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4594,7 +4584,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>17.8</v>
+        <v>0.8</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4637,7 +4627,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 18787-2026</t>
+          <t>A 50294-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4651,10 +4641,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>46128</v>
+        <v>45216</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4666,13 +4656,8 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I46" t="n">
-        <v>7.8</v>
+        <v>3.7</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4732,7 +4717,7 @@
         <v>46146</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4793,7 +4778,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 24579-2026</t>
+          <t>A 5264-2023</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4807,10 +4792,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>46170</v>
+        <v>44959</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4823,7 +4808,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>2.1</v>
+        <v>5.8</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4866,7 +4851,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 31160-2022</t>
+          <t>A 51587-2023</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4880,10 +4865,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>44770</v>
+        <v>45215</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4895,8 +4880,13 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I49" t="n">
-        <v>3.7</v>
+        <v>2.6</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4939,7 +4929,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 58598-2025</t>
+          <t>A 24579-2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4953,10 +4943,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45986</v>
+        <v>46170</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4968,13 +4958,8 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I50" t="n">
-        <v>4.5</v>
+        <v>2.1</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5017,7 +5002,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 26633-2026</t>
+          <t>A 58598-2025</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5031,10 +5016,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>46184</v>
+        <v>45986</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5046,8 +5031,13 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I51" t="n">
-        <v>0.7</v>
+        <v>4.5</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5090,7 +5080,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 26625-2026</t>
+          <t>A 59848-2022</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5104,10 +5094,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>46184</v>
+        <v>44901</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5119,8 +5109,13 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I52" t="n">
-        <v>5.3</v>
+        <v>10.7</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5163,7 +5158,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 3754-2026</t>
+          <t>A 31160-2022</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5177,10 +5172,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>46043</v>
+        <v>44770</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5192,13 +5187,8 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I53" t="n">
-        <v>5.1</v>
+        <v>3.7</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5258,7 +5248,7 @@
         <v>45279</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5314,7 +5304,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 23098-2024</t>
+          <t>A 26625-2026</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5328,10 +5318,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45450</v>
+        <v>46184</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5343,13 +5333,8 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I55" t="n">
-        <v>1</v>
+        <v>5.3</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5392,7 +5377,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 28735-2026</t>
+          <t>A 26633-2026</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5406,10 +5391,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>46198</v>
+        <v>46184</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5422,7 +5407,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>3.5</v>
+        <v>0.7</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5465,7 +5450,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 28740-2026</t>
+          <t>A 3754-2026</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5479,10 +5464,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>46198</v>
+        <v>46043</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5494,8 +5479,13 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I57" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5538,7 +5528,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 28797-2026</t>
+          <t>A 9655-2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5552,10 +5542,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>46198</v>
+        <v>46070</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5567,8 +5557,13 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I58" t="n">
-        <v>2.2</v>
+        <v>17.2</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5611,7 +5606,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 59377-2024</t>
+          <t>A 28797-2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5625,10 +5620,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45638</v>
+        <v>46198</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5641,7 +5636,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>0.6</v>
+        <v>2.2</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5684,7 +5679,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 59402-2022</t>
+          <t>A 28740-2026</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5698,10 +5693,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>44906</v>
+        <v>46198</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5714,7 +5709,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>1.8</v>
+        <v>4.8</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5757,7 +5752,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 5264-2023</t>
+          <t>A 7275-2022</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5771,10 +5766,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>44959</v>
+        <v>44606</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5786,8 +5781,13 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I61" t="n">
-        <v>5.8</v>
+        <v>9.6</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5830,7 +5830,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 31714-2026</t>
+          <t>A 28735-2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5844,10 +5844,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>46226</v>
+        <v>46198</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5860,7 +5860,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>5</v>
+        <v>3.5</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5903,7 +5903,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 51587-2023</t>
+          <t>A 2602-2024</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5917,10 +5917,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45215</v>
+        <v>45313</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5932,13 +5932,8 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I63" t="n">
-        <v>2.6</v>
+        <v>0.7</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5981,7 +5976,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 72524-2021</t>
+          <t>A 59402-2022</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5995,10 +5990,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>44546</v>
+        <v>44906</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6011,7 +6006,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>3.6</v>
+        <v>1.8</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6054,7 +6049,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 4338-2023</t>
+          <t>A 3630-2023</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6068,10 +6063,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>44953</v>
+        <v>44950</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6084,7 +6079,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6127,7 +6122,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 59848-2022</t>
+          <t>A 7860-2024</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6141,10 +6136,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>44901</v>
+        <v>45348</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6162,7 +6157,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>10.7</v>
+        <v>1.9</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6205,7 +6200,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 33058-2026</t>
+          <t>A 18787-2026</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6215,14 +6210,14 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>46245</v>
+        <v>46128</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6234,8 +6229,13 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I67" t="n">
-        <v>1.3</v>
+        <v>7.8</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6278,7 +6278,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 59700-2021</t>
+          <t>A 18813-2026</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6292,10 +6292,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>44494</v>
+        <v>46128</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6313,7 +6313,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>4.8</v>
+        <v>56</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6356,7 +6356,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 7275-2022</t>
+          <t>A 18818-2026</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6370,10 +6370,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>44606</v>
+        <v>46128</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6391,7 +6391,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>9.6</v>
+        <v>17.8</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6434,7 +6434,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 64107-2023</t>
+          <t>A 18778-2026</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6448,10 +6448,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45279</v>
+        <v>46128</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6463,8 +6463,13 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I70" t="n">
-        <v>0.3</v>
+        <v>4.5</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6507,7 +6512,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 7112-2025</t>
+          <t>A 64105-2023</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6521,10 +6526,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45701</v>
+        <v>45279</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6537,7 +6542,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6580,7 +6585,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 38902-2024</t>
+          <t>A 64114-2023</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6594,10 +6599,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45547</v>
+        <v>45279</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6609,13 +6614,8 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I72" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6658,7 +6658,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 23615-2025</t>
+          <t>A 31714-2026</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6672,10 +6672,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45792</v>
+        <v>46226</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6688,7 +6688,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>1.3</v>
+        <v>5</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6731,7 +6731,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 23627-2025</t>
+          <t>A 33058-2026</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6741,14 +6741,14 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45792</v>
+        <v>46245</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6761,7 +6761,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>1.7</v>
+        <v>1.3</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6821,7 +6821,7 @@
         <v>44558</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>

--- a/Översikt UPPLANDS-BRO.xlsx
+++ b/Översikt UPPLANDS-BRO.xlsx
@@ -601,7 +601,7 @@
         <v>44481</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -714,7 +714,7 @@
         <v>44552</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -822,7 +822,7 @@
         <v>44552</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -930,7 +930,7 @@
         <v>45232</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1042,7 +1042,7 @@
         <v>44552</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 18790-2026</t>
+          <t>A 18772-2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1148,7 +1148,7 @@
         <v>46128</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1166,16 +1166,16 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>5.5</v>
+        <v>19.5</v>
       </c>
       <c r="J7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -1190,7 +1190,7 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -1206,147 +1206,147 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
+          <t>Svedjenäva
+Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="W7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 18772-2026 artfynd.xlsx", "A 18772-2026")</f>
+        <v/>
+      </c>
+      <c r="X7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 18772-2026 karta.png", "A 18772-2026")</f>
+        <v/>
+      </c>
+      <c r="Y7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 18772-2026 georefererad karta.tif", "A 18772-2026")</f>
+        <v/>
+      </c>
+      <c r="AA7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 18772-2026 FSC-klagomål.docx", "A 18772-2026")</f>
+        <v/>
+      </c>
+      <c r="AB7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 18772-2026 FSC-klagomål mail.docx", "A 18772-2026")</f>
+        <v/>
+      </c>
+      <c r="AC7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 18772-2026 tillsynsbegäran.docx", "A 18772-2026")</f>
+        <v/>
+      </c>
+      <c r="AD7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 18772-2026 tillsynsbegäran mail.docx", "A 18772-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="15" customHeight="1">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>A 18790-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D8" s="1" t="n">
+        <v>46128</v>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>46304</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>UPPLANDS-BRO</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="J8" t="n">
+        <v>2</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>2</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
           <t>Fläcknycklar
 Nattviol</t>
         </is>
       </c>
-      <c r="W7">
+      <c r="W8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 18790-2026 artfynd.xlsx", "A 18790-2026")</f>
         <v/>
       </c>
-      <c r="X7">
+      <c r="X8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 18790-2026 karta.png", "A 18790-2026")</f>
         <v/>
       </c>
-      <c r="Y7">
+      <c r="Y8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 18790-2026 georefererad karta.tif", "A 18790-2026")</f>
         <v/>
       </c>
-      <c r="AA7">
+      <c r="AA8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 18790-2026 FSC-klagomål.docx", "A 18790-2026")</f>
         <v/>
       </c>
-      <c r="AB7">
+      <c r="AB8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 18790-2026 FSC-klagomål mail.docx", "A 18790-2026")</f>
         <v/>
       </c>
-      <c r="AC7">
+      <c r="AC8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 18790-2026 tillsynsbegäran.docx", "A 18790-2026")</f>
         <v/>
       </c>
-      <c r="AD7">
+      <c r="AD8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 18790-2026 tillsynsbegäran mail.docx", "A 18790-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8" ht="15" customHeight="1">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>A 18772-2026</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D8" s="1" t="n">
-        <v>46128</v>
-      </c>
-      <c r="E8" s="1" t="n">
-        <v>46303</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>UPPLANDS-BRO</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
-      <c r="I8" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="J8" t="n">
-        <v>1</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>1</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>1</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" t="n">
-        <v>2</v>
-      </c>
-      <c r="T8" t="n">
-        <v>2</v>
-      </c>
-      <c r="U8" t="n">
-        <v>0</v>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>Svedjenäva
-Fläcknycklar</t>
-        </is>
-      </c>
-      <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 18772-2026 artfynd.xlsx", "A 18772-2026")</f>
-        <v/>
-      </c>
-      <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 18772-2026 karta.png", "A 18772-2026")</f>
-        <v/>
-      </c>
-      <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 18772-2026 georefererad karta.tif", "A 18772-2026")</f>
-        <v/>
-      </c>
-      <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 18772-2026 FSC-klagomål.docx", "A 18772-2026")</f>
-        <v/>
-      </c>
-      <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 18772-2026 FSC-klagomål mail.docx", "A 18772-2026")</f>
-        <v/>
-      </c>
-      <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 18772-2026 tillsynsbegäran.docx", "A 18772-2026")</f>
-        <v/>
-      </c>
-      <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 18772-2026 tillsynsbegäran mail.docx", "A 18772-2026")</f>
         <v/>
       </c>
     </row>
@@ -1370,7 +1370,7 @@
         <v>45722</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1481,7 +1481,7 @@
         <v>44603</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1570,7 +1570,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 23099-2024</t>
+          <t>A 73787-2021</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1584,10 +1584,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45450</v>
+        <v>44552</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1599,13 +1599,8 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I11" t="n">
-        <v>0.7</v>
+        <v>4.6</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1614,10 +1609,10 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
@@ -1632,7 +1627,7 @@
         <v>1</v>
       </c>
       <c r="R11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1641,46 +1636,46 @@
         <v>1</v>
       </c>
       <c r="U11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>Bredbrämad bastardsvärmare</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 23099-2024 artfynd.xlsx", "A 23099-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 73787-2021 artfynd.xlsx", "A 73787-2021")</f>
         <v/>
       </c>
       <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 23099-2024 karta.png", "A 23099-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 73787-2021 karta.png", "A 73787-2021")</f>
         <v/>
       </c>
       <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 23099-2024 georefererad karta.tif", "A 23099-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 73787-2021 georefererad karta.tif", "A 73787-2021")</f>
         <v/>
       </c>
       <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 23099-2024 FSC-klagomål.docx", "A 23099-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 73787-2021 FSC-klagomål.docx", "A 73787-2021")</f>
         <v/>
       </c>
       <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 23099-2024 FSC-klagomål mail.docx", "A 23099-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 73787-2021 FSC-klagomål mail.docx", "A 73787-2021")</f>
         <v/>
       </c>
       <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 23099-2024 tillsynsbegäran.docx", "A 23099-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 73787-2021 tillsynsbegäran.docx", "A 73787-2021")</f>
         <v/>
       </c>
       <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 23099-2024 tillsynsbegäran mail.docx", "A 23099-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 73787-2021 tillsynsbegäran mail.docx", "A 73787-2021")</f>
         <v/>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 73787-2021</t>
+          <t>A 12363-2025</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1694,10 +1689,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>44552</v>
+        <v>45730</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1710,16 +1705,16 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>4.6</v>
+        <v>0.8</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
@@ -1734,7 +1729,7 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -1750,42 +1745,42 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 73787-2021 artfynd.xlsx", "A 73787-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 12363-2025 artfynd.xlsx", "A 12363-2025")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 73787-2021 karta.png", "A 73787-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 12363-2025 karta.png", "A 12363-2025")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 73787-2021 georefererad karta.tif", "A 73787-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 12363-2025 georefererad karta.tif", "A 12363-2025")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 73787-2021 FSC-klagomål.docx", "A 73787-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 12363-2025 FSC-klagomål.docx", "A 12363-2025")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 73787-2021 FSC-klagomål mail.docx", "A 73787-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 12363-2025 FSC-klagomål mail.docx", "A 12363-2025")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 73787-2021 tillsynsbegäran.docx", "A 73787-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 12363-2025 tillsynsbegäran.docx", "A 12363-2025")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 73787-2021 tillsynsbegäran mail.docx", "A 73787-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 12363-2025 tillsynsbegäran mail.docx", "A 12363-2025")</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 2062-2025</t>
+          <t>A 53357-2025</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1799,10 +1794,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45671</v>
+        <v>45959</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1815,7 +1810,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>1.9</v>
+        <v>2.4</v>
       </c>
       <c r="J13" t="n">
         <v>1</v>
@@ -1824,13 +1819,13 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -1842,59 +1837,55 @@
         <v>1</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
       </c>
       <c r="T13" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="U13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Bombmurkla</t>
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 2062-2025 artfynd.xlsx", "A 2062-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 53357-2025 artfynd.xlsx", "A 53357-2025")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 2062-2025 karta.png", "A 2062-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 53357-2025 karta.png", "A 53357-2025")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 2062-2025 georefererad karta.tif", "A 2062-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 53357-2025 georefererad karta.tif", "A 53357-2025")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 2062-2025 FSC-klagomål.docx", "A 2062-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 53357-2025 FSC-klagomål.docx", "A 53357-2025")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 2062-2025 FSC-klagomål mail.docx", "A 2062-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 53357-2025 FSC-klagomål mail.docx", "A 53357-2025")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 2062-2025 tillsynsbegäran.docx", "A 2062-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 53357-2025 tillsynsbegäran.docx", "A 53357-2025")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 2062-2025 tillsynsbegäran mail.docx", "A 2062-2025")</f>
-        <v/>
-      </c>
-      <c r="AE13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/fåglar/A 2062-2025 prioriterade fågelarter.docx", "A 2062-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 53357-2025 tillsynsbegäran mail.docx", "A 53357-2025")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 12363-2025</t>
+          <t>A 23099-2024</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1908,10 +1899,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45730</v>
+        <v>45450</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1923,20 +1914,25 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I14" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="J14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -1948,10 +1944,10 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
@@ -1960,46 +1956,46 @@
         <v>1</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Bredbrämad bastardsvärmare</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 12363-2025 artfynd.xlsx", "A 12363-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 23099-2024 artfynd.xlsx", "A 23099-2024")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 12363-2025 karta.png", "A 12363-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 23099-2024 karta.png", "A 23099-2024")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 12363-2025 georefererad karta.tif", "A 12363-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 23099-2024 georefererad karta.tif", "A 23099-2024")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 12363-2025 FSC-klagomål.docx", "A 12363-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 23099-2024 FSC-klagomål.docx", "A 23099-2024")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 12363-2025 FSC-klagomål mail.docx", "A 12363-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 23099-2024 FSC-klagomål mail.docx", "A 23099-2024")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 12363-2025 tillsynsbegäran.docx", "A 12363-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 23099-2024 tillsynsbegäran.docx", "A 23099-2024")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 12363-2025 tillsynsbegäran mail.docx", "A 12363-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 23099-2024 tillsynsbegäran mail.docx", "A 23099-2024")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 25561-2025</t>
+          <t>A 46438-2023</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2013,10 +2009,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45803</v>
+        <v>45197</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2029,7 +2025,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>1.6</v>
+        <v>0.5</v>
       </c>
       <c r="J15" t="n">
         <v>1</v>
@@ -2073,38 +2069,38 @@
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 25561-2025 artfynd.xlsx", "A 25561-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 46438-2023 artfynd.xlsx", "A 46438-2023")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 25561-2025 karta.png", "A 25561-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 46438-2023 karta.png", "A 46438-2023")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 25561-2025 georefererad karta.tif", "A 25561-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 46438-2023 georefererad karta.tif", "A 46438-2023")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 25561-2025 FSC-klagomål.docx", "A 25561-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 46438-2023 FSC-klagomål.docx", "A 46438-2023")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 25561-2025 FSC-klagomål mail.docx", "A 25561-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 46438-2023 FSC-klagomål mail.docx", "A 46438-2023")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 25561-2025 tillsynsbegäran.docx", "A 25561-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 46438-2023 tillsynsbegäran.docx", "A 46438-2023")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 25561-2025 tillsynsbegäran mail.docx", "A 25561-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 46438-2023 tillsynsbegäran mail.docx", "A 46438-2023")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 64098-2023</t>
+          <t>A 11447-2025</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2114,14 +2110,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45279</v>
+        <v>45726</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2134,16 +2130,16 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>0.3</v>
+        <v>1.5</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
@@ -2158,7 +2154,7 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -2174,35 +2170,35 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Skogsalmsdvärgmal</t>
+          <t>Myskbock</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 64098-2023 artfynd.xlsx", "A 64098-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 11447-2025 artfynd.xlsx", "A 11447-2025")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 64098-2023 karta.png", "A 64098-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 11447-2025 karta.png", "A 11447-2025")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 64098-2023 georefererad karta.tif", "A 64098-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 11447-2025 georefererad karta.tif", "A 11447-2025")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 64098-2023 FSC-klagomål.docx", "A 64098-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 11447-2025 FSC-klagomål.docx", "A 11447-2025")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 64098-2023 FSC-klagomål mail.docx", "A 64098-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 11447-2025 FSC-klagomål mail.docx", "A 11447-2025")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 64098-2023 tillsynsbegäran.docx", "A 64098-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 11447-2025 tillsynsbegäran.docx", "A 11447-2025")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 64098-2023 tillsynsbegäran mail.docx", "A 64098-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 11447-2025 tillsynsbegäran mail.docx", "A 11447-2025")</f>
         <v/>
       </c>
     </row>
@@ -2226,7 +2222,7 @@
         <v>44973</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2314,7 +2310,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 53357-2025</t>
+          <t>A 26196-2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2324,14 +2320,14 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45959</v>
+        <v>46182</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2344,10 +2340,10 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>2.4</v>
+        <v>53.1</v>
       </c>
       <c r="J18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
@@ -2359,7 +2355,7 @@
         <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2368,58 +2364,58 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
       </c>
       <c r="T18" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Bombmurkla</t>
+          <t>Liljekonvalj</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 53357-2025 artfynd.xlsx", "A 53357-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 26196-2026 artfynd.xlsx", "A 26196-2026")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 53357-2025 karta.png", "A 53357-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 26196-2026 karta.png", "A 26196-2026")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 53357-2025 georefererad karta.tif", "A 53357-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 26196-2026 georefererad karta.tif", "A 26196-2026")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 53357-2025 FSC-klagomål.docx", "A 53357-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 26196-2026 FSC-klagomål.docx", "A 26196-2026")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 53357-2025 FSC-klagomål mail.docx", "A 53357-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 26196-2026 FSC-klagomål mail.docx", "A 26196-2026")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 53357-2025 tillsynsbegäran.docx", "A 53357-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 26196-2026 tillsynsbegäran.docx", "A 26196-2026")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 53357-2025 tillsynsbegäran mail.docx", "A 53357-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 26196-2026 tillsynsbegäran mail.docx", "A 26196-2026")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 46438-2023</t>
+          <t>A 64098-2023</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2433,10 +2429,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45197</v>
+        <v>45279</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2449,22 +2445,22 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="J19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M19" t="n">
         <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2476,7 +2472,7 @@
         <v>1</v>
       </c>
       <c r="R19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
@@ -2489,42 +2485,42 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Bombmurkla</t>
+          <t>Skogsalmsdvärgmal</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 46438-2023 artfynd.xlsx", "A 46438-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 64098-2023 artfynd.xlsx", "A 64098-2023")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 46438-2023 karta.png", "A 46438-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 64098-2023 karta.png", "A 64098-2023")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 46438-2023 georefererad karta.tif", "A 46438-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 64098-2023 georefererad karta.tif", "A 64098-2023")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 46438-2023 FSC-klagomål.docx", "A 46438-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 64098-2023 FSC-klagomål.docx", "A 64098-2023")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 46438-2023 FSC-klagomål mail.docx", "A 46438-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 64098-2023 FSC-klagomål mail.docx", "A 64098-2023")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 46438-2023 tillsynsbegäran.docx", "A 46438-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 64098-2023 tillsynsbegäran.docx", "A 64098-2023")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 46438-2023 tillsynsbegäran mail.docx", "A 46438-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 64098-2023 tillsynsbegäran mail.docx", "A 64098-2023")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 11447-2025</t>
+          <t>A 2062-2025</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2534,14 +2530,14 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45726</v>
+        <v>45671</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2554,16 +2550,16 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>1.5</v>
+        <v>1.9</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M20" t="n">
         <v>0</v>
@@ -2578,7 +2574,7 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
@@ -2590,46 +2586,50 @@
         <v>1</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>Myskbock</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 11447-2025 artfynd.xlsx", "A 11447-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 2062-2025 artfynd.xlsx", "A 2062-2025")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 11447-2025 karta.png", "A 11447-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 2062-2025 karta.png", "A 2062-2025")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 11447-2025 georefererad karta.tif", "A 11447-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 2062-2025 georefererad karta.tif", "A 2062-2025")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 11447-2025 FSC-klagomål.docx", "A 11447-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 2062-2025 FSC-klagomål.docx", "A 2062-2025")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 11447-2025 FSC-klagomål mail.docx", "A 11447-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 2062-2025 FSC-klagomål mail.docx", "A 2062-2025")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 11447-2025 tillsynsbegäran.docx", "A 11447-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 2062-2025 tillsynsbegäran.docx", "A 2062-2025")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 11447-2025 tillsynsbegäran mail.docx", "A 11447-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 2062-2025 tillsynsbegäran mail.docx", "A 2062-2025")</f>
+        <v/>
+      </c>
+      <c r="AE20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/fåglar/A 2062-2025 prioriterade fågelarter.docx", "A 2062-2025")</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 26196-2026</t>
+          <t>A 25561-2025</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2639,14 +2639,14 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46182</v>
+        <v>45803</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2659,10 +2659,10 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>53.1</v>
+        <v>1.6</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
@@ -2674,7 +2674,7 @@
         <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2683,58 +2683,58 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S21" t="n">
         <v>1</v>
       </c>
       <c r="T21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Liljekonvalj</t>
+          <t>Bombmurkla</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 26196-2026 artfynd.xlsx", "A 26196-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 25561-2025 artfynd.xlsx", "A 25561-2025")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 26196-2026 karta.png", "A 26196-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 25561-2025 karta.png", "A 25561-2025")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 26196-2026 georefererad karta.tif", "A 26196-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 25561-2025 georefererad karta.tif", "A 25561-2025")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 26196-2026 FSC-klagomål.docx", "A 26196-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 25561-2025 FSC-klagomål.docx", "A 25561-2025")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 26196-2026 FSC-klagomål mail.docx", "A 26196-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 25561-2025 FSC-klagomål mail.docx", "A 25561-2025")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 26196-2026 tillsynsbegäran.docx", "A 26196-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 25561-2025 tillsynsbegäran.docx", "A 25561-2025")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 26196-2026 tillsynsbegäran mail.docx", "A 26196-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 25561-2025 tillsynsbegäran mail.docx", "A 25561-2025")</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 26623-2026</t>
+          <t>A 26637-2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2751,7 +2751,7 @@
         <v>46184</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2764,7 +2764,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>4.6</v>
+        <v>5.4</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2773,10 +2773,10 @@
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N22" t="n">
         <v>0</v>
@@ -2791,7 +2791,7 @@
         <v>1</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S22" t="n">
         <v>1</v>
@@ -2804,42 +2804,42 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>Svartöra</t>
+          <t>Igelkott</t>
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 26623-2026 artfynd.xlsx", "A 26623-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 26637-2026 artfynd.xlsx", "A 26637-2026")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 26623-2026 karta.png", "A 26623-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 26637-2026 karta.png", "A 26637-2026")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 26623-2026 georefererad karta.tif", "A 26623-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 26637-2026 georefererad karta.tif", "A 26637-2026")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 26623-2026 FSC-klagomål.docx", "A 26623-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 26637-2026 FSC-klagomål.docx", "A 26637-2026")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 26623-2026 FSC-klagomål mail.docx", "A 26623-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 26637-2026 FSC-klagomål mail.docx", "A 26637-2026")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 26623-2026 tillsynsbegäran.docx", "A 26623-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 26637-2026 tillsynsbegäran.docx", "A 26637-2026")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 26623-2026 tillsynsbegäran mail.docx", "A 26623-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 26637-2026 tillsynsbegäran mail.docx", "A 26637-2026")</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 26637-2026</t>
+          <t>A 26623-2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2856,7 +2856,7 @@
         <v>46184</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2869,7 +2869,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>5.4</v>
+        <v>4.6</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2878,10 +2878,10 @@
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
         <v>0</v>
@@ -2896,7 +2896,7 @@
         <v>1</v>
       </c>
       <c r="R23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
         <v>1</v>
@@ -2909,35 +2909,35 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Igelkott</t>
+          <t>Svartöra</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 26637-2026 artfynd.xlsx", "A 26637-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 26623-2026 artfynd.xlsx", "A 26623-2026")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 26637-2026 karta.png", "A 26637-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 26623-2026 karta.png", "A 26623-2026")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 26637-2026 georefererad karta.tif", "A 26637-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 26623-2026 georefererad karta.tif", "A 26623-2026")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 26637-2026 FSC-klagomål.docx", "A 26637-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 26623-2026 FSC-klagomål.docx", "A 26623-2026")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 26637-2026 FSC-klagomål mail.docx", "A 26637-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 26623-2026 FSC-klagomål mail.docx", "A 26623-2026")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 26637-2026 tillsynsbegäran.docx", "A 26637-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 26623-2026 tillsynsbegäran.docx", "A 26623-2026")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 26637-2026 tillsynsbegäran mail.docx", "A 26637-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 26623-2026 tillsynsbegäran mail.docx", "A 26623-2026")</f>
         <v/>
       </c>
     </row>
@@ -2961,7 +2961,7 @@
         <v>44558</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3066,7 +3066,7 @@
         <v>44609</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3139,7 +3139,7 @@
         <v>44489</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3217,7 +3217,7 @@
         <v>44546</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3290,7 +3290,7 @@
         <v>44700</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3363,7 +3363,7 @@
         <v>44587</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3419,7 +3419,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 23098-2024</t>
+          <t>A 14719-2022</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3433,10 +3433,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45450</v>
+        <v>44655</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3450,11 +3450,11 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Övriga statliga verk och myndigheter</t>
+          <t>Allmännings- och besparingsskogar</t>
         </is>
       </c>
       <c r="I30" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3497,7 +3497,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 14719-2022</t>
+          <t>A 2602-2024</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3511,10 +3511,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44655</v>
+        <v>45313</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3526,13 +3526,8 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I31" t="n">
-        <v>1.2</v>
+        <v>0.7</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3575,7 +3570,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 7112-2025</t>
+          <t>A 59844-2022</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3589,10 +3584,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45701</v>
+        <v>44901</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3604,8 +3599,13 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I32" t="n">
-        <v>2.4</v>
+        <v>11.9</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3648,7 +3648,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 59844-2022</t>
+          <t>A 64105-2023</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3662,10 +3662,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44901</v>
+        <v>45279</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3677,13 +3677,8 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I33" t="n">
-        <v>11.9</v>
+        <v>2.2</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3726,7 +3721,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 54222-2023</t>
+          <t>A 23093-2024</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3740,10 +3735,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45225</v>
+        <v>45450</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3761,7 +3756,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>8.300000000000001</v>
+        <v>0.9</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3804,7 +3799,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 23615-2025</t>
+          <t>A 3630-2023</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3818,10 +3813,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45792</v>
+        <v>44950</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3834,7 +3829,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3877,7 +3872,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 23627-2025</t>
+          <t>A 54222-2023</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3891,10 +3886,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45792</v>
+        <v>45225</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3906,8 +3901,13 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I36" t="n">
-        <v>1.7</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3950,7 +3950,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 4338-2023</t>
+          <t>A 7860-2024</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3964,10 +3964,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44953</v>
+        <v>45348</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3979,8 +3979,13 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I37" t="n">
-        <v>1.1</v>
+        <v>1.9</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4023,7 +4028,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 58011-2021</t>
+          <t>A 27313-2023</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4037,10 +4042,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44487</v>
+        <v>45096</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4052,13 +4057,8 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I38" t="n">
-        <v>9.199999999999999</v>
+        <v>1.8</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4101,7 +4101,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 72524-2021</t>
+          <t>A 64114-2023</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4115,10 +4115,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44546</v>
+        <v>45279</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4131,7 +4131,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>3.6</v>
+        <v>0.4</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4174,7 +4174,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 64107-2023</t>
+          <t>A 50294-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4188,10 +4188,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45279</v>
+        <v>45216</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4204,7 +4204,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>0.3</v>
+        <v>3.7</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4247,7 +4247,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 23093-2024</t>
+          <t>A 58011-2021</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4261,10 +4261,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45450</v>
+        <v>44487</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4282,7 +4282,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>0.9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4325,7 +4325,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 59700-2021</t>
+          <t>A 18778-2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4339,10 +4339,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44494</v>
+        <v>46128</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4360,7 +4360,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4403,7 +4403,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 27313-2023</t>
+          <t>A 18813-2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4417,10 +4417,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45096</v>
+        <v>46128</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4432,8 +4432,13 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I43" t="n">
-        <v>1.8</v>
+        <v>56</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4476,7 +4481,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 59377-2024</t>
+          <t>A 18818-2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4490,10 +4495,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45638</v>
+        <v>46128</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4505,8 +4510,13 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I44" t="n">
-        <v>0.6</v>
+        <v>17.8</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4549,7 +4559,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 38902-2024</t>
+          <t>A 18787-2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4563,10 +4573,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45547</v>
+        <v>46128</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4584,7 +4594,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.8</v>
+        <v>7.8</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4627,7 +4637,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 50294-2023</t>
+          <t>A 64110-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4641,10 +4651,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45216</v>
+        <v>45279</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4657,7 +4667,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>3.7</v>
+        <v>0.4</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4700,7 +4710,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 21206-2026</t>
+          <t>A 23098-2024</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4714,10 +4724,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>46146</v>
+        <v>45450</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4735,7 +4745,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4778,7 +4788,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 5264-2023</t>
+          <t>A 59377-2024</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4792,10 +4802,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>44959</v>
+        <v>45638</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4808,7 +4818,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>5.8</v>
+        <v>0.6</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4851,7 +4861,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 51587-2023</t>
+          <t>A 59402-2022</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4865,10 +4875,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45215</v>
+        <v>44906</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4880,13 +4890,8 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I49" t="n">
-        <v>2.6</v>
+        <v>1.8</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4929,7 +4934,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 24579-2026</t>
+          <t>A 5264-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4943,10 +4948,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>46170</v>
+        <v>44959</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4959,7 +4964,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>2.1</v>
+        <v>5.8</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5002,7 +5007,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 58598-2025</t>
+          <t>A 9655-2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5016,10 +5021,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45986</v>
+        <v>46070</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5037,7 +5042,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>4.5</v>
+        <v>17.2</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5080,7 +5085,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 59848-2022</t>
+          <t>A 51587-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5094,10 +5099,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>44901</v>
+        <v>45215</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5111,11 +5116,11 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Övriga statliga verk och myndigheter</t>
+          <t>Allmännings- och besparingsskogar</t>
         </is>
       </c>
       <c r="I52" t="n">
-        <v>10.7</v>
+        <v>2.6</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5158,7 +5163,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 31160-2022</t>
+          <t>A 21206-2026</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5172,10 +5177,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>44770</v>
+        <v>46146</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5187,8 +5192,13 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I53" t="n">
-        <v>3.7</v>
+        <v>0.9</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5231,7 +5241,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 64110-2023</t>
+          <t>A 72524-2021</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5245,10 +5255,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45279</v>
+        <v>44546</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5261,7 +5271,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>0.4</v>
+        <v>3.6</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5304,7 +5314,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 26625-2026</t>
+          <t>A 4338-2023</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5318,10 +5328,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>46184</v>
+        <v>44953</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5334,7 +5344,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>5.3</v>
+        <v>1.1</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5377,7 +5387,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 26633-2026</t>
+          <t>A 59848-2022</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5391,10 +5401,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>46184</v>
+        <v>44901</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5406,8 +5416,13 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I56" t="n">
-        <v>0.7</v>
+        <v>10.7</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5450,7 +5465,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 3754-2026</t>
+          <t>A 24579-2026</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5464,10 +5479,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>46043</v>
+        <v>46170</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5479,13 +5494,8 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I57" t="n">
-        <v>5.1</v>
+        <v>2.1</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5528,7 +5538,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 9655-2026</t>
+          <t>A 59700-2021</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5542,10 +5552,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>46070</v>
+        <v>44494</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5563,7 +5573,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>17.2</v>
+        <v>4.8</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5606,7 +5616,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 28797-2026</t>
+          <t>A 31160-2022</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5620,10 +5630,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>46198</v>
+        <v>44770</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5636,7 +5646,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>2.2</v>
+        <v>3.7</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5679,7 +5689,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 28740-2026</t>
+          <t>A 58598-2025</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5693,10 +5703,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>46198</v>
+        <v>45986</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5708,8 +5718,13 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I60" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5752,7 +5767,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 7275-2022</t>
+          <t>A 26633-2026</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5766,10 +5781,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>44606</v>
+        <v>46184</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5781,13 +5796,8 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I61" t="n">
-        <v>9.6</v>
+        <v>0.7</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5830,7 +5840,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 28735-2026</t>
+          <t>A 3754-2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5844,10 +5854,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>46198</v>
+        <v>46043</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5859,8 +5869,13 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I62" t="n">
-        <v>3.5</v>
+        <v>5.1</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5903,7 +5918,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 2602-2024</t>
+          <t>A 28735-2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5917,10 +5932,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45313</v>
+        <v>46198</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5933,7 +5948,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>0.7</v>
+        <v>3.5</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5976,7 +5991,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 59402-2022</t>
+          <t>A 28740-2026</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5990,10 +6005,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>44906</v>
+        <v>46198</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6006,7 +6021,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>1.8</v>
+        <v>4.8</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6049,7 +6064,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 3630-2023</t>
+          <t>A 28797-2026</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6063,10 +6078,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>44950</v>
+        <v>46198</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6079,7 +6094,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>1.4</v>
+        <v>2.2</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6122,7 +6137,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 7860-2024</t>
+          <t>A 7275-2022</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6136,10 +6151,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45348</v>
+        <v>44606</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6157,7 +6172,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>1.9</v>
+        <v>9.6</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6200,7 +6215,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 18787-2026</t>
+          <t>A 31714-2026</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6214,10 +6229,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>46128</v>
+        <v>46226</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6229,13 +6244,8 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I67" t="n">
-        <v>7.8</v>
+        <v>5</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6278,7 +6288,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 18813-2026</t>
+          <t>A 64107-2023</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6292,10 +6302,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>46128</v>
+        <v>45279</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6307,13 +6317,8 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I68" t="n">
-        <v>56</v>
+        <v>0.3</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6356,7 +6361,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 18818-2026</t>
+          <t>A 7112-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6370,10 +6375,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>46128</v>
+        <v>45701</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6385,13 +6390,8 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I69" t="n">
-        <v>17.8</v>
+        <v>2.4</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6434,7 +6434,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 18778-2026</t>
+          <t>A 38902-2024</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6448,10 +6448,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>46128</v>
+        <v>45547</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6469,7 +6469,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>4.5</v>
+        <v>0.8</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6512,7 +6512,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 64105-2023</t>
+          <t>A 23615-2025</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6526,10 +6526,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45279</v>
+        <v>45792</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6542,7 +6542,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>2.2</v>
+        <v>1.3</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6585,7 +6585,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 64114-2023</t>
+          <t>A 23627-2025</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6599,10 +6599,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45279</v>
+        <v>45792</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6615,7 +6615,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>0.4</v>
+        <v>1.7</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6658,7 +6658,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 31714-2026</t>
+          <t>A 33058-2026</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6668,14 +6668,14 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>46226</v>
+        <v>46245</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6688,7 +6688,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>5</v>
+        <v>1.3</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6731,7 +6731,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 33058-2026</t>
+          <t>A 26625-2026</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6741,14 +6741,14 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>46245</v>
+        <v>46184</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6761,7 +6761,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>1.3</v>
+        <v>5.3</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6821,7 +6821,7 @@
         <v>44558</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>

--- a/Översikt UPPLANDS-BRO.xlsx
+++ b/Översikt UPPLANDS-BRO.xlsx
@@ -601,7 +601,7 @@
         <v>44481</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -714,7 +714,7 @@
         <v>44552</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -822,7 +822,7 @@
         <v>44552</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -930,7 +930,7 @@
         <v>45232</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1042,7 +1042,7 @@
         <v>44552</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 18772-2026</t>
+          <t>A 18790-2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1148,7 +1148,7 @@
         <v>46128</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1166,16 +1166,16 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>19.5</v>
+        <v>5.5</v>
       </c>
       <c r="J7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -1190,7 +1190,7 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -1206,147 +1206,147 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
+          <t>Fläcknycklar
+Nattviol</t>
+        </is>
+      </c>
+      <c r="W7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 18790-2026 artfynd.xlsx", "A 18790-2026")</f>
+        <v/>
+      </c>
+      <c r="X7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 18790-2026 karta.png", "A 18790-2026")</f>
+        <v/>
+      </c>
+      <c r="Y7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 18790-2026 georefererad karta.tif", "A 18790-2026")</f>
+        <v/>
+      </c>
+      <c r="AA7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 18790-2026 FSC-klagomål.docx", "A 18790-2026")</f>
+        <v/>
+      </c>
+      <c r="AB7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 18790-2026 FSC-klagomål mail.docx", "A 18790-2026")</f>
+        <v/>
+      </c>
+      <c r="AC7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 18790-2026 tillsynsbegäran.docx", "A 18790-2026")</f>
+        <v/>
+      </c>
+      <c r="AD7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 18790-2026 tillsynsbegäran mail.docx", "A 18790-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="15" customHeight="1">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>A 18772-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D8" s="1" t="n">
+        <v>46128</v>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>46305</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>UPPLANDS-BRO</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="J8" t="n">
+        <v>1</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>2</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
           <t>Svedjenäva
 Fläcknycklar</t>
         </is>
       </c>
-      <c r="W7">
+      <c r="W8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 18772-2026 artfynd.xlsx", "A 18772-2026")</f>
         <v/>
       </c>
-      <c r="X7">
+      <c r="X8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 18772-2026 karta.png", "A 18772-2026")</f>
         <v/>
       </c>
-      <c r="Y7">
+      <c r="Y8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 18772-2026 georefererad karta.tif", "A 18772-2026")</f>
         <v/>
       </c>
-      <c r="AA7">
+      <c r="AA8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 18772-2026 FSC-klagomål.docx", "A 18772-2026")</f>
         <v/>
       </c>
-      <c r="AB7">
+      <c r="AB8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 18772-2026 FSC-klagomål mail.docx", "A 18772-2026")</f>
         <v/>
       </c>
-      <c r="AC7">
+      <c r="AC8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 18772-2026 tillsynsbegäran.docx", "A 18772-2026")</f>
         <v/>
       </c>
-      <c r="AD7">
+      <c r="AD8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 18772-2026 tillsynsbegäran mail.docx", "A 18772-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8" ht="15" customHeight="1">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>A 18790-2026</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D8" s="1" t="n">
-        <v>46128</v>
-      </c>
-      <c r="E8" s="1" t="n">
-        <v>46304</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>UPPLANDS-BRO</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
-      <c r="I8" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="J8" t="n">
-        <v>2</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" t="n">
-        <v>2</v>
-      </c>
-      <c r="T8" t="n">
-        <v>2</v>
-      </c>
-      <c r="U8" t="n">
-        <v>0</v>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>Fläcknycklar
-Nattviol</t>
-        </is>
-      </c>
-      <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 18790-2026 artfynd.xlsx", "A 18790-2026")</f>
-        <v/>
-      </c>
-      <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 18790-2026 karta.png", "A 18790-2026")</f>
-        <v/>
-      </c>
-      <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 18790-2026 georefererad karta.tif", "A 18790-2026")</f>
-        <v/>
-      </c>
-      <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 18790-2026 FSC-klagomål.docx", "A 18790-2026")</f>
-        <v/>
-      </c>
-      <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 18790-2026 FSC-klagomål mail.docx", "A 18790-2026")</f>
-        <v/>
-      </c>
-      <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 18790-2026 tillsynsbegäran.docx", "A 18790-2026")</f>
-        <v/>
-      </c>
-      <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 18790-2026 tillsynsbegäran mail.docx", "A 18790-2026")</f>
         <v/>
       </c>
     </row>
@@ -1370,7 +1370,7 @@
         <v>45722</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1481,7 +1481,7 @@
         <v>44603</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1587,7 +1587,7 @@
         <v>44552</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1675,7 +1675,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 12363-2025</t>
+          <t>A 64098-2023</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1689,10 +1689,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45730</v>
+        <v>45279</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1705,16 +1705,16 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>0.8</v>
+        <v>0.3</v>
       </c>
       <c r="J12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
@@ -1729,7 +1729,7 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -1745,42 +1745,42 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Skogsalmsdvärgmal</t>
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 12363-2025 artfynd.xlsx", "A 12363-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 64098-2023 artfynd.xlsx", "A 64098-2023")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 12363-2025 karta.png", "A 12363-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 64098-2023 karta.png", "A 64098-2023")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 12363-2025 georefererad karta.tif", "A 12363-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 64098-2023 georefererad karta.tif", "A 64098-2023")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 12363-2025 FSC-klagomål.docx", "A 12363-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 64098-2023 FSC-klagomål.docx", "A 64098-2023")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 12363-2025 FSC-klagomål mail.docx", "A 12363-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 64098-2023 FSC-klagomål mail.docx", "A 64098-2023")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 12363-2025 tillsynsbegäran.docx", "A 12363-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 64098-2023 tillsynsbegäran.docx", "A 64098-2023")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 12363-2025 tillsynsbegäran mail.docx", "A 12363-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 64098-2023 tillsynsbegäran mail.docx", "A 64098-2023")</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 53357-2025</t>
+          <t>A 7955-2023</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1794,10 +1794,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45959</v>
+        <v>44973</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1810,7 +1810,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>2.4</v>
+        <v>2.9</v>
       </c>
       <c r="J13" t="n">
         <v>1</v>
@@ -1843,10 +1843,10 @@
         <v>1</v>
       </c>
       <c r="T13" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
@@ -1854,38 +1854,38 @@
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 53357-2025 artfynd.xlsx", "A 53357-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 7955-2023 artfynd.xlsx", "A 7955-2023")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 53357-2025 karta.png", "A 53357-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 7955-2023 karta.png", "A 7955-2023")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 53357-2025 georefererad karta.tif", "A 53357-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 7955-2023 georefererad karta.tif", "A 7955-2023")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 53357-2025 FSC-klagomål.docx", "A 53357-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 7955-2023 FSC-klagomål.docx", "A 7955-2023")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 53357-2025 FSC-klagomål mail.docx", "A 53357-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 7955-2023 FSC-klagomål mail.docx", "A 7955-2023")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 53357-2025 tillsynsbegäran.docx", "A 53357-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 7955-2023 tillsynsbegäran.docx", "A 7955-2023")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 53357-2025 tillsynsbegäran mail.docx", "A 53357-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 7955-2023 tillsynsbegäran mail.docx", "A 7955-2023")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 23099-2024</t>
+          <t>A 12363-2025</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1899,10 +1899,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45450</v>
+        <v>45730</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1914,25 +1914,20 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I14" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -1944,10 +1939,10 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
@@ -1956,46 +1951,46 @@
         <v>1</v>
       </c>
       <c r="U14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Bredbrämad bastardsvärmare</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 23099-2024 artfynd.xlsx", "A 23099-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 12363-2025 artfynd.xlsx", "A 12363-2025")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 23099-2024 karta.png", "A 23099-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 12363-2025 karta.png", "A 12363-2025")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 23099-2024 georefererad karta.tif", "A 23099-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 12363-2025 georefererad karta.tif", "A 12363-2025")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 23099-2024 FSC-klagomål.docx", "A 23099-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 12363-2025 FSC-klagomål.docx", "A 12363-2025")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 23099-2024 FSC-klagomål mail.docx", "A 23099-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 12363-2025 FSC-klagomål mail.docx", "A 12363-2025")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 23099-2024 tillsynsbegäran.docx", "A 23099-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 12363-2025 tillsynsbegäran.docx", "A 12363-2025")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 23099-2024 tillsynsbegäran mail.docx", "A 23099-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 12363-2025 tillsynsbegäran mail.docx", "A 12363-2025")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 46438-2023</t>
+          <t>A 2062-2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2009,10 +2004,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45197</v>
+        <v>45671</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2025,7 +2020,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>0.5</v>
+        <v>1.9</v>
       </c>
       <c r="J15" t="n">
         <v>1</v>
@@ -2034,13 +2029,13 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M15" t="n">
         <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2052,7 +2047,7 @@
         <v>1</v>
       </c>
       <c r="R15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
         <v>1</v>
@@ -2061,46 +2056,50 @@
         <v>1</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Bombmurkla</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 46438-2023 artfynd.xlsx", "A 46438-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 2062-2025 artfynd.xlsx", "A 2062-2025")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 46438-2023 karta.png", "A 46438-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 2062-2025 karta.png", "A 2062-2025")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 46438-2023 georefererad karta.tif", "A 46438-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 2062-2025 georefererad karta.tif", "A 2062-2025")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 46438-2023 FSC-klagomål.docx", "A 46438-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 2062-2025 FSC-klagomål.docx", "A 2062-2025")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 46438-2023 FSC-klagomål mail.docx", "A 46438-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 2062-2025 FSC-klagomål mail.docx", "A 2062-2025")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 46438-2023 tillsynsbegäran.docx", "A 46438-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 2062-2025 tillsynsbegäran.docx", "A 2062-2025")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 46438-2023 tillsynsbegäran mail.docx", "A 46438-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 2062-2025 tillsynsbegäran mail.docx", "A 2062-2025")</f>
+        <v/>
+      </c>
+      <c r="AE15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/fåglar/A 2062-2025 prioriterade fågelarter.docx", "A 2062-2025")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 11447-2025</t>
+          <t>A 46438-2023</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2110,14 +2109,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45726</v>
+        <v>45197</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2130,13 +2129,13 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -2145,7 +2144,7 @@
         <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2154,10 +2153,10 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
@@ -2170,42 +2169,42 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Myskbock</t>
+          <t>Bombmurkla</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 11447-2025 artfynd.xlsx", "A 11447-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 46438-2023 artfynd.xlsx", "A 46438-2023")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 11447-2025 karta.png", "A 11447-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 46438-2023 karta.png", "A 46438-2023")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 11447-2025 georefererad karta.tif", "A 11447-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 46438-2023 georefererad karta.tif", "A 46438-2023")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 11447-2025 FSC-klagomål.docx", "A 11447-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 46438-2023 FSC-klagomål.docx", "A 46438-2023")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 11447-2025 FSC-klagomål mail.docx", "A 11447-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 46438-2023 FSC-klagomål mail.docx", "A 46438-2023")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 11447-2025 tillsynsbegäran.docx", "A 11447-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 46438-2023 tillsynsbegäran.docx", "A 46438-2023")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 11447-2025 tillsynsbegäran mail.docx", "A 11447-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 46438-2023 tillsynsbegäran mail.docx", "A 46438-2023")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 7955-2023</t>
+          <t>A 25561-2025</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2219,10 +2218,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>44973</v>
+        <v>45803</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2235,7 +2234,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>2.9</v>
+        <v>1.6</v>
       </c>
       <c r="J17" t="n">
         <v>1</v>
@@ -2271,7 +2270,7 @@
         <v>1</v>
       </c>
       <c r="U17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
@@ -2279,38 +2278,38 @@
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 7955-2023 artfynd.xlsx", "A 7955-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 25561-2025 artfynd.xlsx", "A 25561-2025")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 7955-2023 karta.png", "A 7955-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 25561-2025 karta.png", "A 25561-2025")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 7955-2023 georefererad karta.tif", "A 7955-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 25561-2025 georefererad karta.tif", "A 25561-2025")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 7955-2023 FSC-klagomål.docx", "A 7955-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 25561-2025 FSC-klagomål.docx", "A 25561-2025")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 7955-2023 FSC-klagomål mail.docx", "A 7955-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 25561-2025 FSC-klagomål mail.docx", "A 25561-2025")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 7955-2023 tillsynsbegäran.docx", "A 7955-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 25561-2025 tillsynsbegäran.docx", "A 25561-2025")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 7955-2023 tillsynsbegäran mail.docx", "A 7955-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 25561-2025 tillsynsbegäran mail.docx", "A 25561-2025")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 26196-2026</t>
+          <t>A 53357-2025</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2320,14 +2319,14 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46182</v>
+        <v>45959</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2340,10 +2339,10 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>53.1</v>
+        <v>2.4</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
@@ -2355,7 +2354,7 @@
         <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2364,58 +2363,58 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
       </c>
       <c r="T18" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="U18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Liljekonvalj</t>
+          <t>Bombmurkla</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 26196-2026 artfynd.xlsx", "A 26196-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 53357-2025 artfynd.xlsx", "A 53357-2025")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 26196-2026 karta.png", "A 26196-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 53357-2025 karta.png", "A 53357-2025")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 26196-2026 georefererad karta.tif", "A 26196-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 53357-2025 georefererad karta.tif", "A 53357-2025")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 26196-2026 FSC-klagomål.docx", "A 26196-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 53357-2025 FSC-klagomål.docx", "A 53357-2025")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 26196-2026 FSC-klagomål mail.docx", "A 26196-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 53357-2025 FSC-klagomål mail.docx", "A 53357-2025")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 26196-2026 tillsynsbegäran.docx", "A 26196-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 53357-2025 tillsynsbegäran.docx", "A 53357-2025")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 26196-2026 tillsynsbegäran mail.docx", "A 26196-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 53357-2025 tillsynsbegäran mail.docx", "A 53357-2025")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 64098-2023</t>
+          <t>A 11447-2025</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2425,14 +2424,14 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45279</v>
+        <v>45726</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2445,16 +2444,16 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>0.3</v>
+        <v>1.5</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
         <v>0</v>
@@ -2469,7 +2468,7 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
@@ -2485,42 +2484,42 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Skogsalmsdvärgmal</t>
+          <t>Myskbock</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 64098-2023 artfynd.xlsx", "A 64098-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 11447-2025 artfynd.xlsx", "A 11447-2025")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 64098-2023 karta.png", "A 64098-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 11447-2025 karta.png", "A 11447-2025")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 64098-2023 georefererad karta.tif", "A 64098-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 11447-2025 georefererad karta.tif", "A 11447-2025")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 64098-2023 FSC-klagomål.docx", "A 64098-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 11447-2025 FSC-klagomål.docx", "A 11447-2025")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 64098-2023 FSC-klagomål mail.docx", "A 64098-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 11447-2025 FSC-klagomål mail.docx", "A 11447-2025")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 64098-2023 tillsynsbegäran.docx", "A 64098-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 11447-2025 tillsynsbegäran.docx", "A 11447-2025")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 64098-2023 tillsynsbegäran mail.docx", "A 64098-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 11447-2025 tillsynsbegäran mail.docx", "A 11447-2025")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 2062-2025</t>
+          <t>A 23099-2024</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2534,10 +2533,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45671</v>
+        <v>45450</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2549,20 +2548,25 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I20" t="n">
-        <v>1.9</v>
+        <v>0.7</v>
       </c>
       <c r="J20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N20" t="n">
         <v>0</v>
@@ -2577,7 +2581,7 @@
         <v>1</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>
@@ -2590,46 +2594,42 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Bredbrämad bastardsvärmare</t>
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 2062-2025 artfynd.xlsx", "A 2062-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 23099-2024 artfynd.xlsx", "A 23099-2024")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 2062-2025 karta.png", "A 2062-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 23099-2024 karta.png", "A 23099-2024")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 2062-2025 georefererad karta.tif", "A 2062-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 23099-2024 georefererad karta.tif", "A 23099-2024")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 2062-2025 FSC-klagomål.docx", "A 2062-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 23099-2024 FSC-klagomål.docx", "A 23099-2024")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 2062-2025 FSC-klagomål mail.docx", "A 2062-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 23099-2024 FSC-klagomål mail.docx", "A 23099-2024")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 2062-2025 tillsynsbegäran.docx", "A 2062-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 23099-2024 tillsynsbegäran.docx", "A 23099-2024")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 2062-2025 tillsynsbegäran mail.docx", "A 2062-2025")</f>
-        <v/>
-      </c>
-      <c r="AE20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/fåglar/A 2062-2025 prioriterade fågelarter.docx", "A 2062-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 23099-2024 tillsynsbegäran mail.docx", "A 23099-2024")</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 25561-2025</t>
+          <t>A 26196-2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2639,14 +2639,14 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45803</v>
+        <v>46182</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2659,10 +2659,10 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>1.6</v>
+        <v>53.1</v>
       </c>
       <c r="J21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
@@ -2674,7 +2674,7 @@
         <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2683,51 +2683,51 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
         <v>1</v>
       </c>
       <c r="T21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Bombmurkla</t>
+          <t>Liljekonvalj</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 25561-2025 artfynd.xlsx", "A 25561-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 26196-2026 artfynd.xlsx", "A 26196-2026")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 25561-2025 karta.png", "A 25561-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 26196-2026 karta.png", "A 26196-2026")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 25561-2025 georefererad karta.tif", "A 25561-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 26196-2026 georefererad karta.tif", "A 26196-2026")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 25561-2025 FSC-klagomål.docx", "A 25561-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 26196-2026 FSC-klagomål.docx", "A 26196-2026")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 25561-2025 FSC-klagomål mail.docx", "A 25561-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 26196-2026 FSC-klagomål mail.docx", "A 26196-2026")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 25561-2025 tillsynsbegäran.docx", "A 25561-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 26196-2026 tillsynsbegäran.docx", "A 26196-2026")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 25561-2025 tillsynsbegäran mail.docx", "A 25561-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 26196-2026 tillsynsbegäran mail.docx", "A 26196-2026")</f>
         <v/>
       </c>
     </row>
@@ -2751,7 +2751,7 @@
         <v>46184</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2856,7 +2856,7 @@
         <v>46184</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2961,7 +2961,7 @@
         <v>44558</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3066,7 +3066,7 @@
         <v>44609</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3139,7 +3139,7 @@
         <v>44489</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3217,7 +3217,7 @@
         <v>44546</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3290,7 +3290,7 @@
         <v>44700</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3363,7 +3363,7 @@
         <v>44587</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3436,7 +3436,7 @@
         <v>44655</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3497,7 +3497,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 2602-2024</t>
+          <t>A 54222-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3511,10 +3511,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45313</v>
+        <v>45225</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3526,8 +3526,13 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I31" t="n">
-        <v>0.7</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3570,7 +3575,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 59844-2022</t>
+          <t>A 64105-2023</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3584,10 +3589,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44901</v>
+        <v>45279</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3599,13 +3604,8 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I32" t="n">
-        <v>11.9</v>
+        <v>2.2</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3648,7 +3648,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 64105-2023</t>
+          <t>A 4338-2023</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3662,10 +3662,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45279</v>
+        <v>44953</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3678,7 +3678,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>2.2</v>
+        <v>1.1</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3721,7 +3721,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 23093-2024</t>
+          <t>A 58011-2021</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3735,10 +3735,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45450</v>
+        <v>44487</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3756,7 +3756,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>0.9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3799,7 +3799,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 3630-2023</t>
+          <t>A 72524-2021</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3813,10 +3813,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44950</v>
+        <v>44546</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3829,7 +3829,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>1.4</v>
+        <v>3.6</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3872,7 +3872,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 54222-2023</t>
+          <t>A 64114-2023</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3886,10 +3886,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45225</v>
+        <v>45279</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3901,13 +3901,8 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I36" t="n">
-        <v>8.300000000000001</v>
+        <v>0.4</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3950,7 +3945,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 7860-2024</t>
+          <t>A 64107-2023</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3964,10 +3959,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45348</v>
+        <v>45279</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3979,13 +3974,8 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I37" t="n">
-        <v>1.9</v>
+        <v>0.3</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4028,7 +4018,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 27313-2023</t>
+          <t>A 23093-2024</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4042,10 +4032,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45096</v>
+        <v>45450</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4057,8 +4047,13 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I38" t="n">
-        <v>1.8</v>
+        <v>0.9</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4101,7 +4096,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 64114-2023</t>
+          <t>A 59700-2021</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4115,10 +4110,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45279</v>
+        <v>44494</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4130,8 +4125,13 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I39" t="n">
-        <v>0.4</v>
+        <v>4.8</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4174,7 +4174,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 50294-2023</t>
+          <t>A 7112-2025</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4188,10 +4188,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45216</v>
+        <v>45701</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4204,7 +4204,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>3.7</v>
+        <v>2.4</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4247,7 +4247,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 58011-2021</t>
+          <t>A 27313-2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4261,10 +4261,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44487</v>
+        <v>45096</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4276,13 +4276,8 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I41" t="n">
-        <v>9.199999999999999</v>
+        <v>1.8</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4325,7 +4320,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 18778-2026</t>
+          <t>A 59377-2024</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4339,10 +4334,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>46128</v>
+        <v>45638</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4354,13 +4349,8 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I42" t="n">
-        <v>4.5</v>
+        <v>0.6</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4403,7 +4393,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 18813-2026</t>
+          <t>A 38902-2024</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4417,10 +4407,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>46128</v>
+        <v>45547</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4438,7 +4428,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>56</v>
+        <v>0.8</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4481,7 +4471,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 18818-2026</t>
+          <t>A 50294-2023</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4495,10 +4485,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>46128</v>
+        <v>45216</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4510,13 +4500,8 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I44" t="n">
-        <v>17.8</v>
+        <v>3.7</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4559,7 +4544,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 18787-2026</t>
+          <t>A 23615-2025</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4573,10 +4558,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>46128</v>
+        <v>45792</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4588,13 +4573,8 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I45" t="n">
-        <v>7.8</v>
+        <v>1.3</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4637,7 +4617,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 64110-2023</t>
+          <t>A 23627-2025</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4651,10 +4631,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45279</v>
+        <v>45792</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4667,7 +4647,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>0.4</v>
+        <v>1.7</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4710,7 +4690,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 23098-2024</t>
+          <t>A 5264-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4724,10 +4704,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45450</v>
+        <v>44959</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4739,13 +4719,8 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I47" t="n">
-        <v>1</v>
+        <v>5.8</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4788,7 +4763,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 59377-2024</t>
+          <t>A 51587-2023</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4802,10 +4777,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45638</v>
+        <v>45215</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4817,8 +4792,13 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I48" t="n">
-        <v>0.6</v>
+        <v>2.6</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4861,7 +4841,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 59402-2022</t>
+          <t>A 23098-2024</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4875,10 +4855,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>44906</v>
+        <v>45450</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4890,8 +4870,13 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I49" t="n">
-        <v>1.8</v>
+        <v>1</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4934,7 +4919,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 5264-2023</t>
+          <t>A 59848-2022</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4948,10 +4933,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>44959</v>
+        <v>44901</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4963,8 +4948,13 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I50" t="n">
-        <v>5.8</v>
+        <v>10.7</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5007,7 +4997,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 9655-2026</t>
+          <t>A 64110-2023</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5021,10 +5011,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>46070</v>
+        <v>45279</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5036,13 +5026,8 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I51" t="n">
-        <v>17.2</v>
+        <v>0.4</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5085,7 +5070,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 51587-2023</t>
+          <t>A 59844-2022</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5099,10 +5084,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45215</v>
+        <v>44901</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5116,11 +5101,11 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Allmännings- och besparingsskogar</t>
+          <t>Övriga statliga verk och myndigheter</t>
         </is>
       </c>
       <c r="I52" t="n">
-        <v>2.6</v>
+        <v>11.9</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5163,7 +5148,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 21206-2026</t>
+          <t>A 18787-2026</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5177,10 +5162,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>46146</v>
+        <v>46128</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5198,7 +5183,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>0.9</v>
+        <v>7.8</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5241,7 +5226,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 72524-2021</t>
+          <t>A 18813-2026</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5255,10 +5240,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>44546</v>
+        <v>46128</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5270,8 +5255,13 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I54" t="n">
-        <v>3.6</v>
+        <v>56</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5314,7 +5304,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 4338-2023</t>
+          <t>A 18818-2026</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5328,10 +5318,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44953</v>
+        <v>46128</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5343,8 +5333,13 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I55" t="n">
-        <v>1.1</v>
+        <v>17.8</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5387,7 +5382,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 59848-2022</t>
+          <t>A 18778-2026</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5401,10 +5396,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>44901</v>
+        <v>46128</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5422,7 +5417,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>10.7</v>
+        <v>4.5</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5465,7 +5460,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 24579-2026</t>
+          <t>A 7275-2022</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5479,10 +5474,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>46170</v>
+        <v>44606</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5494,8 +5489,13 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I57" t="n">
-        <v>2.1</v>
+        <v>9.6</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5538,7 +5538,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 59700-2021</t>
+          <t>A 2602-2024</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5552,10 +5552,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>44494</v>
+        <v>45313</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5567,13 +5567,8 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I58" t="n">
-        <v>4.8</v>
+        <v>0.7</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5616,7 +5611,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 31160-2022</t>
+          <t>A 59402-2022</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5630,10 +5625,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>44770</v>
+        <v>44906</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5646,7 +5641,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>3.7</v>
+        <v>1.8</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5689,7 +5684,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 58598-2025</t>
+          <t>A 3630-2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5703,10 +5698,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45986</v>
+        <v>44950</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5718,13 +5713,8 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I60" t="n">
-        <v>4.5</v>
+        <v>1.4</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5767,7 +5757,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 26633-2026</t>
+          <t>A 7860-2024</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5781,10 +5771,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>46184</v>
+        <v>45348</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5796,8 +5786,13 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I61" t="n">
-        <v>0.7</v>
+        <v>1.9</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5840,7 +5835,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 3754-2026</t>
+          <t>A 21206-2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5854,10 +5849,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>46043</v>
+        <v>46146</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5875,7 +5870,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>5.1</v>
+        <v>0.9</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5918,7 +5913,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 28735-2026</t>
+          <t>A 9655-2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5932,10 +5927,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>46198</v>
+        <v>46070</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5947,8 +5942,13 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I63" t="n">
-        <v>3.5</v>
+        <v>17.2</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5991,7 +5991,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 28740-2026</t>
+          <t>A 24579-2026</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6005,10 +6005,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>46198</v>
+        <v>46170</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6021,7 +6021,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>4.8</v>
+        <v>2.1</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6064,7 +6064,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 28797-2026</t>
+          <t>A 58598-2025</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6078,10 +6078,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>46198</v>
+        <v>45986</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6093,8 +6093,13 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I65" t="n">
-        <v>2.2</v>
+        <v>4.5</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6137,7 +6142,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 7275-2022</t>
+          <t>A 31160-2022</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6151,10 +6156,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>44606</v>
+        <v>44770</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6166,13 +6171,8 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I66" t="n">
-        <v>9.6</v>
+        <v>3.7</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6215,7 +6215,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 31714-2026</t>
+          <t>A 26633-2026</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6229,10 +6229,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>46226</v>
+        <v>46184</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>5</v>
+        <v>0.7</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6288,7 +6288,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 64107-2023</t>
+          <t>A 3754-2026</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6302,10 +6302,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45279</v>
+        <v>46043</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6317,8 +6317,13 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I68" t="n">
-        <v>0.3</v>
+        <v>5.1</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6361,7 +6366,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 7112-2025</t>
+          <t>A 28797-2026</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6375,10 +6380,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45701</v>
+        <v>46198</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6391,7 +6396,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6434,7 +6439,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 38902-2024</t>
+          <t>A 28740-2026</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6448,10 +6453,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45547</v>
+        <v>46198</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6463,13 +6468,8 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I70" t="n">
-        <v>0.8</v>
+        <v>4.8</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6512,7 +6512,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 23615-2025</t>
+          <t>A 28735-2026</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6526,10 +6526,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45792</v>
+        <v>46198</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6542,7 +6542,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>1.3</v>
+        <v>3.5</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6585,7 +6585,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 23627-2025</t>
+          <t>A 31714-2026</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6599,10 +6599,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45792</v>
+        <v>46226</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6615,7 +6615,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>1.7</v>
+        <v>5</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6675,7 +6675,7 @@
         <v>46245</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6748,7 +6748,7 @@
         <v>46184</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6821,7 +6821,7 @@
         <v>44558</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>

--- a/Översikt UPPLANDS-BRO.xlsx
+++ b/Översikt UPPLANDS-BRO.xlsx
@@ -601,7 +601,7 @@
         <v>44481</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -714,7 +714,7 @@
         <v>44552</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -822,7 +822,7 @@
         <v>44552</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -930,7 +930,7 @@
         <v>45232</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1042,7 +1042,7 @@
         <v>44552</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1148,7 +1148,7 @@
         <v>46128</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1259,7 +1259,7 @@
         <v>46128</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1370,7 +1370,7 @@
         <v>45722</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1481,7 +1481,7 @@
         <v>44603</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1587,7 +1587,7 @@
         <v>44552</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1692,7 +1692,7 @@
         <v>45279</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1797,7 +1797,7 @@
         <v>44973</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1902,7 +1902,7 @@
         <v>45730</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2007,7 +2007,7 @@
         <v>45671</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2116,7 +2116,7 @@
         <v>45197</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2221,7 +2221,7 @@
         <v>45803</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2326,7 +2326,7 @@
         <v>45959</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2431,7 +2431,7 @@
         <v>45726</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2536,7 +2536,7 @@
         <v>45450</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2646,7 +2646,7 @@
         <v>46182</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2751,7 +2751,7 @@
         <v>46184</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2856,7 +2856,7 @@
         <v>46184</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2961,7 +2961,7 @@
         <v>44558</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3066,7 +3066,7 @@
         <v>44609</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3139,7 +3139,7 @@
         <v>44489</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3217,7 +3217,7 @@
         <v>44546</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3290,7 +3290,7 @@
         <v>44700</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3363,7 +3363,7 @@
         <v>44587</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3436,7 +3436,7 @@
         <v>44655</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3514,7 +3514,7 @@
         <v>45225</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3592,7 +3592,7 @@
         <v>45279</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3665,7 +3665,7 @@
         <v>44953</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
         <v>44487</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3816,7 +3816,7 @@
         <v>44546</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3889,7 +3889,7 @@
         <v>45279</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3962,7 +3962,7 @@
         <v>45279</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4035,7 +4035,7 @@
         <v>45450</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4113,7 +4113,7 @@
         <v>44494</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4191,7 +4191,7 @@
         <v>45701</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4264,7 +4264,7 @@
         <v>45096</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4337,7 +4337,7 @@
         <v>45638</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4410,7 +4410,7 @@
         <v>45547</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4488,7 +4488,7 @@
         <v>45216</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4561,7 +4561,7 @@
         <v>45792</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4634,7 +4634,7 @@
         <v>45792</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4707,7 +4707,7 @@
         <v>44959</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4780,7 +4780,7 @@
         <v>45215</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4858,7 +4858,7 @@
         <v>45450</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4936,7 +4936,7 @@
         <v>44901</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5014,7 +5014,7 @@
         <v>45279</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5087,7 +5087,7 @@
         <v>44901</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5165,7 +5165,7 @@
         <v>46128</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5243,7 +5243,7 @@
         <v>46128</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5321,7 +5321,7 @@
         <v>46128</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5399,7 +5399,7 @@
         <v>46128</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5477,7 +5477,7 @@
         <v>44606</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5555,7 +5555,7 @@
         <v>45313</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5628,7 +5628,7 @@
         <v>44906</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5701,7 +5701,7 @@
         <v>44950</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5774,7 +5774,7 @@
         <v>45348</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5852,7 +5852,7 @@
         <v>46146</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5930,7 +5930,7 @@
         <v>46070</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6008,7 +6008,7 @@
         <v>46170</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6081,7 +6081,7 @@
         <v>45986</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6159,7 +6159,7 @@
         <v>44770</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6232,7 +6232,7 @@
         <v>46184</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6305,7 +6305,7 @@
         <v>46043</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6383,7 +6383,7 @@
         <v>46198</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6456,7 +6456,7 @@
         <v>46198</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6529,7 +6529,7 @@
         <v>46198</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6602,7 +6602,7 @@
         <v>46226</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6675,7 +6675,7 @@
         <v>46245</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6748,7 +6748,7 @@
         <v>46184</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6821,7 +6821,7 @@
         <v>44558</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>

--- a/Översikt UPPLANDS-BRO.xlsx
+++ b/Översikt UPPLANDS-BRO.xlsx
@@ -601,7 +601,7 @@
         <v>44481</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -714,7 +714,7 @@
         <v>44552</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -822,7 +822,7 @@
         <v>44552</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -930,7 +930,7 @@
         <v>45232</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1042,7 +1042,7 @@
         <v>44552</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1148,7 +1148,7 @@
         <v>46128</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1259,7 +1259,7 @@
         <v>46128</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1370,7 +1370,7 @@
         <v>45722</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1481,7 +1481,7 @@
         <v>44603</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1587,7 +1587,7 @@
         <v>44552</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1692,7 +1692,7 @@
         <v>45279</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1797,7 +1797,7 @@
         <v>44973</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1902,7 +1902,7 @@
         <v>45730</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2007,7 +2007,7 @@
         <v>45671</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2116,7 +2116,7 @@
         <v>45197</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2221,7 +2221,7 @@
         <v>45803</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2326,7 +2326,7 @@
         <v>45959</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2431,7 +2431,7 @@
         <v>45726</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2536,7 +2536,7 @@
         <v>45450</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2646,7 +2646,7 @@
         <v>46182</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2751,7 +2751,7 @@
         <v>46184</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2856,7 +2856,7 @@
         <v>46184</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2961,7 +2961,7 @@
         <v>44558</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3066,7 +3066,7 @@
         <v>44609</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3139,7 +3139,7 @@
         <v>44489</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3217,7 +3217,7 @@
         <v>44546</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3290,7 +3290,7 @@
         <v>44700</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3363,7 +3363,7 @@
         <v>44587</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3436,7 +3436,7 @@
         <v>44655</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3514,7 +3514,7 @@
         <v>45225</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3592,7 +3592,7 @@
         <v>45279</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3665,7 +3665,7 @@
         <v>44953</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
         <v>44487</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3816,7 +3816,7 @@
         <v>44546</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3889,7 +3889,7 @@
         <v>45279</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3962,7 +3962,7 @@
         <v>45279</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4035,7 +4035,7 @@
         <v>45450</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4113,7 +4113,7 @@
         <v>44494</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4191,7 +4191,7 @@
         <v>45701</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4264,7 +4264,7 @@
         <v>45096</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4337,7 +4337,7 @@
         <v>45638</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4410,7 +4410,7 @@
         <v>45547</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4488,7 +4488,7 @@
         <v>45216</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4561,7 +4561,7 @@
         <v>45792</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4634,7 +4634,7 @@
         <v>45792</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4707,7 +4707,7 @@
         <v>44959</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4780,7 +4780,7 @@
         <v>45215</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4858,7 +4858,7 @@
         <v>45450</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4936,7 +4936,7 @@
         <v>44901</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5014,7 +5014,7 @@
         <v>45279</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5087,7 +5087,7 @@
         <v>44901</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5165,7 +5165,7 @@
         <v>46128</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5243,7 +5243,7 @@
         <v>46128</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5321,7 +5321,7 @@
         <v>46128</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5399,7 +5399,7 @@
         <v>46128</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5477,7 +5477,7 @@
         <v>44606</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5555,7 +5555,7 @@
         <v>45313</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5628,7 +5628,7 @@
         <v>44906</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5701,7 +5701,7 @@
         <v>44950</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5774,7 +5774,7 @@
         <v>45348</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5852,7 +5852,7 @@
         <v>46146</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5930,7 +5930,7 @@
         <v>46070</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6008,7 +6008,7 @@
         <v>46170</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6081,7 +6081,7 @@
         <v>45986</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6159,7 +6159,7 @@
         <v>44770</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6232,7 +6232,7 @@
         <v>46184</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6305,7 +6305,7 @@
         <v>46043</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6383,7 +6383,7 @@
         <v>46198</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6456,7 +6456,7 @@
         <v>46198</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6529,7 +6529,7 @@
         <v>46198</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6602,7 +6602,7 @@
         <v>46226</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6675,7 +6675,7 @@
         <v>46245</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6748,7 +6748,7 @@
         <v>46184</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6821,7 +6821,7 @@
         <v>44558</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>

--- a/Översikt UPPLANDS-BRO.xlsx
+++ b/Översikt UPPLANDS-BRO.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE75"/>
+  <dimension ref="A1:AE74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -584,7 +584,7 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A 56756-2021</t>
+          <t>A 73783-2021</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>44481</v>
+        <v>44552</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -614,16 +614,16 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>1.1</v>
+        <v>5.9</v>
       </c>
       <c r="J2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M2" t="n">
         <v>0</v>
@@ -638,134 +638,21 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V2" s="2" t="inlineStr">
-        <is>
-          <t>Entita
-Spillkråka
-Tallbit
-Grönsiska
-Kungsfågel</t>
-        </is>
-      </c>
-      <c r="W2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 56756-2021 artfynd.xlsx", "A 56756-2021")</f>
-        <v/>
-      </c>
-      <c r="X2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 56756-2021 karta.png", "A 56756-2021")</f>
-        <v/>
-      </c>
-      <c r="Y2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 56756-2021 georefererad karta.tif", "A 56756-2021")</f>
-        <v/>
-      </c>
-      <c r="AA2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 56756-2021 FSC-klagomål.docx", "A 56756-2021")</f>
-        <v/>
-      </c>
-      <c r="AB2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 56756-2021 FSC-klagomål mail.docx", "A 56756-2021")</f>
-        <v/>
-      </c>
-      <c r="AC2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 56756-2021 tillsynsbegäran.docx", "A 56756-2021")</f>
-        <v/>
-      </c>
-      <c r="AD2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 56756-2021 tillsynsbegäran mail.docx", "A 56756-2021")</f>
-        <v/>
-      </c>
-      <c r="AE2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/fåglar/A 56756-2021 prioriterade fågelarter.docx", "A 56756-2021")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="3" ht="15" customHeight="1">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>A 73783-2021</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D3" s="1" t="n">
-        <v>44552</v>
-      </c>
-      <c r="E3" s="1" t="n">
-        <v>46307</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>UPPLANDS-BRO</t>
-        </is>
-      </c>
-      <c r="I3" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="J3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L3" t="n">
-        <v>4</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>4</v>
-      </c>
-      <c r="R3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S3" t="n">
-        <v>4</v>
-      </c>
-      <c r="T3" t="n">
-        <v>6</v>
-      </c>
-      <c r="U3" t="n">
-        <v>1</v>
-      </c>
-      <c r="V3" s="2" t="inlineStr">
         <is>
           <t>Blek fingersvamp
 Dofttaggsvamp
@@ -773,107 +660,107 @@
 Svartvit taggsvamp</t>
         </is>
       </c>
-      <c r="W3">
+      <c r="W2">
         <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 73783-2021 artfynd.xlsx", "A 73783-2021")</f>
         <v/>
       </c>
-      <c r="X3">
+      <c r="X2">
         <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 73783-2021 karta.png", "A 73783-2021")</f>
         <v/>
       </c>
-      <c r="Y3">
+      <c r="Y2">
         <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 73783-2021 georefererad karta.tif", "A 73783-2021")</f>
         <v/>
       </c>
-      <c r="AA3">
+      <c r="AA2">
         <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 73783-2021 FSC-klagomål.docx", "A 73783-2021")</f>
         <v/>
       </c>
-      <c r="AB3">
+      <c r="AB2">
         <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 73783-2021 FSC-klagomål mail.docx", "A 73783-2021")</f>
         <v/>
       </c>
-      <c r="AC3">
+      <c r="AC2">
         <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 73783-2021 tillsynsbegäran.docx", "A 73783-2021")</f>
         <v/>
       </c>
-      <c r="AD3">
+      <c r="AD2">
         <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 73783-2021 tillsynsbegäran mail.docx", "A 73783-2021")</f>
         <v/>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1">
-      <c r="A4" t="inlineStr">
+    <row r="3" ht="15" customHeight="1">
+      <c r="A3" t="inlineStr">
         <is>
           <t>A 73783-2021</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D4" s="1" t="n">
+      <c r="D3" s="1" t="n">
         <v>44552</v>
       </c>
-      <c r="E4" s="1" t="n">
-        <v>46307</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>UPPLANDS-BRO</t>
-        </is>
-      </c>
-      <c r="I4" t="n">
+      <c r="E3" s="1" t="n">
+        <v>46308</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>UPPLANDS-BRO</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
         <v>5.9</v>
       </c>
-      <c r="J4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
         <v>4</v>
       </c>
-      <c r="M4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q4" t="n">
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="n">
         <v>4</v>
       </c>
-      <c r="R4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S4" t="n">
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" t="n">
         <v>4</v>
       </c>
-      <c r="T4" t="n">
+      <c r="T3" t="n">
         <v>6</v>
       </c>
-      <c r="U4" t="n">
-        <v>1</v>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
+      <c r="U3" t="n">
+        <v>1</v>
+      </c>
+      <c r="V3" s="2" t="inlineStr">
         <is>
           <t>Blek fingersvamp
 Dofttaggsvamp
@@ -881,151 +768,262 @@
 Svartvit taggsvamp</t>
         </is>
       </c>
-      <c r="W4">
+      <c r="W3">
         <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 73783-2021 artfynd.xlsx", "A 73783-2021")</f>
         <v/>
       </c>
-      <c r="X4">
+      <c r="X3">
         <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 73783-2021 karta.png", "A 73783-2021")</f>
         <v/>
       </c>
-      <c r="Y4">
+      <c r="Y3">
         <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 73783-2021 georefererad karta.tif", "A 73783-2021")</f>
         <v/>
       </c>
-      <c r="AA4">
+      <c r="AA3">
         <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 73783-2021 FSC-klagomål.docx", "A 73783-2021")</f>
         <v/>
       </c>
-      <c r="AB4">
+      <c r="AB3">
         <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 73783-2021 FSC-klagomål mail.docx", "A 73783-2021")</f>
         <v/>
       </c>
-      <c r="AC4">
+      <c r="AC3">
         <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 73783-2021 tillsynsbegäran.docx", "A 73783-2021")</f>
         <v/>
       </c>
-      <c r="AD4">
+      <c r="AD3">
         <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 73783-2021 tillsynsbegäran mail.docx", "A 73783-2021")</f>
         <v/>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1">
-      <c r="A5" t="inlineStr">
+    <row r="4" ht="15" customHeight="1">
+      <c r="A4" t="inlineStr">
         <is>
           <t>A 55586-2023</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D5" s="1" t="n">
+      <c r="D4" s="1" t="n">
         <v>45232</v>
       </c>
-      <c r="E5" s="1" t="n">
-        <v>46307</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>UPPLANDS-BRO</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
+      <c r="E4" s="1" t="n">
+        <v>46308</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>UPPLANDS-BRO</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
         <is>
           <t>Övriga statliga verk och myndigheter</t>
         </is>
       </c>
-      <c r="I5" t="n">
+      <c r="I4" t="n">
         <v>38.9</v>
       </c>
-      <c r="J5" t="n">
+      <c r="J4" t="n">
         <v>2</v>
       </c>
-      <c r="K5" t="n">
-        <v>1</v>
-      </c>
-      <c r="L5" t="n">
-        <v>1</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>1</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" t="n">
+      <c r="K4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>1</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="n">
         <v>3</v>
       </c>
-      <c r="T5" t="n">
+      <c r="T4" t="n">
         <v>4</v>
       </c>
-      <c r="U5" t="n">
+      <c r="U4" t="n">
         <v>2</v>
       </c>
-      <c r="V5" s="2" t="inlineStr">
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>Fyrflikig jordstjärna
 Nästrot
 Blåsippa</t>
         </is>
       </c>
+      <c r="W4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 55586-2023 artfynd.xlsx", "A 55586-2023")</f>
+        <v/>
+      </c>
+      <c r="X4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 55586-2023 karta.png", "A 55586-2023")</f>
+        <v/>
+      </c>
+      <c r="Y4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 55586-2023 georefererad karta.tif", "A 55586-2023")</f>
+        <v/>
+      </c>
+      <c r="AA4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 55586-2023 FSC-klagomål.docx", "A 55586-2023")</f>
+        <v/>
+      </c>
+      <c r="AB4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 55586-2023 FSC-klagomål mail.docx", "A 55586-2023")</f>
+        <v/>
+      </c>
+      <c r="AC4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 55586-2023 tillsynsbegäran.docx", "A 55586-2023")</f>
+        <v/>
+      </c>
+      <c r="AD4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 55586-2023 tillsynsbegäran mail.docx", "A 55586-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>A 18772-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="n">
+        <v>46128</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>46308</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>UPPLANDS-BRO</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="J5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>1</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>2</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
+          <t>Svedjenäva
+Fläcknycklar</t>
+        </is>
+      </c>
       <c r="W5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 55586-2023 artfynd.xlsx", "A 55586-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 18772-2026 artfynd.xlsx", "A 18772-2026")</f>
         <v/>
       </c>
       <c r="X5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 55586-2023 karta.png", "A 55586-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 18772-2026 karta.png", "A 18772-2026")</f>
         <v/>
       </c>
       <c r="Y5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 55586-2023 georefererad karta.tif", "A 55586-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 18772-2026 georefererad karta.tif", "A 18772-2026")</f>
         <v/>
       </c>
       <c r="AA5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 55586-2023 FSC-klagomål.docx", "A 55586-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 18772-2026 FSC-klagomål.docx", "A 18772-2026")</f>
         <v/>
       </c>
       <c r="AB5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 55586-2023 FSC-klagomål mail.docx", "A 55586-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 18772-2026 FSC-klagomål mail.docx", "A 18772-2026")</f>
         <v/>
       </c>
       <c r="AC5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 55586-2023 tillsynsbegäran.docx", "A 55586-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 18772-2026 tillsynsbegäran.docx", "A 18772-2026")</f>
         <v/>
       </c>
       <c r="AD5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 55586-2023 tillsynsbegäran mail.docx", "A 55586-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 18772-2026 tillsynsbegäran mail.docx", "A 18772-2026")</f>
         <v/>
       </c>
     </row>
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 73773-2021</t>
+          <t>A 18790-2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1039,10 +1037,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>44552</v>
+        <v>46128</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1054,8 +1052,13 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I6" t="n">
-        <v>1.9</v>
+        <v>5.5</v>
       </c>
       <c r="J6" t="n">
         <v>2</v>
@@ -1088,289 +1091,284 @@
         <v>2</v>
       </c>
       <c r="T6" t="n">
+        <v>2</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>Fläcknycklar
+Nattviol</t>
+        </is>
+      </c>
+      <c r="W6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 18790-2026 artfynd.xlsx", "A 18790-2026")</f>
+        <v/>
+      </c>
+      <c r="X6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 18790-2026 karta.png", "A 18790-2026")</f>
+        <v/>
+      </c>
+      <c r="Y6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 18790-2026 georefererad karta.tif", "A 18790-2026")</f>
+        <v/>
+      </c>
+      <c r="AA6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 18790-2026 FSC-klagomål.docx", "A 18790-2026")</f>
+        <v/>
+      </c>
+      <c r="AB6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 18790-2026 FSC-klagomål mail.docx", "A 18790-2026")</f>
+        <v/>
+      </c>
+      <c r="AC6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 18790-2026 tillsynsbegäran.docx", "A 18790-2026")</f>
+        <v/>
+      </c>
+      <c r="AD6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 18790-2026 tillsynsbegäran mail.docx", "A 18790-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>A 10909-2025</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>45722</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>46308</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>UPPLANDS-BRO</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>2</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2</v>
+      </c>
+      <c r="U7" t="n">
+        <v>2</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>Arommusseron
+Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="W7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 10909-2025 artfynd.xlsx", "A 10909-2025")</f>
+        <v/>
+      </c>
+      <c r="X7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 10909-2025 karta.png", "A 10909-2025")</f>
+        <v/>
+      </c>
+      <c r="Y7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 10909-2025 georefererad karta.tif", "A 10909-2025")</f>
+        <v/>
+      </c>
+      <c r="AA7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 10909-2025 FSC-klagomål.docx", "A 10909-2025")</f>
+        <v/>
+      </c>
+      <c r="AB7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 10909-2025 FSC-klagomål mail.docx", "A 10909-2025")</f>
+        <v/>
+      </c>
+      <c r="AC7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 10909-2025 tillsynsbegäran.docx", "A 10909-2025")</f>
+        <v/>
+      </c>
+      <c r="AD7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 10909-2025 tillsynsbegäran mail.docx", "A 10909-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="15" customHeight="1">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>A 73773-2021</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D8" s="1" t="n">
+        <v>44552</v>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>46308</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>UPPLANDS-BRO</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="J8" t="n">
+        <v>2</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>2</v>
+      </c>
+      <c r="T8" t="n">
         <v>3</v>
       </c>
-      <c r="U6" t="n">
+      <c r="U8" t="n">
         <v>3</v>
       </c>
-      <c r="V6" s="2" t="inlineStr">
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>Kopparödla
 Gullviva</t>
         </is>
       </c>
-      <c r="W6">
+      <c r="W8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 73773-2021 artfynd.xlsx", "A 73773-2021")</f>
         <v/>
       </c>
-      <c r="X6">
+      <c r="X8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 73773-2021 karta.png", "A 73773-2021")</f>
         <v/>
       </c>
-      <c r="Y6">
+      <c r="Y8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 73773-2021 georefererad karta.tif", "A 73773-2021")</f>
         <v/>
       </c>
-      <c r="AA6">
+      <c r="AA8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 73773-2021 FSC-klagomål.docx", "A 73773-2021")</f>
         <v/>
       </c>
-      <c r="AB6">
+      <c r="AB8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 73773-2021 FSC-klagomål mail.docx", "A 73773-2021")</f>
         <v/>
       </c>
-      <c r="AC6">
+      <c r="AC8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 73773-2021 tillsynsbegäran.docx", "A 73773-2021")</f>
         <v/>
       </c>
-      <c r="AD6">
+      <c r="AD8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 73773-2021 tillsynsbegäran mail.docx", "A 73773-2021")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>A 18790-2026</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>46128</v>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>46307</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>UPPLANDS-BRO</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="J7" t="n">
-        <v>2</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
-        <v>2</v>
-      </c>
-      <c r="T7" t="n">
-        <v>2</v>
-      </c>
-      <c r="U7" t="n">
-        <v>0</v>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>Fläcknycklar
-Nattviol</t>
-        </is>
-      </c>
-      <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 18790-2026 artfynd.xlsx", "A 18790-2026")</f>
-        <v/>
-      </c>
-      <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 18790-2026 karta.png", "A 18790-2026")</f>
-        <v/>
-      </c>
-      <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 18790-2026 georefererad karta.tif", "A 18790-2026")</f>
-        <v/>
-      </c>
-      <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 18790-2026 FSC-klagomål.docx", "A 18790-2026")</f>
-        <v/>
-      </c>
-      <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 18790-2026 FSC-klagomål mail.docx", "A 18790-2026")</f>
-        <v/>
-      </c>
-      <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 18790-2026 tillsynsbegäran.docx", "A 18790-2026")</f>
-        <v/>
-      </c>
-      <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 18790-2026 tillsynsbegäran mail.docx", "A 18790-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8" ht="15" customHeight="1">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>A 18772-2026</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D8" s="1" t="n">
-        <v>46128</v>
-      </c>
-      <c r="E8" s="1" t="n">
-        <v>46307</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>UPPLANDS-BRO</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
-      <c r="I8" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="J8" t="n">
-        <v>1</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>1</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>1</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" t="n">
-        <v>2</v>
-      </c>
-      <c r="T8" t="n">
-        <v>2</v>
-      </c>
-      <c r="U8" t="n">
-        <v>0</v>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>Svedjenäva
-Fläcknycklar</t>
-        </is>
-      </c>
-      <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 18772-2026 artfynd.xlsx", "A 18772-2026")</f>
-        <v/>
-      </c>
-      <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 18772-2026 karta.png", "A 18772-2026")</f>
-        <v/>
-      </c>
-      <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 18772-2026 georefererad karta.tif", "A 18772-2026")</f>
-        <v/>
-      </c>
-      <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 18772-2026 FSC-klagomål.docx", "A 18772-2026")</f>
-        <v/>
-      </c>
-      <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 18772-2026 FSC-klagomål mail.docx", "A 18772-2026")</f>
-        <v/>
-      </c>
-      <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 18772-2026 tillsynsbegäran.docx", "A 18772-2026")</f>
-        <v/>
-      </c>
-      <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 18772-2026 tillsynsbegäran mail.docx", "A 18772-2026")</f>
         <v/>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 10909-2025</t>
+          <t>S 800-2022</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>avverkningsanmälan</t>
+          <t>samrådsanmälan</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45722</v>
+        <v>44603</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1382,13 +1380,8 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I9" t="n">
-        <v>11.2</v>
+        <v>4.3</v>
       </c>
       <c r="J9" t="n">
         <v>1</v>
@@ -1397,13 +1390,13 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1415,73 +1408,73 @@
         <v>1</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S9" t="n">
         <v>2</v>
       </c>
       <c r="T9" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="U9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>Arommusseron
-Fläcknycklar</t>
+          <t>Ask
+Mistel</t>
         </is>
       </c>
       <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 10909-2025 artfynd.xlsx", "A 10909-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/S 800-2022 artfynd.xlsx", "S 800-2022")</f>
         <v/>
       </c>
       <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 10909-2025 karta.png", "A 10909-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/S 800-2022 karta.png", "S 800-2022")</f>
         <v/>
       </c>
       <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 10909-2025 georefererad karta.tif", "A 10909-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/S 800-2022 georefererad karta.tif", "S 800-2022")</f>
         <v/>
       </c>
       <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 10909-2025 FSC-klagomål.docx", "A 10909-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/S 800-2022 FSC-klagomål.docx", "S 800-2022")</f>
         <v/>
       </c>
       <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 10909-2025 FSC-klagomål mail.docx", "A 10909-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/S 800-2022 FSC-klagomål mail.docx", "S 800-2022")</f>
         <v/>
       </c>
       <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 10909-2025 tillsynsbegäran.docx", "A 10909-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/S 800-2022 tillsynsbegäran.docx", "S 800-2022")</f>
         <v/>
       </c>
       <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 10909-2025 tillsynsbegäran mail.docx", "A 10909-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/S 800-2022 tillsynsbegäran mail.docx", "S 800-2022")</f>
         <v/>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>S 800-2022</t>
+          <t>A 73787-2021</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>samrådsanmälan</t>
+          <t>avverkningsanmälan</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Annan skogsbruksåtgärd</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>44603</v>
+        <v>44552</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1494,22 +1487,22 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="J10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1521,56 +1514,55 @@
         <v>1</v>
       </c>
       <c r="R10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T10" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="U10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>Ask
-Mistel</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/S 800-2022 artfynd.xlsx", "S 800-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 73787-2021 artfynd.xlsx", "A 73787-2021")</f>
         <v/>
       </c>
       <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/S 800-2022 karta.png", "S 800-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 73787-2021 karta.png", "A 73787-2021")</f>
         <v/>
       </c>
       <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/S 800-2022 georefererad karta.tif", "S 800-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 73787-2021 georefererad karta.tif", "A 73787-2021")</f>
         <v/>
       </c>
       <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/S 800-2022 FSC-klagomål.docx", "S 800-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 73787-2021 FSC-klagomål.docx", "A 73787-2021")</f>
         <v/>
       </c>
       <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/S 800-2022 FSC-klagomål mail.docx", "S 800-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 73787-2021 FSC-klagomål mail.docx", "A 73787-2021")</f>
         <v/>
       </c>
       <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/S 800-2022 tillsynsbegäran.docx", "S 800-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 73787-2021 tillsynsbegäran.docx", "A 73787-2021")</f>
         <v/>
       </c>
       <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/S 800-2022 tillsynsbegäran mail.docx", "S 800-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 73787-2021 tillsynsbegäran mail.docx", "A 73787-2021")</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 73787-2021</t>
+          <t>A 12363-2025</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1584,10 +1576,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>44552</v>
+        <v>45730</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1600,16 +1592,16 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>4.6</v>
+        <v>0.8</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
@@ -1624,7 +1616,7 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -1640,42 +1632,42 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 73787-2021 artfynd.xlsx", "A 73787-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 12363-2025 artfynd.xlsx", "A 12363-2025")</f>
         <v/>
       </c>
       <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 73787-2021 karta.png", "A 73787-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 12363-2025 karta.png", "A 12363-2025")</f>
         <v/>
       </c>
       <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 73787-2021 georefererad karta.tif", "A 73787-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 12363-2025 georefererad karta.tif", "A 12363-2025")</f>
         <v/>
       </c>
       <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 73787-2021 FSC-klagomål.docx", "A 73787-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 12363-2025 FSC-klagomål.docx", "A 12363-2025")</f>
         <v/>
       </c>
       <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 73787-2021 FSC-klagomål mail.docx", "A 73787-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 12363-2025 FSC-klagomål mail.docx", "A 12363-2025")</f>
         <v/>
       </c>
       <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 73787-2021 tillsynsbegäran.docx", "A 73787-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 12363-2025 tillsynsbegäran.docx", "A 12363-2025")</f>
         <v/>
       </c>
       <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 73787-2021 tillsynsbegäran mail.docx", "A 73787-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 12363-2025 tillsynsbegäran mail.docx", "A 12363-2025")</f>
         <v/>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 64098-2023</t>
+          <t>A 26196-2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1685,14 +1677,14 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45279</v>
+        <v>46182</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1705,7 +1697,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>0.3</v>
+        <v>53.1</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1714,7 +1706,7 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
@@ -1729,7 +1721,7 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -1738,49 +1730,49 @@
         <v>1</v>
       </c>
       <c r="T12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>Skogsalmsdvärgmal</t>
+          <t>Liljekonvalj</t>
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 64098-2023 artfynd.xlsx", "A 64098-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 26196-2026 artfynd.xlsx", "A 26196-2026")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 64098-2023 karta.png", "A 64098-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 26196-2026 karta.png", "A 26196-2026")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 64098-2023 georefererad karta.tif", "A 64098-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 26196-2026 georefererad karta.tif", "A 26196-2026")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 64098-2023 FSC-klagomål.docx", "A 64098-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 26196-2026 FSC-klagomål.docx", "A 26196-2026")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 64098-2023 FSC-klagomål mail.docx", "A 64098-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 26196-2026 FSC-klagomål mail.docx", "A 26196-2026")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 64098-2023 tillsynsbegäran.docx", "A 64098-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 26196-2026 tillsynsbegäran.docx", "A 26196-2026")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 64098-2023 tillsynsbegäran mail.docx", "A 64098-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 26196-2026 tillsynsbegäran mail.docx", "A 26196-2026")</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 7955-2023</t>
+          <t>A 64098-2023</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1794,10 +1786,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>44973</v>
+        <v>45279</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1810,22 +1802,22 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>2.9</v>
+        <v>0.3</v>
       </c>
       <c r="J13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -1837,7 +1829,7 @@
         <v>1</v>
       </c>
       <c r="R13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
@@ -1846,46 +1838,46 @@
         <v>1</v>
       </c>
       <c r="U13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>Bombmurkla</t>
+          <t>Skogsalmsdvärgmal</t>
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 7955-2023 artfynd.xlsx", "A 7955-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 64098-2023 artfynd.xlsx", "A 64098-2023")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 7955-2023 karta.png", "A 7955-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 64098-2023 karta.png", "A 64098-2023")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 7955-2023 georefererad karta.tif", "A 7955-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 64098-2023 georefererad karta.tif", "A 64098-2023")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 7955-2023 FSC-klagomål.docx", "A 7955-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 64098-2023 FSC-klagomål.docx", "A 64098-2023")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 7955-2023 FSC-klagomål mail.docx", "A 7955-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 64098-2023 FSC-klagomål mail.docx", "A 64098-2023")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 7955-2023 tillsynsbegäran.docx", "A 7955-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 64098-2023 tillsynsbegäran.docx", "A 64098-2023")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 7955-2023 tillsynsbegäran mail.docx", "A 7955-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 64098-2023 tillsynsbegäran mail.docx", "A 64098-2023")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 12363-2025</t>
+          <t>A 53357-2025</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1899,10 +1891,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45730</v>
+        <v>45959</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1915,13 +1907,13 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>0.8</v>
+        <v>2.4</v>
       </c>
       <c r="J14" t="n">
         <v>1</v>
       </c>
       <c r="K14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
@@ -1930,7 +1922,7 @@
         <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -1939,51 +1931,51 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
       </c>
       <c r="T14" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="U14" t="n">
         <v>0</v>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Bombmurkla</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 12363-2025 artfynd.xlsx", "A 12363-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 53357-2025 artfynd.xlsx", "A 53357-2025")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 12363-2025 karta.png", "A 12363-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 53357-2025 karta.png", "A 53357-2025")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 12363-2025 georefererad karta.tif", "A 12363-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 53357-2025 georefererad karta.tif", "A 53357-2025")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 12363-2025 FSC-klagomål.docx", "A 12363-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 53357-2025 FSC-klagomål.docx", "A 53357-2025")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 12363-2025 FSC-klagomål mail.docx", "A 12363-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 53357-2025 FSC-klagomål mail.docx", "A 53357-2025")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 12363-2025 tillsynsbegäran.docx", "A 12363-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 53357-2025 tillsynsbegäran.docx", "A 53357-2025")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 12363-2025 tillsynsbegäran mail.docx", "A 12363-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 53357-2025 tillsynsbegäran mail.docx", "A 53357-2025")</f>
         <v/>
       </c>
     </row>
@@ -2007,7 +1999,7 @@
         <v>45671</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2099,7 +2091,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 46438-2023</t>
+          <t>A 25561-2025</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2113,10 +2105,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45197</v>
+        <v>45803</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2129,7 +2121,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>0.5</v>
+        <v>1.6</v>
       </c>
       <c r="J16" t="n">
         <v>1</v>
@@ -2173,38 +2165,38 @@
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 46438-2023 artfynd.xlsx", "A 46438-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 25561-2025 artfynd.xlsx", "A 25561-2025")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 46438-2023 karta.png", "A 46438-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 25561-2025 karta.png", "A 25561-2025")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 46438-2023 georefererad karta.tif", "A 46438-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 25561-2025 georefererad karta.tif", "A 25561-2025")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 46438-2023 FSC-klagomål.docx", "A 46438-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 25561-2025 FSC-klagomål.docx", "A 25561-2025")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 46438-2023 FSC-klagomål mail.docx", "A 46438-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 25561-2025 FSC-klagomål mail.docx", "A 25561-2025")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 46438-2023 tillsynsbegäran.docx", "A 46438-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 25561-2025 tillsynsbegäran.docx", "A 25561-2025")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 46438-2023 tillsynsbegäran mail.docx", "A 46438-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 25561-2025 tillsynsbegäran mail.docx", "A 25561-2025")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 25561-2025</t>
+          <t>A 26637-2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2218,10 +2210,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45803</v>
+        <v>46184</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2234,10 +2226,10 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>1.6</v>
+        <v>5.4</v>
       </c>
       <c r="J17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
@@ -2246,10 +2238,10 @@
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2274,42 +2266,42 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Bombmurkla</t>
+          <t>Igelkott</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 25561-2025 artfynd.xlsx", "A 25561-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 26637-2026 artfynd.xlsx", "A 26637-2026")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 25561-2025 karta.png", "A 25561-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 26637-2026 karta.png", "A 26637-2026")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 25561-2025 georefererad karta.tif", "A 25561-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 26637-2026 georefererad karta.tif", "A 26637-2026")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 25561-2025 FSC-klagomål.docx", "A 25561-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 26637-2026 FSC-klagomål.docx", "A 26637-2026")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 25561-2025 FSC-klagomål mail.docx", "A 25561-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 26637-2026 FSC-klagomål mail.docx", "A 26637-2026")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 25561-2025 tillsynsbegäran.docx", "A 25561-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 26637-2026 tillsynsbegäran.docx", "A 26637-2026")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 25561-2025 tillsynsbegäran mail.docx", "A 25561-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 26637-2026 tillsynsbegäran mail.docx", "A 26637-2026")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 53357-2025</t>
+          <t>A 26623-2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2323,10 +2315,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45959</v>
+        <v>46184</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2339,22 +2331,22 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>2.4</v>
+        <v>4.6</v>
       </c>
       <c r="J18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2366,55 +2358,55 @@
         <v>1</v>
       </c>
       <c r="R18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
       </c>
       <c r="T18" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="U18" t="n">
         <v>0</v>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Bombmurkla</t>
+          <t>Svartöra</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 53357-2025 artfynd.xlsx", "A 53357-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 26623-2026 artfynd.xlsx", "A 26623-2026")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 53357-2025 karta.png", "A 53357-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 26623-2026 karta.png", "A 26623-2026")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 53357-2025 georefererad karta.tif", "A 53357-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 26623-2026 georefererad karta.tif", "A 26623-2026")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 53357-2025 FSC-klagomål.docx", "A 53357-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 26623-2026 FSC-klagomål.docx", "A 26623-2026")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 53357-2025 FSC-klagomål mail.docx", "A 53357-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 26623-2026 FSC-klagomål mail.docx", "A 26623-2026")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 53357-2025 tillsynsbegäran.docx", "A 53357-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 26623-2026 tillsynsbegäran.docx", "A 26623-2026")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 53357-2025 tillsynsbegäran mail.docx", "A 53357-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 26623-2026 tillsynsbegäran mail.docx", "A 26623-2026")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 11447-2025</t>
+          <t>A 23099-2024</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2424,14 +2416,14 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45726</v>
+        <v>45450</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2443,20 +2435,25 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I19" t="n">
-        <v>1.5</v>
+        <v>0.7</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
@@ -2468,10 +2465,10 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
@@ -2480,46 +2477,46 @@
         <v>1</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Myskbock</t>
+          <t>Bredbrämad bastardsvärmare</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 11447-2025 artfynd.xlsx", "A 11447-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 23099-2024 artfynd.xlsx", "A 23099-2024")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 11447-2025 karta.png", "A 11447-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 23099-2024 karta.png", "A 23099-2024")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 11447-2025 georefererad karta.tif", "A 11447-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 23099-2024 georefererad karta.tif", "A 23099-2024")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 11447-2025 FSC-klagomål.docx", "A 11447-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 23099-2024 FSC-klagomål.docx", "A 23099-2024")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 11447-2025 FSC-klagomål mail.docx", "A 11447-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 23099-2024 FSC-klagomål mail.docx", "A 23099-2024")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 11447-2025 tillsynsbegäran.docx", "A 11447-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 23099-2024 tillsynsbegäran.docx", "A 23099-2024")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 11447-2025 tillsynsbegäran mail.docx", "A 11447-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 23099-2024 tillsynsbegäran mail.docx", "A 23099-2024")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 23099-2024</t>
+          <t>A 46438-2023</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2533,10 +2530,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45450</v>
+        <v>45197</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2548,16 +2545,11 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I20" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
@@ -2566,10 +2558,10 @@
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2590,46 +2582,46 @@
         <v>1</v>
       </c>
       <c r="U20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>Bredbrämad bastardsvärmare</t>
+          <t>Bombmurkla</t>
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 23099-2024 artfynd.xlsx", "A 23099-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 46438-2023 artfynd.xlsx", "A 46438-2023")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 23099-2024 karta.png", "A 23099-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 46438-2023 karta.png", "A 46438-2023")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 23099-2024 georefererad karta.tif", "A 23099-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 46438-2023 georefererad karta.tif", "A 46438-2023")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 23099-2024 FSC-klagomål.docx", "A 23099-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 46438-2023 FSC-klagomål.docx", "A 46438-2023")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 23099-2024 FSC-klagomål mail.docx", "A 23099-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 46438-2023 FSC-klagomål mail.docx", "A 46438-2023")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 23099-2024 tillsynsbegäran.docx", "A 23099-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 46438-2023 tillsynsbegäran.docx", "A 46438-2023")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 23099-2024 tillsynsbegäran mail.docx", "A 23099-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 46438-2023 tillsynsbegäran mail.docx", "A 46438-2023")</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 26196-2026</t>
+          <t>A 11447-2025</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2643,10 +2635,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46182</v>
+        <v>45726</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2659,13 +2651,13 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>53.1</v>
+        <v>1.5</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
@@ -2692,49 +2684,49 @@
         <v>1</v>
       </c>
       <c r="T21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Liljekonvalj</t>
+          <t>Myskbock</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 26196-2026 artfynd.xlsx", "A 26196-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 11447-2025 artfynd.xlsx", "A 11447-2025")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 26196-2026 karta.png", "A 26196-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 11447-2025 karta.png", "A 11447-2025")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 26196-2026 georefererad karta.tif", "A 26196-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 11447-2025 georefererad karta.tif", "A 11447-2025")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 26196-2026 FSC-klagomål.docx", "A 26196-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 11447-2025 FSC-klagomål.docx", "A 11447-2025")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 26196-2026 FSC-klagomål mail.docx", "A 26196-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 11447-2025 FSC-klagomål mail.docx", "A 11447-2025")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 26196-2026 tillsynsbegäran.docx", "A 26196-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 11447-2025 tillsynsbegäran.docx", "A 11447-2025")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 26196-2026 tillsynsbegäran mail.docx", "A 26196-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 11447-2025 tillsynsbegäran mail.docx", "A 11447-2025")</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 26637-2026</t>
+          <t>A 7955-2023</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2748,10 +2740,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46184</v>
+        <v>44973</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2764,10 +2756,10 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>5.4</v>
+        <v>2.9</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
@@ -2776,10 +2768,10 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -2800,63 +2792,63 @@
         <v>1</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>Igelkott</t>
+          <t>Bombmurkla</t>
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 26637-2026 artfynd.xlsx", "A 26637-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 7955-2023 artfynd.xlsx", "A 7955-2023")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 26637-2026 karta.png", "A 26637-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 7955-2023 karta.png", "A 7955-2023")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 26637-2026 georefererad karta.tif", "A 26637-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 7955-2023 georefererad karta.tif", "A 7955-2023")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 26637-2026 FSC-klagomål.docx", "A 26637-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 7955-2023 FSC-klagomål.docx", "A 7955-2023")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 26637-2026 FSC-klagomål mail.docx", "A 26637-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 7955-2023 FSC-klagomål mail.docx", "A 7955-2023")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 26637-2026 tillsynsbegäran.docx", "A 26637-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 7955-2023 tillsynsbegäran.docx", "A 7955-2023")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 26637-2026 tillsynsbegäran mail.docx", "A 26637-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 7955-2023 tillsynsbegäran mail.docx", "A 7955-2023")</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 26623-2026</t>
+          <t>S 10446-2021</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>avverkningsanmälan</t>
+          <t>samrådsanmälan</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46184</v>
+        <v>44558</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2869,7 +2861,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>4.6</v>
+        <v>3.2</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2902,66 +2894,66 @@
         <v>1</v>
       </c>
       <c r="T23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U23" t="n">
         <v>0</v>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Svartöra</t>
+          <t>Korskovall</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 26623-2026 artfynd.xlsx", "A 26623-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/S 10446-2021 artfynd.xlsx", "S 10446-2021")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 26623-2026 karta.png", "A 26623-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/S 10446-2021 karta.png", "S 10446-2021")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 26623-2026 georefererad karta.tif", "A 26623-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/S 10446-2021 georefererad karta.tif", "S 10446-2021")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 26623-2026 FSC-klagomål.docx", "A 26623-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/S 10446-2021 FSC-klagomål.docx", "S 10446-2021")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 26623-2026 FSC-klagomål mail.docx", "A 26623-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/S 10446-2021 FSC-klagomål mail.docx", "S 10446-2021")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 26623-2026 tillsynsbegäran.docx", "A 26623-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/S 10446-2021 tillsynsbegäran.docx", "S 10446-2021")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 26623-2026 tillsynsbegäran mail.docx", "A 26623-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/S 10446-2021 tillsynsbegäran mail.docx", "S 10446-2021")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>S 10446-2021</t>
+          <t>A 8261-2022</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>samrådsanmälan</t>
+          <t>avverkningsanmälan</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Annan skogsbruksåtgärd</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>44558</v>
+        <v>44609</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2974,7 +2966,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>3.2</v>
+        <v>0.8</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2983,7 +2975,7 @@
         <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
         <v>0</v>
@@ -2998,58 +2990,26 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
         <v>0</v>
       </c>
-      <c r="V24" s="2" t="inlineStr">
-        <is>
-          <t>Korskovall</t>
-        </is>
-      </c>
-      <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/S 10446-2021 artfynd.xlsx", "S 10446-2021")</f>
-        <v/>
-      </c>
-      <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/S 10446-2021 karta.png", "S 10446-2021")</f>
-        <v/>
-      </c>
-      <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/S 10446-2021 georefererad karta.tif", "S 10446-2021")</f>
-        <v/>
-      </c>
-      <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/S 10446-2021 FSC-klagomål.docx", "S 10446-2021")</f>
-        <v/>
-      </c>
-      <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/S 10446-2021 FSC-klagomål mail.docx", "S 10446-2021")</f>
-        <v/>
-      </c>
-      <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/S 10446-2021 tillsynsbegäran.docx", "S 10446-2021")</f>
-        <v/>
-      </c>
-      <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/S 10446-2021 tillsynsbegäran mail.docx", "S 10446-2021")</f>
-        <v/>
-      </c>
+      <c r="V24" s="2" t="inlineStr"/>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 8261-2022</t>
+          <t>A 58663-2021</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3063,10 +3023,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>44609</v>
+        <v>44489</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3078,8 +3038,13 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I25" t="n">
-        <v>0.8</v>
+        <v>4.3</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -3122,7 +3087,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 58663-2021</t>
+          <t>A 72523-2021</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3136,10 +3101,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44489</v>
+        <v>44546</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3151,13 +3116,8 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I26" t="n">
-        <v>4.3</v>
+        <v>2</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -3200,7 +3160,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 72523-2021</t>
+          <t>A 20604-2022</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3214,10 +3174,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44546</v>
+        <v>44700</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3273,7 +3233,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 20604-2022</t>
+          <t>A 3838-2022</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3287,10 +3247,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44700</v>
+        <v>44587</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3303,7 +3263,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>2</v>
+        <v>2.9</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3346,7 +3306,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 3838-2022</t>
+          <t>A 14719-2022</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3360,10 +3320,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44587</v>
+        <v>44655</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3375,8 +3335,13 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I29" t="n">
-        <v>2.9</v>
+        <v>1.2</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3419,7 +3384,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 14719-2022</t>
+          <t>A 64105-2023</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3433,10 +3398,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>44655</v>
+        <v>45279</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3448,13 +3413,8 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I30" t="n">
-        <v>1.2</v>
+        <v>2.2</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3497,7 +3457,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 54222-2023</t>
+          <t>A 7275-2022</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3511,10 +3471,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45225</v>
+        <v>44606</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3532,7 +3492,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>8.300000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3575,7 +3535,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 64105-2023</t>
+          <t>A 31160-2022</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3589,10 +3549,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45279</v>
+        <v>44770</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3605,7 +3565,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>2.2</v>
+        <v>3.7</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3648,7 +3608,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 4338-2023</t>
+          <t>A 58598-2025</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3662,10 +3622,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44953</v>
+        <v>45986</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3677,8 +3637,13 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I33" t="n">
-        <v>1.1</v>
+        <v>4.5</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3721,7 +3686,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 58011-2021</t>
+          <t>A 26633-2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3735,10 +3700,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44487</v>
+        <v>46184</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3750,13 +3715,8 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I34" t="n">
-        <v>9.199999999999999</v>
+        <v>0.7</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3799,7 +3759,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 72524-2021</t>
+          <t>A 2602-2024</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3813,10 +3773,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44546</v>
+        <v>45313</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3829,7 +3789,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>3.6</v>
+        <v>0.7</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3872,7 +3832,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 64114-2023</t>
+          <t>A 3754-2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3886,10 +3846,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45279</v>
+        <v>46043</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3901,8 +3861,13 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I36" t="n">
-        <v>0.4</v>
+        <v>5.1</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3962,7 +3927,7 @@
         <v>45279</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4018,7 +3983,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 23093-2024</t>
+          <t>A 7112-2025</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4032,10 +3997,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45450</v>
+        <v>45701</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4047,13 +4012,8 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I38" t="n">
-        <v>0.9</v>
+        <v>2.4</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4096,7 +4056,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 59700-2021</t>
+          <t>A 59844-2022</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4110,10 +4070,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44494</v>
+        <v>44901</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4131,7 +4091,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>4.8</v>
+        <v>11.9</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4174,7 +4134,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 7112-2025</t>
+          <t>A 28735-2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4188,10 +4148,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45701</v>
+        <v>46198</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4204,7 +4164,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>2.4</v>
+        <v>3.5</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4247,7 +4207,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 27313-2023</t>
+          <t>A 38902-2024</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4261,10 +4221,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45096</v>
+        <v>45547</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4276,8 +4236,13 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I41" t="n">
-        <v>1.8</v>
+        <v>0.8</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4320,7 +4285,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 59377-2024</t>
+          <t>A 28740-2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4334,10 +4299,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45638</v>
+        <v>46198</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4350,7 +4315,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>0.6</v>
+        <v>4.8</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4393,7 +4358,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 38902-2024</t>
+          <t>A 28797-2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4407,10 +4372,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45547</v>
+        <v>46198</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4422,13 +4387,8 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I43" t="n">
-        <v>0.8</v>
+        <v>2.2</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4471,7 +4431,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 50294-2023</t>
+          <t>A 23615-2025</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4485,10 +4445,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45216</v>
+        <v>45792</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4501,7 +4461,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>3.7</v>
+        <v>1.3</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4544,7 +4504,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 23615-2025</t>
+          <t>A 23627-2025</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4561,7 +4521,7 @@
         <v>45792</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4574,7 +4534,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4617,7 +4577,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 23627-2025</t>
+          <t>A 31714-2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4631,10 +4591,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45792</v>
+        <v>46226</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4647,7 +4607,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1.7</v>
+        <v>5</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4690,7 +4650,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 5264-2023</t>
+          <t>A 33058-2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4700,14 +4660,14 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>44959</v>
+        <v>46245</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4720,7 +4680,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>5.8</v>
+        <v>1.3</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4763,7 +4723,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 51587-2023</t>
+          <t>A 9655-2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4777,10 +4737,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45215</v>
+        <v>46070</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4794,11 +4754,11 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Allmännings- och besparingsskogar</t>
+          <t>Övriga statliga verk och myndigheter</t>
         </is>
       </c>
       <c r="I48" t="n">
-        <v>2.6</v>
+        <v>17.2</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4841,7 +4801,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 23098-2024</t>
+          <t>A 3630-2023</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4855,10 +4815,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45450</v>
+        <v>44950</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4870,13 +4830,8 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I49" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4919,7 +4874,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 59848-2022</t>
+          <t>A 23093-2024</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4933,10 +4888,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>44901</v>
+        <v>45450</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4954,7 +4909,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>10.7</v>
+        <v>0.9</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4997,7 +4952,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 64110-2023</t>
+          <t>A 54222-2023</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5011,10 +4966,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45279</v>
+        <v>45225</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5026,8 +4981,13 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I51" t="n">
-        <v>0.4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5070,7 +5030,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 59844-2022</t>
+          <t>A 26625-2026</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5084,10 +5044,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>44901</v>
+        <v>46184</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5099,13 +5059,8 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I52" t="n">
-        <v>11.9</v>
+        <v>5.3</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5148,7 +5103,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 18787-2026</t>
+          <t>A 18778-2026</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5165,7 +5120,7 @@
         <v>46128</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5183,7 +5138,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>7.8</v>
+        <v>4.5</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5243,7 +5198,7 @@
         <v>46128</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5321,7 +5276,7 @@
         <v>46128</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5382,7 +5337,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 18778-2026</t>
+          <t>A 18787-2026</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5399,7 +5354,7 @@
         <v>46128</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5417,7 +5372,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>4.5</v>
+        <v>7.8</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5460,7 +5415,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 7275-2022</t>
+          <t>A 7860-2024</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5474,10 +5429,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>44606</v>
+        <v>45348</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5495,7 +5450,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>9.6</v>
+        <v>1.9</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5538,7 +5493,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 2602-2024</t>
+          <t>A 27313-2023</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5552,10 +5507,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45313</v>
+        <v>45096</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5568,7 +5523,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>0.7</v>
+        <v>1.8</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5611,7 +5566,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 59402-2022</t>
+          <t>A 21206-2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5625,10 +5580,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>44906</v>
+        <v>46146</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5640,8 +5595,13 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I59" t="n">
-        <v>1.8</v>
+        <v>0.9</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5684,7 +5644,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 3630-2023</t>
+          <t>A 64114-2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5698,10 +5658,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>44950</v>
+        <v>45279</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5714,7 +5674,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>1.4</v>
+        <v>0.4</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5757,7 +5717,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 7860-2024</t>
+          <t>A 50294-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5771,10 +5731,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45348</v>
+        <v>45216</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5786,13 +5746,8 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I61" t="n">
-        <v>1.9</v>
+        <v>3.7</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5835,7 +5790,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 21206-2026</t>
+          <t>A 58011-2021</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5849,10 +5804,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>46146</v>
+        <v>44487</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5870,7 +5825,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>0.9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5913,7 +5868,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 9655-2026</t>
+          <t>A 24579-2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5927,10 +5882,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>46070</v>
+        <v>46170</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5942,13 +5897,8 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I63" t="n">
-        <v>17.2</v>
+        <v>2.1</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5991,7 +5941,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 24579-2026</t>
+          <t>A 64110-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6005,10 +5955,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>46170</v>
+        <v>45279</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6021,7 +5971,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>2.1</v>
+        <v>0.4</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6064,7 +6014,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 58598-2025</t>
+          <t>A 23098-2024</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6078,10 +6028,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45986</v>
+        <v>45450</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6099,7 +6049,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>4.5</v>
+        <v>1</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6142,7 +6092,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 31160-2022</t>
+          <t>A 59377-2024</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6156,10 +6106,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>44770</v>
+        <v>45638</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6172,7 +6122,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>3.7</v>
+        <v>0.6</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6215,7 +6165,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 26633-2026</t>
+          <t>A 59402-2022</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6229,10 +6179,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>46184</v>
+        <v>44906</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6245,7 +6195,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>0.7</v>
+        <v>1.8</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6288,7 +6238,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 3754-2026</t>
+          <t>A 5264-2023</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6302,10 +6252,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>46043</v>
+        <v>44959</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6317,13 +6267,8 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I68" t="n">
-        <v>5.1</v>
+        <v>5.8</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6366,7 +6311,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 28797-2026</t>
+          <t>A 51587-2023</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6380,10 +6325,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>46198</v>
+        <v>45215</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6395,8 +6340,13 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I69" t="n">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6439,7 +6389,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 28740-2026</t>
+          <t>A 72524-2021</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6453,10 +6403,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>46198</v>
+        <v>44546</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6469,7 +6419,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>4.8</v>
+        <v>3.6</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6512,7 +6462,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 28735-2026</t>
+          <t>A 4338-2023</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6526,10 +6476,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>46198</v>
+        <v>44953</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6542,7 +6492,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>3.5</v>
+        <v>1.1</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6585,7 +6535,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 31714-2026</t>
+          <t>A 59848-2022</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6599,10 +6549,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>46226</v>
+        <v>44901</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6614,8 +6564,13 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I72" t="n">
-        <v>5</v>
+        <v>10.7</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6658,7 +6613,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 33058-2026</t>
+          <t>A 59700-2021</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6668,14 +6623,14 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>46245</v>
+        <v>44494</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6687,8 +6642,13 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I73" t="n">
-        <v>1.3</v>
+        <v>4.8</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6728,27 +6688,27 @@
       </c>
       <c r="V73" s="2" t="inlineStr"/>
     </row>
-    <row r="74" ht="15" customHeight="1">
+    <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 26625-2026</t>
+          <t>S 10447-2021</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>avverkningsanmälan</t>
+          <t>samrådsanmälan</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>46184</v>
+        <v>44558</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6761,7 +6721,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>5.3</v>
+        <v>4.4</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6800,79 +6760,6 @@
         <v>0</v>
       </c>
       <c r="V74" s="2" t="inlineStr"/>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>S 10447-2021</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>Annan skogsbruksåtgärd</t>
-        </is>
-      </c>
-      <c r="D75" s="1" t="n">
-        <v>44558</v>
-      </c>
-      <c r="E75" s="1" t="n">
-        <v>46307</v>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>UPPLANDS-BRO</t>
-        </is>
-      </c>
-      <c r="I75" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="J75" t="n">
-        <v>0</v>
-      </c>
-      <c r="K75" t="n">
-        <v>0</v>
-      </c>
-      <c r="L75" t="n">
-        <v>0</v>
-      </c>
-      <c r="M75" t="n">
-        <v>0</v>
-      </c>
-      <c r="N75" t="n">
-        <v>0</v>
-      </c>
-      <c r="O75" t="n">
-        <v>0</v>
-      </c>
-      <c r="P75" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q75" t="n">
-        <v>0</v>
-      </c>
-      <c r="R75" t="n">
-        <v>0</v>
-      </c>
-      <c r="S75" t="n">
-        <v>0</v>
-      </c>
-      <c r="T75" t="n">
-        <v>0</v>
-      </c>
-      <c r="U75" t="n">
-        <v>0</v>
-      </c>
-      <c r="V75" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt UPPLANDS-BRO.xlsx
+++ b/Översikt UPPLANDS-BRO.xlsx
@@ -601,7 +601,7 @@
         <v>44552</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -709,7 +709,7 @@
         <v>44552</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -817,7 +817,7 @@
         <v>45232</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -912,7 +912,7 @@
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 18772-2026</t>
+          <t>A 18790-2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -929,7 +929,7 @@
         <v>46128</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -947,16 +947,16 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>19.5</v>
+        <v>5.5</v>
       </c>
       <c r="J5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
@@ -971,7 +971,7 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -987,147 +987,147 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
+          <t>Fläcknycklar
+Nattviol</t>
+        </is>
+      </c>
+      <c r="W5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 18790-2026 artfynd.xlsx", "A 18790-2026")</f>
+        <v/>
+      </c>
+      <c r="X5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 18790-2026 karta.png", "A 18790-2026")</f>
+        <v/>
+      </c>
+      <c r="Y5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 18790-2026 georefererad karta.tif", "A 18790-2026")</f>
+        <v/>
+      </c>
+      <c r="AA5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 18790-2026 FSC-klagomål.docx", "A 18790-2026")</f>
+        <v/>
+      </c>
+      <c r="AB5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 18790-2026 FSC-klagomål mail.docx", "A 18790-2026")</f>
+        <v/>
+      </c>
+      <c r="AC5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 18790-2026 tillsynsbegäran.docx", "A 18790-2026")</f>
+        <v/>
+      </c>
+      <c r="AD5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 18790-2026 tillsynsbegäran mail.docx", "A 18790-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>A 18772-2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D6" s="1" t="n">
+        <v>46128</v>
+      </c>
+      <c r="E6" s="1" t="n">
+        <v>46309</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>UPPLANDS-BRO</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>1</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
+        <v>2</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
           <t>Svedjenäva
 Fläcknycklar</t>
         </is>
       </c>
-      <c r="W5">
+      <c r="W6">
         <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 18772-2026 artfynd.xlsx", "A 18772-2026")</f>
         <v/>
       </c>
-      <c r="X5">
+      <c r="X6">
         <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 18772-2026 karta.png", "A 18772-2026")</f>
         <v/>
       </c>
-      <c r="Y5">
+      <c r="Y6">
         <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 18772-2026 georefererad karta.tif", "A 18772-2026")</f>
         <v/>
       </c>
-      <c r="AA5">
+      <c r="AA6">
         <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 18772-2026 FSC-klagomål.docx", "A 18772-2026")</f>
         <v/>
       </c>
-      <c r="AB5">
+      <c r="AB6">
         <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 18772-2026 FSC-klagomål mail.docx", "A 18772-2026")</f>
         <v/>
       </c>
-      <c r="AC5">
+      <c r="AC6">
         <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 18772-2026 tillsynsbegäran.docx", "A 18772-2026")</f>
         <v/>
       </c>
-      <c r="AD5">
+      <c r="AD6">
         <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 18772-2026 tillsynsbegäran mail.docx", "A 18772-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6" ht="15" customHeight="1">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>A 18790-2026</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D6" s="1" t="n">
-        <v>46128</v>
-      </c>
-      <c r="E6" s="1" t="n">
-        <v>46308</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>UPPLANDS-BRO</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
-      <c r="I6" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="J6" t="n">
-        <v>2</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" t="n">
-        <v>2</v>
-      </c>
-      <c r="T6" t="n">
-        <v>2</v>
-      </c>
-      <c r="U6" t="n">
-        <v>0</v>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>Fläcknycklar
-Nattviol</t>
-        </is>
-      </c>
-      <c r="W6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 18790-2026 artfynd.xlsx", "A 18790-2026")</f>
-        <v/>
-      </c>
-      <c r="X6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 18790-2026 karta.png", "A 18790-2026")</f>
-        <v/>
-      </c>
-      <c r="Y6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 18790-2026 georefererad karta.tif", "A 18790-2026")</f>
-        <v/>
-      </c>
-      <c r="AA6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 18790-2026 FSC-klagomål.docx", "A 18790-2026")</f>
-        <v/>
-      </c>
-      <c r="AB6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 18790-2026 FSC-klagomål mail.docx", "A 18790-2026")</f>
-        <v/>
-      </c>
-      <c r="AC6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 18790-2026 tillsynsbegäran.docx", "A 18790-2026")</f>
-        <v/>
-      </c>
-      <c r="AD6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 18790-2026 tillsynsbegäran mail.docx", "A 18790-2026")</f>
         <v/>
       </c>
     </row>
@@ -1151,7 +1151,7 @@
         <v>45722</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1262,7 +1262,7 @@
         <v>44552</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1368,7 +1368,7 @@
         <v>44603</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1474,7 +1474,7 @@
         <v>44552</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1562,7 +1562,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 12363-2025</t>
+          <t>A 7955-2023</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1576,10 +1576,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45730</v>
+        <v>44973</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1592,13 +1592,13 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>0.8</v>
+        <v>2.9</v>
       </c>
       <c r="J11" t="n">
         <v>1</v>
       </c>
       <c r="K11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -1607,7 +1607,7 @@
         <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1616,10 +1616,10 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1628,46 +1628,46 @@
         <v>1</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Bombmurkla</t>
         </is>
       </c>
       <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 12363-2025 artfynd.xlsx", "A 12363-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 7955-2023 artfynd.xlsx", "A 7955-2023")</f>
         <v/>
       </c>
       <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 12363-2025 karta.png", "A 12363-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 7955-2023 karta.png", "A 7955-2023")</f>
         <v/>
       </c>
       <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 12363-2025 georefererad karta.tif", "A 12363-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 7955-2023 georefererad karta.tif", "A 7955-2023")</f>
         <v/>
       </c>
       <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 12363-2025 FSC-klagomål.docx", "A 12363-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 7955-2023 FSC-klagomål.docx", "A 7955-2023")</f>
         <v/>
       </c>
       <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 12363-2025 FSC-klagomål mail.docx", "A 12363-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 7955-2023 FSC-klagomål mail.docx", "A 7955-2023")</f>
         <v/>
       </c>
       <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 12363-2025 tillsynsbegäran.docx", "A 12363-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 7955-2023 tillsynsbegäran.docx", "A 7955-2023")</f>
         <v/>
       </c>
       <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 12363-2025 tillsynsbegäran mail.docx", "A 12363-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 7955-2023 tillsynsbegäran mail.docx", "A 7955-2023")</f>
         <v/>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 26196-2026</t>
+          <t>A 25561-2025</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1677,14 +1677,14 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46182</v>
+        <v>45803</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1697,10 +1697,10 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>53.1</v>
+        <v>1.6</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
@@ -1712,7 +1712,7 @@
         <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1721,58 +1721,58 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
       </c>
       <c r="T12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>Liljekonvalj</t>
+          <t>Bombmurkla</t>
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 26196-2026 artfynd.xlsx", "A 26196-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 25561-2025 artfynd.xlsx", "A 25561-2025")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 26196-2026 karta.png", "A 26196-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 25561-2025 karta.png", "A 25561-2025")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 26196-2026 georefererad karta.tif", "A 26196-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 25561-2025 georefererad karta.tif", "A 25561-2025")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 26196-2026 FSC-klagomål.docx", "A 26196-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 25561-2025 FSC-klagomål.docx", "A 25561-2025")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 26196-2026 FSC-klagomål mail.docx", "A 26196-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 25561-2025 FSC-klagomål mail.docx", "A 25561-2025")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 26196-2026 tillsynsbegäran.docx", "A 26196-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 25561-2025 tillsynsbegäran.docx", "A 25561-2025")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 26196-2026 tillsynsbegäran mail.docx", "A 26196-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 25561-2025 tillsynsbegäran mail.docx", "A 25561-2025")</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 64098-2023</t>
+          <t>A 12363-2025</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1786,10 +1786,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45279</v>
+        <v>45730</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1802,16 +1802,16 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>0.3</v>
+        <v>0.8</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
@@ -1826,7 +1826,7 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -1842,42 +1842,42 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>Skogsalmsdvärgmal</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 64098-2023 artfynd.xlsx", "A 64098-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 12363-2025 artfynd.xlsx", "A 12363-2025")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 64098-2023 karta.png", "A 64098-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 12363-2025 karta.png", "A 12363-2025")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 64098-2023 georefererad karta.tif", "A 64098-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 12363-2025 georefererad karta.tif", "A 12363-2025")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 64098-2023 FSC-klagomål.docx", "A 64098-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 12363-2025 FSC-klagomål.docx", "A 12363-2025")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 64098-2023 FSC-klagomål mail.docx", "A 64098-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 12363-2025 FSC-klagomål mail.docx", "A 12363-2025")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 64098-2023 tillsynsbegäran.docx", "A 64098-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 12363-2025 tillsynsbegäran.docx", "A 12363-2025")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 64098-2023 tillsynsbegäran mail.docx", "A 64098-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 12363-2025 tillsynsbegäran mail.docx", "A 12363-2025")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 53357-2025</t>
+          <t>A 46438-2023</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1891,10 +1891,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45959</v>
+        <v>45197</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>2.4</v>
+        <v>0.5</v>
       </c>
       <c r="J14" t="n">
         <v>1</v>
@@ -1940,7 +1940,7 @@
         <v>1</v>
       </c>
       <c r="T14" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="U14" t="n">
         <v>0</v>
@@ -1951,38 +1951,38 @@
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 53357-2025 artfynd.xlsx", "A 53357-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 46438-2023 artfynd.xlsx", "A 46438-2023")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 53357-2025 karta.png", "A 53357-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 46438-2023 karta.png", "A 46438-2023")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 53357-2025 georefererad karta.tif", "A 53357-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 46438-2023 georefererad karta.tif", "A 46438-2023")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 53357-2025 FSC-klagomål.docx", "A 53357-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 46438-2023 FSC-klagomål.docx", "A 46438-2023")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 53357-2025 FSC-klagomål mail.docx", "A 53357-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 46438-2023 FSC-klagomål mail.docx", "A 46438-2023")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 53357-2025 tillsynsbegäran.docx", "A 53357-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 46438-2023 tillsynsbegäran.docx", "A 46438-2023")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 53357-2025 tillsynsbegäran mail.docx", "A 53357-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 46438-2023 tillsynsbegäran mail.docx", "A 46438-2023")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 2062-2025</t>
+          <t>A 53357-2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1996,10 +1996,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45671</v>
+        <v>45959</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2012,7 +2012,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>1.9</v>
+        <v>2.4</v>
       </c>
       <c r="J15" t="n">
         <v>1</v>
@@ -2021,13 +2021,13 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
         <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2039,59 +2039,55 @@
         <v>1</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S15" t="n">
         <v>1</v>
       </c>
       <c r="T15" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="U15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Bombmurkla</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 2062-2025 artfynd.xlsx", "A 2062-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 53357-2025 artfynd.xlsx", "A 53357-2025")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 2062-2025 karta.png", "A 2062-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 53357-2025 karta.png", "A 53357-2025")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 2062-2025 georefererad karta.tif", "A 2062-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 53357-2025 georefererad karta.tif", "A 53357-2025")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 2062-2025 FSC-klagomål.docx", "A 2062-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 53357-2025 FSC-klagomål.docx", "A 53357-2025")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 2062-2025 FSC-klagomål mail.docx", "A 2062-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 53357-2025 FSC-klagomål mail.docx", "A 53357-2025")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 2062-2025 tillsynsbegäran.docx", "A 2062-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 53357-2025 tillsynsbegäran.docx", "A 53357-2025")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 2062-2025 tillsynsbegäran mail.docx", "A 2062-2025")</f>
-        <v/>
-      </c>
-      <c r="AE15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/fåglar/A 2062-2025 prioriterade fågelarter.docx", "A 2062-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 53357-2025 tillsynsbegäran mail.docx", "A 53357-2025")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 25561-2025</t>
+          <t>A 23099-2024</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2105,10 +2101,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45803</v>
+        <v>45450</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2120,11 +2116,16 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I16" t="n">
-        <v>1.6</v>
+        <v>0.7</v>
       </c>
       <c r="J16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
@@ -2133,10 +2134,10 @@
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2157,46 +2158,46 @@
         <v>1</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Bombmurkla</t>
+          <t>Bredbrämad bastardsvärmare</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 25561-2025 artfynd.xlsx", "A 25561-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 23099-2024 artfynd.xlsx", "A 23099-2024")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 25561-2025 karta.png", "A 25561-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 23099-2024 karta.png", "A 23099-2024")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 25561-2025 georefererad karta.tif", "A 25561-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 23099-2024 georefererad karta.tif", "A 23099-2024")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 25561-2025 FSC-klagomål.docx", "A 25561-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 23099-2024 FSC-klagomål.docx", "A 23099-2024")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 25561-2025 FSC-klagomål mail.docx", "A 25561-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 23099-2024 FSC-klagomål mail.docx", "A 23099-2024")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 25561-2025 tillsynsbegäran.docx", "A 25561-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 23099-2024 tillsynsbegäran.docx", "A 23099-2024")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 25561-2025 tillsynsbegäran mail.docx", "A 25561-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 23099-2024 tillsynsbegäran mail.docx", "A 23099-2024")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 26637-2026</t>
+          <t>A 64098-2023</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2210,10 +2211,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46184</v>
+        <v>45279</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2226,7 +2227,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>5.4</v>
+        <v>0.3</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2235,10 +2236,10 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
@@ -2253,7 +2254,7 @@
         <v>1</v>
       </c>
       <c r="R17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
@@ -2266,42 +2267,42 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Igelkott</t>
+          <t>Skogsalmsdvärgmal</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 26637-2026 artfynd.xlsx", "A 26637-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 64098-2023 artfynd.xlsx", "A 64098-2023")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 26637-2026 karta.png", "A 26637-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 64098-2023 karta.png", "A 64098-2023")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 26637-2026 georefererad karta.tif", "A 26637-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 64098-2023 georefererad karta.tif", "A 64098-2023")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 26637-2026 FSC-klagomål.docx", "A 26637-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 64098-2023 FSC-klagomål.docx", "A 64098-2023")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 26637-2026 FSC-klagomål mail.docx", "A 26637-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 64098-2023 FSC-klagomål mail.docx", "A 64098-2023")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 26637-2026 tillsynsbegäran.docx", "A 26637-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 64098-2023 tillsynsbegäran.docx", "A 64098-2023")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 26637-2026 tillsynsbegäran mail.docx", "A 26637-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 64098-2023 tillsynsbegäran mail.docx", "A 64098-2023")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 26623-2026</t>
+          <t>A 26196-2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2311,14 +2312,14 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46184</v>
+        <v>46182</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2331,7 +2332,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>4.6</v>
+        <v>53.1</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2340,7 +2341,7 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
@@ -2355,7 +2356,7 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -2364,49 +2365,49 @@
         <v>1</v>
       </c>
       <c r="T18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Svartöra</t>
+          <t>Liljekonvalj</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 26623-2026 artfynd.xlsx", "A 26623-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 26196-2026 artfynd.xlsx", "A 26196-2026")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 26623-2026 karta.png", "A 26623-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 26196-2026 karta.png", "A 26196-2026")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 26623-2026 georefererad karta.tif", "A 26623-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 26196-2026 georefererad karta.tif", "A 26196-2026")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 26623-2026 FSC-klagomål.docx", "A 26623-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 26196-2026 FSC-klagomål.docx", "A 26196-2026")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 26623-2026 FSC-klagomål mail.docx", "A 26623-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 26196-2026 FSC-klagomål mail.docx", "A 26196-2026")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 26623-2026 tillsynsbegäran.docx", "A 26623-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 26196-2026 tillsynsbegäran.docx", "A 26196-2026")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 26623-2026 tillsynsbegäran mail.docx", "A 26623-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 26196-2026 tillsynsbegäran mail.docx", "A 26196-2026")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 23099-2024</t>
+          <t>A 11447-2025</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2416,14 +2417,14 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45450</v>
+        <v>45726</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2435,25 +2436,20 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I19" t="n">
-        <v>0.7</v>
+        <v>1.5</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
@@ -2465,10 +2461,10 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
@@ -2477,46 +2473,46 @@
         <v>1</v>
       </c>
       <c r="U19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Bredbrämad bastardsvärmare</t>
+          <t>Myskbock</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 23099-2024 artfynd.xlsx", "A 23099-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 11447-2025 artfynd.xlsx", "A 11447-2025")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 23099-2024 karta.png", "A 23099-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 11447-2025 karta.png", "A 11447-2025")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 23099-2024 georefererad karta.tif", "A 23099-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 11447-2025 georefererad karta.tif", "A 11447-2025")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 23099-2024 FSC-klagomål.docx", "A 23099-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 11447-2025 FSC-klagomål.docx", "A 11447-2025")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 23099-2024 FSC-klagomål mail.docx", "A 23099-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 11447-2025 FSC-klagomål mail.docx", "A 11447-2025")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 23099-2024 tillsynsbegäran.docx", "A 23099-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 11447-2025 tillsynsbegäran.docx", "A 11447-2025")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 23099-2024 tillsynsbegäran mail.docx", "A 23099-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 11447-2025 tillsynsbegäran mail.docx", "A 11447-2025")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 46438-2023</t>
+          <t>A 26637-2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2530,10 +2526,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45197</v>
+        <v>46184</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2546,10 +2542,10 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>0.5</v>
+        <v>5.4</v>
       </c>
       <c r="J20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
@@ -2558,10 +2554,10 @@
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2586,42 +2582,42 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>Bombmurkla</t>
+          <t>Igelkott</t>
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 46438-2023 artfynd.xlsx", "A 46438-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 26637-2026 artfynd.xlsx", "A 26637-2026")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 46438-2023 karta.png", "A 46438-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 26637-2026 karta.png", "A 26637-2026")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 46438-2023 georefererad karta.tif", "A 46438-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 26637-2026 georefererad karta.tif", "A 26637-2026")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 46438-2023 FSC-klagomål.docx", "A 46438-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 26637-2026 FSC-klagomål.docx", "A 26637-2026")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 46438-2023 FSC-klagomål mail.docx", "A 46438-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 26637-2026 FSC-klagomål mail.docx", "A 26637-2026")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 46438-2023 tillsynsbegäran.docx", "A 46438-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 26637-2026 tillsynsbegäran.docx", "A 26637-2026")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 46438-2023 tillsynsbegäran mail.docx", "A 46438-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 26637-2026 tillsynsbegäran mail.docx", "A 26637-2026")</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 11447-2025</t>
+          <t>A 2062-2025</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2631,14 +2627,14 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45726</v>
+        <v>45671</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2651,16 +2647,16 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>1.5</v>
+        <v>1.9</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M21" t="n">
         <v>0</v>
@@ -2675,7 +2671,7 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R21" t="n">
         <v>0</v>
@@ -2687,46 +2683,50 @@
         <v>1</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Myskbock</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 11447-2025 artfynd.xlsx", "A 11447-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 2062-2025 artfynd.xlsx", "A 2062-2025")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 11447-2025 karta.png", "A 11447-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 2062-2025 karta.png", "A 2062-2025")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 11447-2025 georefererad karta.tif", "A 11447-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 2062-2025 georefererad karta.tif", "A 2062-2025")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 11447-2025 FSC-klagomål.docx", "A 11447-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 2062-2025 FSC-klagomål.docx", "A 2062-2025")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 11447-2025 FSC-klagomål mail.docx", "A 11447-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 2062-2025 FSC-klagomål mail.docx", "A 2062-2025")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 11447-2025 tillsynsbegäran.docx", "A 11447-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 2062-2025 tillsynsbegäran.docx", "A 2062-2025")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 11447-2025 tillsynsbegäran mail.docx", "A 11447-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 2062-2025 tillsynsbegäran mail.docx", "A 2062-2025")</f>
+        <v/>
+      </c>
+      <c r="AE21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/fåglar/A 2062-2025 prioriterade fågelarter.docx", "A 2062-2025")</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 7955-2023</t>
+          <t>A 26623-2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2740,10 +2740,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>44973</v>
+        <v>46184</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2756,22 +2756,22 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>2.9</v>
+        <v>4.6</v>
       </c>
       <c r="J22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M22" t="n">
         <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -2783,7 +2783,7 @@
         <v>1</v>
       </c>
       <c r="R22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
         <v>1</v>
@@ -2792,39 +2792,39 @@
         <v>1</v>
       </c>
       <c r="U22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>Bombmurkla</t>
+          <t>Svartöra</t>
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 7955-2023 artfynd.xlsx", "A 7955-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 26623-2026 artfynd.xlsx", "A 26623-2026")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 7955-2023 karta.png", "A 7955-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 26623-2026 karta.png", "A 26623-2026")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 7955-2023 georefererad karta.tif", "A 7955-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 26623-2026 georefererad karta.tif", "A 26623-2026")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 7955-2023 FSC-klagomål.docx", "A 7955-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 26623-2026 FSC-klagomål.docx", "A 26623-2026")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 7955-2023 FSC-klagomål mail.docx", "A 7955-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 26623-2026 FSC-klagomål mail.docx", "A 26623-2026")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 7955-2023 tillsynsbegäran.docx", "A 7955-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 26623-2026 tillsynsbegäran.docx", "A 26623-2026")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 7955-2023 tillsynsbegäran mail.docx", "A 7955-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 26623-2026 tillsynsbegäran mail.docx", "A 26623-2026")</f>
         <v/>
       </c>
     </row>
@@ -2848,7 +2848,7 @@
         <v>44558</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2953,7 +2953,7 @@
         <v>44609</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3026,7 +3026,7 @@
         <v>44489</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3104,7 +3104,7 @@
         <v>44546</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3177,7 +3177,7 @@
         <v>44700</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3250,7 +3250,7 @@
         <v>44587</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3323,7 +3323,7 @@
         <v>44655</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3384,7 +3384,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 64105-2023</t>
+          <t>A 23615-2025</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3398,10 +3398,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45279</v>
+        <v>45792</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3414,7 +3414,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>2.2</v>
+        <v>1.3</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3457,7 +3457,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 7275-2022</t>
+          <t>A 23627-2025</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3471,10 +3471,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44606</v>
+        <v>45792</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3486,13 +3486,8 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I31" t="n">
-        <v>9.6</v>
+        <v>1.7</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3535,7 +3530,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 31160-2022</t>
+          <t>A 59700-2021</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3549,10 +3544,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44770</v>
+        <v>44494</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3564,8 +3559,13 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I32" t="n">
-        <v>3.7</v>
+        <v>4.8</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3608,7 +3608,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 58598-2025</t>
+          <t>A 38902-2024</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3622,10 +3622,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45986</v>
+        <v>45547</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3643,7 +3643,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>4.5</v>
+        <v>0.8</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3686,7 +3686,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 26633-2026</t>
+          <t>A 50294-2023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3700,10 +3700,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>46184</v>
+        <v>45216</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3716,7 +3716,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>0.7</v>
+        <v>3.7</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3759,7 +3759,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 2602-2024</t>
+          <t>A 5264-2023</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3773,10 +3773,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45313</v>
+        <v>44959</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3789,7 +3789,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>0.7</v>
+        <v>5.8</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3832,7 +3832,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 3754-2026</t>
+          <t>A 9655-2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3846,10 +3846,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>46043</v>
+        <v>46070</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>5.1</v>
+        <v>17.2</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3910,7 +3910,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 64107-2023</t>
+          <t>A 23098-2024</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3924,10 +3924,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45279</v>
+        <v>45450</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3939,8 +3939,13 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I37" t="n">
-        <v>0.3</v>
+        <v>1</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3983,7 +3988,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 7112-2025</t>
+          <t>A 59844-2022</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3997,10 +4002,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45701</v>
+        <v>44901</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4012,8 +4017,13 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I38" t="n">
-        <v>2.4</v>
+        <v>11.9</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4056,7 +4066,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 59844-2022</t>
+          <t>A 54222-2023</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4070,10 +4080,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44901</v>
+        <v>45225</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4091,7 +4101,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>11.9</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4134,7 +4144,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 28735-2026</t>
+          <t>A 18787-2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4148,10 +4158,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>46198</v>
+        <v>46128</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4163,8 +4173,13 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I40" t="n">
-        <v>3.5</v>
+        <v>7.8</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4207,7 +4222,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 38902-2024</t>
+          <t>A 18813-2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4221,10 +4236,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45547</v>
+        <v>46128</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4242,7 +4257,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>0.8</v>
+        <v>56</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4285,7 +4300,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 28740-2026</t>
+          <t>A 18818-2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4299,10 +4314,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>46198</v>
+        <v>46128</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4314,8 +4329,13 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I42" t="n">
-        <v>4.8</v>
+        <v>17.8</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4358,7 +4378,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 28797-2026</t>
+          <t>A 18778-2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4372,10 +4392,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>46198</v>
+        <v>46128</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4387,8 +4407,13 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I43" t="n">
-        <v>2.2</v>
+        <v>4.5</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4431,7 +4456,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 23615-2025</t>
+          <t>A 4338-2023</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4445,10 +4470,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45792</v>
+        <v>44953</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4461,7 +4486,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4504,7 +4529,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 23627-2025</t>
+          <t>A 58011-2021</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4518,10 +4543,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45792</v>
+        <v>44487</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4533,8 +4558,13 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I45" t="n">
-        <v>1.7</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4577,7 +4607,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 31714-2026</t>
+          <t>A 72524-2021</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4591,10 +4621,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>46226</v>
+        <v>44546</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4607,7 +4637,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>5</v>
+        <v>3.6</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4650,7 +4680,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 33058-2026</t>
+          <t>A 64107-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4660,14 +4690,14 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>46245</v>
+        <v>45279</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4680,7 +4710,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>1.3</v>
+        <v>0.3</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4723,7 +4753,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 9655-2026</t>
+          <t>A 23093-2024</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4737,10 +4767,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>46070</v>
+        <v>45450</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4758,7 +4788,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>17.2</v>
+        <v>0.9</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4801,7 +4831,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 3630-2023</t>
+          <t>A 27313-2023</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4815,10 +4845,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>44950</v>
+        <v>45096</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4831,7 +4861,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4874,7 +4904,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 23093-2024</t>
+          <t>A 59377-2024</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4888,10 +4918,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45450</v>
+        <v>45638</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4903,13 +4933,8 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I50" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4952,7 +4977,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 54222-2023</t>
+          <t>A 21206-2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4966,10 +4991,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45225</v>
+        <v>46146</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4987,7 +5012,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>8.300000000000001</v>
+        <v>0.9</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5030,7 +5055,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 26625-2026</t>
+          <t>A 24579-2026</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5044,10 +5069,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>46184</v>
+        <v>46170</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5060,7 +5085,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>5.3</v>
+        <v>2.1</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5103,7 +5128,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 18778-2026</t>
+          <t>A 51587-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5117,10 +5142,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>46128</v>
+        <v>45215</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5134,11 +5159,11 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Övriga statliga verk och myndigheter</t>
+          <t>Allmännings- och besparingsskogar</t>
         </is>
       </c>
       <c r="I53" t="n">
-        <v>4.5</v>
+        <v>2.6</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5181,7 +5206,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 18813-2026</t>
+          <t>A 58598-2025</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5195,10 +5220,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>46128</v>
+        <v>45986</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5216,7 +5241,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>56</v>
+        <v>4.5</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5259,7 +5284,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 18818-2026</t>
+          <t>A 31160-2022</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5273,10 +5298,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>46128</v>
+        <v>44770</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5288,13 +5313,8 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I55" t="n">
-        <v>17.8</v>
+        <v>3.7</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5337,7 +5357,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 18787-2026</t>
+          <t>A 26633-2026</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5351,10 +5371,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>46128</v>
+        <v>46184</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5366,13 +5386,8 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I56" t="n">
-        <v>7.8</v>
+        <v>0.7</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5415,7 +5430,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 7860-2024</t>
+          <t>A 3754-2026</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5429,10 +5444,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45348</v>
+        <v>46043</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5450,7 +5465,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>1.9</v>
+        <v>5.1</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5493,7 +5508,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 27313-2023</t>
+          <t>A 59848-2022</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5507,10 +5522,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45096</v>
+        <v>44901</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5522,8 +5537,13 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I58" t="n">
-        <v>1.8</v>
+        <v>10.7</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5566,7 +5586,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 21206-2026</t>
+          <t>A 64110-2023</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5580,10 +5600,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>46146</v>
+        <v>45279</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5595,13 +5615,8 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I59" t="n">
-        <v>0.9</v>
+        <v>0.4</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5644,7 +5659,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 64114-2023</t>
+          <t>A 28797-2026</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5658,10 +5673,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45279</v>
+        <v>46198</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5674,7 +5689,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>0.4</v>
+        <v>2.2</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5717,7 +5732,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 50294-2023</t>
+          <t>A 28740-2026</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5731,10 +5746,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45216</v>
+        <v>46198</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5747,7 +5762,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>3.7</v>
+        <v>4.8</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5790,7 +5805,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 58011-2021</t>
+          <t>A 28735-2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5804,10 +5819,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>44487</v>
+        <v>46198</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5819,13 +5834,8 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I62" t="n">
-        <v>9.199999999999999</v>
+        <v>3.5</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5868,7 +5878,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 24579-2026</t>
+          <t>A 7275-2022</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5882,10 +5892,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>46170</v>
+        <v>44606</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5897,8 +5907,13 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I63" t="n">
-        <v>2.1</v>
+        <v>9.6</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5941,7 +5956,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 64110-2023</t>
+          <t>A 2602-2024</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5955,10 +5970,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45279</v>
+        <v>45313</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5971,7 +5986,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6014,7 +6029,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 23098-2024</t>
+          <t>A 31714-2026</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6028,10 +6043,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45450</v>
+        <v>46226</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6043,13 +6058,8 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I65" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6092,7 +6102,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 59377-2024</t>
+          <t>A 59402-2022</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6106,10 +6116,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45638</v>
+        <v>44906</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6122,7 +6132,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>0.6</v>
+        <v>1.8</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6165,7 +6175,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 59402-2022</t>
+          <t>A 3630-2023</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6179,10 +6189,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>44906</v>
+        <v>44950</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6195,7 +6205,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>1.8</v>
+        <v>1.4</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6238,7 +6248,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 5264-2023</t>
+          <t>A 7860-2024</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6252,10 +6262,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>44959</v>
+        <v>45348</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6267,8 +6277,13 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I68" t="n">
-        <v>5.8</v>
+        <v>1.9</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6311,7 +6326,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 51587-2023</t>
+          <t>A 64105-2023</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6325,10 +6340,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45215</v>
+        <v>45279</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6340,13 +6355,8 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I69" t="n">
-        <v>2.6</v>
+        <v>2.2</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6389,7 +6399,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 72524-2021</t>
+          <t>A 33058-2026</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6399,14 +6409,14 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>44546</v>
+        <v>46245</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6419,7 +6429,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>3.6</v>
+        <v>1.3</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6462,7 +6472,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 4338-2023</t>
+          <t>A 64114-2023</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6476,10 +6486,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>44953</v>
+        <v>45279</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6492,7 +6502,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>1.1</v>
+        <v>0.4</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6535,7 +6545,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 59848-2022</t>
+          <t>A 7112-2025</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6549,10 +6559,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>44901</v>
+        <v>45701</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6564,13 +6574,8 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I72" t="n">
-        <v>10.7</v>
+        <v>2.4</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6613,7 +6618,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 59700-2021</t>
+          <t>A 26625-2026</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6627,10 +6632,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>44494</v>
+        <v>46184</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6642,13 +6647,8 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I73" t="n">
-        <v>4.8</v>
+        <v>5.3</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6708,7 +6708,7 @@
         <v>44558</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>

--- a/Översikt UPPLANDS-BRO.xlsx
+++ b/Översikt UPPLANDS-BRO.xlsx
@@ -601,7 +601,7 @@
         <v>44552</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -709,7 +709,7 @@
         <v>44552</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -817,7 +817,7 @@
         <v>45232</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -912,7 +912,7 @@
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 18790-2026</t>
+          <t>A 73773-2021</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -926,10 +926,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>46128</v>
+        <v>44552</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -941,13 +941,8 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I5" t="n">
-        <v>5.5</v>
+        <v>1.9</v>
       </c>
       <c r="J5" t="n">
         <v>2</v>
@@ -980,371 +975,376 @@
         <v>2</v>
       </c>
       <c r="T5" t="n">
+        <v>3</v>
+      </c>
+      <c r="U5" t="n">
+        <v>3</v>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
+          <t>Kopparödla
+Gullviva</t>
+        </is>
+      </c>
+      <c r="W5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 73773-2021 artfynd.xlsx", "A 73773-2021")</f>
+        <v/>
+      </c>
+      <c r="X5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 73773-2021 karta.png", "A 73773-2021")</f>
+        <v/>
+      </c>
+      <c r="Y5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 73773-2021 georefererad karta.tif", "A 73773-2021")</f>
+        <v/>
+      </c>
+      <c r="AA5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 73773-2021 FSC-klagomål.docx", "A 73773-2021")</f>
+        <v/>
+      </c>
+      <c r="AB5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 73773-2021 FSC-klagomål mail.docx", "A 73773-2021")</f>
+        <v/>
+      </c>
+      <c r="AC5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 73773-2021 tillsynsbegäran.docx", "A 73773-2021")</f>
+        <v/>
+      </c>
+      <c r="AD5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 73773-2021 tillsynsbegäran mail.docx", "A 73773-2021")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>A 18772-2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D6" s="1" t="n">
+        <v>46128</v>
+      </c>
+      <c r="E6" s="1" t="n">
+        <v>46310</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>UPPLANDS-BRO</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>1</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
         <v>2</v>
       </c>
-      <c r="U5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
+      <c r="T6" t="n">
+        <v>2</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>Svedjenäva
+Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="W6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 18772-2026 artfynd.xlsx", "A 18772-2026")</f>
+        <v/>
+      </c>
+      <c r="X6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 18772-2026 karta.png", "A 18772-2026")</f>
+        <v/>
+      </c>
+      <c r="Y6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 18772-2026 georefererad karta.tif", "A 18772-2026")</f>
+        <v/>
+      </c>
+      <c r="AA6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 18772-2026 FSC-klagomål.docx", "A 18772-2026")</f>
+        <v/>
+      </c>
+      <c r="AB6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 18772-2026 FSC-klagomål mail.docx", "A 18772-2026")</f>
+        <v/>
+      </c>
+      <c r="AC6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 18772-2026 tillsynsbegäran.docx", "A 18772-2026")</f>
+        <v/>
+      </c>
+      <c r="AD6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 18772-2026 tillsynsbegäran mail.docx", "A 18772-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>A 18790-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>46128</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>46310</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>UPPLANDS-BRO</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="J7" t="n">
+        <v>2</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>2</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>Fläcknycklar
 Nattviol</t>
         </is>
       </c>
-      <c r="W5">
+      <c r="W7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 18790-2026 artfynd.xlsx", "A 18790-2026")</f>
         <v/>
       </c>
-      <c r="X5">
+      <c r="X7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 18790-2026 karta.png", "A 18790-2026")</f>
         <v/>
       </c>
-      <c r="Y5">
+      <c r="Y7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 18790-2026 georefererad karta.tif", "A 18790-2026")</f>
         <v/>
       </c>
-      <c r="AA5">
+      <c r="AA7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 18790-2026 FSC-klagomål.docx", "A 18790-2026")</f>
         <v/>
       </c>
-      <c r="AB5">
+      <c r="AB7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 18790-2026 FSC-klagomål mail.docx", "A 18790-2026")</f>
         <v/>
       </c>
-      <c r="AC5">
+      <c r="AC7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 18790-2026 tillsynsbegäran.docx", "A 18790-2026")</f>
         <v/>
       </c>
-      <c r="AD5">
+      <c r="AD7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 18790-2026 tillsynsbegäran mail.docx", "A 18790-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>A 18772-2026</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
+    <row r="8" ht="15" customHeight="1">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>A 10909-2025</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D6" s="1" t="n">
-        <v>46128</v>
-      </c>
-      <c r="E6" s="1" t="n">
-        <v>46309</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>UPPLANDS-BRO</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
-      <c r="I6" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="J6" t="n">
-        <v>1</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>1</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>1</v>
-      </c>
-      <c r="R6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" t="n">
+      <c r="D8" s="1" t="n">
+        <v>45722</v>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>46310</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>UPPLANDS-BRO</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="J8" t="n">
+        <v>1</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
         <v>2</v>
       </c>
-      <c r="T6" t="n">
+      <c r="T8" t="n">
         <v>2</v>
       </c>
-      <c r="U6" t="n">
-        <v>0</v>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>Svedjenäva
-Fläcknycklar</t>
-        </is>
-      </c>
-      <c r="W6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 18772-2026 artfynd.xlsx", "A 18772-2026")</f>
-        <v/>
-      </c>
-      <c r="X6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 18772-2026 karta.png", "A 18772-2026")</f>
-        <v/>
-      </c>
-      <c r="Y6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 18772-2026 georefererad karta.tif", "A 18772-2026")</f>
-        <v/>
-      </c>
-      <c r="AA6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 18772-2026 FSC-klagomål.docx", "A 18772-2026")</f>
-        <v/>
-      </c>
-      <c r="AB6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 18772-2026 FSC-klagomål mail.docx", "A 18772-2026")</f>
-        <v/>
-      </c>
-      <c r="AC6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 18772-2026 tillsynsbegäran.docx", "A 18772-2026")</f>
-        <v/>
-      </c>
-      <c r="AD6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 18772-2026 tillsynsbegäran mail.docx", "A 18772-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>A 10909-2025</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>45722</v>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>46309</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>UPPLANDS-BRO</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="J7" t="n">
-        <v>1</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>1</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>1</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
+      <c r="U8" t="n">
         <v>2</v>
       </c>
-      <c r="T7" t="n">
-        <v>2</v>
-      </c>
-      <c r="U7" t="n">
-        <v>2</v>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>Arommusseron
 Fläcknycklar</t>
         </is>
       </c>
-      <c r="W7">
+      <c r="W8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 10909-2025 artfynd.xlsx", "A 10909-2025")</f>
         <v/>
       </c>
-      <c r="X7">
+      <c r="X8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 10909-2025 karta.png", "A 10909-2025")</f>
         <v/>
       </c>
-      <c r="Y7">
+      <c r="Y8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 10909-2025 georefererad karta.tif", "A 10909-2025")</f>
         <v/>
       </c>
-      <c r="AA7">
+      <c r="AA8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 10909-2025 FSC-klagomål.docx", "A 10909-2025")</f>
         <v/>
       </c>
-      <c r="AB7">
+      <c r="AB8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 10909-2025 FSC-klagomål mail.docx", "A 10909-2025")</f>
         <v/>
       </c>
-      <c r="AC7">
+      <c r="AC8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 10909-2025 tillsynsbegäran.docx", "A 10909-2025")</f>
         <v/>
       </c>
-      <c r="AD7">
+      <c r="AD8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 10909-2025 tillsynsbegäran mail.docx", "A 10909-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8" ht="15" customHeight="1">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>A 73773-2021</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D8" s="1" t="n">
-        <v>44552</v>
-      </c>
-      <c r="E8" s="1" t="n">
-        <v>46309</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>UPPLANDS-BRO</t>
-        </is>
-      </c>
-      <c r="I8" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="J8" t="n">
-        <v>2</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" t="n">
-        <v>2</v>
-      </c>
-      <c r="T8" t="n">
-        <v>3</v>
-      </c>
-      <c r="U8" t="n">
-        <v>3</v>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>Kopparödla
-Gullviva</t>
-        </is>
-      </c>
-      <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 73773-2021 artfynd.xlsx", "A 73773-2021")</f>
-        <v/>
-      </c>
-      <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 73773-2021 karta.png", "A 73773-2021")</f>
-        <v/>
-      </c>
-      <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 73773-2021 georefererad karta.tif", "A 73773-2021")</f>
-        <v/>
-      </c>
-      <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 73773-2021 FSC-klagomål.docx", "A 73773-2021")</f>
-        <v/>
-      </c>
-      <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 73773-2021 FSC-klagomål mail.docx", "A 73773-2021")</f>
-        <v/>
-      </c>
-      <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 73773-2021 tillsynsbegäran.docx", "A 73773-2021")</f>
-        <v/>
-      </c>
-      <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 73773-2021 tillsynsbegäran mail.docx", "A 73773-2021")</f>
         <v/>
       </c>
     </row>
@@ -1368,7 +1368,7 @@
         <v>44603</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1474,7 +1474,7 @@
         <v>44552</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1562,7 +1562,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 7955-2023</t>
+          <t>A 25561-2025</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1576,10 +1576,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>44973</v>
+        <v>45803</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1592,7 +1592,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>2.9</v>
+        <v>1.6</v>
       </c>
       <c r="J11" t="n">
         <v>1</v>
@@ -1628,7 +1628,7 @@
         <v>1</v>
       </c>
       <c r="U11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
@@ -1636,38 +1636,38 @@
         </is>
       </c>
       <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 7955-2023 artfynd.xlsx", "A 7955-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/artfynd/A 25561-2025 artfynd.xlsx", "A 25561-2025")</f>
         <v/>
       </c>
       <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 7955-2023 karta.png", "A 7955-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor/A 25561-2025 karta.png", "A 25561-2025")</f>
         <v/>
       </c>
       <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 7955-2023 georefererad karta.tif", "A 7955-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/kartor_geotiff/A 25561-2025 georefererad karta.tif", "A 25561-2025")</f>
         <v/>
       </c>
       <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 7955-2023 FSC-klagomål.docx", "A 7955-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomål/A 25561-2025 FSC-klagomål.docx", "A 25561-2025")</f>
         <v/>
       </c>
       <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 7955-2023 FSC-klagomål mail.docx", "A 7955-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/klagomålsmail/A 25561-2025 FSC-klagomål mail.docx", "A 25561-2025")</f>
         <v/>
       </c>
       <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 7955-2023 tillsynsbegäran.docx", "A 7955-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsyn/A 25561-2025 tillsynsbegäran.docx", "A 25561-2025")</f>
         <v/>
       </c>
       <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 7955-2023 tillsynsbegäran mail.docx", "A 7955-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0139/tillsynsmail/A 25561-2025 tillsynsbegäran mail.docx", "A 25561-2025")</f>
         <v/>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 25561-2025</t>
+          <t>A 23099-2024</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1681,10 +1681,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45803</v>
+        <v>45450</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1696,11 +1696,16 @@
           <t>UPPLANDS-BRO</t>
         </is>
       </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I12" t="n">
-        <v>1.6</v>
+        <v>0.7</v>
       </c>
       <c r="J12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
@@ -1709,10 +1714,10 @@
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1733,39 +1738,39 @@
         <v>1</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>Bombmurkla</t>
+          <t>Bredbrämad bastardsvärmare</t>
         </is>
       </c>
       <c r="W12">
-   